--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suivi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracking" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pistes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -542,27 +542,27 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bloc</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ressource</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Fichier</t>
+          <t>File</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Contenu</t>
+          <t>Inherited content</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Lignes</t>
+          <t>Rows</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -572,12 +572,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>État</t>
+          <t>State</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Travail</t>
+          <t>Work</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -592,29 +592,29 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Onglet source</t>
+          <t>Source sheet</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Millésime</t>
+          <t>Vintage</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Ce qui a été fait</t>
+          <t>What was done</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Ce qui reste</t>
+          <t>What is left</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cadrage</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -634,7 +634,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Cadrage</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Horizon 2017-2030</t>
+          <t>horizon 2017-2030</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
@@ -658,12 +658,12 @@
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>terminé</t>
+          <t>done</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>ÉTENDRE</t>
+          <t>EXTEND</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
@@ -680,19 +680,19 @@
       <c r="L3" s="4" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>Horizon 2050. Pas annuel jusqu'en 2035 pour suivre la montée en puissance de Rogun, puis pas de 5 ans. pWeightYear se déduit des écarts (main.gms:718).</t>
+          <t>Horizon 2050. Yearly step until 2035 to follow the ramp-up of Rogun, then a 5-year step. pWeightYear is derived from the gaps (main.gms:718).</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>FAIT (phase 1) : horizon 2026-2050, annuel de 2026 à 2035 puis pas de 5 ans (2040, 2045, 2050), soit 13 années. Le pas annuel jusqu'en 2035 couvre la montée en puissance de Rogun. pWeightYear est dérivé automatiquement des écarts (main.gms:718), rien d'autre à saisir.</t>
+          <t>DONE (phase 1): horizon 2026-2050, yearly from 2026 to 2035 then a 5-year step (2040, 2045, 2050), that is 13 years. The yearly step until 2035 covers the ramp-up of Rogun. pWeightYear is derived automatically from the gaps (main.gms:718), nothing else to enter.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Cadrage</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>16 zones -&gt; 7 pays</t>
+          <t>16 zones -&gt; 7 countries</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -716,12 +716,12 @@
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>DÉCISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Zones_Regions (5 pays)</t>
+          <t>Zones_Regions (5 countries)</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -747,14 +747,14 @@
       <c r="M4" s="4" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Garder les 16 zones. Les 5 nœuds afghans ne sont pas des artefacts comptables mais des îlots radiaux, chacun synchrone d'un voisin différent, que pTransferLimit interconnecte progressivement vers 2030 : les fusionner inventerait une capacité inexistante. Seul geste utile, les renommer géographiquement.</t>
+          <t>Keep the 16 zones. The 5 Afghan nodes are not accounting artefacts but radial islands, each synchronous with a different neighbour, that pTransferLimit interconnects progressively towards 2030: merging them would invent a capacity that does not exist. The only useful move is to rename them geographically.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Cadrage</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>~40 drapeaux et scalaires</t>
+          <t>~40 flags and scalars</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
@@ -778,12 +778,12 @@
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>RÉVISER</t>
+          <t>REVISE</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -805,14 +805,14 @@
       <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>À trancher : carbone (OFF), stockage (OFF), rampes (OFF), MinGen/MUDT (OFF), réserve tournante (OFF).</t>
+          <t>To be settled: carbon (OFF), storage (OFF), ramps (OFF), MinGen/MUDT (OFF), spinning reserve (OFF).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Cadrage</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>modeltype RMIP + options cplex</t>
+          <t>modeltype RMIP + cplex options</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -836,12 +836,12 @@
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>hérité, conforme</t>
+          <t>inherited, fit for purpose</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>GARDER</t>
+          <t>KEEP</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Passer en MIP seulement si on active l'engagement d'unités.</t>
+          <t>Switch to MIP only if unit commitment is turned on.</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr"/>
@@ -870,7 +870,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Cadrage</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>5 saisons x 1 jour x 7 blocs = 8760 h</t>
+          <t>5 seasons x 1 day x 7 blocks = 8760 h</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -898,12 +898,12 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>structure adaptée, données à faire</t>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>RECONSTRUIRE</t>
+          <t>REBUILD</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -928,19 +928,19 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>q = 4 trimestres, la 5e saison de pointe est supprimée. Elle n'était pas une structure mais une rustine : la contrainte de réserve prend un smax sur toutes les tranches (base.gms:991) et n'exige aucune saison dédiée. Q5 ne servait qu'à donner à ce smax un bloc assez court pour voir la vraie pointe, faute de journées types (d=1 dans le modèle 2020).</t>
+          <t>q = 4 quarters, the 5th peak season is removed. It was not a structure but a patch: the reserve constraint takes a smax over all blocks (base.gms:991) and requires no dedicated season. Q5 only served to give that smax a block short enough to see the true peak, for want of representative days (d=1 in the 2020 model).</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>PHASE 8. Reconstruire en 4 trimestres x journées types x heures chronologiques, dont une JOURNÉE TYPE DE POINTE qui remplace l'ancienne saison Q5.</t>
+          <t>PHASE 8. Rebuild as 4 quarters x representative days x chronological hours, including a PEAK REPRESENTATIVE DAY that replaces the former Q5 season.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Cadrage</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>26 couples tech/fuel</t>
+          <t>26 tech/fuel pairs</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -964,12 +964,12 @@
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>ÉTENDRE</t>
+          <t>EXTEND</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -991,14 +991,14 @@
       <c r="M8" s="4" t="inlineStr"/>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Ajouter BESS si on active le stockage.</t>
+          <t>Add BESS if storage is turned on.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Cadrage</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>facteurs CO2 par combustible</t>
+          <t>CO2 factors by fuel</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -1022,12 +1022,12 @@
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>hérité, conforme</t>
+          <t>inherited, fit for purpose</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>GARDER</t>
+          <t>KEEP</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Valeurs standard, aucune raison de bouger.</t>
+          <t>Standard values, no reason to move them.</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr"/>
@@ -1056,7 +1056,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Demande</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="B10" s="3" t="n"/>
@@ -1076,7 +1076,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Demande</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>MW absolus par (z,q,d,y)</t>
+          <t>absolute MW by (z,q,d,y)</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>structure adaptée, données à faire</t>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>RECONSTRUIRE</t>
+          <t>REBUILD</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -1134,19 +1134,19 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Vidé, son contenu dépend du choix des journées types.</t>
+          <t>Emptied, its content depends on the choice of representative days.</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>PHASE 8, à partir de la série horaire agrégée en phase 2.</t>
+          <t>PHASE 8, from the hourly series aggregated in phase 2.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Demande</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>trajectoire de demande par zone, energie GWh et pointe MW</t>
+          <t>demand trajectory by zone, energy GWh and peak MW</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>rempli, compléments à venir</t>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>FAIT</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1204,19 +1204,19 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Rempli par extract_demand.py, scenario DeCA Reference. Demand Evolution couvre 2023-2060 par PAYS : aucune extrapolation n'est necessaire pour l'Asie centrale. Le decoupage intra-pays vient des profils 8760 h et reste constant dans le temps, DeCA ne donnant pas de trajectoire regionale. La pointe zonale est NON COINCIDENTE, comme l'exige generate_demand.gms qui la multiplie par le profil normalise de la zone : on remet donc la pointe propre a l'echelle par la croissance de la pointe pays, via le facteur de coincidence observe (KG 1.03, KZ 1.02, TJ 1.07, TM et UZ 1.00). Trois ecarts assumes, tous documentes dans mappings/zones_demand.csv : le partage tadjik est INVERSE par rapport au modele 2020 (Nord 27.7 % contre 74.9 %), le partage kirghize aussi (Nord 63.9 % contre 93.2 %), et l'Ouest kazakh est rattache a KAZ_N faute de troisieme zone. Le bloc de pointe du carnet TJ etait en GW sous une etiquette MW : corrige par un garde-fou generique, une pointe ne pouvant etre inferieure a la puissance moyenne. AFG et PAK n'ont aucune source 2026 : reconduits depuis le pDemandData de 2020 et prolonges a leur propre taux, confiance BASSE.</t>
+          <t>Filled by extract_demand.py, DeCA Reference scenario. Demand Evolution covers 2023-2060 BY COUNTRY: no extrapolation is needed for Central Asia. The intra- country split comes from the 8760 h profiles and stays constant over time, DeCA giving no regional trajectory. The zonal peak is NON COINCIDENT, as required by generate_demand.gms which multiplies it by the normalised profile of the zone: the own peak is therefore rescaled by the growth of the country peak, through the observed coincidence factor (KG 1.03, KZ 1.02, TJ 1.07, TM and UZ 1.00). Three deliberate departures, all documented in mappings/zones_demand.csv: the Tajik split is REVERSED with respect to the 2020 model (North 27.7 % against 74.9 %), the Kyrgyz split too (North 63.9 % against 93.2 %), and Western Kazakhstan is attached to KAZ_N for want of a third zone. The peak block of the TJ book was in GW under a MW label: corrected by a generic guard, a peak not being allowed to fall below the average power. AFG and PAK have no 2026 source: carried over from the 2020 pDemandData and extended at their own rate, LOW confidence.</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>PHASE 9. Ajouter le scenario DeCA Net Zero en variante. Remplacer AFG et PAK des qu'une source arrive (IGCEP du NTDC en priorite). Revoir le partage TAJ et KGZ avec les TTL : il change le diagnostic de defaillance du modele 2020.</t>
+          <t>PHASE 9. Add the DeCA Net Zero scenario as a variant. Replace AFG and PAK as soon as a source arrives (NTDC IGCEP first). Review the TAJ and KGZ splits with the TTLs: they change the unserved energy diagnosis of the 2020 model.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Demande</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>profil normalisé par (z,q,d,t)</t>
+          <t>normalised profile by (z,q,d,t)</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -1240,12 +1240,12 @@
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>REMPLIR</t>
+          <t>FILL</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -1267,14 +1267,14 @@
       <c r="M13" s="4" t="inlineStr"/>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Dépend de pHours -&gt; repoussé avec lui. Préparer la forme au pas HORAIRE en intermédiaire, l'agrégation vers (q,d,t) est la dernière étape.</t>
+          <t>Depends on pHours -&gt; deferred with it. Prepare the shape at HOURLY resolution as an intermediate, the aggregation to (q,d,t) is the last step.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Demande</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>facteur d'efficacité énergétique</t>
+          <t>energy efficiency factor</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -1298,12 +1298,12 @@
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>hors périmètre</t>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>IGNORER</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -1317,14 +1317,14 @@
       <c r="M14" s="4" t="inlineStr"/>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Sauf si un scénario efficacité est demandé.</t>
+          <t>Only if an efficiency scenario is requested.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Demande</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>types de jour retenus</t>
+          <t>day types retained</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -1348,12 +1348,12 @@
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>RECONSTRUIRE</t>
+          <t>REBUILD</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -1371,14 +1371,14 @@
       <c r="M15" s="4" t="inlineStr"/>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Sortie du pipeline jours représentatifs. Repoussé avec pHours.</t>
+          <t>Output of the representative days pipeline. Deferred with pHours.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="B16" s="3" t="n"/>
@@ -1398,7 +1398,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>centrales : capacité, statut, HR, coûts</t>
+          <t>power plants: capacity, status, HR, costs</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>REMPLACER</t>
+          <t>REPLACE</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1457,14 +1457,14 @@
       <c r="M17" s="4" t="inlineStr"/>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>PHASE 5, le gros morceau. ANOMALIE STRUCTURELLE À ROUVRIR : les candidats génériques portent 10000 MW constructibles dans KAZ, UZB, TUR, PAK et les 5 zones NEPS, mais 0 MW dans KGZ_N, KGZ_S, TAJ_N et TAJ_S (seule exception un CCGT de 200 MW à TAJ_N). Le Kirghizstan et le Tadjikistan ne peuvent donc rien construire hors projets hydro nommés, ce qui explique à lui seul que la défaillance hivernale de TAJ_N ne se résorbe qu'avec Rogun. Ce n'est pas un arbitrage économique du modèle, c'est une porte fermée.</t>
+          <t>PHASE 5, the big one. STRUCTURAL ANOMALY TO REOPEN: the generic candidates carry 10000 MW buildable in KAZ, UZB, TUR, PAK and the 5 NEPS zones, but 0 MW in KGZ_N, KGZ_S, TAJ_N and TAJ_S (the only exception being a 200 MW CCGT at TAJ_N). Kyrgyzstan and Tajikistan can therefore build nothing outside named hydro projects, which alone explains why the winter unserved energy of TAJ_N only clears with Rogun. This is not an economic arbitrage of the model, it is a closed door.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>dispo saisonnière par centrale (g x Q1..Q4)</t>
+          <t>seasonal availability by plant (g x Q1..Q4)</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>structure adaptée, données à faire</t>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>RECONSTRUIRE</t>
+          <t>REBUILD</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1522,19 +1522,19 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Colonne de pointe supprimée. ATTENTION, elle portait une convention : 350 centrales sur 403 avaient Q5=1,0 contre Q1=0,85, soit pleine disponibilité à la pointe. Cette hypothèse de capacité ferme disparaît et doit être réintroduite.</t>
+          <t>Peak column removed. BEWARE, it carried a convention: 350 plants out of 403 had Q5=1.0 against Q1=0.85, that is full availability at the peak. This firm capacity assumption disappears and has to be reintroduced.</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>PHASE 4. Reconstruire depuis les apports mensuels deca_v51 (Hydro Profile + HydroPP Inflows), et réintroduire la capacité ferme de pointe, soit par la journée type de pointe, soit par pCapacityCreditPeakSeason.</t>
+          <t>PHASE 4. Rebuild from the monthly inflows of deca_v51 (Hydro Profile + HydroPP Inflows), and reintroduce firm peak capacity, either through the peak representative day or through pCapacityCreditPeakSeason.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>dispo par défaut (z,tech,fuel)</t>
+          <t>default availability (z,tech,fuel)</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
@@ -1558,12 +1558,12 @@
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>REMPLIR</t>
+          <t>FILL</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
@@ -1581,14 +1581,14 @@
       <c r="M19" s="4" t="inlineStr"/>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>DeCA ne donne PAS les taux d'indisponibilité fortuite du thermique, et l'onglet GenAvailability du gabarit est vide.</t>
+          <t>DeCA does NOT give the forced outage rates of the thermal fleet, and the GenAvailability sheet of the template is empty.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>candidats génériques par zone</t>
+          <t>generic candidates by zone</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -1612,12 +1612,12 @@
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>REMPLIR</t>
+          <t>FILL</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1643,14 +1643,14 @@
       <c r="M20" s="4" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Détermine ce que le modèle a le DROIT de construire. Vide aujourd'hui : l'expansion n'est pilotée que par pGenDataInput.</t>
+          <t>Determines what the model is ALLOWED to build. Empty today: expansion is driven by pGenDataInput alone.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>profil solaire/éolien par (z,tech,q,d)</t>
+          <t>solar/wind profile by (z,tech,q,d)</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>structure adaptée, données à faire</t>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>RECONSTRUIRE</t>
+          <t>REBUILD</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>RenewableProfile (mensuel)</t>
+          <t>RenewableProfile (monthly)</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Vidé, son contenu dépend du choix des journées types.</t>
+          <t>Emptied, its content depends on the choice of representative days.</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -1720,7 +1720,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>CAPEX par centrale dans le temps</t>
+          <t>CAPEX by plant over time</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
@@ -1744,12 +1744,12 @@
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>REMPLIR</t>
+          <t>FILL</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
@@ -1775,14 +1775,14 @@
       <c r="M22" s="4" t="inlineStr"/>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Recaler en USD réel 2025 (exigence du gabarit).</t>
+          <t>Rebase in real 2025 USD (requirement of the template).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>CAPEX par (zone,tech,fuel)</t>
+          <t>CAPEX by (zone,tech,fuel)</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -1806,12 +1806,12 @@
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>hérité, conforme</t>
+          <t>inherited, fit for purpose</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>REMPLIR</t>
+          <t>FILL</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>prix combustibles par pays (c,fuel,année)</t>
+          <t>fuel prices by country (c,fuel,year)</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -1864,12 +1864,12 @@
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>REMPLACER</t>
+          <t>REPLACE</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -1889,20 +1889,20 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2024 réel -&gt; 2050</t>
+          <t>2024 real -&gt; 2050</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr"/>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Le bloc le plus propre du lot : direct, sans arbitrage, sans dépendance temporelle. USD réel 2025.</t>
+          <t>The cleanest block of the lot: direct, no arbitrage, no time dependency. Real 2025 USD.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>stockage (batteries, STEP)</t>
+          <t>storage (batteries, pumped hydro)</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
@@ -1926,12 +1926,12 @@
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>DÉCISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -1953,14 +1953,14 @@
       <c r="M25" s="4" t="inlineStr"/>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>BLOQUÉ PAR LA RÉSOLUTION TEMPORELLE : sans chronologie intra-journalière le stockage n'a aucune valeur dans le modèle. Se tranche donc en même temps que pHours, à la fin.</t>
+          <t>BLOCKED BY THE TIME RESOLUTION: without intra-day chronology, storage has no value in the model. It is therefore settled at the same time as pHours, at the end.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>dérive de disponibilité dans le temps</t>
+          <t>availability drift over time</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
@@ -1984,12 +1984,12 @@
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>hors périmètre</t>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>IGNORER</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
@@ -2006,7 +2006,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Parc</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>solaire à concentration</t>
+          <t>concentrated solar power</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -2030,12 +2030,12 @@
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>hors périmètre</t>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>IGNORER</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -2049,14 +2049,14 @@
       <c r="M27" s="4" t="inlineStr"/>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Pas de CSP dans le périmètre.</t>
+          <t>No CSP in the perimeter.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B28" s="3" t="n"/>
@@ -2076,7 +2076,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>NTC par corridor x saison x année</t>
+          <t>NTC by corridor x season x year</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>structure adaptée, données à faire</t>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>RÉVISER</t>
+          <t>REVISE</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Les 42 lignes Q5 étaient identiques aux Q1 : suppression sans perte, 210 -&gt; 168.</t>
+          <t>The 42 Q5 rows were identical to the Q1 ones: removed without loss, 210 -&gt; 168.</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>PHASE 3. NTC à réviser (source deca_v51 + demande TSO) et colonnes d'années à prolonger jusqu'en 2050, elles s'arrêtent à 2030. Anomalie connue : CASA-1000 est ouvert à 1300 MW toutes saisons dès 2022, d'où 10 TWh/an dans le run 2020.</t>
+          <t>PHASE 3. NTCs to be revised (source deca_v51 + TSO request) and year columns to be extended to 2050, they stop at 2030. Known anomaly: CASA-1000 is open at 1300 MW in all seasons from 2022, hence 10 TWh/yr in the 2020 run.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>corridors sous contrat, par saison</t>
+          <t>contracted corridors, by season</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>RÉVISER</t>
+          <t>REVISE</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -2197,14 +2197,14 @@
       <c r="M30" s="4" t="inlineStr"/>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>PHASE 3. LE SENS DE Q3 A CHANGÉ : dans le modèle 2020 Q3 valait 3652 h, soit mai- septembre, exactement la fenêtre CASA-1000. En trimestres calendaires, Q3 = juillet-septembre. Les 5 flags doivent passer en Q2 + Q3.</t>
+          <t>PHASE 3. THE MEANING OF Q3 HAS CHANGED: in the 2020 model Q3 was worth 3652 h, that is May-September, exactly the CASA-1000 window. In calendar quarters, Q3 = July-September. The 5 flags must move to Q2 + Q3.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>énergie contractée GWh par corridor</t>
+          <t>contracted energy GWh by corridor</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>RÉVISER</t>
+          <t>REVISE</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -2259,14 +2259,14 @@
       <c r="M31" s="4" t="inlineStr"/>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>PHASE 3. Répartir les volumes entre Q2 et Q3 (voir pContractedTradeFlag), et prolonger les colonnes d'années au-delà de 2030. À vérifier contre le PPA : an 1 = 2028, plateau 4434 GWh, tranche minimum 29794 GWh sur 15 ans.</t>
+          <t>PHASE 3. Split the volumes between Q2 and Q3 (see pContractedTradeFlag), and extend the year columns beyond 2030. To be checked against the PPA: year 1 = 2028, plateau 4434 GWh, minimum take 29794 GWh over 15 years.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>corridors plafonnés à l'historique</t>
+          <t>corridors capped at historical levels</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -2290,12 +2290,12 @@
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>RÉVISER</t>
+          <t>REVISE</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -2317,14 +2317,14 @@
       <c r="M32" s="4" t="inlineStr"/>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>N'agit que jusqu'en 2021 : devient inerte si le modèle démarre plus tard.</t>
+          <t>Only acts until 2021: becomes inert if the model starts later.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>pertes par corridor (0,5 % partout)</t>
+          <t>losses by corridor (0.5 % everywhere)</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
@@ -2348,12 +2348,12 @@
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>hérité, conforme</t>
+          <t>inherited, fit for purpose</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>GARDER</t>
+          <t>KEEP</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Valeur uniforme héritée, faible enjeu.</t>
+          <t>Uniform inherited value, low stakes.</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>plafond annuel d'échange par corridor</t>
+          <t>annual trade cap by corridor</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
@@ -2406,12 +2406,12 @@
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>RÉVISER</t>
+          <t>REVISE</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
@@ -2433,14 +2433,14 @@
       <c r="M34" s="4" t="inlineStr"/>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>8 corridors seulement. Vérifier la cohérence avec les nouveaux NTC.</t>
+          <t>8 corridors only. Check consistency with the new NTCs.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>lignes candidates à la construction</t>
+          <t>candidate lines for construction</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -2464,12 +2464,12 @@
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>DÉCISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -2487,14 +2487,14 @@
       <c r="M35" s="4" t="inlineStr"/>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Vide = réseau figé. Pour tester des renforcements (dont une phase 2 CASA-1000), il faut le remplir.</t>
+          <t>Empty = frozen grid. To test reinforcements (including a CASA-1000 phase 2), it has to be filled.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>import minimum obligatoire</t>
+          <t>mandatory minimum import</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -2518,12 +2518,12 @@
       <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>hors périmètre</t>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>IGNORER</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -2537,14 +2537,14 @@
       <c r="M36" s="4" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Alternative à pContractedTrade en cas de besoin d'un enlèvement ferme.</t>
+          <t>Alternative to pContractedTrade should a firm offtake be needed.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>NTC vers zones externes</t>
+          <t>NTC towards external zones</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
@@ -2568,12 +2568,12 @@
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>DÉCISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
@@ -2587,14 +2587,14 @@
       <c r="M37" s="4" t="inlineStr"/>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Enjeu : Russie (KAZ_N), Iran (HERAT), Chine, Inde. Aujourd'hui l'import iranien est modélisé comme une CENTRALE (IRAN_Import, 400 MW), pas comme un échange.</t>
+          <t>At stake: Russia (KAZ_N), Iran (HERAT), China, India. Today the Iranian import is modelled as a POWER PLANT (IRAN_Import, 400 MW), not as an exchange.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>prix aux frontières externes</t>
+          <t>prices at the external borders</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -2618,12 +2618,12 @@
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>DÉCISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
@@ -2641,14 +2641,14 @@
       <c r="M38" s="4" t="inlineStr"/>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>Aucune source. À construire de façon homogène et à assumer comme hypothèse.</t>
+          <t>No source. To be built consistently and owned as an assumption.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>liste des zones externes</t>
+          <t>list of external zones</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -2672,12 +2672,12 @@
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>DÉCISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
@@ -2691,14 +2691,14 @@
       <c r="M39" s="4" t="inlineStr"/>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>Dépend de pExtTransferLimit.</t>
+          <t>Depends on pExtTransferLimit.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Échanges</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>part max d'échange externe</t>
+          <t>max share of external trade</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -2722,12 +2722,12 @@
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>NETTOYER</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -2741,14 +2741,14 @@
       <c r="M40" s="4" t="inlineStr"/>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>En-tête hérité d'un gabarit AFRIQUE (Angola, Burundi, Cameroon...). À vider.</t>
+          <t>Header inherited from an AFRICAN template (Angola, Burundi, Cameroon...). To be emptied.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Contraintes</t>
+          <t>Constraints</t>
         </is>
       </c>
       <c r="B41" s="3" t="n"/>
@@ -2768,7 +2768,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Contraintes</t>
+          <t>Constraints</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>prix carbone 32 -&gt; 50 $/t</t>
+          <t>carbon price 32 -&gt; 50 $/t</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
@@ -2792,12 +2792,12 @@
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>DÉCISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
@@ -2819,14 +2819,14 @@
       <c r="M42" s="4" t="inlineStr"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>DONNÉE PRÉSENTE MAIS INACTIVE (fEnableCarbonPrice = 0). L'activer est le levier le moins cher pour corriger les 17 GW de charbon neuf au Kazakhstan.</t>
+          <t>DATA PRESENT BUT INACTIVE (fEnableCarbonPrice = 0). Turning it on is the cheapest lever to correct the 17 GW of new coal in Kazakhstan.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Contraintes</t>
+          <t>Constraints</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>plafond CO2 par pays</t>
+          <t>CO2 cap by country</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
@@ -2850,12 +2850,12 @@
       <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>REMPLIR</t>
+          <t>FILL</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -2881,14 +2881,14 @@
       <c r="M43" s="4" t="inlineStr"/>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>DeCA donne les trajectoires Net Zero, pas les facteurs par combustible.</t>
+          <t>DeCA gives the Net Zero trajectories, not the factors by fuel.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Contraintes</t>
+          <t>Constraints</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>plafond CO2 système</t>
+          <t>system-wide CO2 cap</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
@@ -2912,12 +2912,12 @@
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>hérité, conforme</t>
+          <t>inherited, fit for purpose</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>DÉCISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Contraintes</t>
+          <t>Constraints</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>limite d'approvisionnement par pays</t>
+          <t>supply limit by country</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
@@ -2958,12 +2958,12 @@
       <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>RÉVISER</t>
+          <t>REVISE</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
@@ -2989,14 +2989,14 @@
       <c r="M45" s="4" t="inlineStr"/>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Seul UZ dispose d'un onglet dédié.</t>
+          <t>Only UZ has a dedicated sheet.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Contraintes</t>
+          <t>Constraints</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>limite par zone (KAZ_N Gas 0,1)</t>
+          <t>limit by zone (KAZ_N Gas 0.1)</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
@@ -3020,12 +3020,12 @@
       <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>RÉVISER</t>
+          <t>REVISE</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -3051,14 +3051,14 @@
       <c r="M46" s="4" t="inlineStr"/>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>La contrainte gaz sur KAZ_N est structurante pour le charbon kazakh : à vérifier en priorité.</t>
+          <t>The gas constraint on KAZ_N is structuring for Kazakh coal: to be checked as a priority.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Contraintes</t>
+          <t>Constraints</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>part max par combustible</t>
+          <t>max share by fuel</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
@@ -3082,12 +3082,12 @@
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>hors périmètre</t>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>IGNORER</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -3104,7 +3104,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Réserves</t>
+          <t>Reserves</t>
         </is>
       </c>
       <c r="B48" s="3" t="n"/>
@@ -3124,7 +3124,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Réserves</t>
+          <t>Reserves</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>marge de réserve, 15 % partout</t>
+          <t>reserve margin, 15 % everywhere</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
@@ -3148,12 +3148,12 @@
       <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>RÉVISER</t>
+          <t>REVISE</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
@@ -3175,14 +3175,14 @@
       <c r="M49" s="4" t="inlineStr"/>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>AUCUNE SOURCE. 15 % uniforme hérité. C'est ce paramètre qui explique l'essentiel de l'écart de coût avec le legacy (pénalité de violation 6256 M$ -&gt; 0).</t>
+          <t>NO SOURCE. Uniform 15 % inherited. This parameter explains most of the cost gap with the legacy run (violation penalty 6256 M$ -&gt; 0).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Réserves</t>
+          <t>Reserves</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>saison de pointe = Q5</t>
+          <t>peak season = Q5</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
@@ -3206,12 +3206,12 @@
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>terminé</t>
+          <t>done</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>RECONSTRUIRE</t>
+          <t>REBUILD</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
@@ -3228,19 +3228,19 @@
       <c r="L50" s="4" t="inlineStr"/>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>Suit la suppression de la saison de pointe. Ce drapeau ne sert qu'à choisir la saison dont on prend la NTC pour le partage de capacité ferme (base.gms:1005) ; il ne dimensionne pas la réserve, qui passe par un smax sur toutes les tranches.</t>
+          <t>Follows the removal of the peak season. This flag only serves to choose the season whose NTC is used for firm capacity sharing (base.gms:1005); it does not size the reserve, which goes through a smax over all blocks.</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>FAIT (phase 1) : Q5 -&gt; Q1. Ce drapeau ne sert qu'à une chose (base.gms:1005) : choisir la saison dont on prend la NTC pour le partage de capacité ferme entre zones. Il ne pilote PAS le dimensionnement de la réserve, qui passe par smax sur toutes les tranches. Q1 = trimestre d'hiver, correct.</t>
+          <t>DONE (phase 1): Q5 -&gt; Q1. This flag serves one purpose only (base.gms:1005): choosing the season whose NTC is used for firm capacity sharing between zones. It does NOT drive the sizing of the reserve, which goes through a smax over all blocks. Q1 = winter quarter, correct.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Réserves</t>
+          <t>Reserves</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>marge par pays</t>
+          <t>margin by country</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
@@ -3264,12 +3264,12 @@
       <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>hors périmètre</t>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>IGNORER</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -3283,14 +3283,14 @@
       <c r="M51" s="4" t="inlineStr"/>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>Redondant avec la version zonale.</t>
+          <t>Redundant with the zonal version.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Réserves</t>
+          <t>Reserves</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>réserve tournante par pays</t>
+          <t>spinning reserve by country</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
@@ -3314,12 +3314,12 @@
       <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>DÉCISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -3337,14 +3337,14 @@
       <c r="M52" s="4" t="inlineStr"/>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>Désactivée dans pSettings, et aucune source.</t>
+          <t>Disabled in pSettings, and no source.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Réserves</t>
+          <t>Reserves</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>réserve tournante système</t>
+          <t>system-wide spinning reserve</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
@@ -3368,12 +3368,12 @@
       <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>hérité, conforme</t>
+          <t>inherited, fit for purpose</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>DÉCISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -3394,7 +3394,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B54" s="3" t="n"/>
@@ -3414,7 +3414,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>hydrogène (5 fichiers dans h2/)</t>
+          <t>hydrogen (5 files in h2/)</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
@@ -3438,12 +3438,12 @@
       <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>hors périmètre</t>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>IGNORER</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -3457,14 +3457,14 @@
       <c r="M55" s="4" t="inlineStr"/>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>Aucun enjeu H2 dans le périmètre CASA.</t>
+          <t>No H2 stakes in the CASA perimeter.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>défauts technologiques génériques</t>
+          <t>generic technology defaults</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
@@ -3488,12 +3488,12 @@
       <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>hérité 2020, à traiter</t>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>DÉCISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -3507,19 +3507,19 @@
       <c r="M56" s="4" t="inlineStr"/>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>Alternative à pGenDataInputDefault.</t>
+          <t>Alternative to pGenDataInputDefault.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>BILAN</t>
+          <t>SUMMARY</t>
         </is>
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>8 terminé | 6 partiel | 27 à faire | 7 hors périmètre</t>
+          <t>8 done | 6 partial | 27 to do | 7 out of scope</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Clé</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Accès</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Couvre</t>
+          <t>Covers</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Où la trouver</t>
+          <t>Where to find it</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Ce qu'elle contient</t>
+          <t>What it contains</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Modèle EPM CASA v7.9, porté et validé</t>
+          <t>EPM CASA model v7.9, ported and validated</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>16 zones, 7 pays, 2017-2030</t>
+          <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Seule source pour l'Afghanistan et le Pakistan : c'est pourquoi le build part d'une copie plutôt que d'une page blanche. Portage validé (demande, production, défaillance et corridors identiques au legacy). Hypothèses de 2020 périmées, profil de charge de millésime 2013.</t>
+          <t>Only source for Afghanistan and Pakistan: that is why the build starts from a copy rather than from a blank slate. Port validated (demand, generation, unserved energy and corridors identical to the legacy run). The 2020 assumptions are stale and the load profile is of 2013 vintage. Covers 16 zones and 7 countries over 2017-2030.</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>KG, KZ, TJ, TM, UZ</t>
+          <t>KAZ, KGZ, TAJ, TUR, UZB</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Un classeur par pays. KG 20 onglets (demande 8760 h Nord/Sud, cascade hydro). KZ 18 onglets, demande 8760 h PAR OBLAST (14) plus agrégats North/South/West, Demand Evolution en deux scénarios Reference et Net Zero, onglet Exchanges with non CA countries ; les échanges intra-Asie centrale sont absents. TJ 18 onglets, demande 8760 h Nord/Sud (2021), onglet Exchanges : liaison DC CASA-1000 300 MW dès 2026 avec fenêtre d'export mai-septembre, TJ vers AF Sangtuda-Kunduz 300 MW, PPA existant 188 MW ; aucun détail sur Rogun. TM 13 onglets, pas d'hydro, et DEMANDE DÉGRADÉE : journée moyenne par mois seulement (~288 points), sans découpage régional. UZ 19 onglets, demande 8760 h par 5 zones, onglet Fuel Availability unique aux cinq carnets.</t>
+          <t>One workbook per country. KG 20 sheets (8760 h demand North/South, hydro cascade). KZ 18 sheets, 8760 h demand PER OBLAST (14) plus North/South/West aggregates, Demand Evolution in two scenarios Reference and Net Zero, sheet Exchanges with non CA countries; intra-Central-Asian exchanges are absent. TJ 18 sheets, 8760 h demand North/South (2021), sheet Exchanges: CASA-1000 DC link 300 MW from 2026 with a May-September export window, TJ to AF Sangtuda-Kunduz 300 MW, existing PPA 188 MW; no detail on Rogun. TM 13 sheets, no hydro, and DEGRADED DEMAND: average day per month only (~288 points), with no regional breakdown. UZ 19 sheets, 8760 h demand over 5 zones, sheet Fuel Availability unique among the five books.</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Ouzbékistan</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Postérieur de 16 mois aux carnets V5.1, donc prioritaire sur eux pour l'UZB. Format .xlsb, lecture via pyxlsb.</t>
+          <t>Sixteen months later than the V5.1 books, hence takes precedence over them for UZB. Format .xlsb, read through pyxlsb.</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Gabarit 2026 CASA CENTRAL ASIA DATA REQUEST</t>
+          <t>2026 template, CASA CENTRAL ASIA DATA REQUEST</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>5 pays d'Asie centrale</t>
+          <t>KAZ, KGZ, TAJ, TUR, UZB</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>25 onglets (5 thèmes x 5 pays), DÉJÀ PRÉ-REMPLI avec les données 2020 nettoyées, zones en libellé texte. C'est le circuit officiel de validation par les TTL pays. Pré-rempli n'est pas validé. Ne couvre NI l'Afghanistan NI le Pakistan.</t>
+          <t>25 sheets (5 themes x 5 countries), ALREADY PRE-FILLED with the cleaned 2020 data, zones as free-text labels. This is the official validation channel through the country TTLs. Pre-filled is not validated. Covers NEITHER Afghanistan NOR Pakistan.</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Retours pays de l'équipe TTL, campagne 2026</t>
+          <t>Country feedback from the TTL team, 2026 campaign</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -3752,11 +3752,15 @@
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>KAZ, KGZ, TAJ, TUR, UZB</t>
+        </is>
+      </c>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Prioritaire sur DeCA et sur le modèle 2020 quand disponible. Les extensions de parc datées 2023+ héritées de 2020 sont des PROJETS, pas des faits : revue TTL obligatoire avant de les garder.</t>
+          <t>Takes precedence over DeCA and over the 2020 model where available. Fleet additions dated 2023+ inherited from 2020 are PROJECTS, not facts: TTL review is mandatory before keeping them.</t>
         </is>
       </c>
     </row>
@@ -3781,15 +3785,19 @@
           <t>client_confidential</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>AFG, KGZ, PAK, TAJ</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>(à localiser)</t>
+          <t>(to be located)</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Quantités contractuelles des 4 flux, à rattacher à pContractedTradeEnergy.</t>
+          <t>Contractual quantities of the 4 flows, to be attached to pContractedTradeEnergy.</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3809,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>EPMRESULTS.xlsx, résultats du modèle legacy</t>
+          <t>EPMRESULTS.xlsx, results of the legacy model</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -3814,7 +3822,11 @@
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
+        </is>
+      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>planning_sharefolder/casa_planning_sharefolder/CASA/1. Model/</t>
@@ -3822,7 +3834,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Référence de non-régression du portage. Signal d'alerte, pas critère d'acceptation.</t>
+          <t>Non-regression reference for the port. A warning signal, not an acceptance criterion.</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3861,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>PAK</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -3859,7 +3871,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>NTDC, Lahmeyer, master plan SNC Lavalin. TROU MAJEUR : 8 ans d'âge, IGCEP absent, alors que le Pakistan pèse 155 TWh, soit 38 % de la demande du modèle.</t>
+          <t>NTDC, Lahmeyer, SNC Lavalin master plan. MAJOR GAP: 8 years old, IGCEP missing, while Pakistan weighs 155 TWh, that is 38 % of the demand of the model.</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3898,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -3896,7 +3908,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>AFGDISPATCH.gms et .xlsx. TROU MAJEUR : antérieur à 2021, aucune source alternative fiable hors Global Energy Monitor.</t>
+          <t>AFGDISPATCH.gms and .xlsx. MAJOR GAP: earlier than 2021, no reliable alternative source outside Global Energy Monitor.</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3920,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Rapport Mercados et modèle PLEXOS associé</t>
+          <t>Mercados report and the associated PLEXOS model</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -3921,7 +3933,11 @@
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>KAZ, KGZ, TAJ, TUR, UZB</t>
+        </is>
+      </c>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
     </row>
@@ -3946,7 +3962,11 @@
           <t>open_source</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
+        </is>
+      </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>renewables.ninja</t>
@@ -3954,7 +3974,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Profils horaires solaire et éolien par coordonnées. Déjà utilisé par pre-analysis/pipelines/vre_pipeline.py.</t>
+          <t>Hourly solar and wind profiles by coordinates. Already used by pre-analysis/pipelines/vre_pipeline.py.</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3986,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Demande directe aux gestionnaires de réseau</t>
+          <t>Direct request to the transmission system operators</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -3979,11 +3999,15 @@
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>NTC et calendriers de mise en service des corridors. Non engagée à ce jour.</t>
+          <t>NTCs and commissioning schedules of the corridors. Not started to date.</t>
         </is>
       </c>
     </row>
@@ -3995,7 +4019,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Sortie du pipeline pre-analysis (journées représentatives, profils VRE)</t>
+          <t>Output of the pre-analysis pipeline (representative days, VRE profiles)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4008,7 +4032,11 @@
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
+        </is>
+      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>EPM/pre-analysis/</t>
@@ -4024,7 +4052,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Décision de l'équipe de modélisation</t>
+          <t>Modelling team decision</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4037,7 +4065,11 @@
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
+        </is>
+      </c>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr"/>
     </row>
@@ -4049,7 +4081,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>AUCUNE SOURCE - hypothèse posée</t>
+          <t>NO SOURCE - assumption made</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4062,11 +4094,15 @@
           <t>assumption</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
+        </is>
+      </c>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>À rendre explicite dans la note de méthode : toute valeur portée ici est à justifier ou à remplacer.</t>
+          <t>To be made explicit in the methodology note: every value carried here is to be justified or replaced.</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4114,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Courriels de l'équipe CASA</t>
+          <t>CASA team emails</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -4091,7 +4127,11 @@
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Context/opening_emails/</t>
@@ -4099,7 +4139,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Circuit de validation imposé : Mercados, puis gabarit, puis revue TTL, puis EPM. Exercice INTERNE, non partageable à l'externe (Kabir Malik, 5 août 2026).</t>
+          <t>Mandated validation channel: Mercados, then template, then TTL review, then EPM. INTERNAL exercise, not to be shared externally (Kabir Malik, 5 August 2026).</t>
         </is>
       </c>
     </row>
@@ -4128,32 +4168,32 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Pays</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Organisme</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Adresse</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Statut</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Contenu constaté</t>
+          <t>What was found</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Ce qu'on en fait</t>
+          <t>What we do with it</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4205,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>NTDC / ISMO — IGCEP 2025-35</t>
+          <t>NTDC / ISMO - IGCEP 2025-35</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -4175,17 +4215,17 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>TESTÉ — DISPONIBLE</t>
+          <t>TESTED - AVAILABLE</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>PDF gratuit de 320 pages, mai 2025 : demande en 3 scénarios jusqu'en 2035 (GWh et MW), parc unité par unité, candidats datés et chiffrés, rendements, facteurs de charge. 43 069 MW en 2024, 64 035 MW visés en 2035.</t>
+          <t>Free 320-page PDF, May 2025: demand in 3 scenarios out to 2035 (GWh and MW), fleet unit by unit, candidates dated and costed, efficiencies, load factors. 43,069 MW in 2024, 64,035 MW targeted in 2035.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>PRIORITÉ 1. Remplace à lui seul le sharefolder de 2018. Deux retraitements : prolonger 2035 vers 2050, et écrire la correspondance 11 DISCO vers nos 3 zones PAK.</t>
+          <t>PRIORITY 1. Replaces the 2018 sharefolder on its own. Two treatments needed: extend 2035 to 2050, and write the mapping from the 11 DISCOs to our 3 PAK zones.</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4237,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>NTDC — IGCEP 2024-34</t>
+          <t>NTDC - IGCEP 2024-34</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4207,17 +4247,17 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>TESTÉ — DISPONIBLE</t>
+          <t>TESTED - AVAILABLE</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>239 pages, avril 2024. Annexe A consommation par catégorie, annexe B parc au 30 juin 2023 et coûts des candidats, annexes C-F scénarios de demande.</t>
+          <t>239 pages, April 2024. Annex A consumption by category, annex B fleet as of 30 June 2023 and candidate costs, annexes C-F demand scenarios.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Millésime de contrôle : l'écart entre les deux éditions révèle les glissements de calendrier des grands barrages.</t>
+          <t>Control vintage: the gap between the two editions reveals the schedule slippage of the large dams.</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4269,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>NEPRA — State of Industry Report 2025</t>
+          <t>NEPRA - State of Industry Report 2025</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -4239,17 +4279,17 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>TESTÉ — DISPONIBLE</t>
+          <t>TESTED - AVAILABLE</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Bilan annuel, paru janvier 2026 : production réalisée, pertes par distributeur, recouvrement, tarifs.</t>
+          <t>Annual review, published January 2026: actual generation, losses by distributor, collection, tariffs.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Source directe de pLossFactor et calage de l'année observée.</t>
+          <t>Direct source for pLossFactor and calibration of the observed year.</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4301,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>KEGOC — rapports annuels intégrés</t>
+          <t>KEGOC - integrated annual reports</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -4271,17 +4311,17 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>TESTÉ — DISPONIBLE</t>
+          <t>TESTED - AVAILABLE</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Bilan électrique et POINTE VENTILÉE PAR ZONE Nord/Sud/Ouest, exactement notre découpage. Pointe du 27/12/2025 à 18h : 17 540 MW (N 10 645, S 4 403, O 2 492). Consommation 2025 : 124 606,5 GWh.</t>
+          <t>Electricity balance and PEAK BROKEN DOWN BY ZONE North/South/West, exactly our split. Peak of 27/12/2025 at 18h: 17,540 MW (N 10,645, S 4,403, W 2,492). Consumption 2025: 124,606.5 GWh.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>VALIDATION EXTERNE DÉJÀ FAITE : notre pointe coïncidente 2026 ressort à 17 886 MW, soit +2,0 % — un an de croissance. Seul paramètre du modèle validé de l'extérieur.</t>
+          <t>EXTERNAL VALIDATION ALREADY DONE: our coincident 2026 peak comes out at 17,886 MW, that is +2.0 %, one year of growth. The only model parameter validated from the outside.</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4333,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Jeu de données nodal (Data in Brief, CC BY)</t>
+          <t>Nodal dataset (Data in Brief, CC BY)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -4303,17 +4343,17 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>TESTÉ — DISPONIBLE</t>
+          <t>TESTED - AVAILABLE</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>193 lignes 220-1150 kV avec paramètres, 24 centres de charge, demande horaire nodale sur une semaine d'été et une d'hiver, centrales avec rendement et disponibilité. Millésime 2015.</t>
+          <t>193 lines 220-1150 kV with parameters, 24 load centres, nodal hourly demand over one summer week and one winter week, power plants with efficiency and availability. 2015 vintage.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Seul jeu nodal ouvert de la région. Indispensable si l'on crée une troisième zone KAZ_W ; à traiter comme une topologie, pas comme un niveau.</t>
+          <t>The only open nodal dataset of the region. Indispensable if a third KAZ_W zone is created; to be treated as a topology, not as a level.</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4365,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>KEGOC marché de gros, Bureau of National Statistics</t>
+          <t>KEGOC wholesale market, Bureau of National Statistics</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -4335,29 +4375,29 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>TESTÉ — PARTIEL</t>
+          <t>TESTED - PARTIAL</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Analyses de marché S1 2025, bilan énergétique au format AIE. Aucune série temporelle brute : l'horaire du marché d'équilibrage reste interne.</t>
+          <t>Market analyses H1 2025, energy balance in IEA format. No raw time series: the hourly data of the balancing market stays internal.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Cadrage sectoriel. Ne comble pas le besoin de profil horaire.</t>
+          <t>Sector framing. Does not fill the need for an hourly profile.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Tadjikistan</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Banque mondiale — MPA Rogun P181029</t>
+          <t>World Bank - MPA Rogun P181029</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4367,29 +4407,29 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TESTÉ — DISPONIBLE</t>
+          <t>TESTED - AVAILABLE</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Approbation du 17/12/2024. Phasage explicite : 1 660 MW à l'horizon 2028 (cote 1 185 m), 3 780 MW en 2035 en six groupes de 630 MW (cote 1 300 m), productible ~14 400 GWh/an.</t>
+          <t>Approval of 17/12/2024. Explicit phasing: 1,660 MW by 2028 (level 1,185 m), 3,780 MW in 2035 in six 630 MW units (level 1,300 m), output ~14,400 GWh/yr.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Corrige directement le parc hérité, qui place six groupes de 600 MW tous datés 2031 — une hypothèse déguisée en calendrier. Fort effet de levier : Rogun est le plus gros poste de capacité du modèle.</t>
+          <t>Directly corrects the inherited fleet, which places six 600 MW units all dated 2031, an assumption disguised as a schedule. High leverage: Rogun is the largest capacity item of the model.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Tadjikistan</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>AIE / OCDE — revues sectorielles</t>
+          <t>IEA / OECD - sector reviews</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -4399,24 +4439,24 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>TESTÉ — DISPONIBLE</t>
+          <t>TESTED - AVAILABLE</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Revue du secteur 2022 financée par l'UE et feuille de route des échanges transfrontaliers : parc, contraintes hivernales, structure des exports.</t>
+          <t>2022 sector review funded by the EU and cross-border trade roadmap: fleet, winter constraints, structure of exports.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Qualifie la saisonnalité tadjike, traduite en pTransferLimit et en disponibilité hydro.</t>
+          <t>Qualifies Tajik seasonality, translated into pTransferLimit and hydro availability.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Tadjikistan</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -4431,29 +4471,29 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>TESTÉ — RIEN</t>
+          <t>TESTED - NOTHING</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Aucun bilan énergétique ni rapport annuel en libre téléchargement. Les chiffres tadjiks en circulation viennent tous d'intermédiaires.</t>
+          <t>No energy balance nor annual report freely downloadable. The Tajik figures in circulation all come from intermediaries.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>À passer par le circuit TTL. C'est là que se réglerait la part du Sougd dans la consommation nationale.</t>
+          <t>To go through the TTL channel. That is where the share of Sughd in national consumption would be settled.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Kirghizstan</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>National Statistical Committee — bilan combustible-énergie</t>
+          <t>National Statistical Committee - fuel and energy balance</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -4463,29 +4503,29 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TESTÉ — DISPONIBLE</t>
+          <t>TESTED - AVAILABLE</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Bilan énergétique annuel en Excel, maquette héritée de l'URSS ; données mensuelles de production et d'échanges également collectées.</t>
+          <t>Annual energy balance in Excel, layout inherited from the USSR; monthly generation and exchange data also collected.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Calage sectoriel de la demande kirghize et vérification indépendante de la clé Nord/Sud.</t>
+          <t>Sector calibration of Kyrgyz demand and independent check of the North/South split.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Kirghizstan</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Portail Open Data</t>
+          <t>Open Data portal</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4495,29 +4535,29 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>TESTÉ — RIEN</t>
+          <t>TESTED - NOTHING</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>22 catégories en JSON, XML et Excel sous CC BY-NC-SA 4.0 — mais AUCUNE catégorie énergie ou électricité.</t>
+          <t>22 categories in JSON, XML and Excel under CC BY-NC-SA 4.0, but NO energy or electricity category.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Sans objet pour le modèle : le bilan énergie est une publication séparée, hors portail.</t>
+          <t>Irrelevant to the model: the energy balance is a separate publication, outside the portal.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Ouzbékistan</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>stat.uz (SDMX) et data.egov.uz</t>
+          <t>stat.uz (SDMX) and data.egov.uz</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -4527,29 +4567,29 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>TESTÉ — PARTIEL</t>
+          <t>TESTED - PARTIAL</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Portail normalisé SDMX, plus de 2 000 indicateurs officiels avec métadonnées ; portail open data national distinct. Rubrique énergie présente.</t>
+          <t>SDMX-standard portal, more than 2,000 official indicators with metadata; separate national open data portal. Energy section present.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Le mieux outillé techniquement de la région, accès machine possible. Reste à identifier les séries électricité utiles : NON FAIT.</t>
+          <t>The best equipped technically in the region, machine access possible. The useful electricity series remain to be identified: NOT DONE.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Ouzbékistan</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Stratégie énergétique 2030 (via profil AIE)</t>
+          <t>Energy strategy 2030 (via the IEA profile)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4559,29 +4599,29 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TESTÉ — DISPONIBLE</t>
+          <t>TESTED - AVAILABLE</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Objectifs officiels : &gt;120 TWh et 54 % de renouvelable en 2030, 27 GW d'ENR. Capacité ~25,8 GW fin 2025 dont 8 GW ENR, production 86,7 TWh en 2025.</t>
+          <t>Official targets: &gt;120 TWh and 54 % renewable in 2030, 27 GW of RE. Capacity ~25.8 GW end 2025 of which 8 GW RE, generation 86.7 TWh in 2025.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Cadrage de scénario et borne haute sur pMaxNewCapacity ENR. Ce sont des objectifs politiques : à traiter comme tels.</t>
+          <t>Scenario framing and upper bound on pMaxNewCapacity for RE. These are policy targets: to be treated as such.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Turkménistan</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Turkmenenergo, statistique d'État</t>
+          <t>Turkmenenergo, state statistics</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4591,17 +4631,17 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>TESTÉ — RIEN</t>
+          <t>TESTED - NOTHING</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Aucune publication officielle accessible. Seules des estimations tierces : ~7,1 GW au gaz, ~44,8 TWh en 2024, aucune capacité ENR en 2025.</t>
+          <t>No accessible official publication. Third-party estimates only: ~7.1 GW gas-fired, ~44.8 TWh in 2024, no RE capacity in 2025.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Le carnet DeCA TM, tout dégradé qu'il soit (journée moyenne par mois, aucune résolution régionale), reste la meilleure source. Hypothèses à expliciter dans la note de méthode.</t>
+          <t>The DeCA TM book, degraded as it is (average day per month, no regional resolution), remains the best source. Assumptions to be made explicit in the methodology note.</t>
         </is>
       </c>
     </row>
@@ -4623,29 +4663,29 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>TESTÉ — RIEN</t>
+          <t>TESTED - NOTHING</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Aucune publication statistique régulière depuis 2021. Éléments épars : ~670 MW importés pour ~280 M USD/an selon DABS, imports de 4,6 à 5,2 TWh sur 2017-2022 selon l'ONU, panorama sectoriel privé de novembre 2025.</t>
+          <t>No regular statistical publication since 2021. Scattered elements: ~670 MW imported for ~280 M USD/yr according to DABS, imports of 4.6 to 5.2 TWh over 2017-2022 according to the UN, private sector overview of November 2025.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Suffit à recaler le NIVEAU des imports afghans, pas à reconstruire une demande zonale. Les cinq zones NEPS restent issues du modèle 2020, confiance basse assumée.</t>
+          <t>Enough to recalibrate the LEVEL of Afghan imports, not to rebuild a zonal demand. The five NEPS zones stay as they came from the 2020 model, low confidence assumed.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Régional</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ember — Monthly &amp; Yearly Electricity Data</t>
+          <t>Ember - Monthly and Yearly Electricity Data</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -4655,29 +4695,29 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>TESTÉ — DISPONIBLE</t>
+          <t>TESTED - AVAILABLE</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Production par filière, demande, capacité et émissions en MENSUEL pour 85 géographies dont nos sept pays, jusqu'à avril 2026. Téléchargement libre.</t>
+          <t>Generation by technology, demand, capacity and emissions MONTHLY for 85 geographies including our seven countries, up to April 2026. Free download.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Quatre années d'actuels que DeCA n'a pas : l'historique des carnets s'arrête en 2022. Calage de l'année de base et seul jeu homogène sur les sept pays.</t>
+          <t>Four years of actuals that DeCA does not have: the history of the books stops in 2022. Base year calibration and the only homogeneous dataset over the seven countries.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Régional</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Global Energy Monitor — Global Integrated Power Tracker</t>
+          <t>Global Energy Monitor - Global Integrated Power Tracker</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -4687,24 +4727,24 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>TESTÉ — DISPONIBLE</t>
+          <t>TESTED - AVAILABLE</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Parc mondial unité par unité, géolocalisé, avec statut et dates. UNE VERSION D'AOÛT 2026 EST PARUE ; nous détenons celle de septembre 2025.</t>
+          <t>Global fleet unit by unit, geolocated, with status and dates. AN AUGUST 2026 RELEASE IS OUT; we hold the September 2025 one.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Rafraîchissement immédiat du parc et seule couverture d'AFG et de PAK avec l'IGCEP. Le Tadjikistan y est sous-représenté : compléter par DeCA.</t>
+          <t>Immediate refresh of the fleet, and the only coverage of AFG and PAK alongside IGCEP. Tajikistan is under-represented there: complete with DeCA.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Régional</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -4719,24 +4759,24 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>TESTÉ — DISPONIBLE</t>
+          <t>TESTED - AVAILABLE</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Profils horaires solaire et éolien simulés en tout point du globe à partir de la réanalyse ERA5.</t>
+          <t>Hourly solar and wind profiles simulated anywhere on the globe from the ERA5 reanalysis.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Seule voie pour pVREProfile au Turkménistan, en Afghanistan et là où DeCA ne donne rien. Déjà branché dans pre-analysis/pipelines/vre_pipeline.py.</t>
+          <t>The only route to pVREProfile in Turkmenistan, in Afghanistan and wherever DeCA gives nothing. Already wired into pre-analysis/pipelines/vre_pipeline.py.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Régional</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -4751,29 +4791,29 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>TESTÉ — PARTIEL</t>
+          <t>TESTED - PARTIAL</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Carte mondiale des lignes prédite depuis les lumières nocturnes et OSM (grid.gpkg, targets.tif), précision annoncée ~70 % à 1 km.</t>
+          <t>Global map of lines predicted from night lights and OSM (grid.gpkg, targets.tif), announced accuracy ~70 % at 1 km.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Contrôle de TOPOLOGIE seulement : vérifier qu'un corridor existe et par où il passe. NE DONNE AUCUNE NTC — les capacités d'échange restent à demander aux opérateurs.</t>
+          <t>TOPOLOGY check only: confirm that a corridor exists and where it runs. GIVES NO NTC, transfer capacities still have to be requested from the operators.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Régional</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AIE profils pays, UN Comtrade, OWID</t>
+          <t>IEA country profiles, UN Comtrade, OWID</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -4783,29 +4823,29 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>TESTÉ — PARTIEL</t>
+          <t>TESTED - PARTIAL</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Bilans énergétiques nationaux en PDF gratuit, flux d'électricité déclarés en douane par paire de pays, séries longues de consommation.</t>
+          <t>National energy balances as free PDFs, electricity flows declared at customs by country pair, long consumption series.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Contrôle croisé des échanges historiques. Comtrade est de qualité inégale en Asie centrale : à ne pas utiliser seul.</t>
+          <t>Cross-check of historical exchanges. Comtrade is of uneven quality in Central Asia: not to be used alone.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Régional</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CASA-1000 — documents projet</t>
+          <t>CASA-1000 - project documents</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -4815,24 +4855,24 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>NON TESTÉ</t>
+          <t>NOT TESTED</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Calendrier, quantités contractuelles, saisonnalité d'export.</t>
+          <t>Schedule, contractual quantities, export seasonality.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Indispensable pour corriger pTransferLimit et pContractedTrade.</t>
+          <t>Indispensable to correct pTransferLimit and pContractedTrade.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Kirghizstan</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -4847,24 +4887,24 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>NON TESTÉ</t>
+          <t>NOT TESTED</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Production de la cascade du Naryn, niveau de Toktogul.</t>
+          <t>Generation of the Naryn cascade, level of Toktogul.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Le niveau de Toktogul est LA variable à suivre pour le bilan hiver.</t>
+          <t>The level of Toktogul is THE variable to watch for the winter balance.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Ouzbékistan</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -4879,17 +4919,17 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>NON TESTÉ</t>
+          <t>NOT TESTED</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Réseau et échanges régionaux.</t>
+          <t>Grid and regional exchanges.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>UZB est le pivot du CAPS : ce sont ses NTC internes qui conditionnent un éventuel découpage.</t>
+          <t>UZB is the pivot of the CAPS: it is its internal NTCs that condition any future split.</t>
         </is>
       </c>
     </row>

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>equipe</t>
+          <t>team</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, gabarit_2026</t>
+          <t>deca_v51, template_2026</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Filled by extract_demand.py, DeCA Reference scenario. Demand Evolution covers 2023-2060 BY COUNTRY: no extrapolation is needed for Central Asia. The intra- country split comes from the 8760 h profiles and stays constant over time, DeCA giving no regional trajectory. The zonal peak is NON COINCIDENT, as required by generate_demand.gms which multiplies it by the normalised profile of the zone: the own peak is therefore rescaled by the growth of the country peak, through the observed coincidence factor (KG 1.03, KZ 1.02, TJ 1.07, TM and UZ 1.00). Three deliberate departures, all documented in mappings/zones_demand.csv: the Tajik split is REVERSED with respect to the 2020 model (North 27.7 % against 74.9 %), the Kyrgyz split too (North 63.9 % against 93.2 %), and Western Kazakhstan is attached to KAZ_N for want of a third zone. The peak block of the TJ book was in GW under a MW label: corrected by a generic guard, a peak not being allowed to fall below the average power. AFG and PAK have no 2026 source: carried over from the 2020 pDemandData and extended at their own rate, LOW confidence.</t>
+          <t>Filled by extract_demand.py, DeCA Reference scenario. Demand Evolution covers 2023-2060 BY COUNTRY: no extrapolation is needed for Central Asia. The intra- country split comes from the 8760 h profiles and stays constant over time, DeCA giving no regional trajectory. The zonal peak is NON COINCIDENT, as required by generate_demand.gms which multiplies it by the normalised profile of the zone: the own peak is therefore rescaled by the growth of the country peak, through the observed coincidence factor (KG 1.03, KZ 1.02, TJ 1.07, TM and UZ 1.00). Three deliberate departures, all documented in mappings/zones_demand.csv: the Tajik split is REVERSED with respect to the 2020 model (North 27.7 % against 74.9 %), the Kyrgyz split too (North 63.9 % against 93.2 %), and Western Kazakhstan is OUT OF PERIMETER. The West (Atyrau, Mangystau) is a gas island synchronous with Russia, unable to trade with CAPS; the 2020 model folded its load into KAZ_N without its plants, which overstated the tightness of the North. It keeps its 12.9 % share of the national energy so that the North and the South are not inflated by it, and is dropped from the output: the KZ split is KAZ_N 64.4 %, KAZ_S 22.7 %, out of perimeter 12.9 %. Modelled Kazakhstan is North plus South, about 87 % of national consumption, which is what the results must be read against. The peak block of the TJ book was in GW under a MW label: corrected by a generic guard, a peak not being allowed to fall below the average power. AFG and PAK have no 2026 source: carried over from the 2020 pDemandData and extended at their own rate, LOW confidence.</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, gabarit_2026</t>
+          <t>deca_v51, template_2026</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>hypothese</t>
+          <t>assumed</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, hypothese</t>
+          <t>deca_v51, assumed</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, demande_tso</t>
+          <t>deca_v51, tso_request</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>hypothese</t>
+          <t>assumed</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr"/>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>hypothese</t>
+          <t>assumed</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>hypothese</t>
+          <t>assumed</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>hypothese</t>
+          <t>assumed</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr"/>
@@ -3697,7 +3697,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>gabarit_2026</t>
+          <t>template_2026</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>demande_tso</t>
+          <t>tso_request</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -4047,7 +4047,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>equipe</t>
+          <t>team</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -4076,7 +4076,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>hypothese</t>
+          <t>assumed</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -4109,7 +4109,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>courriels_equipe</t>
+          <t>team_emails</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -74,12 +74,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -769,16 +769,20 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>~40 flags and scalars</t>
+          <t>~40 flags and scalars, one of them set by the build</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -793,7 +797,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>casa_2020</t>
+          <t>casa_2020, pipeline</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
@@ -802,10 +806,14 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 8 TURNED fUseSimplifiedDemand ON, which is the only value the build overrides: the other forty are the 2020 ones and are kept as they are, the verb editing single cells rather than rewriting the file. At 1 the model reads pDemandProfile and pDemandForecast and builds pDemandData itself by the NLP at generate_demand.gms:63. At 0 it would read pDemandData, which is empty by design. See pDemandProfile for the two routes and why this one was taken.</t>
+        </is>
+      </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>To be settled: carbon (OFF), storage (OFF), ramps (OFF), MinGen/MUDT (OFF), spinning reserve (OFF).</t>
+          <t>PHASE 7 SETTLED THE RESERVE FLAGS, all of them by leaving them where they are: fApplyZonalPlanningReserve on and fApplyPlanningReserveConstraint on with an empty country margin, which is the 2020 formulation; both spinning reserve flags off, DeCA holding no operating reserve either. See pPlanningReserveMarginZone and pSpinningReserveReqCountry. TWO TRAPS FOUND AND LEFT IN PLACE BECAUSE THEY ARE INERT TODAY. 1. sPeakLoadProximityThreshold IS EMPTY, hence zero, and main.gms:677 tests a strict inequality against it, so pAllHours is zero everywhere and main.gms:686 gives EVERY SOLAR AND WIND UNIT A CAPACITY CREDIT OF ZERO. It costs nothing today, pCapacityCredit feeding only the country and system reserves which generate no row here, but anyone switching to a country reserve in phase 9 would silently be telling the model that renewables are worth no firm capacity at all. 2. fUseSimplifiedDemand SETTLED BY PHASE 8 AND NOW AT 1, the profile being built. The trap it was is worth remembering: at 0 the model reads pDemandData and at 1 it rebuilds it out of pDemandProfile, and until phase 8 BOTH were empty, so the model had no demand at all whichever way the flag was set. Still to be settled elsewhere: carbon (OFF, phase 9), storage (OFF), ramps (OFF), MinGen and MUDT (OFF, dispatch only).</t>
         </is>
       </c>
     </row>
@@ -844,7 +852,7 @@
           <t>KEEP</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -885,25 +893,21 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>5 seasons x 1 day x 7 blocks = 8760 h</t>
+          <t>4 seasons x 3 representative days x 24 chronological hours = 288 blocks, 8760 h</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>structure adapted, data to do</t>
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>REBUILD</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -928,12 +932,12 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>q = 4 quarters, the 5th peak season is removed. It was not a structure but a patch: the reserve constraint takes a smax over all blocks (base.gms:991) and requires no dedicated season. Q5 only served to give that smax a block short enough to see the true peak, for want of representative days (d=1 in the 2020 model).</t>
+          <t>q = 4 quarters, the 5th peak season is removed. It was not a structure but a patch: the reserve constraint takes a smax over all blocks (base.gms:991) and requires no dedicated season. Q5 only served to give that smax a block short enough to see the true peak, for want of representative days (d=1 in the 2020 model). THE FOUR QUARTERS ARE NOT CALENDAR QUARTERS, and the months behind them are now written down in data_build/mappings/seasons_months.csv: Q1 December to February, Q2 March and April, Q3 May to September, Q4 October and November. That split is read off the 2020 durations, Q1 and Q5 together 2180 h that is 90.8 days, Q2 1464 h exactly 61 days, Q3 3652 h that is 152.2 days, Q4 1464 h exactly 61 days, and it lands on 8760 h to the hour. Q3 is the irrigation release window and the window of the CASA-1000 contract, 1 May to 30 September. Every season-indexed resource is built against that mapping. PHASE 8 REBUILT IT, and this is the file that defines the sets q, d and t for the whole model: main.gms:214 reads pHours(q&lt;,d&lt;,t&lt;), so every other hourly resource follows whatever shape is written here. It is now four seasons by three representative days by twenty four chronological hours, the canonical EPM shape that epm/input/data_test also carries, and each cell holds THE NUMBER OF DAYS the representative day stands for, repeated over its 24 hours, summing to 8760. THE PEAK REPRESENTATIVE DAY REPLACES THE OLD PEAK SEASON. In each season, d1 is the calendar day carrying the highest system load of that season and weighs one day; d2 and d3 are the mean days of the two halves of the rest of the season, split by daily energy. Energy and peak are therefore both exact by construction, which is what base.gms needs when it takes an smax over (q,d,t) for the reserve. The four peak days chosen are 12 December, 18 March, 28 June and 29 November. The season durations are unchanged, 90 / 61 / 153 / 61 days, so pAvailability and pTransferLimit did not have to be rebuilt.</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>PHASE 8. Rebuild as 4 quarters x representative days x chronological hours, including a PEAK REPRESENTATIVE DAY that replaces the former Q5 season.</t>
+          <t>THE NUMBER OF REPRESENTATIVE DAYS IS ONE ARGUMENT, --days, and three is a starting point rather than a result: the model went from 35 blocks in 2020 to 288 here, and if the solve turns out to be comfortable the count should go up, the days being grouped by demand alone today and therefore carrying no renewable variability. See pVREProfile, where the same limit bites harder.</t>
         </is>
       </c>
     </row>
@@ -972,7 +976,7 @@
           <t>EXTEND</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1013,7 +1017,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>CO2 factors by fuel</t>
+          <t>CO2 factors by fuel, tCO2 per MMBtu</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -1037,18 +1041,18 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>casa_2020</t>
+          <t>casa_2020, epa_ghg_factors</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>EPA factors, stable since 2014</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Standard values, no reason to move them.</t>
+          <t>PHASE 6.4 checked and sourced, and nothing moves. The table is not a CASA estimate at all, it is the EPA emission factor set read off the standard table: natural gas 53.06 kg CO2 per MMBtu, sub-bituminous coal 97.17, residual fuel oil No. 6 75.10, which are the 0.05306, 0.09717 and 0.0751 of this file to the last digit. They are combustion chemistry rather than country data, so no DeCA book could improve them and none of the five tries. Coal_KAZ_S carries the same factor as Coal, both being the sub-bituminous line; the two are separated by their price and their transport, not by their carbon. Import = 0 IS AN ASSUMPTION AND NOT A FACT: electricity imported from outside the sixteen zones is counted as emitting nothing, so any accounting that leans on it will flatter a zone that imports. It is the right default here, the model having no view of what is on the other side of an external tie, but a national footprint drawn from these results has to say so.</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr"/>
@@ -1097,12 +1101,8 @@
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>structure adapted, data to do</t>
         </is>
@@ -1112,7 +1112,7 @@
           <t>REBUILD</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Emptied, its content depends on the choice of representative days.</t>
+          <t>DELIBERATELY EMPTY, and it stays that way. Phase 8 chose the other of the two routes generate_demand.gms offers: pDemandProfile carries the shape, the peak and the energy of pDemandForecast carry the level, and the model builds pDemandData itself, year by year, by the NLP at generate_demand.gms:63. Writing it here would mean freezing thirteen years of hourly load in a csv, which is neither reviewable nor scenario friendly.</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>PHASE 8, from the hourly series aggregated in phase 2.</t>
+          <t>Only if a study needs a load shape that changes with the year, which nothing in the sources supports today.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
           <t>P9</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>filled, more to come</t>
         </is>
@@ -1231,43 +1231,51 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>normalised profile by (z,q,d,t)</t>
+          <t>normalised load shape by (z,q,d,t), maximum 1</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>deca_v51</t>
+          <t>deca_v51, casa_2020</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Demand Profile</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr"/>
+          <t>Demand Profile (8760 h)</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>KZ 2022 / TJ 2021 / KG / UZ</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 8 FILLED IT, AND IT IS WHAT MAKES THE MODEL RUNNABLE. Until this step both pDemandData and pDemandProfile were empty, every zone was dead and nothing could be solved. EIGHT ZONES READ THEIR OWN 8760 HOURS, the series extract_demand.py aggregated in phase 2: the two Kazakh zones, the two Kyrgyz, the two Tajik, Turkmenistan and Uzbekistan. Turkmenistan states one average day per month, 288 points, expanded over the days of each month; the zone is single and only its shape is used. EIGHT ZONES READ THE 2020 MODEL, the five Afghan ones and the three Pakistani ones, DeCA covering neither country. Their blocks are chronological hour of day groups and not a load duration curve, which the 2020 pVREProfile proves on its own: solar reads zero in the first and the last block and peaks in the middle one. The widths are read off the 2020 pHours, 6-5-3-3-4-3 hours, and each block is held flat over its own hours. Those zones have one shape per season and no day to day variation; their peak day is lifted by the ratio the old peak season carried over their seasonal days, which is the one piece of peak information it held. THE PEAK DAY OF EACH SEASON IS CHOSEN ON THE EIGHT SOURCED ZONES ALONE. Pakistan is a large share of the demand of the model and cannot vote on it, so the coincidence between Central Asia and Pakistan is inherited from the 2020 shapes rather than modelled. THE PROFILE IS NORMALISED TO A MAXIMUM OF EXACTLY 1, which is what generate_demand.gms expects: with fUseSimplifiedDemand at 1 it multiplies the profile by the peak of pDemandForecast, then adds a correction proportional to (max - profile) until the annual energy matches, a correction that is null at the peak. The peak of the profile is therefore the peak of the forecast, and the shape carries the rest. pDemandData stays empty on purpose: the year by year scaling is the work of the model, not of the pipeline. A CROSS CHECK THAT LARGELY PASSES. The load factor implied by this profile and the one implied by pDemandForecast were built from different sheets of the same books and agree to a thousandth on eleven zones of sixteen. Three do not, and the gap is DeCA disagreeing with itself: see the todo.</t>
+        </is>
+      </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Depends on pHours -&gt; deferred with it. Prepare the shape at HOURLY resolution as an intermediate, the aggregation to (q,d,t) is the last step.</t>
+          <t>THREE ZONES WHERE THE PROFILE AND THE FORECAST DISAGREE, profile load factor against forecast load factor: TAJ_N 0.715 against 0.618, TAJ_S 0.675 against 0.545, TUR 0.719 against 0.815. On the two Tajik zones the profile is flatter than the stated peak implies, which means the peak of pDemandForecast is high by some 14 per cent, and the Tajik peak is precisely the one phase 2 had to repair, the TJ book stating it in GW under a MW label. The simplified demand routine will absorb the gap by digging the valleys, so nothing breaks, but the Tajik reserve requirement is overstated until the peak is settled. ASK THE TJ AND TM SOURCES. No day to day variation for Afghanistan and Pakistan. The NTDC IGCEP would replace the Pakistani shape, which is the largest single gap left in the demand.</t>
         </is>
       </c>
     </row>
@@ -1413,25 +1421,25 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>power plants: capacity, status, HR, costs</t>
+          <t>power plants: capacity, status, HR, costs, 403 units</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>REPLACE</t>
+          <t>FILL</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1441,23 +1449,27 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, template_2026</t>
+          <t>deca_v51, casa_2020, assumed</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Thermal PP / Expansion / Candidates + HydroPP + Renewable PP</t>
+          <t>RenewableMaxEntry and CAPEX of the five books, tech_lifetime.csv and fleet_retirement.csv, over the 2020 table</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>2022 base</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr"/>
+          <t>2022 base, retirement rebuilt 2026</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 5 done, on the structure. Two rebuilds, both driven by mappings/ and both re-runnable with data_build/build_fleet.py. THE RETIREMENT SCHEDULE. The 2020 schedule was mechanical, min(max(StYr + Life, 2023), 2031), and that reproduces 208 of its 232 existing units exactly. Neither bound was a decision: 2031 was where that model stopped looking, 2023 was the day it was built. Carried into a run that goes to 2050 they wiped out 66 GW in one year, Nurek, Toktogul and Ekibastuz included, and left 375 MW standing in the whole model in 2050. Rebuilt from an operating life stated per technology in mappings/tech_lifetime.csv, with a floor at the start year plus four so that a plant running today does not vanish at the first year, and anything reaching 2050 still standing written as 2051, which in EPM means it never retires inside the run. Central Asia now goes 51.3 GW in 2026 to 23.5 GW in 2050, hydro holding at 16.4 GW throughout. 12 units keep a dated year, held in mappings/fleet_retirement.csv: the eight Nurek units taken off one at a time for rehabilitation, whose refurbished replacements are already in the table, and Bishkek CHP, which the 2020 model had itself singled out. DeCA GIVES NO RETIREMENT DATES. It carries a commissioning year and nothing on the end of life, so the lives in tech_lifetime.csv are an assumption, not a measurement, and they are the assumption most worth challenging with the TSOs. PHASE 8 FOUND THAT LIFE IS NOT A DURATION TO THIS MODEL, IT IS A FLAG, and the first run stopped on it. main.gms:879 reads a life of 99 as "this unit may never be retired" and fixes vRetire to zero for it, while main.gms:864 fixes the capacity of any unit to zero from its retirement year on. A unit carrying both a life of 99, which tech_lifetime.csv gives to hydro, and a dated stop inside the horizon is therefore asked to lose its whole capacity with nothing allowed to move: base.gms:770 and base.gms:775 came out infeasible on the eight Nurek units and the run aborted before solving. build_fleet.py now writes, for a unit whose stop is dated, the life that decision implies rather than the flag, Nurek 3 for instance stopping after 53 years. Nothing else changes: no equation of the model reads the life of a generator for anything but that flag, and retirement carries no cost in the objective. THE CANDIDATES, 124 lines touched, driven by mappings/candidate_limits.csv. Three things were wrong for a 2050 run. First the closed door: main.gms:754 makes the Capacity column the cumulative build limit of a candidate and it was 0 for 30 of them, every generic candidate of KGZ_N, KGZ_S, TAJ_N and TAJ_S bar a 200 MW CCGT, and four of KAZ_S. Kyrgyzstan and Tajikistan could build nothing at all outside named hydro projects, which alone explains why the winter unserved energy of TAJ_N only cleared with Rogun. Opened. Second the missing speed limit: BuildLimitperYear was ten million MW everywhere, so solar and wind could appear at any rate. DeCA states a real one per country in RenewableMaxEntry, 3000 MW a year of each for KZ and UZ, 500 for KG, TJ and TM, and it steps up after 2030 to 6000, 1500 and 3000. EPM has one column and cannot step, so each zone carries two candidates: the first from the opening of the run with the early rate, a second from 2031 with the increment. The national rate is shared across the zones of a country by their share of the national peak in 2050. Third, the cumulative cap of those VRE candidates is now derived from the rate rather than left at the round 10000 of the 2020 table, which was another number that meant no cap over a horizon stopping in 2031 and would have meant four years of Kazakh solar over one running to 2050. PHASE 6, THE COST COLUMNS. HeatRate and VOM of the existing Central Asian thermal fleet are rebuilt by build_costs.py from mappings/thermal_plants.csv, which carries all 70 of those units one by one against the DeCA Thermal PP sheets. 63 are matched to a named DeCA plant and 7 are not, each with its reason in the mapping: two Kazakh residual aggregates that are not plants, the Balkhash Ulken project and Karaganda TPS-2 which DeCA does not carry, Yavan likewise, and Almaty-1 and Fergana where the model and DeCA disagree on the fuel itself. THE HEAT RATE IS TAKEN FROM DeCA WHEREVER A UNIT IS MATCHED, because a stated per-plant efficiency beats a per-technology constant: the 2020 model gave every Kazakh coal CHP the same 11.23 where DeCA separates them from 0.208 at Astana-2, which becomes 16.40, to 0.275 at Pavlodar-3, which becomes 12.42. 15 of the 63 units were already carrying the DeCA value, which is a good sign on the match. Shymkent moves the other way, 11.23 to 6.09, DeCA giving it a combined cycle efficiency of 0.560. THE VOM IS TAKEN ONLY WHERE DeCA DEPARTS FROM ITS OWN DEFAULT. It writes 3.400 $/MWh for 128 of its 136 thermal units, across five countries and every technology at once, which is a filler and not a measurement, and adopting it would flatten the technology spread the 2020 model does carry. Where it does depart, the departure is the information: the old Uzbek steam sets at 9.100, Takhiatash at 3.540, Navoi at 3.500, the combined cycles at 4.250. KAZAKH GAS TRANSPORT LANDS IN THE VOM rather than in pFuelPrice, because it is the one genuinely regional fuel cost in the region and the model carries only two Kazakh gas plants, at opposite ends of it. Zhambyl takes 0.370 $/MMBtu over its own 9.399 MMBtu/MWh and Shymkent 4.998 over 6.093, so their VOM reads 18.9 and 39.2 $/MWh. That looks alarming and is not: the decomposition moved, the total did not, and both plants come out cheaper than before, 67.2 to 50.0 $/MWh at Zhambyl and 64.7 to 59.4 at Shymkent. The step is idempotent, every value it writes being absolute and the VOM baseline always read from the 2020 reference rather than from the file under the pen. RUN ORDER IS build_fleet.py THEN build_costs.py, the second rewriting the file the first produces. PHASE 6, THE CANDIDATE COSTS. HeatRate, Capex, FOMperMW, VOM and Life of the 86 thermal candidates are rebuilt from the Thermal PP Candidates sheet through mappings/thermal_candidates.csv, which says which DeCA line each of the eleven (tech, fuel) pairs of the model reads. 79 rows move and 7 keep their 2020 costs, the coal fired CHPs and the oil fired steam turbines, DeCA carrying neither. THAT SHEET IS A TECHNOLOGY TABLE AND NOT A COUNTRY ONE: the five books state the same numbers to the dollar, so it is read from all five at once and any book that departs is outvoted and the departure printed. One does, TJ pricing new coal at 500,000 $/MW where the other four say 2,500,000, which is a typo and not a Tajik discount. Being a technology table is also what licenses using it in Pakistan and Afghanistan, outside the DeCA perimeter: the 2020 model applied ONE GLOBAL COST SET to all sixteen zones, so holding those two on 2020 while the five move would not preserve a country difference, it would invent one and let the model arbitrage on it. NEW COAL IS READ ON THE Supercritical LINE AND NOT ON THE ONE HEADED Coal, which is the judgement of the step. The Coal line states an efficiency of 0.33 at 2,500,000 $/MW while Supercritical, four rows below it in the same table, states 0.46137 at 2,250,000: cheaper to build, cheaper to run and half again as efficient, so the plain line is dominated by its own neighbour and no planner would ever pick it. The 2020 model already carried 0.42 here, a supercritical class unit. One word in the mapping falls back to the subcritical line. LIFE MOVES WITH THE COSTS BECAUSE IT MUST: main.gms:742 builds the capital recovery factor out of it, so taking a CAPEX without the amortization period stated beside it would annualize the new number on the old horizon. CCGT and gas turbines go from 30 years to 25, coal from 40 to 35, engines from 20 to 25, and nuclear from 40 to 60. WHAT IT COSTS, levelised at a 75 per cent capacity factor and a WACC of 10 per cent, before and after: CCGT 77.8 to 68.9 $/MWh, gas turbine 109.2 to 90.2, gas CHP 119.9 to 104.3, coal 58.9 to 52.6, engines 26.1 to 17.8, nuclear 107.0 to 106.6. EVERY THERMAL CANDIDATE GETS CHEAPER, which is the honest reading of a 2025 cost book against a 2020 one, and nuclear barely moves because its CAPEX rising by a third is cancelled by sixty years to amortize it over and a variable cost that falls from 16.83 to 0.67. Capacity, StYr and BuildLimitperYear are untouched, being the shape of the menu and not its cost, and so is the DeCA Max Capacity column, which is carried in the report and out of the table: it reads like a unit size, 300 MW for a coal or combined cycle block and 1200 for a nuclear one, but DeCA never says so and EPM reads Capacity as a cumulative build limit, so writing 300 there would silently cap all new coal in a country at one block. The fixed cost of the EXISTING units is still the 2020 value, DeCA stating none.</t>
+        </is>
+      </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>PHASE 5, the big one. STRUCTURAL ANOMALY TO REOPEN: the generic candidates carry 10000 MW buildable in KAZ, UZB, TUR, PAK and the 5 NEPS zones, but 0 MW in KGZ_N, KGZ_S, TAJ_N and TAJ_S (the only exception being a 200 MW CCGT at TAJ_N). Kyrgyzstan and Tajikistan can therefore build nothing outside named hydro projects, which alone explains why the winter unserved energy of TAJ_N only clears with Rogun. This is not an economic arbitrage of the model, it is a closed door.</t>
+          <t>PHASE 6, WHAT THE HEAT RATE REBUILD EXPOSES. DeCA states the ELECTRICAL efficiency of a plant, and for a CHP that is only part of the story: Astana-2 at 0.208 sends most of its fuel to district heat, so charging all of it to electricity at 16.40 MMBtu/MWh over-prices the unit, and the flat 11.23 of the 2020 model was implicitly crediting the heat. EPM carries no heat, so the honest repair is not a softer heat rate but a winter must-run. PHASE 7 LOOKED FOR THAT LEVER AND IT IS NOT THERE: MinLimitShare is a dead column in this version, read by no equation of base.gms or main.gms, and the real must-run switch is MinGenCommitment, which base.gms:847 guards with fDispatchMode. It therefore binds in an hourly dispatch run and NOT in the expansion, which is what this model is. So the Kazakh CHPs stay too far down the merit order for now, and the two honest ways out are both later: run the dispatch of phase 8 with MinGenCommitment on, or credit the CHPs for their heat inside the heat rate itself, which is a phase 9 assumption and not a repair. PHASE 6, WHAT IS NOT DONE. FOMperMW of the EXISTING units is still the 2020 value everywhere. DeCA states no fixed cost for an existing unit at all, only for its candidates, and putting a candidate figure on a fifty year old CHP would be worse than leaving it. A NEW KAZAKH GAS UNIT PAYS NO FUEL TRANSPORT WHERE AN EXISTING ONE DOES, and that asymmetry is the one thing the candidate step leaves crooked. Kazakh gas transport is regional, 0 on the Atyrau fields to 13.3 at the end of the pipeline, so it sits in the VOM of the two existing plants rather than in the price; a candidate has no site, so it pays the molecule alone and comes out systematically cheaper to fuel than the fleet it competes with. The capacity weighted national mean is 3.851 $/MMBtu, some 21 $/MWh on a combined cycle, which is not a rounding error. The repair is either a zone mean adder on the Kazakh gas candidates or siting them, and it wants the Zones_Regions sheet. THERMAL CANDIDATES CARRY NO CAPEX TRAJECTORY: only solar, wind and batteries have one, so a 2025 combined cycle cost is charged unchanged in 2050. That is defensible for mature thermal plant and it is what DeCA states, but it should be said out loud rather than left as a silent flat line. THE DeCA CANDIDATE MENU IS WIDER THAN THE MODEL USES. CCGT with CCS, coal with CCS, ultrasupercritical coal, CCGT on biogas and the dual gas/hydrogen machine are all priced in the same sheet and none of them exists as a candidate in this model. They are the natural furniture of a decarbonization scenario in phase 9, alongside the CCS capture costs the KZ book carries region by region, 13.32 to 19.32 $/tCO2. PHASE 5, what is left: the existing fleet against DeCA. Its Thermal PP sheets carry 136 units and 51.9 GW over the five countries, where this table has 31.5 GW of Central Asian plant of every kind. Whole plants are missing: the 598 MW of Tajik thermal, Dushanbe-1 and Dushanbe-2, sits here at zero capacity and retired; Bishkek is 666 MW here against 812 MW in DeCA; Turkmenistan is 5.8 GW here against 7.7 GW. The named hydro candidates stuck at Capacity 0 are the other half of it: NARYN, KOKEMEREN-1 and 2, DASHTIJUM, against a DeCA pipeline that carries Rogun at 3380 MW by 2033, Kambarata-1 at 1860, Kambarata-2 at 240, Kulanak at 100, Pskem at 404, Mullalak at 240, an uprating of Nurek of 385 and of Kayrakum of 48. Those are project decisions, not a rule, so they go one by one in a mapping of their own. DeCA also caps its own solar and wind candidates by region, Max. Capacity (MW) in Renewable PP Candidates. That is a resource limit and not a connection rate, and it is not used here because it is stated per oblast and not per model zone.</t>
         </is>
       </c>
     </row>
@@ -1479,25 +1491,21 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>seasonal availability by plant (g x Q1..Q4)</t>
+          <t>seasonal availability by plant, 403 units x 4 seasons</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>403</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>structure adapted, data to do</t>
+        <v>419</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>REBUILD</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1507,27 +1515,27 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>deca_v51</t>
+          <t>deca_v51, casa_2020</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Hydro Profile + HydroPP (Inflows)</t>
+          <t>HydroPP + Hydro Profile, Reference hydrology</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Peak column removed. BEWARE, it carried a convention: 350 plants out of 403 had Q5=1.0 against Q1=0.85, that is full availability at the peak. This firm capacity assumption disappears and has to be reintroduced.</t>
+          <t>Rebuilt by build_hydro.py from data_build/mappings/hydro_plants.csv, which carries the 134 hydro units of the model one by one, and from data_build/mappings/seasons_months.csv, which says which months each season holds. 45 units out of 134 now rest on DeCA: 11 take its monthly profile directly, the 5 Kazakh plants whose profile is plant-specific and the Pskem and Upper Naryn candidates; 34 keep the 2020 seasonal shape, which describes the reservoir operation, and have their level brought back to the DeCA capacity factor. THE 2020 MODEL WAS OPTIMISTIC ON CENTRAL ASIAN HYDRO: it allowed Toktogul 1.64 times, Uch-Kurgan 1.71 times and Charvak 1.75 times the energy DeCA gives them. The seasonal availability is the water constraint of the model, base.gms:806 caps the energy of a season with it, so that gap was a gift of water. Kazakhstan runs the other way, DeCA being more generous than 2020 on Bukhtarma and Ust-Kamenogorsk. The 89 remaining units keep their 2020 values, each with its reason in the mapping. The peak column of the 2020 model is gone with the peak season, see pHours. It carried a convention, 267 plants out of 403 at Q5 = 1.0 and 313 valued above their Q1, that is firm capacity at the peak. PHASE 7 SETTLED WHAT BECOMES OF IT: the convention is not restored, the credit stays at the real 0.85, and the consequence is measured in pPlanningReserveMarginZone. PHASE 7 ALSO CLOSED A HOLE THIS BUILD HAD OPENED ITSELF. The 2020 table covered its 403 units exactly; the 16 solar and wind candidates added from 2031 had no line, and a generator absent from pAvailability is not defaulted to one, it is READ AS ZERO, base.gms:812 then writing vPwrOut = 0 over the whole horizon. Solar was rescued by the generic fallback of the model, which carries a PV/Solar line; wind was not, its technology being WT here and OnshoreWind there, so EIGHT WIND CANDIDATES COULD BE BUILT AND WOULD HAVE PRODUCED NOTHING. build_hydro.py now completes the table against the fleet, giving a missing unit what its own technology and fuel carry elsewhere by majority, and refusing to guess on a tie or on a pair it has never seen. RUN ORDER IS build_fleet.py THEN build_hydro.py.</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>PHASE 4. Rebuild from the monthly inflows of deca_v51 (Hydro Profile + HydroPP Inflows), and reintroduce firm peak capacity, either through the peak representative day or through pCapacityCreditPeakSeason.</t>
+          <t>1. Kambarata-2, Rogun and Shardara have a DeCA yearly production above their own capacity, the production of the full project against one unit, so their level could not be used. 2. Farhad is carried at 311 MW here against 126 MW in DeCA, and its DeCA production gives an annual 0.02: the plant identity has to be settled in phase 5. 3. Pakistan, 41 units, and Afghanistan, 15 units, are outside the DeCA perimeter and still rest on the 2020 model: they need the NTDC IGCEP and the DABS fleet. 4. The dry and wet hydrologies are in the same sheets, read with --scenario, and are waiting for the scenario phase.</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1563,11 @@
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
           <t>inherited 2020, to process</t>
@@ -1563,25 +1575,33 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>assumed</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr"/>
+          <t>deca_v51, assumed</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Thermal PP, columns Forced Outage Rate / Scheduled Outage Rate</t>
+        </is>
+      </c>
       <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Empty, and it changes nothing today: all 403 units of the fleet carry a line of their own in pAvailability, and this table only speaks for a unit that has none. It will start to matter with the candidates of phase 5. CORRECTION to an earlier reading of the sources: DeCA DOES give outage rates. It carries 0.05 forced and 0.05 scheduled, 0.10 unavailable in all, for every thermal plant of the five countries, 136 units, with no distinction of country or technology. That is a convention, not a measurement, so adopting it would only trade the 0.85 of the 2020 model for a more generous 0.90.</t>
+        </is>
+      </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>DeCA does NOT give the forced outage rates of the thermal fleet, and the GenAvailability sheet of the template is empty.</t>
+          <t>PHASE 5, with the candidates: either keep the 0.85 of the 2020 model, or take the 0.90 of DeCA, and say which. A real outage rate would have to come from the TSOs.</t>
         </is>
       </c>
     </row>
@@ -1665,55 +1685,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>solar/wind profile by (z,tech,q,d)</t>
+          <t>solar and wind production by (z,tech,q,d,t), as a fraction of capacity</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>structure adapted, data to do</t>
+        <v>384</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>REBUILD</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, renewables_ninja</t>
+          <t>deca_v51, casa_2020</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>RenewableProfile (monthly)</t>
+          <t>RenewableProfile, monthly utilization factors</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025 level / 2020 shape</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Emptied, its content depends on the choice of representative days.</t>
+          <t>PHASE 8 BUILT IT FROM TWO SOURCES BECAUSE NEITHER GIVES BOTH HALVES. base.gms:812 writes the output of every solar and wind unit as this profile times the availability times the capacity, so the table is the whole renewable production, in level as much as in shape. DeCA GIVES THE LEVEL AND NOT THE SHAPE: RenewableProfile states a monthly utilization factor per plant and no hour of the day. Its own header says so, in a line the authors left for themselves, "Hourly profiles are also needed for all WPP and SPP power plants". THE 2020 MODEL GIVES THE SHAPE and a level five years old. So the day shape comes from the 2020 profile, normalised to a mean of one, and is multiplied by the DeCA seasonal factor, the month length weighted mean over the months of the season and over the plants mappings/vre_profiles.csv selects. THE FACTOR IS A COUNTRY MEAN over every plant of the technology, existing and candidate, high yield and low yield sites together, because the five books name no zone for their existing plants. That is an average site, which is what a generic candidate is. Sixty four of the 128 seasonal factors move; the Afghan and Pakistani zones keep their 2020 level, being outside the DeCA perimeter. WHAT MOVES: mean solar capacity factor 0.169 to 0.152, mean wind 0.333 to 0.354. Solar loses most in winter, KAZ_N Q1 going from 0.144 to 0.089, which matters in a system that peaks in December. TWO TRAPS THE MAPPING STEPS AROUND. The Tajik book labels its own regions with a KZ prefix, Khatlon and Sougd and Gorno-Badakhshan all reading "KZ ...", so the selection keys on the workbook and not on the name. And one Kazakh SOLAR plant is named Arm Wind: the exclude column of the mapping settles it on the _SP suffix, and the builder refuses outright any row two technologies claim at once.</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>PHASE 8.</t>
+          <t>EVERY REPRESENTATIVE DAY OF A SEASON CARRIES THE SAME RENEWABLE DAY, because a monthly factor holds no day to day variation. There is no cloudy day and no calm day in this model, only an average one, which understates the backup a large renewable fleet needs. It costs little today, the VRE fleet being small, and it becomes the binding weakness of the time structure as soon as the model starts building solar and wind at scale. The repair is an hourly renewable source, Renewables.ninja or the ERA5 reanalysis, clustered on the same representative days as the demand.</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1768,7 @@
           <t>FILL</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1801,12 +1817,12 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>inherited, fit for purpose</t>
+          <t>done</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1814,7 +1830,7 @@
           <t>FILL</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1831,10 +1847,14 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>2025-2050</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr"/>
+          <t>2023-2050, normalised at 2026</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 5 done. The table was empty, so every candidate cost the same in 2050 as in 2026. It now carries the DeCA cost curve as a multiplier normalised at 2026, for solar, wind and the battery, in every zone: solar to 0.46 by 2050, wind to 0.88, the four-hour battery to 0.64. Applied in every zone, Pakistan and Afghanistan included, because the five DeCA books carry the same CAPEX sheet byte for byte. That makes it a technology curve and not a country one, and there is no reason a Pakistani panel would be spared a fall in the world price of panels. The battery rows stop at the DeCA perimeter, only because that is where the battery candidates are. PHASE 8 HAD TO COMPLETE THE TABLE, and the reason is worth recording because it contradicts what phase 5 wrote here. Leaving thermal out is not neutral: input_treatment.py joins this table on the (zone, tech, fuel) of EVERY generator of the fleet and stops the run when one of them finds no row, "Missing values in default is not permitted". Forty rows against a hundred and thirty-eight triples was an aborted run, not a flat cost. So the builder now writes a FLAT CURVE, one everywhere, for every triple the fleet carries and the cost curve says nothing about: a gas turbine of 2050 is assumed to cost in real terms what it costs today, which is what DeCA says of it and what the model would otherwise have assumed by default. The DeCA curve still applies to solar, wind and the battery alone, and the print of build_fleet.py says how many rows are on a curve.</t>
+        </is>
+      </c>
       <c r="N23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1862,14 +1882,14 @@
         <v>25</v>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>REPLACE</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -1879,23 +1899,27 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>deca_v51</t>
+          <t>deca_v51, casa_2020</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Fuel Prices</t>
+          <t>Fuel Prices for gas and nuclear, Thermal PP column Local Fuel Costs Adopted for coal</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2024 real -&gt; 2050</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr"/>
+          <t>2024-2060 real 2021 USD, read on 2026-2050</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 6 done. THE TABLE WAS THE MOST DAMAGING DEFECT LEFT IN THE MODEL: it ran 2017 to 2030 against a horizon that runs 2026 to 2050, and main.gms:737 reads pFuelCost = pFuelPrice * pHeatRate with no interpolation and no default, so every fuel in every zone was FREE from 2031 on. Half the horizon was arbitrating thermal against renewable at zero fuel cost. Rebuilt by build_costs.py from mappings/fuel_prices.csv, which carries the 25 country and fuel pairs one by one. 8 rest on DeCA and 17 keep the 2020 series held flat: DeCA prices neither heavy fuel oil nor LNG, Pakistan and Afghanistan are outside its perimeter, and its coal is unusable in two of the five countries, see below. GAS AND NUCLEAR COME FROM THE Fuel Prices SHEET. Gas is already in $/MMBtu and is taken as it stands; the stated method is the actual 2024 price of each country converging linearly to the netback value of the Chinese gas price by 2030, which is a documented economic price and the right thing for a planning model. Nuclear is stated at 2.92 $/MWh of electricity and divided by the heat rate the model itself carries for its uranium units, 8.322 MMBtu/MWh, giving 0.3509 $/MMBtu against 0.3842 in the 2020 model, a 9 per cent gap that is a good check on the method. Where the transport adder of DeCA is a national constant it is added here: Uzbek gas 1.866 over 22 units, Turkmen gas 0.140 over 17. COAL DOES NOT COME FROM THAT SHEET, and this is the judgement of the phase. The sheet is headed International Prices, its coal row is the same 33.53 $/mt in all five countries and in every year from 2024 to 2060, and the convergence method printed underneath is written for gas alone. It is the seaborne benchmark. Nobody burns Angren lignite or Ekibastuz coal at the seaborne price, and taking it would have tripled Kazakh coal and quadrupled Uzbek coal on no evidence at all. Coal is read instead from the Local Fuel Costs Adopted column of Thermal PP, the price DeCA fed its own plants. THAT COLUMN IS FILLED FOR TWO BOOKS ONLY, and not in the same unit in both: in UZ it is $/MWh of electricity, the product of the value and the plant efficiency being constant at 9.0 to 9.4 across the 22 gas units, while in KG it is $/MMBtu per plant. Reconverted and capacity weighted it gives 3.438 $/MMBtu for Angren, against 1.202 in the 2020 model, and 2.684 for Kyrgyzstan, against 4.280. Both are delivered prices per plant, so no transport is added on top and NO CALORIFIC VALUE IS ASSUMED ANYWHERE, which removes what was the weakest link of an earlier draft of this table. KAZAKH AND TAJIK COAL THEREFORE HAVE NO DeCA PRICE AT ALL: those books leave the local column empty. They keep the 2020 model held flat, which also preserves the 1.467 delivered ratio between northern and southern Kazakhstan. KAZAKH GAS TRANSPORT IS NOT HERE EITHER. It is the one genuinely regional fuel cost in the region, 0 on the Atyrau gas fields to 13.3 at the end of the pipeline in Akmola, a spread wider than the commodity itself. A national mean would be meaningless when the model carries two Kazakh gas plants sitting at opposite ends of that range, so each takes its own through its VOM. See pGenDataInput. WHAT IT DOES TO THE MERIT ORDER, short-run marginal cost in 2026, before and after: Ekibastuz 19.7 to 19.5 $/MWh, Aksu 19.7 to 18.4, Astana-2 22.5 to 26.9, Angren 24.0 to 47.9, Novo-Angren 24.3 to 46.3, Bishkek 60.9 to 43.0, Syrdarya 68.0 to 73.1, Mary 57.3 to 40.0, Zhambyl 67.2 to 50.0. Uzbek coal doubling is the one number to challenge, and it is DeCA saying the 2020 model priced it too low.</t>
+        </is>
+      </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>The cleanest block of the lot: direct, no arbitrage, no time dependency. Real 2025 USD.</t>
+          <t>1. KAZAKH AND TAJIK COAL ARE THE FIRST DATA REQUEST of this phase: neither book states a local price, so both still rest on a 2020 figure held flat to 2050. The Kazakh one matters most, it prices roughly 10 GW of the fleet. 2. Coal carries no trajectory anywhere: the two DeCA local prices are single 2020 figures and the other two are held flat. Nothing in this table makes coal dearer or cheaper over twenty-five years. 3. Heavy fuel oil, LNG, and everything Pakistani and Afghan rest on the 2020 model held flat. Pakistan needs the NTDC IGCEP fuel assumptions.</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1945,22 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>FILL</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1946,14 +1970,22 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>PP Candidates</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr"/>
+          <t>CAPEX, columns 2h / 4h / 6h / 8h BESS</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>2023-2060, read at 2026</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 5 done. The table was empty, in a model that runs to 2050. It now carries one four-hour battery candidate per Central Asian zone, eight of them, open from 2028. The cost is read, not assumed. DeCA prices a battery at 2, 4, 6 and 8 hours and those four prices are exactly linear in duration in every year from 2023 to 2060, so the slope is the cost of an hour of energy and the intercept is the cost of the power: 247,638 $/MW and 202.3 $/kWh in 2026, falling to 198,754 $/MW and 118.2 $/kWh in 2050. build_fleet.py re-checks that linearity and refuses to write anything if a later version of the book breaks it. Four hours is a choice, and it is the one that makes EPM exact: EPM applies a single CAPEX multiplier to both the power and the energy part of a battery, and those two decline at different rates in DeCA. At a fixed duration the multiplier is exact on the total, which is what is being bought. The perimeter is the five DeCA countries, mappings/country_book.csv. Pakistan and Afghanistan keep no storage, as in the 2020 model. DeCA gives no round-trip efficiency and no operating life for storage: 0.9 and 20 years are the EPM reference values, data_test.</t>
+        </is>
+      </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED BY THE TIME RESOLUTION: without intra-day chronology, storage has no value in the model. It is therefore settled at the same time as pHours, at the end.</t>
+          <t>Storage only earns its keep once the model has intra-day chronology. The candidate is in place so that phase 8 has something to switch on, but nothing will be built until pHours carries real hours. Pumped storage is a separate question: DeCA carries Hodjikent PSH-2 in Uzbekistan, which sits in pGenDataInput as a hydro candidate rather than here.</t>
         </is>
       </c>
     </row>
@@ -2095,21 +2127,17 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>168</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>structure adapted, data to do</t>
+        <v>210</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>done</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>REVISE</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -2119,7 +2147,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, tso_request</t>
+          <t>deca_v51, casa_2020, tso_request</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -2129,17 +2157,17 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>2024-2031</t>
+          <t>2024-2060</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>The 42 Q5 rows were identical to the Q1 ones: removed without loss, 210 -&gt; 168.</t>
+          <t>Rebuilt from data_build/mappings/corridors.csv, which carries the 42 directed corridors with their anchor years and, for each, the source it rests on. Three corrections against the 2020 model. Turkmenistan to Afghanistan: the two directions were swapped, the 80 MW leg could not carry the 2100 GWh/y that pMaxAnnualTransfer requires. CASA-1000 to Pakistan: 1000 MW and not 1300, the 1300 being the rating of the whole DC link including the Afghan tap. Tajikistan to Afghanistan: 188 MW all year plus a May-September window at 638 MW, which is the first seasonal corridor of the model. The Q5 rows dropped by an earlier build are restored: Q5 is the peak season of pHours, and without them no zone could import at the peak.</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>PHASE 3. NTCs to be revised (source deca_v51 + TSO request) and year columns to be extended to 2050, they stop at 2030. Known anomaly: CASA-1000 is open at 1300 MW in all seasons from 2022, hence 10 TWh/yr in the 2020 run.</t>
+          <t>DONE for the corridors that have a source. Two gaps left, both needing an external answer: the intra-CAPS NTCs rest on the 2020 model alone (TSO request pending), and the Surkhan to Puli-Khumri 500 kV between Uzbekistan and Afghanistan is not in any source we hold, so UZB to NEPS_UZB stays at 400 MW.</t>
         </is>
       </c>
     </row>
@@ -2167,19 +2195,15 @@
       <c r="E30" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>inherited, fit for purpose</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>REVISE</t>
+          <t>KEEP</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -2194,10 +2218,14 @@
       </c>
       <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Q3 is not a calendar quarter. In pHours it is worth 3652 h, that is 152 days, which is the May-September export window of CASA-1000 to within one day. The five flags are therefore already on the right season and must not be moved.</t>
+        </is>
+      </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>PHASE 3. THE MEANING OF Q3 HAS CHANGED: in the 2020 model Q3 was worth 3652 h, that is May-September, exactly the CASA-1000 window. In calendar quarters, Q3 = July-September. The 5 flags must move to Q2 + Q3.</t>
+          <t>DONE. Constraint carried to phase 8: the representative-day pipeline has to reproduce this season structure, Q3 = May-September, or every contracted flow of the model moves with it.</t>
         </is>
       </c>
     </row>
@@ -2225,19 +2253,15 @@
       <c r="E31" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>REVISE</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -2247,19 +2271,23 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>casa1000_ppa</t>
+          <t>casa1000_ppa, casa_2020, assumed</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>2022-2030</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr"/>
+          <t>2022-2030 held to 2050</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Re-based on the model years. The volumes stopped at 2030, so the contract simply disappeared from 2031 on, a year GAMS reads as zero. The 2030 value is now held to 2050, which ASSUMES the contract is renewed. The three flows total 4343 GWh in Q3, against a 4434 GWh plateau in the PPA note: consistent.</t>
+        </is>
+      </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>PHASE 3. Split the volumes between Q2 and Q3 (see pContractedTradeFlag), and extend the year columns beyond 2030. To be checked against the PPA: year 1 = 2028, plateau 4434 GWh, minimum take 29794 GWh over 15 years.</t>
+          <t>Needs the PPA file, still to be located, to replace the assumption by the real schedule: year 1 is said to be 2028 and the term 15 years, so the flows should start in 2028 and stop in 2042, where the model holds them flat throughout.</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2326,7 @@
           <t>REVISE</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2414,7 +2442,7 @@
           <t>REVISE</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2472,7 +2500,7 @@
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2576,7 +2604,7 @@
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2626,7 +2654,7 @@
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2680,7 +2708,7 @@
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2720,14 +2748,14 @@
         <v>0</v>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>done</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -2735,15 +2763,19 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>casa_2020</t>
+        </is>
+      </c>
       <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr"/>
-      <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>Header inherited from an AFRICAN template (Angola, Burundi, Cameroon...). To be emptied.</t>
-        </is>
-      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>The header carried the countries of an African study (Angola, Burundi, Cameroon, CAR, Chad, Congo, DRC, Equatorial Guinea, Gabon, Rwanda, Sao Tome). Replaced by the seven countries of the perimeter. The file holds no row: the parameter is empty either way, but the index was wrong.</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2800,7 +2832,7 @@
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2819,7 +2851,7 @@
       <c r="M42" s="4" t="inlineStr"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>DATA PRESENT BUT INACTIVE (fEnableCarbonPrice = 0). Turning it on is the cheapest lever to correct the 17 GW of new coal in Kazakhstan.</t>
+          <t>DATA PRESENT BUT INACTIVE (fEnableCarbonPrice = 0). Turning it on is the cheapest lever to correct the 17 GW of new coal in Kazakhstan. PHASE 6.4 LEFT IT ALONE, ON PURPOSE, but it carries the same 2030 cliff as the fuel limits did: the series runs 2017 to 2030 and main.gms reads it year by year, so switching the flag on today would price carbon at 50 $/t to 2030 and at nothing whatever afterwards, which is worse than not pricing it at all. It has to be extended to 2050 in the same movement as it is enabled, and that is phase 9 with the scenarios, alongside the emission caps above and the CCS candidates DeCA prices and this model does not carry.</t>
         </is>
       </c>
     </row>
@@ -2841,13 +2873,17 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>CO2 cap by country</t>
+          <t>CO2 cap by country, tons</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
           <t>inherited 2020, to process</t>
@@ -2858,7 +2894,7 @@
           <t>FILL</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2878,10 +2914,14 @@
           <t>2030-2060</t>
         </is>
       </c>
-      <c r="M43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 6.4 PREPARED BUT DELIBERATELY NOT WIRED IN. The file stays empty and fApplyCountryCo2Constraint stays 0. build_constraints.py writes the DeCA path out to extracted/pEmissionsCountry_netzero.csv, on the horizon and in the tons EPM counts in, so that phase 9 can switch it on in one line once three things are settled. The path itself: the first Net Zero row of each Emissions sheet, five books of the seven countries, held flat before the first year it states and interpolated between the years it does. Kazakhstan 93.1 MtCO2-eq in 2030 to 4.66 in 2050, Uzbekistan 63.3 to 3.16, Turkmenistan 16.3 to 0.82, Tajikistan 4.17 to 0.21, Kyrgyzstan 1.36 to 0.068. Each is built by DeCA off the country NDC and then run down to a residual by 2060, and each book states its own arithmetic: Kazakhstan takes a third of the 1990 heat and power sector, Turkmenistan 0.85 of energy times 0.36 of electricity and heat, and so on. THE UZ BOOK STATES THE PATH TWICE, once economy-wide and once for electricity and heat at three tenths of it, and it is the sector row that is read. WHY IT IS NOT A BASELINE. It is a scenario, DeCA says so, and dropping it into the reference case would silently make the reference case a net zero case.</t>
+        </is>
+      </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>DeCA gives the Net Zero trajectories, not the factors by fuel.</t>
+          <t>PHASE 9, THE THREE THINGS TO SETTLE BEFORE THIS BECOMES A CONSTRAINT. 1. SCOPE. The path covers ELECTRICITY AND HEAT and EPM carries no heat. In Kazakhstan heat was 87.1 of the 112.4 MtCO2-eq the sector emitted in 1990, so a heat and power cap read onto a power only model is loose by a factor nobody has measured, and the Kazakh CHPs sit on both sides of that line. 2. COVERAGE. base.gms:1253 writes eEmissionsCountry for EVERY country at once when the flag is on, and a country absent from the table gets a cap of zero, softened only by the penalised backstop. Pakistan and Afghanistan have no NDC path in these books, so switching the flag on with this file as it stands would order them to emit nothing. Either they get a path of their own or the constraint has to be written for a subset. 3. THE FIRST FOUR YEARS. Nothing is stated before 2030, so the path is held flat backwards to 2026, which binds four years earlier than any NDC intended. Harmless while the cap is loose, not harmless if it is tight.</t>
         </is>
       </c>
     </row>
@@ -2903,16 +2943,20 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>system-wide CO2 cap</t>
+          <t>system-wide CO2 cap, tons</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>inherited, fit for purpose</t>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2929,7 +2973,11 @@
       <c r="K44" s="4" t="inlineStr"/>
       <c r="L44" s="4" t="inlineStr"/>
       <c r="M44" s="4" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr"/>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 9. Empty, and fApplySystemCo2Constraint is 0. A regional cap over seven countries five of which have separate national NDCs is a different scenario from the national caps in pEmissionsCountry, not a complement to them: it would let Kazakh coal buy its way out on a Kyrgyz margin. To be chosen against the country caps rather than filled in beside them.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2949,47 +2997,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>supply limit by country</t>
+          <t>supply limit by country and fuel, million MMBtu</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>REVISE</t>
-        </is>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>deca_v51</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>UZ &gt; Fuel Availability</t>
-        </is>
-      </c>
+          <t>casa_2020</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr"/>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="M45" s="4" t="inlineStr"/>
+          <t>2020 series, carried to 2050</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 6.4 done, and it is the same defect as the fuel prices. The table ran 2017 to 2030 against a horizon that runs 2026 to 2050, and base.gms:817 writes the constraint only where the value is strictly positive, so PAST 2030 EVERY LIMIT SIMPLY VANISHED while fApplyFuelConstraint stayed on. Nothing crashed, which is what made it dangerous. Rebuilt by build_constraints.py from mappings/fuel_limits.csv, which carries the nine rows of the two tables one by one. All five country rows are the 2020 series held flat past its last year: DeCA states a national fuel availability nowhere, Pakistan and Afghanistan are outside its perimeter, and an assumption of no further change is at least visible where a silent zero was not. THE UZBEK COAL LINE IS THE ONE PLACE DeCA COULD HAVE SPOKEN AND IS NOT USED. Its Fuel Availability sheet states coal for power in M m3, a VOLUME, and turning that into MMBtu would need a density and a calorific value the book never states, which is exactly the assumption phase 6 spent its time removing from the coal prices. The 2020 series is held flat instead, and the gap is written down rather than papered over with two invented conversion factors.</t>
+        </is>
+      </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Only UZ has a dedicated sheet.</t>
+          <t>PHASE 6.4, WHAT RESTS ON 2020. Pakistani gas and LNG both do, and both want the NTDC IGCEP: indigenous Pakistani gas is on a declining path that a flat line does not represent, and the LNG row is a regasification terminal limit rather than a resource one, so holding it flat quietly forbids any new terminal. Kyrgyz and Tajik gas are import contracts of the 2020 model, neither of them binding. Uzbek coal is discussed in the note.</t>
         </is>
       </c>
     </row>
@@ -3011,31 +3063,35 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>limit by zone (KAZ_N Gas 0.1)</t>
+          <t>supply limit by zone and fuel, million MMBtu</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>REVISE</t>
-        </is>
-      </c>
-      <c r="I46" s="8" t="inlineStr">
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>deca_v51</t>
+          <t>deca_v51, casa_2020</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -3045,13 +3101,17 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="M46" s="4" t="inlineStr"/>
+          <t>2022-2030 stated, held to 2050</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 6.4 done. Same repair as the country table, carried to 2050 by build_constraints.py, and one of the four rows genuinely moves. UZBEK GAS FOR POWER FALLS BY A THIRD. The UZ Fuel Availability sheet is the only one of the five books to exist, and it states 12.1 bcm available for electricity production, sourced to the Concept Note for ensuring electricity supply in Uzbekistan in 2020-2030, with the book saying in as many words that it holds that limit to 2060. At 36 million MMBtu per bcm, which is the BP conversion and the only one this step makes, that is 435.6 against the 667.6 the 2020 model allowed, and the sheet shows why: Uzbek gas production does rise to 2030, 51.7 to 66.1 bcm, but domestic demand rises faster and exports have already been cut to zero, so power gets less of a bigger pie. The 2026 to 2029 values interpolate between the 12.7 bcm stated for 2025 and the 12.1 of 2030 rather than jumping. THIS WILL STRUCTURE THE UZBEK EXPANSION, roughly 36 TWh at a modern combined cycle where the fleet needs more. The three other zone rows are the 2020 series held flat, Pakistani coal being outside the DeCA perimeter and Kazakh gas being the decision below.</t>
+        </is>
+      </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>The gas constraint on KAZ_N is structuring for Kazakh coal: to be checked as a priority.</t>
+          <t>PHASE 6.4, THE DECISION OF THE PHASE, and it is left to the team rather than taken here. KAZ_N Gas = 0.1 million MMBtu is not a limit, it is a statement that NORTHERN KAZAKHSTAN HAS NO GAS AT ALL, and it is what forces the coal expansion there: no gas candidate can run whatever the carbon price, so the only thermal answer to Kazakh load growth is more coal. The assumption was defensible in 2020. It is doubtful in 2026, the Saryarka pipeline having reached Nur-Sultan in 2019 and Kokshetau since, and DeCA'S OWN KZ TRANSPORT TABLE QUOTES A DELIVERED GAS PRICE IN AKMOLA, 13.3 $/MMBtu on top of the commodity, which is a strange thing to state for a region where no gas can arrive. Raising it needs the Saryarka throughput and the volumes already committed to heat and industry, and it is the single most consequential unresolved number left in this model. Kept as it stands until then, so that it is a decision and not a drift.</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3158,11 @@
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr"/>
       <c r="L47" s="4" t="inlineStr"/>
-      <c r="M47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 6.4 checked, still empty and still out of scope. Its header runs z, tech, f, 2025, 2040 and it would cap the generation of a fuel in a zone. Nothing in DeCA is stated in that form, and the two things it would be used for are already carried elsewhere: the physical availability of a fuel by pMaxFuellimitZone, and any policy share by the emission caps.</t>
+        </is>
+      </c>
       <c r="N47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3139,13 +3203,17 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>reserve margin, 15 % everywhere</t>
+          <t>reserve margin, 15 % on each of the 16 zones</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
           <t>inherited 2020, to process</t>
@@ -3153,17 +3221,17 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>REVISE</t>
-        </is>
-      </c>
-      <c r="I49" s="8" t="inlineStr">
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>assumed</t>
+          <t>assumed, team</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr"/>
@@ -3172,10 +3240,14 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="M49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 7 examined, and the 0.15 does not move. What moved is what it is applied to, and the change is large enough that it has to be written down. THE 2020 MODEL VALUED FIRM CAPACITY AT NAMEPLATE. base.gms:1005 counts the firm capacity of a zone at the availability of each unit IN THE FLAGGED SEASON alone, and the 2020 model flagged an artificial peak season in which 267 units out of 403 carried 1.0, and 313 were worth more than in Q1. That season was an artefact of the old time slicing and phase 1 removed it, so the flag now points at Q1, where those same units carry their true 0.85. A coal CHP is no longer worth its nameplate at the winter peak. WHAT IT COSTS, measured by data_build/check_reserve.py against the DeCA peaks: in 2026 the region has to find some 11 GW MORE firm capacity than the same model would have asked for under the 2020 convention. Kazakhstan 2.2 GW, Pakistan 4.8, Uzbekistan 2.1, Kyrgyzstan 0.6, Turkmenistan 0.9, Tajikistan 0.5. THE NEW CONVENTION IS THE RIGHT ONE and that is why it is kept: a planning margin belongs on top of DERATED capacity, and a 15 per cent margin over nameplate is not a margin at all once forced outages are counted, it is roughly zero. The model is now tighter than the 2020 reference and will build more firm plant. That is a real change in the results and not an accounting detail. The margin is uniform across sixteen zones with no source behind it. DeCA states none: the five books carry no reserve margin, no loss of load expectation and no capacity credit of any kind.</t>
+        </is>
+      </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>NO SOURCE. Uniform 15 % inherited. This parameter explains most of the cost gap with the legacy run (violation penalty 6256 M$ -&gt; 0).</t>
+          <t>PHASE 7, WHAT IS LEFT TO DECIDE, and it is a team call rather than a data gap. 1. THE 0.15 ITSELF has no source. It is defensible as a placeholder, it is not defensible in a published result, and the same number is applied to a Pakistani zone with a thermal fleet and a Kyrgyz zone that is nearly all hydro. The national regulators are the source to ask for. 2. THE 0.85 UNDER IT is inherited too, and the two multiply: the requirement is really 1.15 / 0.85 = 1.35 times the peak in nameplate terms. Whether the thermal fleet of the region is available 85 or 90 per cent of the time is worth one question to the TTLs, because it moves the answer by 4 GW in 2026. 3. SOLAR IS VALUED AT ITS BEST HOUR OF Q1 (main.gms:700), which for a system whose winter peak is in the evening is generous. Nothing depends on it yet, the VRE candidates being small, but it should be reviewed before the capacity mix is published.</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3305,7 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>DONE (phase 1): Q5 -&gt; Q1. This flag serves one purpose only (base.gms:1005): choosing the season whose NTC is used for firm capacity sharing between zones. It does NOT drive the sizing of the reserve, which goes through a smax over all blocks. Q1 = winter quarter, correct.</t>
+          <t>DONE (phase 1): Q5 -&gt; Q1. This flag serves one purpose only (base.gms:1005): choosing the season whose NTC is used for firm capacity sharing between zones. It does NOT drive the sizing of the reserve, which goes through a smax over all blocks. Q1 = winter quarter, correct. DONE (phase 7): the check this todo owed is made, and the answer is that the credit does fall from 1.0 to 0.85 and that it is kept there. Some 11 GW more firm capacity is asked of the region in 2026 as a result. The reasoning is in pPlanningReserveMarginZone, where it belongs; Q1 stays flagged.</t>
         </is>
       </c>
     </row>
@@ -3280,12 +3352,12 @@
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr"/>
       <c r="L51" s="4" t="inlineStr"/>
-      <c r="M51" s="4" t="inlineStr"/>
-      <c r="N51" s="4" t="inlineStr">
-        <is>
-          <t>Redundant with the zonal version.</t>
-        </is>
-      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 7 checked, deliberately left empty. It is not redundant, it is the ALTERNATIVE: base.gms:1017 says a study that switches the zonal reserve on will normally leave this one empty, otherwise both apply at once and the zones are held to their own margin and to their country's. Empty here is what keeps the country equation from generating any row, since it is guarded by the margin itself and not by the flag, which is on. Pooling reserves by country rather than by zone would be a defensible variant for Kazakhstan and Kyrgyzstan, whose two zones are strongly connected; it would relax the model. It is a scenario, not a correction.</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -3312,14 +3384,14 @@
         <v>0</v>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>inherited, fit for purpose</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>DECIDE</t>
+          <t>KEEP</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -3329,17 +3401,21 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>assumed</t>
-        </is>
-      </c>
-      <c r="K52" s="4" t="inlineStr"/>
+          <t>deca_v51, casa_2020</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>Thermal PP, column Operating Reserve</t>
+        </is>
+      </c>
       <c r="L52" s="4" t="inlineStr"/>
-      <c r="M52" s="4" t="inlineStr"/>
-      <c r="N52" s="4" t="inlineStr">
-        <is>
-          <t>Disabled in pSettings, and no source.</t>
-        </is>
-      </c>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 7 checked and left empty and off, and this is now a sourced decision rather than an omission. Every one of the five books carries an Operating Reserve column on its Thermal PP sheet, and IT IS ZERO ON ALL 112 UNITS THAT FILL IT, the UZ book leaving it blank altogether: the reference study holds no spinning reserve on its thermal fleet either. fApplyCountrySpinReserveConstraint and fApplySystemSpinReserveConstraint stay at 0. Turning it on is expensive for what it buys: the comment at base.gms:950 says the country equation multiplies solving time by three, and the model would need a ResLimShare per unit that nothing in the sources supports. The right place for an operating reserve in this study is the hourly dispatch run of phase 8, not the expansion.</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -3373,7 +3449,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>DECIDE</t>
+          <t>KEEP</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -3383,12 +3459,16 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>assumed</t>
+          <t>deca_v51, casa_2020</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr"/>
       <c r="L53" s="4" t="inlineStr"/>
-      <c r="M53" s="4" t="inlineStr"/>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 7, same decision and same reason as pSpinningReserveReqCountry: empty and off, DeCA holding no operating reserve either. A regional spinning reserve over seven countries that do not share a control area would in any case be a strong assumption about market integration, which is the subject of the study rather than an input to it.</t>
+        </is>
+      </c>
       <c r="N53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
@@ -3519,7 +3599,7 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>8 done | 6 partial | 27 to do | 7 out of scope</t>
+          <t>11 done | 13 partial | 17 to do | 7 out of scope</t>
         </is>
       </c>
     </row>
@@ -3534,16 +3614,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3564,20 +3645,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Access</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Covers</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Where to find it</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>What it contains</t>
         </is>
@@ -3601,20 +3687,25 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>EPM/epm/input/data_casa_2020</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Only source for Afghanistan and Pakistan: that is why the build starts from a copy rather than from a blank slate. Port validated (demand, generation, unserved energy and corridors identical to the legacy run). The 2020 assumptions are stale and the load profile is of 2013 vintage. Covers 16 zones and 7 countries over 2017-2030.</t>
         </is>
@@ -3638,20 +3729,25 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>KAZ, KGZ, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>data_collection/Mercados/</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>One workbook per country. KG 20 sheets (8760 h demand North/South, hydro cascade). KZ 18 sheets, 8760 h demand PER OBLAST (14) plus North/South/West aggregates, Demand Evolution in two scenarios Reference and Net Zero, sheet Exchanges with non CA countries; intra-Central-Asian exchanges are absent. TJ 18 sheets, 8760 h demand North/South (2021), sheet Exchanges: CASA-1000 DC link 300 MW from 2026 with a May-September export window, TJ to AF Sangtuda-Kunduz 300 MW, existing PPA 188 MW; no detail on Rogun. TM 13 sheets, no hydro, and DEGRADED DEMAND: average day per month only (~288 points), with no regional breakdown. UZ 19 sheets, 8760 h demand over 5 zones, sheet Fuel Availability unique among the five books.</t>
         </is>
@@ -3675,20 +3771,25 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>UZB</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>data_collection/Mercados/20260709_UZ_CC_AssumptionBook_WB_MAI.xlsb</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Sixteen months later than the V5.1 books, hence takes precedence over them for UZB. Format .xlsb, read through pyxlsb.</t>
         </is>
@@ -3712,20 +3813,25 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>KAZ, KGZ, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Context/opening_emails/</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>25 sheets (5 themes x 5 countries), ALREADY PRE-FILLED with the cleaned 2020 data, zones as free-text labels. This is the official validation channel through the country TTLs. Pre-filled is not validated. Covers NEITHER Afghanistan NOR Pakistan.</t>
         </is>
@@ -3749,16 +3855,21 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>KAZ, KGZ, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Takes precedence over DeCA and over the 2020 model where available. Fleet additions dated 2023+ inherited from 2020 are PROJECTS, not facts: TTL review is mandatory before keeping them.</t>
         </is>
@@ -3782,20 +3893,25 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>client_confidential</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>AFG, KGZ, PAK, TAJ</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>(to be located)</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Contractual quantities of the 4 flows, to be attached to pContractedTradeEnergy.</t>
         </is>
@@ -3819,20 +3935,25 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>planning_sharefolder/casa_planning_sharefolder/CASA/1. Model/</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Non-regression reference for the port. A warning signal, not an acceptance criterion.</t>
         </is>
@@ -3856,20 +3977,25 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>PAK</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>planning_sharefolder/pakistan_planning_sharefolder/</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>NTDC, Lahmeyer, SNC Lavalin master plan. MAJOR GAP: 8 years old, IGCEP missing, while Pakistan weighs 155 TWh, that is 38 % of the demand of the model.</t>
         </is>
@@ -3893,20 +4019,25 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>AFG</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>planning_sharefolder/afghanistan_planning_sharefolder/</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>AFGDISPATCH.gms and .xlsx. MAJOR GAP: earlier than 2021, no reliable alternative source outside Global Energy Monitor.</t>
         </is>
@@ -3930,16 +4061,21 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>KAZ, KGZ, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3959,20 +4095,25 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
           <t>open_source</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>renewables.ninja</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Hourly solar and wind profiles by coordinates. Already used by pre-analysis/pipelines/vre_pipeline.py.</t>
         </is>
@@ -3981,45 +4122,54 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>tso_request</t>
+          <t>epa_ghg_factors</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Direct request to the transmission system operators</t>
+          <t>US EPA greenhouse gas emission factors for stationary combustion</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>internal_wb</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
+          <t>open_source</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
           <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>NTCs and commissioning schedules of the corridors. Not started to date.</t>
+          <t>epa.gov, Emission Factors for Greenhouse Gas Inventories</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Combustion chemistry rather than country data, hence covers everything: natural gas 53.06 kg CO2 per MMBtu, sub-bituminous coal 97.17, residual fuel oil No. 6 75.10. These are the values pFuelCarbonContent has always carried; naming the source only makes visible what was already there.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>tso_request</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Output of the pre-analysis pipeline (representative days, VRE profiles)</t>
+          <t>Direct request to the transmission system operators</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4029,30 +4179,35 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>EPM/pre-analysis/</t>
-        </is>
-      </c>
       <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>NTCs and commissioning schedules of the corridors. Not started to date.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Modelling team decision</t>
+          <t>Output of the pre-analysis pipeline (representative days, VRE profiles)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4062,26 +4217,35 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>EPM/pre-analysis/</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>assumed</t>
+          <t>team</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>NO SOURCE - assumption made</t>
+          <t>Modelling team decision</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4091,53 +4255,97 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>placeholder</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
+          <t>internal_wb</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
           <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>To be made explicit in the methodology note: every value carried here is to be justified or replaced.</t>
-        </is>
-      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>NO SOURCE - assumption made</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>To be made explicit in the methodology note: every value carried here is to be justified or replaced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>team_emails</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>CASA team emails</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Context/opening_emails/</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Mandated validation channel: Mercados, then template, then TTL review, then EPM. INTERNAL exercise, not to be shared externally (Kabir Malik, 5 August 2026).</t>
         </is>
@@ -4373,7 +4581,7 @@
           <t>kegoc.kz, stat.gov.kz</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>TESTED - PARTIAL</t>
         </is>
@@ -4565,7 +4773,7 @@
           <t>stat.uz, data.egov.uz</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>TESTED - PARTIAL</t>
         </is>
@@ -4789,7 +4997,7 @@
           <t>energydata.info, gridfinder.rdrn.me</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>TESTED - PARTIAL</t>
         </is>
@@ -4821,7 +5029,7 @@
           <t>iea.org/countries, comtradeplus.un.org</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>TESTED - PARTIAL</t>
         </is>

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>casa_2020, pipeline</t>
+          <t>casa_2020, team</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>deca_v51, team</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>team</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>team</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr"/>
@@ -3614,7 +3614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>placeholder</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -4075,7 +4075,11 @@
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Same consultant and same 2025 study as the AssumptionBooks, a DIFFERENT deliverable: the report and the PLEXOS database behind it. We hold the five Excel books, not the model. Graded a placeholder for that reason.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -4202,12 +4206,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>team</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Output of the pre-analysis pipeline (representative days, VRE profiles)</t>
+          <t>Modelling team decision</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4217,7 +4221,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>placeholder</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -4230,22 +4234,18 @@
           <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>EPM/pre-analysis/</t>
-        </is>
-      </c>
+      <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>assumed</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Modelling team decision</t>
+          <t>NO SOURCE - assumption made</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>internal_wb</t>
+          <t>assumption</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -4269,32 +4269,36 @@
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>To be made explicit in the methodology note: every value carried here is to be justified or replaced.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>assumed</t>
+          <t>team_emails</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>NO SOURCE - assumption made</t>
+          <t>CASA team emails</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>internal_wb</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -4302,50 +4306,12 @@
           <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Context/opening_emails/</t>
+        </is>
+      </c>
       <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>To be made explicit in the methodology note: every value carried here is to be justified or replaced.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>team_emails</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>CASA team emails</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>internal_wb</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Context/opening_emails/</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Mandated validation channel: Mercados, then template, then TTL review, then EPM. INTERNAL exercise, not to be shared externally (Kabir Malik, 5 August 2026).</t>
         </is>

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -4245,7 +4245,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>NO SOURCE - assumption made</t>
+          <t>No source - assumption made</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -932,12 +932,12 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>q = 4 quarters, the 5th peak season is removed. It was not a structure but a patch: the reserve constraint takes a smax over all blocks (base.gms:991) and requires no dedicated season. Q5 only served to give that smax a block short enough to see the true peak, for want of representative days (d=1 in the 2020 model). THE FOUR QUARTERS ARE NOT CALENDAR QUARTERS, and the months behind them are now written down in data_build/mappings/seasons_months.csv: Q1 December to February, Q2 March and April, Q3 May to September, Q4 October and November. That split is read off the 2020 durations, Q1 and Q5 together 2180 h that is 90.8 days, Q2 1464 h exactly 61 days, Q3 3652 h that is 152.2 days, Q4 1464 h exactly 61 days, and it lands on 8760 h to the hour. Q3 is the irrigation release window and the window of the CASA-1000 contract, 1 May to 30 September. Every season-indexed resource is built against that mapping. PHASE 8 REBUILT IT, and this is the file that defines the sets q, d and t for the whole model: main.gms:214 reads pHours(q&lt;,d&lt;,t&lt;), so every other hourly resource follows whatever shape is written here. It is now four seasons by three representative days by twenty four chronological hours, the canonical EPM shape that epm/input/data_test also carries, and each cell holds THE NUMBER OF DAYS the representative day stands for, repeated over its 24 hours, summing to 8760. THE PEAK REPRESENTATIVE DAY REPLACES THE OLD PEAK SEASON. In each season, d1 is the calendar day carrying the highest system load of that season and weighs one day; d2 and d3 are the mean days of the two halves of the rest of the season, split by daily energy. Energy and peak are therefore both exact by construction, which is what base.gms needs when it takes an smax over (q,d,t) for the reserve. The four peak days chosen are 12 December, 18 March, 28 June and 29 November. The season durations are unchanged, 90 / 61 / 153 / 61 days, so pAvailability and pTransferLimit did not have to be rebuilt.</t>
+          <t>q = 4 quarters, the 5th peak season is removed. It was not a structure but a patch: the reserve constraint takes a smax over all blocks (base.gms:991) and requires no dedicated season. Q5 only served to give that smax a block short enough to see the true peak, for want of representative days (d=1 in the 2020 model). THE FOUR QUARTERS ARE NOT CALENDAR QUARTERS, and the months behind them are now written down in data_build/mappings/seasons_months.csv: Q1 December to February, Q2 March and April, Q3 May to September, Q4 October and November. That split is read off the 2020 durations, Q1 and Q5 together 2180 h that is 90.8 days, Q2 1464 h exactly 61 days, Q3 3652 h that is 152.2 days, Q4 1464 h exactly 61 days, and it lands on 8760 h to the hour. Q3 is the irrigation release window and the window of the CASA-1000 contract, 1 May to 30 September. Every season-indexed resource is built against that mapping. PHASE 8 REBUILT IT, and this is the file that defines the sets q, d and t for the whole model: main.gms:214 reads pHours(q&lt;,d&lt;,t&lt;), so every other hourly resource follows whatever shape is written here. It is now four seasons by three representative days by twenty four chronological hours, the canonical EPM shape that epm/input/data_test also carries, and each cell holds THE NUMBER OF DAYS the representative day stands for, repeated over its 24 hours, summing to 8760. THE PEAK REPRESENTATIVE DAY REPLACES THE OLD PEAK SEASON. In each season d1 is a calendar day and weighs one day, which is what base.gms needs when it takes an smax over (q,d,t) for the reserve. The day chosen is the one that stresses the most zones at once, each zone counted against its own maximum rather than in megawatts, because a sum in megawatts is decided by Kazakhstan and Uzbekistan alone and the reserve of EPM is written per zone. The four days are 12 December, 1 March, 24 July and 21 November. THE OTHER TWO ARE REAL DAYS AS WELL, AND THEIR WEIGHTS ARE SOLVED, NOT COUNTED. The rest of the season is split in two by daily energy and each half is represented by its medoid, the real day closest to the average of that half. A medoid is the most typical day of its group and not the day carrying its average energy, so the two weights are then solved rather than taken from the sizes of the groups: two unknowns, two equations, the days of the season and the energy of the season, rounded to whole days at the end because input_verification.py compares the sum of this table to 8760 with no tolerance at all and refuses a block of zero hours. The weights that come out are 53 and 36 days for Q1, 28 and 32 for Q2, 79 and 73 for Q3, 29 and 31 for Q4. WHY NOT THE MEAN OF EACH GROUP, WHICH IS WHAT THIS STEP DID FIRST. Averaging seventy-six days flattens every trough that does not fall at the same hour twice, and the model reads that flattening as a baseload the system does not have. See pDemandProfile, which carries the measurement and the table of it. The season durations are unchanged, 90 / 61 / 153 / 61 days, so pAvailability and pTransferLimit did not have to be rebuilt.</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>THE NUMBER OF REPRESENTATIVE DAYS IS ONE ARGUMENT, --days, and three is a starting point rather than a result: the model went from 35 blocks in 2020 to 288 here, and if the solve turns out to be comfortable the count should go up, the days being grouped by demand alone today and therefore carrying no renewable variability. See pVREProfile, where the same limit bites harder.</t>
+          <t>THE NUMBER OF REPRESENTATIVE DAYS IS ONE ARGUMENT, --days, and three is a starting point rather than a result: the model went from 35 blocks in 2020 to 288 here, and if the solve turns out to be comfortable the count should go up, the days being grouped by demand alone today and therefore carrying no renewable variability. See pVREProfile, where the same limit bites harder. THE WEIGHT SOLVER IS EXACT FOR TWO GROUPS AND LEAST SQUARES BEYOND, so raising --days above three leaves a residual on the energy of the season. It is reported in the demand test and it is small; it would be removed by adding a third condition, the peak of each group, rather than by another solver. Q3 STILL COVERS FIVE MONTHS, May to September, because that is the CASA-1000 contract window. Splitting it in two, May-June against July-September, is the next thing worth doing to this file: the irrigation release and the summer cooling peak do not belong to the same shape.</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>PHASE 8 FILLED IT, AND IT IS WHAT MAKES THE MODEL RUNNABLE. Until this step both pDemandData and pDemandProfile were empty, every zone was dead and nothing could be solved. EIGHT ZONES READ THEIR OWN 8760 HOURS, the series extract_demand.py aggregated in phase 2: the two Kazakh zones, the two Kyrgyz, the two Tajik, Turkmenistan and Uzbekistan. Turkmenistan states one average day per month, 288 points, expanded over the days of each month; the zone is single and only its shape is used. EIGHT ZONES READ THE 2020 MODEL, the five Afghan ones and the three Pakistani ones, DeCA covering neither country. Their blocks are chronological hour of day groups and not a load duration curve, which the 2020 pVREProfile proves on its own: solar reads zero in the first and the last block and peaks in the middle one. The widths are read off the 2020 pHours, 6-5-3-3-4-3 hours, and each block is held flat over its own hours. Those zones have one shape per season and no day to day variation; their peak day is lifted by the ratio the old peak season carried over their seasonal days, which is the one piece of peak information it held. THE PEAK DAY OF EACH SEASON IS CHOSEN ON THE EIGHT SOURCED ZONES ALONE. Pakistan is a large share of the demand of the model and cannot vote on it, so the coincidence between Central Asia and Pakistan is inherited from the 2020 shapes rather than modelled. THE PROFILE IS NORMALISED TO A MAXIMUM OF EXACTLY 1, which is what generate_demand.gms expects: with fUseSimplifiedDemand at 1 it multiplies the profile by the peak of pDemandForecast, then adds a correction proportional to (max - profile) until the annual energy matches, a correction that is null at the peak. The peak of the profile is therefore the peak of the forecast, and the shape carries the rest. pDemandData stays empty on purpose: the year by year scaling is the work of the model, not of the pipeline. A CROSS CHECK THAT LARGELY PASSES. The load factor implied by this profile and the one implied by pDemandForecast were built from different sheets of the same books and agree to a thousandth on eleven zones of sixteen. Three do not, and the gap is DeCA disagreeing with itself: see the todo.</t>
+          <t>PHASE 8 FILLED IT, AND IT IS WHAT MAKES THE MODEL RUNNABLE. Until this step both pDemandData and pDemandProfile were empty, every zone was dead and nothing could be solved. EIGHT ZONES READ THEIR OWN 8760 HOURS, the series extract_demand.py aggregated in phase 2: the two Kazakh zones, the two Kyrgyz, the two Tajik, Turkmenistan and Uzbekistan. Turkmenistan states one average day per month, 288 points, expanded over the days of each month; the zone is single and only its shape is used. EIGHT ZONES READ THE 2020 MODEL, the five Afghan ones and the three Pakistani ones, DeCA covering neither country. Their blocks are chronological hour of day groups and not a load duration curve, which the 2020 pVREProfile proves on its own: solar reads zero in the first and the last block and peaks in the middle one. The widths are read off the 2020 pHours, 6-5-3-3-4-3 hours, and each block is held flat over its own hours. Those zones have one shape per season and no day to day variation; their peak day is lifted by the ratio the old peak season carried over their seasonal days, which is the one piece of peak information it held. THE PEAK DAY OF EACH SEASON IS CHOSEN ON THE EIGHT SOURCED ZONES ALONE. Pakistan is a large share of the demand of the model and cannot vote on it, so the coincidence between Central Asia and Pakistan is inherited from the 2020 shapes rather than modelled. THE PROFILE IS NORMALISED TO A MAXIMUM OF EXACTLY 1, which is what generate_demand.gms expects: with fUseSimplifiedDemand at 1 it multiplies the profile by the peak of pDemandForecast, then adds a correction proportional to (max - profile) until the annual energy matches, a correction that is null at the peak. The peak of the profile is therefore the peak of the forecast, and the shape carries the rest. pDemandData stays empty on purpose: the year by year scaling is the work of the model, not of the pipeline. THE OTHER DAYS ARE REAL DAYS TOO, WHICH THEY WERE NOT AT FIRST. Each group was first represented by the average of its days, and averaging seventy-six days flattens every trough that does not fall at the same hour twice. The model does not read that flattening as a flat shape, it reads it as a baseload the system does not have: the load factor of northern Tajikistan came out at 0.715 where its own series shows 0.600, and generate_demand.gms, which is handed both the peak and the energy of the zone and has to make the shape fit both, took the excess out of the nights and left TAJ_S at three per cent of its peak at four in the morning, under a smelter that never stops. Each group is now represented by its medoid, the real day closest to the average of the group, and the number of days it stands for is solved so that the energy of the season comes out right: two unknowns, the count of days and the energy, two equations. Nothing else changed, the structure is still 4 x 3 x 24. THE PEAK DAY IS CHOSEN ON THE STRESS OF EVERY ZONE, NOT ON THE MEGAWATTS. Summed in MW the peak day of a season is decided by Kazakhstan and Uzbekistan alone, and on the days that won southern Tajikistan sat at 78 per cent of its own maximum and Turkmenistan at 91. The planning reserve of EPM is written per zone, so those two would have been sized against a peak the model never sees. Each zone is divided by its own maximum before the sum, which gives every zone one vote. Energy is still counted in megawatts: that question is about size, this one is not. AND EACH ZONE IS LIFTED ONTO ITS OWN MAXIMUM. One day per season is shared by sixteen zones, so no single day is the day on which each of them separately peaks; northern Tajikistan still only reached 84 per cent of its own. The peak days are therefore multiplied, one factor per zone, until the highest hour of the profile is the highest hour of the series, 1.185 for TAJ_N and 1.05 or less for six of the eight. It is an assumption about coincidence, it is reported per zone as peak_uplift, and it is the same convention the 2020 model already used for Afghanistan and Pakistan, applied here to measured data instead of an inherited one. THE BUILD NOW TESTS ITSELF, which is the point of the table above. Twelve days are asked to stand for three hundred and sixty five and nothing in the model would ever have said how well they do it, so build_demand.py measures it against the series the days were drawn from and writes the answer beside them: the load factor the twelve days produce against the one the year really has, the annual energy, and the largest gap between the two load duration curves read at every five per cent of the year. Every sourced zone now lands within 0.02 of its true load factor, against 0.15 before, the annual energy is within 2.7 per cent, and the duration curve within 5.2 per cent of the peak. The measurement is rerun by the build, so the next change to this step cannot pass unnoticed.</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>THREE ZONES WHERE THE PROFILE AND THE FORECAST DISAGREE, profile load factor against forecast load factor: TAJ_N 0.715 against 0.618, TAJ_S 0.675 against 0.545, TUR 0.719 against 0.815. On the two Tajik zones the profile is flatter than the stated peak implies, which means the peak of pDemandForecast is high by some 14 per cent, and the Tajik peak is precisely the one phase 2 had to repair, the TJ book stating it in GW under a MW label. The simplified demand routine will absorb the gap by digging the valleys, so nothing breaks, but the Tajik reserve requirement is overstated until the peak is settled. ASK THE TJ AND TM SOURCES. No day to day variation for Afghanistan and Pakistan. The NTDC IGCEP would replace the Pakistani shape, which is the largest single gap left in the demand.</t>
+          <t>TURKMENISTAN IS THE ONE ZONE LEFT WHERE THE PROFILE AND THE FORECAST DISAGREE, 0.693 against 0.815, and the disagreement is inside DeCA rather than in this step: the TM book states one average day per month, 288 points and no day to day variation at all, so the shape cannot show the peak the Demand Evolution sheet implies. The simplified demand routine absorbs it by raising the nights of Turkmenistan some 40 per cent above what the profile says. ASK THE TM SOURCE for an hourly series, or fall back on Renewables.ninja for the shape. A NOTE ON WHAT IS NOW SETTLED, since it was written here as an open question and it was wrong: the Tajik profiles do not disagree with the Tajik forecast. Measured against the 8760 hour series, DeCA agrees with itself to within 0.02 of load factor on both zones. The gap of 0.15 recorded here earlier was made by this pipeline, by averaging days, and it is gone. No day to day variation for Afghanistan and Pakistan. The NTDC IGCEP would replace the Pakistani shape, which is the largest single gap left in the demand.</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>PHASE 5 done, on the structure. Two rebuilds, both driven by mappings/ and both re-runnable with data_build/build_fleet.py. THE RETIREMENT SCHEDULE. The 2020 schedule was mechanical, min(max(StYr + Life, 2023), 2031), and that reproduces 208 of its 232 existing units exactly. Neither bound was a decision: 2031 was where that model stopped looking, 2023 was the day it was built. Carried into a run that goes to 2050 they wiped out 66 GW in one year, Nurek, Toktogul and Ekibastuz included, and left 375 MW standing in the whole model in 2050. Rebuilt from an operating life stated per technology in mappings/tech_lifetime.csv, with a floor at the start year plus four so that a plant running today does not vanish at the first year, and anything reaching 2050 still standing written as 2051, which in EPM means it never retires inside the run. Central Asia now goes 51.3 GW in 2026 to 23.5 GW in 2050, hydro holding at 16.4 GW throughout. 12 units keep a dated year, held in mappings/fleet_retirement.csv: the eight Nurek units taken off one at a time for rehabilitation, whose refurbished replacements are already in the table, and Bishkek CHP, which the 2020 model had itself singled out. DeCA GIVES NO RETIREMENT DATES. It carries a commissioning year and nothing on the end of life, so the lives in tech_lifetime.csv are an assumption, not a measurement, and they are the assumption most worth challenging with the TSOs. PHASE 8 FOUND THAT LIFE IS NOT A DURATION TO THIS MODEL, IT IS A FLAG, and the first run stopped on it. main.gms:879 reads a life of 99 as "this unit may never be retired" and fixes vRetire to zero for it, while main.gms:864 fixes the capacity of any unit to zero from its retirement year on. A unit carrying both a life of 99, which tech_lifetime.csv gives to hydro, and a dated stop inside the horizon is therefore asked to lose its whole capacity with nothing allowed to move: base.gms:770 and base.gms:775 came out infeasible on the eight Nurek units and the run aborted before solving. build_fleet.py now writes, for a unit whose stop is dated, the life that decision implies rather than the flag, Nurek 3 for instance stopping after 53 years. Nothing else changes: no equation of the model reads the life of a generator for anything but that flag, and retirement carries no cost in the objective. THE CANDIDATES, 124 lines touched, driven by mappings/candidate_limits.csv. Three things were wrong for a 2050 run. First the closed door: main.gms:754 makes the Capacity column the cumulative build limit of a candidate and it was 0 for 30 of them, every generic candidate of KGZ_N, KGZ_S, TAJ_N and TAJ_S bar a 200 MW CCGT, and four of KAZ_S. Kyrgyzstan and Tajikistan could build nothing at all outside named hydro projects, which alone explains why the winter unserved energy of TAJ_N only cleared with Rogun. Opened. Second the missing speed limit: BuildLimitperYear was ten million MW everywhere, so solar and wind could appear at any rate. DeCA states a real one per country in RenewableMaxEntry, 3000 MW a year of each for KZ and UZ, 500 for KG, TJ and TM, and it steps up after 2030 to 6000, 1500 and 3000. EPM has one column and cannot step, so each zone carries two candidates: the first from the opening of the run with the early rate, a second from 2031 with the increment. The national rate is shared across the zones of a country by their share of the national peak in 2050. Third, the cumulative cap of those VRE candidates is now derived from the rate rather than left at the round 10000 of the 2020 table, which was another number that meant no cap over a horizon stopping in 2031 and would have meant four years of Kazakh solar over one running to 2050. PHASE 6, THE COST COLUMNS. HeatRate and VOM of the existing Central Asian thermal fleet are rebuilt by build_costs.py from mappings/thermal_plants.csv, which carries all 70 of those units one by one against the DeCA Thermal PP sheets. 63 are matched to a named DeCA plant and 7 are not, each with its reason in the mapping: two Kazakh residual aggregates that are not plants, the Balkhash Ulken project and Karaganda TPS-2 which DeCA does not carry, Yavan likewise, and Almaty-1 and Fergana where the model and DeCA disagree on the fuel itself. THE HEAT RATE IS TAKEN FROM DeCA WHEREVER A UNIT IS MATCHED, because a stated per-plant efficiency beats a per-technology constant: the 2020 model gave every Kazakh coal CHP the same 11.23 where DeCA separates them from 0.208 at Astana-2, which becomes 16.40, to 0.275 at Pavlodar-3, which becomes 12.42. 15 of the 63 units were already carrying the DeCA value, which is a good sign on the match. Shymkent moves the other way, 11.23 to 6.09, DeCA giving it a combined cycle efficiency of 0.560. THE VOM IS TAKEN ONLY WHERE DeCA DEPARTS FROM ITS OWN DEFAULT. It writes 3.400 $/MWh for 128 of its 136 thermal units, across five countries and every technology at once, which is a filler and not a measurement, and adopting it would flatten the technology spread the 2020 model does carry. Where it does depart, the departure is the information: the old Uzbek steam sets at 9.100, Takhiatash at 3.540, Navoi at 3.500, the combined cycles at 4.250. KAZAKH GAS TRANSPORT LANDS IN THE VOM rather than in pFuelPrice, because it is the one genuinely regional fuel cost in the region and the model carries only two Kazakh gas plants, at opposite ends of it. Zhambyl takes 0.370 $/MMBtu over its own 9.399 MMBtu/MWh and Shymkent 4.998 over 6.093, so their VOM reads 18.9 and 39.2 $/MWh. That looks alarming and is not: the decomposition moved, the total did not, and both plants come out cheaper than before, 67.2 to 50.0 $/MWh at Zhambyl and 64.7 to 59.4 at Shymkent. The step is idempotent, every value it writes being absolute and the VOM baseline always read from the 2020 reference rather than from the file under the pen. RUN ORDER IS build_fleet.py THEN build_costs.py, the second rewriting the file the first produces. PHASE 6, THE CANDIDATE COSTS. HeatRate, Capex, FOMperMW, VOM and Life of the 86 thermal candidates are rebuilt from the Thermal PP Candidates sheet through mappings/thermal_candidates.csv, which says which DeCA line each of the eleven (tech, fuel) pairs of the model reads. 79 rows move and 7 keep their 2020 costs, the coal fired CHPs and the oil fired steam turbines, DeCA carrying neither. THAT SHEET IS A TECHNOLOGY TABLE AND NOT A COUNTRY ONE: the five books state the same numbers to the dollar, so it is read from all five at once and any book that departs is outvoted and the departure printed. One does, TJ pricing new coal at 500,000 $/MW where the other four say 2,500,000, which is a typo and not a Tajik discount. Being a technology table is also what licenses using it in Pakistan and Afghanistan, outside the DeCA perimeter: the 2020 model applied ONE GLOBAL COST SET to all sixteen zones, so holding those two on 2020 while the five move would not preserve a country difference, it would invent one and let the model arbitrage on it. NEW COAL IS READ ON THE Supercritical LINE AND NOT ON THE ONE HEADED Coal, which is the judgement of the step. The Coal line states an efficiency of 0.33 at 2,500,000 $/MW while Supercritical, four rows below it in the same table, states 0.46137 at 2,250,000: cheaper to build, cheaper to run and half again as efficient, so the plain line is dominated by its own neighbour and no planner would ever pick it. The 2020 model already carried 0.42 here, a supercritical class unit. One word in the mapping falls back to the subcritical line. LIFE MOVES WITH THE COSTS BECAUSE IT MUST: main.gms:742 builds the capital recovery factor out of it, so taking a CAPEX without the amortization period stated beside it would annualize the new number on the old horizon. CCGT and gas turbines go from 30 years to 25, coal from 40 to 35, engines from 20 to 25, and nuclear from 40 to 60. WHAT IT COSTS, levelised at a 75 per cent capacity factor and a WACC of 10 per cent, before and after: CCGT 77.8 to 68.9 $/MWh, gas turbine 109.2 to 90.2, gas CHP 119.9 to 104.3, coal 58.9 to 52.6, engines 26.1 to 17.8, nuclear 107.0 to 106.6. EVERY THERMAL CANDIDATE GETS CHEAPER, which is the honest reading of a 2025 cost book against a 2020 one, and nuclear barely moves because its CAPEX rising by a third is cancelled by sixty years to amortize it over and a variable cost that falls from 16.83 to 0.67. Capacity, StYr and BuildLimitperYear are untouched, being the shape of the menu and not its cost, and so is the DeCA Max Capacity column, which is carried in the report and out of the table: it reads like a unit size, 300 MW for a coal or combined cycle block and 1200 for a nuclear one, but DeCA never says so and EPM reads Capacity as a cumulative build limit, so writing 300 there would silently cap all new coal in a country at one block. The fixed cost of the EXISTING units is still the 2020 value, DeCA stating none.</t>
+          <t>PHASE 5 done, on the structure. Two rebuilds, both driven by mappings/ and both re-runnable with data_build/build_fleet.py. THE RETIREMENT SCHEDULE. The 2020 schedule was mechanical, min(max(StYr + Life, 2023), 2031), and that reproduces 208 of its 232 existing units exactly. Neither bound was a decision: 2031 was where that model stopped looking, 2023 was the day it was built. Carried into a run that goes to 2050 they wiped out 66 GW in one year, Nurek, Toktogul and Ekibastuz included, and left 375 MW standing in the whole model in 2050. Rebuilt from an operating life stated per technology in mappings/tech_lifetime.csv, with a floor at the start year plus four so that a plant running today does not vanish at the first year, and anything reaching 2050 still standing written as 2051, which in EPM means it never retires inside the run. Central Asia now goes 51.3 GW in 2026 to 23.5 GW in 2050, hydro holding at 16.4 GW throughout. 12 units keep a dated year, held in mappings/fleet_retirement.csv: the eight Nurek units taken off one at a time for rehabilitation, whose refurbished replacements are already in the table, and Bishkek CHP, which the 2020 model had itself singled out. DeCA GIVES NO RETIREMENT DATES. It carries a commissioning year and nothing on the end of life, so the lives in tech_lifetime.csv are an assumption, not a measurement, and they are the assumption most worth challenging with the TSOs. PHASE 8 FOUND THAT LIFE IS NOT A DURATION TO THIS MODEL, IT IS A FLAG, and the first run stopped on it. main.gms:879 reads a life of 99 as "this unit may never be retired" and fixes vRetire to zero for it, while main.gms:864 fixes the capacity of any unit to zero from its retirement year on. A unit carrying both a life of 99, which tech_lifetime.csv gives to hydro, and a dated stop inside the horizon is therefore asked to lose its whole capacity with nothing allowed to move: base.gms:770 and base.gms:775 came out infeasible on the eight Nurek units and the run aborted before solving. build_fleet.py now writes, for a unit whose stop is dated, the life that decision implies rather than the flag, Nurek 3 for instance stopping after 53 years. Nothing else changes: no equation of the model reads the life of a generator for anything but that flag, and retirement carries no cost in the objective. THE CANDIDATES, 124 lines touched, driven by mappings/candidate_limits.csv. Three things were wrong for a 2050 run. First the closed door: main.gms:754 makes the Capacity column the cumulative build limit of a candidate and it was 0 for 30 of them, every generic candidate of KGZ_N, KGZ_S, TAJ_N and TAJ_S bar a 200 MW CCGT, and four of KAZ_S. Kyrgyzstan and Tajikistan could build nothing at all outside named hydro projects, which alone explains why the winter unserved energy of TAJ_N only cleared with Rogun. Opened. Second the missing speed limit: BuildLimitperYear was ten million MW everywhere, so solar and wind could appear at any rate. DeCA states a real one per country in RenewableMaxEntry, 3000 MW a year of each for KZ and UZ, 500 for KG, TJ and TM, and it steps up after 2030 to 6000, 1500 and 3000. EPM has one column and cannot step, so each zone carries two candidates: the first from the opening of the run with the early rate, a second from 2031 with the increment. The national rate is shared across the zones of a country by their share of the national peak in 2050. Third, the cumulative cap of those VRE candidates is now derived from the rate rather than left at the round 10000 of the 2020 table, which was another number that meant no cap over a horizon stopping in 2031 and would have meant four years of Kazakh solar over one running to 2050. THE SPEED LIMIT NOW COVERS EVERYTHING, NOT ONLY SOLAR AND WIND. Until this step the ten million MW a year still stood on every thermal, nuclear and hydro menu entry, and the first run spent it: 27 GW of new gas in 2026 alone, and ten gigawatts of Kazakh nuclear available from 2022 because that is the year the 2020 table carried. No source states how fast a country can commission a thermal unit the way DeCA states it for renewables, so a rate is assumed, and it is assumed in the open: mappings/candidate_limits.csv now carries, per technology, a share of the peak the zone already serves and a floor in MW below which that share may not fall. Combined cycle and open cycle gas and reciprocating engines get 5 per cent a year, coal and oil steam and cogeneration 3 per cent, the two Kazakh hydro menu entries 2 per cent, with floors of one machine, 400 MW for a CCGT block, 300 for a supercritical unit, 200 for a gas turbine, 100 for an engine or a CHP, 50 for small hydro. Northern Kazakhstan may therefore add 574 MW of CCGT a year and Kyrgyzstan 400, which is the floor doing its work: the share alone would have barred a small system from ever building one machine. NUCLEAR IS DATED, NOT ONLY RATED. Two per cent of the zone peak is 230 MW a year in northern Kazakhstan, one 1200 MW unit every five years, which is the pace of a real programme rather than a wall of capacity; and the same file now carries a first year, 2035, against a candidate whose start year in the 2020 table was 2022. The October 2024 referendum approved a first plant at Ulken, Rosatom was selected in June 2025, and the commissioning date stated publicly is 2035 to 2036. Nothing else in the table has a first year imposed on it. PAKISTAN AND AFGHANISTAN KEEP A RATE THEY WERE NEVER GIVEN. DeCA has no book for them, so their solar and wind candidates fell through the RenewableMaxEntry rule and kept the ten million MW. Rather than invent a number, the rate DeCA states for the five countries it does cover is read as a share of the peak each of them already serves, 18.7 per cent for Kazakhstan down to 11.6 for Tajikistan, and the median of those five, 15.7 per cent, is applied to the Pakistani and Afghan zones. It is a substitute taken from the source rather than from nowhere, and it is flat: the step up after 2030 that the five countries get is not extended to the two, so the two are the conservative case until the IGCEP arrives. WHAT THIS IS NOT. It is not a source. The shares and the floors are an assumption about how fast a power system can build, they are the first numbers to challenge with the TSOs, and they are the reason this resource is graded on assumed as well as on DeCA. Every named project is untouched: a project is not a menu entry, its capacity is the capacity of that project, and the loop never asks this file about it. PHASE 6, THE COST COLUMNS. HeatRate and VOM of the existing Central Asian thermal fleet are rebuilt by build_costs.py from mappings/thermal_plants.csv, which carries all 70 of those units one by one against the DeCA Thermal PP sheets. 63 are matched to a named DeCA plant and 7 are not, each with its reason in the mapping: two Kazakh residual aggregates that are not plants, the Balkhash Ulken project and Karaganda TPS-2 which DeCA does not carry, Yavan likewise, and Almaty-1 and Fergana where the model and DeCA disagree on the fuel itself. THE HEAT RATE IS TAKEN FROM DeCA WHEREVER A UNIT IS MATCHED, because a stated per-plant efficiency beats a per-technology constant: the 2020 model gave every Kazakh coal CHP the same 11.23 where DeCA separates them from 0.208 at Astana-2, which becomes 16.40, to 0.275 at Pavlodar-3, which becomes 12.42. 15 of the 63 units were already carrying the DeCA value, which is a good sign on the match. Shymkent moves the other way, 11.23 to 6.09, DeCA giving it a combined cycle efficiency of 0.560. THE VOM IS TAKEN ONLY WHERE DeCA DEPARTS FROM ITS OWN DEFAULT. It writes 3.400 $/MWh for 128 of its 136 thermal units, across five countries and every technology at once, which is a filler and not a measurement, and adopting it would flatten the technology spread the 2020 model does carry. Where it does depart, the departure is the information: the old Uzbek steam sets at 9.100, Takhiatash at 3.540, Navoi at 3.500, the combined cycles at 4.250. KAZAKH GAS TRANSPORT LANDS IN THE VOM rather than in pFuelPrice, because it is the one genuinely regional fuel cost in the region and the model carries only two Kazakh gas plants, at opposite ends of it. Zhambyl takes 0.370 $/MMBtu over its own 9.399 MMBtu/MWh and Shymkent 4.998 over 6.093, so their VOM reads 18.9 and 39.2 $/MWh. That looks alarming and is not: the decomposition moved, the total did not, and both plants come out cheaper than before, 67.2 to 50.0 $/MWh at Zhambyl and 64.7 to 59.4 at Shymkent. The step is idempotent, every value it writes being absolute and the VOM baseline always read from the 2020 reference rather than from the file under the pen. RUN ORDER IS build_fleet.py THEN build_costs.py, the second rewriting the file the first produces. PHASE 6, THE CANDIDATE COSTS. HeatRate, Capex, FOMperMW, VOM and Life of the 86 thermal candidates are rebuilt from the Thermal PP Candidates sheet through mappings/thermal_candidates.csv, which says which DeCA line each of the eleven (tech, fuel) pairs of the model reads. 79 rows move and 7 keep their 2020 costs, the coal fired CHPs and the oil fired steam turbines, DeCA carrying neither. THAT SHEET IS A TECHNOLOGY TABLE AND NOT A COUNTRY ONE: the five books state the same numbers to the dollar, so it is read from all five at once and any book that departs is outvoted and the departure printed. One does, TJ pricing new coal at 500,000 $/MW where the other four say 2,500,000, which is a typo and not a Tajik discount. Being a technology table is also what licenses using it in Pakistan and Afghanistan, outside the DeCA perimeter: the 2020 model applied ONE GLOBAL COST SET to all sixteen zones, so holding those two on 2020 while the five move would not preserve a country difference, it would invent one and let the model arbitrage on it. NEW COAL IS READ ON THE Supercritical LINE AND NOT ON THE ONE HEADED Coal, which is the judgement of the step. The Coal line states an efficiency of 0.33 at 2,500,000 $/MW while Supercritical, four rows below it in the same table, states 0.46137 at 2,250,000: cheaper to build, cheaper to run and half again as efficient, so the plain line is dominated by its own neighbour and no planner would ever pick it. The 2020 model already carried 0.42 here, a supercritical class unit. One word in the mapping falls back to the subcritical line. LIFE MOVES WITH THE COSTS BECAUSE IT MUST: main.gms:742 builds the capital recovery factor out of it, so taking a CAPEX without the amortization period stated beside it would annualize the new number on the old horizon. CCGT and gas turbines go from 30 years to 25, coal from 40 to 35, engines from 20 to 25, and nuclear from 40 to 60. WHAT IT COSTS, levelised at a 75 per cent capacity factor and a WACC of 10 per cent, before and after: CCGT 77.8 to 68.9 $/MWh, gas turbine 109.2 to 90.2, gas CHP 119.9 to 104.3, coal 58.9 to 52.6, engines 26.1 to 17.8, nuclear 107.0 to 106.6. EVERY THERMAL CANDIDATE GETS CHEAPER, which is the honest reading of a 2025 cost book against a 2020 one, and nuclear barely moves because its CAPEX rising by a third is cancelled by sixty years to amortize it over and a variable cost that falls from 16.83 to 0.67. Capacity, StYr and BuildLimitperYear are untouched, being the shape of the menu and not its cost, and so is the DeCA Max Capacity column, which is carried in the report and out of the table: it reads like a unit size, 300 MW for a coal or combined cycle block and 1200 for a nuclear one, but DeCA never says so and EPM reads Capacity as a cumulative build limit, so writing 300 there would silently cap all new coal in a country at one block. The fixed cost of the EXISTING units is still the 2020 value, DeCA stating none.</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -893,11 +893,11 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>4 seasons x 3 representative days x 24 chronological hours = 288 blocks, 8760 h</t>
+          <t>5 seasons x 3 representative days x 24 chronological hours = 360 blocks, 8760 h</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="8" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>q = 4 quarters, the 5th peak season is removed. It was not a structure but a patch: the reserve constraint takes a smax over all blocks (base.gms:991) and requires no dedicated season. Q5 only served to give that smax a block short enough to see the true peak, for want of representative days (d=1 in the 2020 model). THE FOUR QUARTERS ARE NOT CALENDAR QUARTERS, and the months behind them are now written down in data_build/mappings/seasons_months.csv: Q1 December to February, Q2 March and April, Q3 May to September, Q4 October and November. That split is read off the 2020 durations, Q1 and Q5 together 2180 h that is 90.8 days, Q2 1464 h exactly 61 days, Q3 3652 h that is 152.2 days, Q4 1464 h exactly 61 days, and it lands on 8760 h to the hour. Q3 is the irrigation release window and the window of the CASA-1000 contract, 1 May to 30 September. Every season-indexed resource is built against that mapping. PHASE 8 REBUILT IT, and this is the file that defines the sets q, d and t for the whole model: main.gms:214 reads pHours(q&lt;,d&lt;,t&lt;), so every other hourly resource follows whatever shape is written here. It is now four seasons by three representative days by twenty four chronological hours, the canonical EPM shape that epm/input/data_test also carries, and each cell holds THE NUMBER OF DAYS the representative day stands for, repeated over its 24 hours, summing to 8760. THE PEAK REPRESENTATIVE DAY REPLACES THE OLD PEAK SEASON. In each season d1 is a calendar day and weighs one day, which is what base.gms needs when it takes an smax over (q,d,t) for the reserve. The day chosen is the one that stresses the most zones at once, each zone counted against its own maximum rather than in megawatts, because a sum in megawatts is decided by Kazakhstan and Uzbekistan alone and the reserve of EPM is written per zone. The four days are 12 December, 1 March, 24 July and 21 November. THE OTHER TWO ARE REAL DAYS AS WELL, AND THEIR WEIGHTS ARE SOLVED, NOT COUNTED. The rest of the season is split in two by daily energy and each half is represented by its medoid, the real day closest to the average of that half. A medoid is the most typical day of its group and not the day carrying its average energy, so the two weights are then solved rather than taken from the sizes of the groups: two unknowns, two equations, the days of the season and the energy of the season, rounded to whole days at the end because input_verification.py compares the sum of this table to 8760 with no tolerance at all and refuses a block of zero hours. The weights that come out are 53 and 36 days for Q1, 28 and 32 for Q2, 79 and 73 for Q3, 29 and 31 for Q4. WHY NOT THE MEAN OF EACH GROUP, WHICH IS WHAT THIS STEP DID FIRST. Averaging seventy-six days flattens every trough that does not fall at the same hour twice, and the model reads that flattening as a baseload the system does not have. See pDemandProfile, which carries the measurement and the table of it. The season durations are unchanged, 90 / 61 / 153 / 61 days, so pAvailability and pTransferLimit did not have to be rebuilt.</t>
+          <t>q = 4 quarters, the 5th peak season is removed. It was not a structure but a patch: the reserve constraint takes a smax over all blocks (base.gms:991) and requires no dedicated season. Q5 only served to give that smax a block short enough to see the true peak, for want of representative days (d=1 in the 2020 model). THE SEASONS ARE NOT CALENDAR QUARTERS, and the months behind them are written down in data_build/mappings/seasons_months.csv, which is the single place the year is cut: Q1 December to February, Q2 March and April, Q3 May and June, Q5 July to September, Q4 October and November. The first cut was read off the 2020 durations, Q1 and the peak block together 2180 h that is 90.8 days, Q2 1464 h exactly 61 days, Q3 3652 h that is 152.2 days, Q4 1464 h exactly 61 days, and it lands on 8760 h to the hour. Every season-indexed resource is built against that mapping. PHASE 4 SPLIT THE SUMMER IN TWO, May-June against July-September. One season of five months held two different things at once: the irrigation release, where the reservoirs open for the fields downstream and the hydro runs whether the load calls for it or not, and the cooling peak, where it is the load that is high. A single season had to pick one, and it picked the peak: its representative days were 24 July and two medians drawn from a five-month pool. They are now 27 June for Q3 and 24 July for Q5, and May-June has its own shape at last. THE NAME Q5 IS RECYCLED, not restored. The 2020 model had a Q5 too and it was the 130 h peak block, not a season. Nothing of that block is here. The seasons mapping carries a legacy column saying which 2020 season each of ours draws its inherited shapes from, and ours sends both halves of the summer to the 2020 Q3; without it build_vre matched on the name alone and dressed July-September in a winter peak block, which input_verification.py caught as a capacity factor of 1.24 on KAZ_N solar. NO SEASON IS NAMED ANYWHERE ELSE. The CASA-1000 contract window and the seasonal corridor to Afghanistan are written in months in their own mappings and resolved against this file, so the year can be re-cut again without touching them; a window that would take part of a season stops the build rather than being guessed at. PHASE 8 REBUILT IT, and this is the file that defines the sets q, d and t for the whole model: main.gms:214 reads pHours(q&lt;,d&lt;,t&lt;), so every other hourly resource follows whatever shape is written here. It is now four seasons by three representative days by twenty four chronological hours, the canonical EPM shape that epm/input/data_test also carries, and each cell holds THE NUMBER OF DAYS the representative day stands for, repeated over its 24 hours, summing to 8760. THE PEAK REPRESENTATIVE DAY REPLACES THE OLD PEAK SEASON. In each season d1 is a calendar day and weighs one day, which is what base.gms needs when it takes an smax over (q,d,t) for the reserve. The day chosen is the one that stresses the most zones at once, each zone counted against its own maximum rather than in megawatts, because a sum in megawatts is decided by Kazakhstan and Uzbekistan alone and the reserve of EPM is written per zone. The five days are 12 December, 1 March, 27 June, 24 July and 21 November. THE OTHER TWO ARE REAL DAYS AS WELL, AND THEIR WEIGHTS ARE SOLVED, NOT COUNTED. The rest of the season is split in two by daily energy and each half is represented by its medoid, the real day closest to the average of that half. A medoid is the most typical day of its group and not the day carrying its average energy, so the two weights are then solved rather than taken from the sizes of the groups: two unknowns, two equations, the days of the season and the energy of the season, rounded to whole days at the end because input_verification.py compares the sum of this table to 8760 with no tolerance at all and refuses a block of zero hours. The weights that come out are 53 and 36 days for Q1, 28 and 32 for Q2, 31 and 29 for Q3, 42 and 49 for Q5, 29 and 31 for Q4. WHY NOT THE MEAN OF EACH GROUP, WHICH IS WHAT THIS STEP DID FIRST. Averaging seventy-six days flattens every trough that does not fall at the same hour twice, and the model reads that flattening as a baseload the system does not have. See pDemandProfile, which carries the measurement and the table of it. The season durations are 90 / 61 / 61 / 92 / 61 days, and every seasonal resource is rebuilt from them: pDemandProfile, pVREProfile, pAvailability, pTransferLimit, pContractedTradeFlag and pContractedTradeEnergy.</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>THE NUMBER OF REPRESENTATIVE DAYS IS ONE ARGUMENT, --days, and three is a starting point rather than a result: the model went from 35 blocks in 2020 to 288 here, and if the solve turns out to be comfortable the count should go up, the days being grouped by demand alone today and therefore carrying no renewable variability. See pVREProfile, where the same limit bites harder. THE WEIGHT SOLVER IS EXACT FOR TWO GROUPS AND LEAST SQUARES BEYOND, so raising --days above three leaves a residual on the energy of the season. It is reported in the demand test and it is small; it would be removed by adding a third condition, the peak of each group, rather than by another solver. Q3 STILL COVERS FIVE MONTHS, May to September, because that is the CASA-1000 contract window. Splitting it in two, May-June against July-September, is the next thing worth doing to this file: the irrigation release and the summer cooling peak do not belong to the same shape.</t>
+          <t>THE NUMBER OF REPRESENTATIVE DAYS IS ONE ARGUMENT, --days, and three is a starting point rather than a result: the model went from 35 blocks in 2020 to 288 here, and if the solve turns out to be comfortable the count should go up, the days being grouped by demand alone today and therefore carrying no renewable variability. See pVREProfile, where the same limit bites harder. THE WEIGHT SOLVER IS EXACT FOR TWO GROUPS AND LEAST SQUARES BEYOND, so raising --days above three leaves a residual on the energy of the season. It is reported in the demand test and it is small; it would be removed by adding a third condition, the peak of each group, rather than by another solver. PHASE 4 SPLIT THE SUMMER: Q3 is May-June, the irrigation release, and Q5 is July-September, the cooling peak. 360 blocks now instead of 288. It shows in the representative days, which no longer share one: Q3 peaks on 27 June and Q5 on 24 July, where the single five-month season kept only 24 July and drowned May-June in two median days. The contract window did not move, it is written in months now and spans the two seasons.</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="8" t="inlineStr">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>384</v>
+        <v>480</v>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="8" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>PHASE 8 BUILT IT FROM TWO SOURCES BECAUSE NEITHER GIVES BOTH HALVES. base.gms:812 writes the output of every solar and wind unit as this profile times the availability times the capacity, so the table is the whole renewable production, in level as much as in shape. DeCA GIVES THE LEVEL AND NOT THE SHAPE: RenewableProfile states a monthly utilization factor per plant and no hour of the day. Its own header says so, in a line the authors left for themselves, "Hourly profiles are also needed for all WPP and SPP power plants". THE 2020 MODEL GIVES THE SHAPE and a level five years old. So the day shape comes from the 2020 profile, normalised to a mean of one, and is multiplied by the DeCA seasonal factor, the month length weighted mean over the months of the season and over the plants mappings/vre_profiles.csv selects. THE FACTOR IS A COUNTRY MEAN over every plant of the technology, existing and candidate, high yield and low yield sites together, because the five books name no zone for their existing plants. That is an average site, which is what a generic candidate is. Sixty four of the 128 seasonal factors move; the Afghan and Pakistani zones keep their 2020 level, being outside the DeCA perimeter. WHAT MOVES: mean solar capacity factor 0.169 to 0.152, mean wind 0.333 to 0.354. Solar loses most in winter, KAZ_N Q1 going from 0.144 to 0.089, which matters in a system that peaks in December. TWO TRAPS THE MAPPING STEPS AROUND. The Tajik book labels its own regions with a KZ prefix, Khatlon and Sougd and Gorno-Badakhshan all reading "KZ ...", so the selection keys on the workbook and not on the name. And one Kazakh SOLAR plant is named Arm Wind: the exclude column of the mapping settles it on the _SP suffix, and the builder refuses outright any row two technologies claim at once.</t>
+          <t>PHASE 8 BUILT IT FROM TWO SOURCES BECAUSE NEITHER GIVES BOTH HALVES. base.gms:812 writes the output of every solar and wind unit as this profile times the availability times the capacity, so the table is the whole renewable production, in level as much as in shape. DeCA GIVES THE LEVEL AND NOT THE SHAPE: RenewableProfile states a monthly utilization factor per plant and no hour of the day. Its own header says so, in a line the authors left for themselves, "Hourly profiles are also needed for all WPP and SPP power plants". THE 2020 MODEL GIVES THE SHAPE and a level five years old. So the day shape comes from the 2020 profile, normalised to a mean of one, and is multiplied by the DeCA seasonal factor, the month length weighted mean over the months of the season and over the plants mappings/vre_profiles.csv selects. THE FACTOR IS A COUNTRY MEAN over every plant of the technology, existing and candidate, high yield and low yield sites together, because the five books name no zone for their existing plants. That is an average site, which is what a generic candidate is. Eighty of the 160 seasonal factors move; the Afghan and Pakistani zones keep their 2020 level, being outside the DeCA perimeter. WHAT MOVES: mean solar capacity factor 0.174 to 0.169, mean wind 0.333 to 0.369. Solar loses most in winter, KAZ_N Q1 going from 0.144 to 0.089, which matters in a system that peaks in December. THE 2020 SHAPE IS DRAWN BY MONTHS, NOT BY NAME, since phase 4 split the summer. Both halves take the 2020 Q3 day and are rescaled to their own DeCA factor, 0.208 for KAZ_N solar in Q3 against 0.207 in Q5. Matching on the name instead handed July-September the 2020 peak block, a 130 h winter artefact, and produced a capacity factor of 1.24; the column that says which season feeds which lives in mappings/seasons_months.csv. TWO TRAPS THE MAPPING STEPS AROUND. The Tajik book labels its own regions with a KZ prefix, Khatlon and Sougd and Gorno-Badakhshan all reading "KZ ...", so the selection keys on the workbook and not on the name. And one Kazakh SOLAR plant is named Arm Wind: the exclude column of the mapping settles it on the _SP suffix, and the builder refuses outright any row two technologies claim at once.</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Rebuilt from data_build/mappings/corridors.csv, which carries the 42 directed corridors with their anchor years and, for each, the source it rests on. Three corrections against the 2020 model. Turkmenistan to Afghanistan: the two directions were swapped, the 80 MW leg could not carry the 2100 GWh/y that pMaxAnnualTransfer requires. CASA-1000 to Pakistan: 1000 MW and not 1300, the 1300 being the rating of the whole DC link including the Afghan tap. Tajikistan to Afghanistan: 188 MW all year plus a May-September window at 638 MW, which is the first seasonal corridor of the model. The Q5 rows dropped by an earlier build are restored: Q5 is the peak season of pHours, and without them no zone could import at the peak.</t>
+          <t>Rebuilt from data_build/mappings/corridors.csv, which carries the 42 directed corridors with their anchor years and, for each, the source it rests on. Three corrections against the 2020 model. Turkmenistan to Afghanistan: the two directions were swapped, the 80 MW leg could not carry the 2100 GWh/y that pMaxAnnualTransfer requires. CASA-1000 to Pakistan: 1000 MW and not 1300, the 1300 being the rating of the whole DC link including the Afghan tap. Tajikistan to Afghanistan: 188 MW all year plus a May-September window at 638 MW, which is the first seasonal corridor of the model. That window is written in months and not in season names, so the phase 4 split carried it into Q3 and Q5 by itself. The file used to carry Q5 rows inherited from the 2020 season set while pHours had only four seasons: the season set now comes from seasons_months.csv like every other seasonal resource, so the two cannot drift apart again.</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2193,17 +2193,17 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>inherited, fit for purpose</t>
+          <t>done</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>KEEP</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       <c r="L30" s="4" t="inlineStr"/>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Q3 is not a calendar quarter. In pHours it is worth 3652 h, that is 152 days, which is the May-September export window of CASA-1000 to within one day. The five flags are therefore already on the right season and must not be moved.</t>
+          <t>NO LONGER WRITTEN BY HAND, and no longer naming a season. The window of the contract is declared in months in data_build/mappings/contracts.csv, 1 May to 30 September for the five CASA-1000 legs, and the build turns it into whatever seasons cover those months. Phase 4 split the summer in two and the flags followed on their own: ten rows now, Q3 and Q5 for each leg, where there were five on Q3. Two of the five legs carry no volume on purpose; the contracted equality then reads zero and holds the counter-flow shut, which is how the 2020 model suppressed them.</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>DONE. Constraint carried to phase 8: the representative-day pipeline has to reproduce this season structure, Q3 = May-September, or every contracted flow of the model moves with it.</t>
+          <t>DONE. The build refuses a window that takes part of a season, so a later re-cut of the year cannot move the contract silently: it stops.</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="8" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Re-based on the model years. The volumes stopped at 2030, so the contract simply disappeared from 2031 on, a year GAMS reads as zero. The 2030 value is now held to 2050, which ASSUMES the contract is renewed. The three flows total 4343 GWh in Q3, against a 4434 GWh plateau in the PPA note: consistent.</t>
+          <t>Re-based on the model years. The volumes stopped at 2030, so the contract simply disappeared from 2031 on, a year GAMS reads as zero. The 2030 value is now held to 2050, which ASSUMES the contract is renewed. The three flows total 4343 GWh over the window, against a 4434 GWh plateau in the PPA note: consistent. PHASE 4 SPLIT THE VOLUME, IT DID NOT DUPLICATE IT. The contracted equality of base.gms is written season by season, so the May-September total is now shared between Q3 and Q5 PRO RATA BY DAYS, 61 against 92: KGZ_S to TAJ_N goes from 1595 GWh on one season to 636 and 959 on two. Copying the figure into both would have doubled every contracted flow of the model. The seasons of the reference table are ignored on the way in, only the pair and the yearly total are kept: Q3 there was the 2020 way of cutting the year, not a property of the contract.</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>PHASE 7 SETTLED THE RESERVE FLAGS, all of them by leaving them where they are: fApplyZonalPlanningReserve on and fApplyPlanningReserveConstraint on with an empty country margin, which is the 2020 formulation; both spinning reserve flags off, DeCA holding no operating reserve either. See pPlanningReserveMarginZone and pSpinningReserveReqCountry. TWO TRAPS FOUND AND LEFT IN PLACE BECAUSE THEY ARE INERT TODAY. 1. sPeakLoadProximityThreshold IS EMPTY, hence zero, and main.gms:677 tests a strict inequality against it, so pAllHours is zero everywhere and main.gms:686 gives EVERY SOLAR AND WIND UNIT A CAPACITY CREDIT OF ZERO. It costs nothing today, pCapacityCredit feeding only the country and system reserves which generate no row here, but anyone switching to a country reserve in phase 9 would silently be telling the model that renewables are worth no firm capacity at all. 2. fUseSimplifiedDemand SETTLED BY PHASE 8 AND NOW AT 1, the profile being built. The trap it was is worth remembering: at 0 the model reads pDemandData and at 1 it rebuilds it out of pDemandProfile, and until phase 8 BOTH were empty, so the model had no demand at all whichever way the flag was set. Still to be settled elsewhere: carbon (OFF, phase 9), storage (OFF), ramps (OFF), MinGen and MUDT (OFF, dispatch only).</t>
+          <t>PHASE 7 SETTLED THE RESERVE FLAGS, all of them by leaving them where they are: fApplyZonalPlanningReserve on and fApplyPlanningReserveConstraint on with an empty country margin, which is the 2020 formulation; both spinning reserve flags off, DeCA holding no operating reserve either. See pPlanningReserveMarginZone and pSpinningReserveReqCountry. TWO TRAPS FOUND AND LEFT IN PLACE BECAUSE THEY ARE INERT TODAY. 1. sPeakLoadProximityThreshold IS EMPTY, hence zero, and main.gms:677 tests a strict inequality against it, so pAllHours is zero everywhere and main.gms:686 gives EVERY SOLAR AND WIND UNIT A CAPACITY CREDIT OF ZERO. It costs nothing today, pCapacityCredit feeding only the country and system reserves which generate no row here, but anyone switching to a country reserve in phase 9 would silently be telling the model that renewables are worth no firm capacity at all. 2. fUseSimplifiedDemand SETTLED BY PHASE 8 AND NOW AT 1, the profile being built. The trap it was is worth remembering: at 0 the model reads pDemandData and at 1 it rebuilds it out of pDemandProfile, and until phase 8 BOTH were empty, so the model had no demand at all whichever way the flag was set. PHASE 5 TURNED fEnableStorage ON, the second value the build overrides. The eight four-hour battery candidates of pStorageDataInput were written in phase 4 and were dead while the flag was 0: base.gms only generates the storage balance, the charge and the state-of-charge equations under it, so the rows were read and then never entered an equation. The vocabulary was never the obstacle, Storage/Battery having been in pTechFuel since 2020: the switch was. Still to be settled elsewhere: carbon (OFF, phase 9), ramps (OFF), MinGen and MUDT (OFF, dispatch only).</t>
         </is>
       </c>
     </row>
@@ -959,21 +959,25 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>26 tech/fuel pairs</t>
+          <t>26 tech/fuel pairs, two of them wrongly flagged</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>EXTEND</t>
+          <t>REVISE</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -983,19 +987,23 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>casa_2020</t>
+          <t>casa_2020, epm_resources</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr"/>
+          <t>2020, two flags corrected in 2026</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>THIS TABLE IS THE VOCABULARY OF THE MODEL. main.gms:169 declares the tech and f sets from it and from nothing else, main.gms:598 and 601 read HourlyVariation to build the VRE set and RETechnology to build the RE set, and base.gms:811 then writes a different equation for a unit inside the VRE set than for one outside it. A wrong flag here is not a label, it is a change of formulation. TWO WERE WRONG AND ARE CORRECTED, both against the EPM reference vocabulary in epm/resources/pTechFuel.csv. 1. INT/Import CARRIED HourlyVariation 1, so every import contract landed in the VRE set and base.gms:811 forced its output to pVREgenProfile x availability x capacity. pVREProfile holds solar and wind only, so the profile of an import is zero and the equation reads: produce nothing, every hour of every year. The model has one such unit, IRAN_Import, 400 MW into NEPS_HERAT, and the solved run confirms it: pPlantMerged carries its 400 MW of capacity in all 13 years and not one row of energy. The 2020 model had the same flag and the same silence. At 0 it becomes what it is, a dispatchable 400 MW at 70 USD/MWh, availability 0.9. The reference calls the technology ImportTransmission and flags it 0,0. 2. HY/Water CARRIED RETechnology 0, so no hydro of the model counted as renewable. It is inert today, base.gms:786 firing only when a renewable target is set and sMinRenewableSharePct being 0, but it would have quietly halved the renewable share of any target scenario. The reference flags ReservoirHydro/Water 1. HourlyVariation stays 0: reservoir hydro is dispatched against its seasonal availability, not against an hourly profile. FOUR ROWS ARE USED BY NO UNIT and are kept all the same, aligned on the reference: CSPPlant/CSP, PVwSTO/Solar, STOPV/Solar and ROR/Water. They are not spare labels. main.gms:604-625 names those four strings literally to build the cs, so, stp and ror sets, and the strings exist only because this table declares them; deleting the rows would stop the compilation. Storage/Battery WAS ALREADY HERE and needed nothing. What the eight battery candidates were missing was not a vocabulary entry but the switch, and phase 5 turned it on: see fEnableStorage in pSettings.</t>
+        </is>
+      </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Add BESS if storage is turned on.</t>
+          <t>PHASE 9: the DeCA candidate menu this model has no vocabulary for, CCGT with CCS, coal with CCS, ultrasupercritical coal, CCGT on biogas and the dual gas/hydrogen machine. Each needs a row here before it can need anything else.</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1472,12 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>PHASE 5 done, on the structure. Two rebuilds, both driven by mappings/ and both re-runnable with data_build/build_fleet.py. THE RETIREMENT SCHEDULE. The 2020 schedule was mechanical, min(max(StYr + Life, 2023), 2031), and that reproduces 208 of its 232 existing units exactly. Neither bound was a decision: 2031 was where that model stopped looking, 2023 was the day it was built. Carried into a run that goes to 2050 they wiped out 66 GW in one year, Nurek, Toktogul and Ekibastuz included, and left 375 MW standing in the whole model in 2050. Rebuilt from an operating life stated per technology in mappings/tech_lifetime.csv, with a floor at the start year plus four so that a plant running today does not vanish at the first year, and anything reaching 2050 still standing written as 2051, which in EPM means it never retires inside the run. Central Asia now goes 51.3 GW in 2026 to 23.5 GW in 2050, hydro holding at 16.4 GW throughout. 12 units keep a dated year, held in mappings/fleet_retirement.csv: the eight Nurek units taken off one at a time for rehabilitation, whose refurbished replacements are already in the table, and Bishkek CHP, which the 2020 model had itself singled out. DeCA GIVES NO RETIREMENT DATES. It carries a commissioning year and nothing on the end of life, so the lives in tech_lifetime.csv are an assumption, not a measurement, and they are the assumption most worth challenging with the TSOs. PHASE 8 FOUND THAT LIFE IS NOT A DURATION TO THIS MODEL, IT IS A FLAG, and the first run stopped on it. main.gms:879 reads a life of 99 as "this unit may never be retired" and fixes vRetire to zero for it, while main.gms:864 fixes the capacity of any unit to zero from its retirement year on. A unit carrying both a life of 99, which tech_lifetime.csv gives to hydro, and a dated stop inside the horizon is therefore asked to lose its whole capacity with nothing allowed to move: base.gms:770 and base.gms:775 came out infeasible on the eight Nurek units and the run aborted before solving. build_fleet.py now writes, for a unit whose stop is dated, the life that decision implies rather than the flag, Nurek 3 for instance stopping after 53 years. Nothing else changes: no equation of the model reads the life of a generator for anything but that flag, and retirement carries no cost in the objective. THE CANDIDATES, 124 lines touched, driven by mappings/candidate_limits.csv. Three things were wrong for a 2050 run. First the closed door: main.gms:754 makes the Capacity column the cumulative build limit of a candidate and it was 0 for 30 of them, every generic candidate of KGZ_N, KGZ_S, TAJ_N and TAJ_S bar a 200 MW CCGT, and four of KAZ_S. Kyrgyzstan and Tajikistan could build nothing at all outside named hydro projects, which alone explains why the winter unserved energy of TAJ_N only cleared with Rogun. Opened. Second the missing speed limit: BuildLimitperYear was ten million MW everywhere, so solar and wind could appear at any rate. DeCA states a real one per country in RenewableMaxEntry, 3000 MW a year of each for KZ and UZ, 500 for KG, TJ and TM, and it steps up after 2030 to 6000, 1500 and 3000. EPM has one column and cannot step, so each zone carries two candidates: the first from the opening of the run with the early rate, a second from 2031 with the increment. The national rate is shared across the zones of a country by their share of the national peak in 2050. Third, the cumulative cap of those VRE candidates is now derived from the rate rather than left at the round 10000 of the 2020 table, which was another number that meant no cap over a horizon stopping in 2031 and would have meant four years of Kazakh solar over one running to 2050. THE SPEED LIMIT NOW COVERS EVERYTHING, NOT ONLY SOLAR AND WIND. Until this step the ten million MW a year still stood on every thermal, nuclear and hydro menu entry, and the first run spent it: 27 GW of new gas in 2026 alone, and ten gigawatts of Kazakh nuclear available from 2022 because that is the year the 2020 table carried. No source states how fast a country can commission a thermal unit the way DeCA states it for renewables, so a rate is assumed, and it is assumed in the open: mappings/candidate_limits.csv now carries, per technology, a share of the peak the zone already serves and a floor in MW below which that share may not fall. Combined cycle and open cycle gas and reciprocating engines get 5 per cent a year, coal and oil steam and cogeneration 3 per cent, the two Kazakh hydro menu entries 2 per cent, with floors of one machine, 400 MW for a CCGT block, 300 for a supercritical unit, 200 for a gas turbine, 100 for an engine or a CHP, 50 for small hydro. Northern Kazakhstan may therefore add 574 MW of CCGT a year and Kyrgyzstan 400, which is the floor doing its work: the share alone would have barred a small system from ever building one machine. NUCLEAR IS DATED, NOT ONLY RATED. Two per cent of the zone peak is 230 MW a year in northern Kazakhstan, one 1200 MW unit every five years, which is the pace of a real programme rather than a wall of capacity; and the same file now carries a first year, 2035, against a candidate whose start year in the 2020 table was 2022. The October 2024 referendum approved a first plant at Ulken, Rosatom was selected in June 2025, and the commissioning date stated publicly is 2035 to 2036. Nothing else in the table has a first year imposed on it. PAKISTAN AND AFGHANISTAN KEEP A RATE THEY WERE NEVER GIVEN. DeCA has no book for them, so their solar and wind candidates fell through the RenewableMaxEntry rule and kept the ten million MW. Rather than invent a number, the rate DeCA states for the five countries it does cover is read as a share of the peak each of them already serves, 18.7 per cent for Kazakhstan down to 11.6 for Tajikistan, and the median of those five, 15.7 per cent, is applied to the Pakistani and Afghan zones. It is a substitute taken from the source rather than from nowhere, and it is flat: the step up after 2030 that the five countries get is not extended to the two, so the two are the conservative case until the IGCEP arrives. WHAT THIS IS NOT. It is not a source. The shares and the floors are an assumption about how fast a power system can build, they are the first numbers to challenge with the TSOs, and they are the reason this resource is graded on assumed as well as on DeCA. Every named project is untouched: a project is not a menu entry, its capacity is the capacity of that project, and the loop never asks this file about it. PHASE 6, THE COST COLUMNS. HeatRate and VOM of the existing Central Asian thermal fleet are rebuilt by build_costs.py from mappings/thermal_plants.csv, which carries all 70 of those units one by one against the DeCA Thermal PP sheets. 63 are matched to a named DeCA plant and 7 are not, each with its reason in the mapping: two Kazakh residual aggregates that are not plants, the Balkhash Ulken project and Karaganda TPS-2 which DeCA does not carry, Yavan likewise, and Almaty-1 and Fergana where the model and DeCA disagree on the fuel itself. THE HEAT RATE IS TAKEN FROM DeCA WHEREVER A UNIT IS MATCHED, because a stated per-plant efficiency beats a per-technology constant: the 2020 model gave every Kazakh coal CHP the same 11.23 where DeCA separates them from 0.208 at Astana-2, which becomes 16.40, to 0.275 at Pavlodar-3, which becomes 12.42. 15 of the 63 units were already carrying the DeCA value, which is a good sign on the match. Shymkent moves the other way, 11.23 to 6.09, DeCA giving it a combined cycle efficiency of 0.560. THE VOM IS TAKEN ONLY WHERE DeCA DEPARTS FROM ITS OWN DEFAULT. It writes 3.400 $/MWh for 128 of its 136 thermal units, across five countries and every technology at once, which is a filler and not a measurement, and adopting it would flatten the technology spread the 2020 model does carry. Where it does depart, the departure is the information: the old Uzbek steam sets at 9.100, Takhiatash at 3.540, Navoi at 3.500, the combined cycles at 4.250. KAZAKH GAS TRANSPORT LANDS IN THE VOM rather than in pFuelPrice, because it is the one genuinely regional fuel cost in the region and the model carries only two Kazakh gas plants, at opposite ends of it. Zhambyl takes 0.370 $/MMBtu over its own 9.399 MMBtu/MWh and Shymkent 4.998 over 6.093, so their VOM reads 18.9 and 39.2 $/MWh. That looks alarming and is not: the decomposition moved, the total did not, and both plants come out cheaper than before, 67.2 to 50.0 $/MWh at Zhambyl and 64.7 to 59.4 at Shymkent. The step is idempotent, every value it writes being absolute and the VOM baseline always read from the 2020 reference rather than from the file under the pen. RUN ORDER IS build_fleet.py THEN build_costs.py, the second rewriting the file the first produces. PHASE 6, THE CANDIDATE COSTS. HeatRate, Capex, FOMperMW, VOM and Life of the 86 thermal candidates are rebuilt from the Thermal PP Candidates sheet through mappings/thermal_candidates.csv, which says which DeCA line each of the eleven (tech, fuel) pairs of the model reads. 79 rows move and 7 keep their 2020 costs, the coal fired CHPs and the oil fired steam turbines, DeCA carrying neither. THAT SHEET IS A TECHNOLOGY TABLE AND NOT A COUNTRY ONE: the five books state the same numbers to the dollar, so it is read from all five at once and any book that departs is outvoted and the departure printed. One does, TJ pricing new coal at 500,000 $/MW where the other four say 2,500,000, which is a typo and not a Tajik discount. Being a technology table is also what licenses using it in Pakistan and Afghanistan, outside the DeCA perimeter: the 2020 model applied ONE GLOBAL COST SET to all sixteen zones, so holding those two on 2020 while the five move would not preserve a country difference, it would invent one and let the model arbitrage on it. NEW COAL IS READ ON THE Supercritical LINE AND NOT ON THE ONE HEADED Coal, which is the judgement of the step. The Coal line states an efficiency of 0.33 at 2,500,000 $/MW while Supercritical, four rows below it in the same table, states 0.46137 at 2,250,000: cheaper to build, cheaper to run and half again as efficient, so the plain line is dominated by its own neighbour and no planner would ever pick it. The 2020 model already carried 0.42 here, a supercritical class unit. One word in the mapping falls back to the subcritical line. LIFE MOVES WITH THE COSTS BECAUSE IT MUST: main.gms:742 builds the capital recovery factor out of it, so taking a CAPEX without the amortization period stated beside it would annualize the new number on the old horizon. CCGT and gas turbines go from 30 years to 25, coal from 40 to 35, engines from 20 to 25, and nuclear from 40 to 60. WHAT IT COSTS, levelised at a 75 per cent capacity factor and a WACC of 10 per cent, before and after: CCGT 77.8 to 68.9 $/MWh, gas turbine 109.2 to 90.2, gas CHP 119.9 to 104.3, coal 58.9 to 52.6, engines 26.1 to 17.8, nuclear 107.0 to 106.6. EVERY THERMAL CANDIDATE GETS CHEAPER, which is the honest reading of a 2025 cost book against a 2020 one, and nuclear barely moves because its CAPEX rising by a third is cancelled by sixty years to amortize it over and a variable cost that falls from 16.83 to 0.67. Capacity, StYr and BuildLimitperYear are untouched, being the shape of the menu and not its cost, and so is the DeCA Max Capacity column, which is carried in the report and out of the table: it reads like a unit size, 300 MW for a coal or combined cycle block and 1200 for a nuclear one, but DeCA never says so and EPM reads Capacity as a cumulative build limit, so writing 300 there would silently cap all new coal in a country at one block. The fixed cost of the EXISTING units is still the 2020 value, DeCA stating none.</t>
+          <t>PHASE 5 done, on the structure. Two rebuilds, both driven by mappings/ and both re-runnable with data_build/build_fleet.py. THE RETIREMENT SCHEDULE. The 2020 schedule was mechanical, min(max(StYr + Life, 2023), 2031), and that reproduces 208 of its 232 existing units exactly. Neither bound was a decision: 2031 was where that model stopped looking, 2023 was the day it was built. Carried into a run that goes to 2050 they wiped out 66 GW in one year, Nurek, Toktogul and Ekibastuz included, and left 375 MW standing in the whole model in 2050. Rebuilt from an operating life stated per technology in mappings/tech_lifetime.csv, with a floor at the start year plus four so that a plant running today does not vanish at the first year, and anything reaching 2050 still standing written as 2051, which in EPM means it never retires inside the run. Central Asia now goes 51.3 GW in 2026 to 23.5 GW in 2050, hydro holding at 16.4 GW throughout. 12 units keep a dated year, held in mappings/fleet_retirement.csv: the eight Nurek units taken off one at a time for rehabilitation, whose refurbished replacements are already in the table, and Bishkek CHP, which the 2020 model had itself singled out. DeCA GIVES NO RETIREMENT DATES. It carries a commissioning year and nothing on the end of life, so the lives in tech_lifetime.csv are an assumption, not a measurement, and they are the assumption most worth challenging with the TSOs. PHASE 8 FOUND THAT LIFE IS NOT A DURATION TO THIS MODEL, IT IS A FLAG, and the first run stopped on it. main.gms:879 reads a life of 99 as "this unit may never be retired" and fixes vRetire to zero for it, while main.gms:864 fixes the capacity of any unit to zero from its retirement year on. A unit carrying both a life of 99, which tech_lifetime.csv gives to hydro, and a dated stop inside the horizon is therefore asked to lose its whole capacity with nothing allowed to move: base.gms:770 and base.gms:775 came out infeasible on the eight Nurek units and the run aborted before solving. build_fleet.py now writes, for a unit whose stop is dated, the life that decision implies rather than the flag, Nurek 3 for instance stopping after 53 years. Nothing else changes: no equation of the model reads the life of a generator for anything but that flag, and retirement carries no cost in the objective. THE CANDIDATES, 124 lines touched, driven by mappings/candidate_limits.csv. Three things were wrong for a 2050 run. First the closed door: main.gms:754 makes the Capacity column the cumulative build limit of a candidate and it was 0 for 30 of them, every generic candidate of KGZ_N, KGZ_S, TAJ_N and TAJ_S bar a 200 MW CCGT, and four of KAZ_S. Kyrgyzstan and Tajikistan could build nothing at all outside named hydro projects, which alone explains why the winter unserved energy of TAJ_N only cleared with Rogun. Opened. Second the missing speed limit: BuildLimitperYear was ten million MW everywhere, so solar and wind could appear at any rate. DeCA states a real one per country in RenewableMaxEntry, 3000 MW a year of each for KZ and UZ, 500 for KG, TJ and TM, and it steps up after 2030 to 6000, 1500 and 3000. EPM has one column and cannot step, so each zone carries two candidates: the first from the opening of the run with the early rate, a second from 2031 with the increment. The national rate is shared across the zones of a country by their share of the national peak in 2050. Third, the cumulative cap of those VRE candidates is now derived from the rate rather than left at the round 10000 of the 2020 table, which was another number that meant no cap over a horizon stopping in 2031 and would have meant four years of Kazakh solar over one running to 2050. THE SPEED LIMIT NOW COVERS EVERYTHING, NOT ONLY SOLAR AND WIND. Until this step the ten million MW a year still stood on every thermal, nuclear and hydro menu entry, and the first run spent it: 27 GW of new gas in 2026 alone, and ten gigawatts of Kazakh nuclear available from 2022 because that is the year the 2020 table carried. No source states how fast a country can commission a thermal unit the way DeCA states it for renewables, so a rate is assumed, and it is assumed in the open: mappings/candidate_limits.csv now carries, per technology, a share of the peak the zone already serves and a floor in MW below which that share may not fall. Combined cycle and open cycle gas and reciprocating engines get 5 per cent a year, coal and oil steam and cogeneration 3 per cent, the two Kazakh hydro menu entries 2 per cent, with floors of one machine, 400 MW for a CCGT block, 300 for a supercritical unit, 200 for a gas turbine, 100 for an engine or a CHP, 50 for small hydro. Northern Kazakhstan may therefore add 574 MW of CCGT a year and Kyrgyzstan 400, which is the floor doing its work: the share alone would have barred a small system from ever building one machine. NUCLEAR IS DATED, NOT ONLY RATED. Two per cent of the zone peak is 230 MW a year in northern Kazakhstan, one 1200 MW unit every five years, which is the pace of a real programme rather than a wall of capacity; and the same file now carries a first year, 2035, against a candidate whose start year in the 2020 table was 2022. The October 2024 referendum approved a first plant at Ulken, Rosatom was selected in June 2025, and the commissioning date stated publicly is 2035 to 2036. Nothing else in the table has a first year imposed on it. PAKISTAN AND AFGHANISTAN KEEP A RATE THEY WERE NEVER GIVEN. DeCA has no book for them, so their solar and wind candidates fell through the RenewableMaxEntry rule and kept the ten million MW. Rather than invent a number, the rate DeCA states for the five countries it does cover is read as a share of the peak each of them already serves, 18.7 per cent for Kazakhstan down to 11.6 for Tajikistan, and the median of those five, 15.7 per cent, is applied to the Pakistani and Afghan zones. It is a substitute taken from the source rather than from nowhere, and it is flat: the step up after 2030 that the five countries get is not extended to the two, so the two are the conservative case until the IGCEP arrives. WHAT THIS IS NOT. It is not a source. The shares and the floors are an assumption about how fast a power system can build, they are the first numbers to challenge with the TSOs, and they are the reason this resource is graded on assumed as well as on DeCA. Every named project is untouched: a project is not a menu entry, its capacity is the capacity of that project, and the loop never asks this file about it. PHASE 6, THE COST COLUMNS. HeatRate and VOM of the existing Central Asian thermal fleet are rebuilt by build_costs.py from mappings/thermal_plants.csv, which carries all 70 of those units one by one against the DeCA Thermal PP sheets. 63 are matched to a named DeCA plant and 7 are not, each with its reason in the mapping: two Kazakh residual aggregates that are not plants, the Balkhash Ulken project and Karaganda TPS-2 which DeCA does not carry, Yavan likewise, and Almaty-1 and Fergana where the model and DeCA disagree on the fuel itself. THE HEAT RATE IS TAKEN FROM DeCA WHEREVER A UNIT IS MATCHED, because a stated per-plant efficiency beats a per-technology constant: the 2020 model gave every Kazakh coal CHP the same 11.23 where DeCA separates them from 0.208 at Astana-2, which becomes 16.40, to 0.275 at Pavlodar-3, which becomes 12.42. 15 of the 63 units were already carrying the DeCA value, which is a good sign on the match. Shymkent moves the other way, 11.23 to 6.09, DeCA giving it a combined cycle efficiency of 0.560. THE VOM IS TAKEN ONLY WHERE DeCA DEPARTS FROM ITS OWN DEFAULT. It writes 3.400 $/MWh for 128 of its 136 thermal units, across five countries and every technology at once, which is a filler and not a measurement, and adopting it would flatten the technology spread the 2020 model does carry. Where it does depart, the departure is the information: the old Uzbek steam sets at 9.100, Takhiatash at 3.540, Navoi at 3.500, the combined cycles at 4.250. KAZAKH GAS TRANSPORT LANDS IN THE VOM rather than in pFuelPrice, because it is the one genuinely regional fuel cost in the region and the model carries only two Kazakh gas plants, at opposite ends of it. Zhambyl takes 0.370 $/MMBtu over its own 9.399 MMBtu/MWh and Shymkent 4.998 over 6.093, so their VOM reads 18.9 and 39.2 $/MWh. That looks alarming and is not: the decomposition moved, the total did not, and both plants come out cheaper than before, 67.2 to 50.0 $/MWh at Zhambyl and 64.7 to 59.4 at Shymkent. The step is idempotent, every value it writes being absolute and the VOM baseline always read from the 2020 reference rather than from the file under the pen. RUN ORDER IS build_fleet.py THEN build_costs.py, the second rewriting the file the first produces. PHASE 6, THE CANDIDATE COSTS. HeatRate, Capex, FOMperMW, VOM and Life of the 86 thermal candidates are rebuilt from the Thermal PP Candidates sheet through mappings/thermal_candidates.csv, which says which DeCA line each of the eleven (tech, fuel) pairs of the model reads. 79 rows move and 7 keep their 2020 costs, the coal fired CHPs and the oil fired steam turbines, DeCA carrying neither. THAT SHEET IS A TECHNOLOGY TABLE AND NOT A COUNTRY ONE: the five books state the same numbers to the dollar, so it is read from all five at once and any book that departs is outvoted and the departure printed. One does, TJ pricing new coal at 500,000 $/MW where the other four say 2,500,000, which is a typo and not a Tajik discount. Being a technology table is also what licenses using it in Pakistan and Afghanistan, outside the DeCA perimeter: the 2020 model applied ONE GLOBAL COST SET to all sixteen zones, so holding those two on 2020 while the five move would not preserve a country difference, it would invent one and let the model arbitrage on it. NEW COAL IS READ ON THE Supercritical LINE AND NOT ON THE ONE HEADED Coal, which is the judgement of the step. The Coal line states an efficiency of 0.33 at 2,500,000 $/MW while Supercritical, four rows below it in the same table, states 0.46137 at 2,250,000: cheaper to build, cheaper to run and half again as efficient, so the plain line is dominated by its own neighbour and no planner would ever pick it. The 2020 model already carried 0.42 here, a supercritical class unit. One word in the mapping falls back to the subcritical line. LIFE MOVES WITH THE COSTS BECAUSE IT MUST: main.gms:742 builds the capital recovery factor out of it, so taking a CAPEX without the amortization period stated beside it would annualize the new number on the old horizon. CCGT and gas turbines go from 30 years to 25, coal from 40 to 35, engines from 20 to 25, and nuclear from 40 to 60. WHAT IT COSTS, levelised at a 75 per cent capacity factor and a WACC of 10 per cent, before and after: CCGT 77.8 to 68.9 $/MWh, gas turbine 109.2 to 90.2, gas CHP 119.9 to 104.3, coal 58.9 to 52.6, engines 26.1 to 17.8, nuclear 107.0 to 106.6. EVERY THERMAL CANDIDATE GETS CHEAPER, which is the honest reading of a 2025 cost book against a 2020 one, and nuclear barely moves because its CAPEX rising by a third is cancelled by sixty years to amortize it over and a variable cost that falls from 16.83 to 0.67. Capacity, StYr and BuildLimitperYear are untouched, being the shape of the menu and not its cost, and so is the DeCA Max Capacity column, which is carried in the report and out of the table: it reads like a unit size, 300 MW for a coal or combined cycle block and 1200 for a nuclear one, but DeCA never says so and EPM reads Capacity as a cumulative build limit, so writing 300 there would silently cap all new coal in a country at one block. The fixed cost of the EXISTING units is still the 2020 value, DeCA stating none. PHASE 5, THE NAMED PROJECTS THAT COULD NEVER BE BUILT. Six hydro rows of the 2020 table named a real plant and carried a capacity of 0, and in this table that column is the cumulative build limit, so the model was shown 5.9 GW of Kyrgyz and Tajik hydro and forbidden to build one megawatt of it. Two of them were not even candidates, KAMBARATA-1 and NUREK-2 being written with the existing status, so they also counted as zero standing capacity. Five are now sized from DeCA through mappings/named_candidates.csv, which holds one line per project against the sheet and the row it comes from, 4126 MW in all. KOKEMEREN-1 takes Kokomerenskaya, 360 MW at 4.4667 M$/MW, and KOKEMEREN-2 takes Kokomeren, 912 MW at 1.6206, both from 2035. NARYN takes the whole Upper Naryn cascade, 237.7 MW at 3.0627 from 2035, which is what its name says and what DeCA aggregates; ITS ZONE MOVES FROM KGZ_S TO KGZ_N, DeCA putting every plant of the cascade in the Naryn region, area North, and KGZ_N having had no hydro candidate at all. KAMBARATA-1 takes 1860 MW at 1.5677 from 2032, DeCA calling it Committed where it calls the cascades Candidate; the status is left at 1, which lets the model build it rather than forcing it, turning it into a forced commitment being a scenario switch and not a data fix. DASHTIJUM IS THE ONE TO ARGUE ABOUT. DeCA does not name it: its Tajik candidate list is Fondaryo, Nurobad 1 and 2, Shurob, Yavan, Sanobod and Ayni, plus one generic envelope per region, and the dam on the Panj is not in it. What DeCA does state for uncommitted Khatlon hydro is that envelope, TJ Khatlon HPP, 756 MW at 2.4653 M$/MW from 2035, and Dashtijum sits in Khatlon, which is TAJ_S. So the row now carries the provincial envelope and no longer the dam, which the feasibility literature sizes an order of magnitude larger. The rule for this build is DeCA over 2020 and that is what was applied, but a TTL could as easily restore the project size or drop the row, and the mapping is one line either way. NUREK-2 IS LEFT AT ZERO, deliberately. It is a dead duplicate: the Nurek rehabilitation is already in the table as the NUREK_*_REHAB units that fleet_retirement.csv pairs with the retiring NUREK_1 to 9, and sizing this row too would count the same plant twice. NO DOUBLE COUNTING WITH THE GENERIC MENU. The only generic hydro candidates of the model are in KAZ_N and KAZ_S; KGZ_N, KGZ_S and TAJ_S have none, so nothing competes with the five projects in their own zones. WHAT DeCA CARRIES AND THIS TABLE DOES NOT, reported rather than silently added, the model having no row to put it in: Karakol 33 MW, the third plant of the Suusamyr-Kokomeren cascade; Kulanak 100 MW; the Kazarman cascade 997 MW; about 32 MW of Kyrgyz small hydro; and Nurobad 1 and 2, 920 MW in Tajikistan.</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>PHASE 6, WHAT THE HEAT RATE REBUILD EXPOSES. DeCA states the ELECTRICAL efficiency of a plant, and for a CHP that is only part of the story: Astana-2 at 0.208 sends most of its fuel to district heat, so charging all of it to electricity at 16.40 MMBtu/MWh over-prices the unit, and the flat 11.23 of the 2020 model was implicitly crediting the heat. EPM carries no heat, so the honest repair is not a softer heat rate but a winter must-run. PHASE 7 LOOKED FOR THAT LEVER AND IT IS NOT THERE: MinLimitShare is a dead column in this version, read by no equation of base.gms or main.gms, and the real must-run switch is MinGenCommitment, which base.gms:847 guards with fDispatchMode. It therefore binds in an hourly dispatch run and NOT in the expansion, which is what this model is. So the Kazakh CHPs stay too far down the merit order for now, and the two honest ways out are both later: run the dispatch of phase 8 with MinGenCommitment on, or credit the CHPs for their heat inside the heat rate itself, which is a phase 9 assumption and not a repair. PHASE 6, WHAT IS NOT DONE. FOMperMW of the EXISTING units is still the 2020 value everywhere. DeCA states no fixed cost for an existing unit at all, only for its candidates, and putting a candidate figure on a fifty year old CHP would be worse than leaving it. A NEW KAZAKH GAS UNIT PAYS NO FUEL TRANSPORT WHERE AN EXISTING ONE DOES, and that asymmetry is the one thing the candidate step leaves crooked. Kazakh gas transport is regional, 0 on the Atyrau fields to 13.3 at the end of the pipeline, so it sits in the VOM of the two existing plants rather than in the price; a candidate has no site, so it pays the molecule alone and comes out systematically cheaper to fuel than the fleet it competes with. The capacity weighted national mean is 3.851 $/MMBtu, some 21 $/MWh on a combined cycle, which is not a rounding error. The repair is either a zone mean adder on the Kazakh gas candidates or siting them, and it wants the Zones_Regions sheet. THERMAL CANDIDATES CARRY NO CAPEX TRAJECTORY: only solar, wind and batteries have one, so a 2025 combined cycle cost is charged unchanged in 2050. That is defensible for mature thermal plant and it is what DeCA states, but it should be said out loud rather than left as a silent flat line. THE DeCA CANDIDATE MENU IS WIDER THAN THE MODEL USES. CCGT with CCS, coal with CCS, ultrasupercritical coal, CCGT on biogas and the dual gas/hydrogen machine are all priced in the same sheet and none of them exists as a candidate in this model. They are the natural furniture of a decarbonization scenario in phase 9, alongside the CCS capture costs the KZ book carries region by region, 13.32 to 19.32 $/tCO2. PHASE 5, what is left: the existing fleet against DeCA. Its Thermal PP sheets carry 136 units and 51.9 GW over the five countries, where this table has 31.5 GW of Central Asian plant of every kind. Whole plants are missing: the 598 MW of Tajik thermal, Dushanbe-1 and Dushanbe-2, sits here at zero capacity and retired; Bishkek is 666 MW here against 812 MW in DeCA; Turkmenistan is 5.8 GW here against 7.7 GW. The named hydro candidates stuck at Capacity 0 are the other half of it: NARYN, KOKEMEREN-1 and 2, DASHTIJUM, against a DeCA pipeline that carries Rogun at 3380 MW by 2033, Kambarata-1 at 1860, Kambarata-2 at 240, Kulanak at 100, Pskem at 404, Mullalak at 240, an uprating of Nurek of 385 and of Kayrakum of 48. Those are project decisions, not a rule, so they go one by one in a mapping of their own. DeCA also caps its own solar and wind candidates by region, Max. Capacity (MW) in Renewable PP Candidates. That is a resource limit and not a connection rate, and it is not used here because it is stated per oblast and not per model zone.</t>
+          <t>PHASE 6, WHAT THE HEAT RATE REBUILD EXPOSES. DeCA states the ELECTRICAL efficiency of a plant, and for a CHP that is only part of the story: Astana-2 at 0.208 sends most of its fuel to district heat, so charging all of it to electricity at 16.40 MMBtu/MWh over-prices the unit, and the flat 11.23 of the 2020 model was implicitly crediting the heat. EPM carries no heat, so the honest repair is not a softer heat rate but a winter must-run. PHASE 7 LOOKED FOR THAT LEVER AND IT IS NOT THERE: MinLimitShare is a dead column in this version, read by no equation of base.gms or main.gms, and the real must-run switch is MinGenCommitment, which base.gms:847 guards with fDispatchMode. It therefore binds in an hourly dispatch run and NOT in the expansion, which is what this model is. So the Kazakh CHPs stay too far down the merit order for now, and the two honest ways out are both later: run the dispatch of phase 8 with MinGenCommitment on, or credit the CHPs for their heat inside the heat rate itself, which is a phase 9 assumption and not a repair. PHASE 6, WHAT IS NOT DONE. FOMperMW of the EXISTING units is still the 2020 value everywhere. DeCA states no fixed cost for an existing unit at all, only for its candidates, and putting a candidate figure on a fifty year old CHP would be worse than leaving it. A NEW KAZAKH GAS UNIT PAYS NO FUEL TRANSPORT WHERE AN EXISTING ONE DOES, and that asymmetry is the one thing the candidate step leaves crooked. Kazakh gas transport is regional, 0 on the Atyrau fields to 13.3 at the end of the pipeline, so it sits in the VOM of the two existing plants rather than in the price; a candidate has no site, so it pays the molecule alone and comes out systematically cheaper to fuel than the fleet it competes with. The capacity weighted national mean is 3.851 $/MMBtu, some 21 $/MWh on a combined cycle, which is not a rounding error. The repair is either a zone mean adder on the Kazakh gas candidates or siting them, and it wants the Zones_Regions sheet. THERMAL CANDIDATES CARRY NO CAPEX TRAJECTORY: only solar, wind and batteries have one, so a 2025 combined cycle cost is charged unchanged in 2050. That is defensible for mature thermal plant and it is what DeCA states, but it should be said out loud rather than left as a silent flat line. THE DeCA CANDIDATE MENU IS WIDER THAN THE MODEL USES. CCGT with CCS, coal with CCS, ultrasupercritical coal, CCGT on biogas and the dual gas/hydrogen machine are all priced in the same sheet and none of them exists as a candidate in this model. They are the natural furniture of a decarbonization scenario in phase 9, alongside the CCS capture costs the KZ book carries region by region, 13.32 to 19.32 $/tCO2. PHASE 5, what is left: the existing fleet against DeCA. Its Thermal PP sheets carry 136 units and 51.9 GW over the five countries, where this table has 31.5 GW of Central Asian plant of every kind. Whole plants are missing: the 598 MW of Tajik thermal, Dushanbe-1 and Dushanbe-2, sits here at zero capacity and retired; Bishkek is 666 MW here against 812 MW in DeCA; Turkmenistan is 5.8 GW here against 7.7 GW. Those three are still open and are a fleet question, to be put to the TSOs with the rest of the fleet data request. THE OTHER HALF OF IT IS NOW CLOSED. The named hydro candidates stuck at Capacity 0, NARYN, KOKEMEREN-1 and 2, KAMBARATA-1 and DASHTIJUM, are sized from DeCA through mappings/named_candidates.csv, 4126 MW, and the reasoning is written out under pGenDataInput. What the DeCA pipeline carries and this model still has no row for: Kambarata-2 at 240 MW, Kulanak at 100, Mullalak at 240, an uprating of Kayrakum of 48, the Kazarman cascade at 997 and Nurobad 1 and 2 at 920. Rogun at 3380 MW by 2033, Pskem at 404 and the Nurek uprating of 385 are already in the table under their own names. DeCA also caps its own solar and wind candidates by region, Max. Capacity (MW) in Renewable PP Candidates. That is a resource limit and not a connection rate, and it is not used here because it is stated per oblast and not per model zone.</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1499,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>seasonal availability by plant, 403 units x 4 seasons</t>
+          <t>seasonal availability by plant, 419 units x 5 seasons</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -1530,12 +1538,12 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Rebuilt by build_hydro.py from data_build/mappings/hydro_plants.csv, which carries the 134 hydro units of the model one by one, and from data_build/mappings/seasons_months.csv, which says which months each season holds. 45 units out of 134 now rest on DeCA: 11 take its monthly profile directly, the 5 Kazakh plants whose profile is plant-specific and the Pskem and Upper Naryn candidates; 34 keep the 2020 seasonal shape, which describes the reservoir operation, and have their level brought back to the DeCA capacity factor. THE 2020 MODEL WAS OPTIMISTIC ON CENTRAL ASIAN HYDRO: it allowed Toktogul 1.64 times, Uch-Kurgan 1.71 times and Charvak 1.75 times the energy DeCA gives them. The seasonal availability is the water constraint of the model, base.gms:806 caps the energy of a season with it, so that gap was a gift of water. Kazakhstan runs the other way, DeCA being more generous than 2020 on Bukhtarma and Ust-Kamenogorsk. The 89 remaining units keep their 2020 values, each with its reason in the mapping. The peak column of the 2020 model is gone with the peak season, see pHours. It carried a convention, 267 plants out of 403 at Q5 = 1.0 and 313 valued above their Q1, that is firm capacity at the peak. PHASE 7 SETTLED WHAT BECOMES OF IT: the convention is not restored, the credit stays at the real 0.85, and the consequence is measured in pPlanningReserveMarginZone. PHASE 7 ALSO CLOSED A HOLE THIS BUILD HAD OPENED ITSELF. The 2020 table covered its 403 units exactly; the 16 solar and wind candidates added from 2031 had no line, and a generator absent from pAvailability is not defaulted to one, it is READ AS ZERO, base.gms:812 then writing vPwrOut = 0 over the whole horizon. Solar was rescued by the generic fallback of the model, which carries a PV/Solar line; wind was not, its technology being WT here and OnshoreWind there, so EIGHT WIND CANDIDATES COULD BE BUILT AND WOULD HAVE PRODUCED NOTHING. build_hydro.py now completes the table against the fleet, giving a missing unit what its own technology and fuel carry elsewhere by majority, and refusing to guess on a tie or on a pair it has never seen. RUN ORDER IS build_fleet.py THEN build_hydro.py.</t>
+          <t>Rebuilt by build_hydro.py from data_build/mappings/hydro_plants.csv, which carries the 134 hydro units of the model one by one, and from data_build/mappings/seasons_months.csv, which says which months each season holds. 45 units out of 134 now rest on DeCA: 11 take its monthly profile directly, the 5 Kazakh plants whose profile is plant-specific and the Pskem and Upper Naryn candidates; 34 keep the 2020 seasonal shape, which describes the reservoir operation, and have their level brought back to the DeCA capacity factor. THE 2020 MODEL WAS OPTIMISTIC ON CENTRAL ASIAN HYDRO: it allowed Toktogul 1.64 times, Uch-Kurgan 1.71 times and Charvak 1.75 times the energy DeCA gives them. The seasonal availability is the water constraint of the model, base.gms:806 caps the energy of a season with it, so that gap was a gift of water. Kazakhstan runs the other way, DeCA being more generous than 2020 on Bukhtarma and Ust-Kamenogorsk. The 89 remaining units keep their 2020 values, each with its reason in the mapping. The peak column of the 2020 model is gone with the peak season, see pHours. It carried a convention, 267 plants out of 403 at Q5 = 1.0 and 313 valued above their Q1, that is firm capacity at the peak. PHASE 7 SETTLED WHAT BECOMES OF IT: the convention is not restored, the credit stays at the real 0.85, and the consequence is measured in pPlanningReserveMarginZone. PHASE 5 REBUILT THE THERMAL SIDE OF THIS TABLE, and it asks a different question of a plant that exists than of one that does not. 156 of the 228 thermal units moved; the other 72 are Pakistani and Afghan and deliberately did not. A CANDIDATE GETS 0.90, the pair rate of data_build/mappings/availability.csv over the ten (tech, fuel) pairs it states. That is DeCA's own arithmetic for a plant in working order, 0.05 forced outage and 0.05 scheduled, against the 0.85 the 2020 model wrote without a source. 86 units. A plant not yet built has no history of neglect, so the technology rate is the whole of what can be said about it. Three of those 86 were not even at 0.85 and the same pass corrects them: KGZ_N_ST_Coal_cand and KGZ_S_ST_Coal_cand sat at 1.00, a fifth of a year of outage missing on 15 GW of candidate coal, and NEPS_HERAT_ST_Coal_cand had 0.0328654 in Q1 and 0.85 in the other four, which is a typing accident and not an assumption. AN EXISTING UNIT GETS ITS OWN DERATING, which is the correction phase 5 owes the first pass of this table. DeCA states an Available capacity beside the Installed capacity of every plant it carries, and the gap between the two is that plant's condition, stated unit by unit; the first pass wrote a flat 0.90 and threw that column away. 70 units now carry it, 63 read off their own book plant and 7 at the median of the fleet DeCA does describe, and the spread is the point: 0.3857 for the three Turkmenbashi sets, 180 MW available out of 420, against 0.90 for the second Dushanbe set, 360 out of 400. A flat rate said a Soviet CHP nobody has maintained since 1991 and a 2018 combined cycle were the same machine. 17 of the 63 sit below 0.60. The ratio is carried and not the absolute capacity, because 17 DeCA plants map to several rows of this model at once and a row-by-row capacity rewrite would invent or destroy gigawatts; the Capacity column is left to the fleet data request, see pGenDataInput. BISHKEK_CHP_2023 IS THE ROW THAT SETTLED THE METHOD. It sat at 0.308528 in the 2020 table, a real derating written in the availability column rather than in the capacity one, and the flat 0.90 of the first pass would have taken the plant from 205 MW effective to 599 on the strength of nothing. DeCA derates Bishkek itself, 420 MW available out of 812, so the number is 0.4655 and the plant reads 310 MW effective on the 666 MW this model carries. The 2020 team's instinct was right and its arithmetic was undocumented; DeCA documents it. NOTHING MOVES OUTSIDE THE FIVE COUNTRIES. The 41 Pakistani and 15 Afghan thermal units, plus the 16 the completion pass added, keep their 2020 availability, because the rule of this build is that DeCA wins where DeCA and 2020 DISAGREE and on a Pakistani plant DeCA says nothing at all. Carrying the Central Asian median south would invent a number for a fleet no source in hand describes, and invent it in the one place it moves the answer: Pakistan is the demand this study asks whether Central Asian power is worth exporting to, and derating it is the assumption that makes the interconnector look good. The median is written into extracted/thermal_derating.csv all the same, applied only to the 7 units inside the perimeter that the mapping could not match to a book plant, where the country is described and only the plant is not. HYDRO, SOLAR, WIND, IMPORTS AND STORAGE ARE UNTOUCHED by all of it: for them the column is the resource and not an outage. PHASE 7 ALSO CLOSED A HOLE THIS BUILD HAD OPENED ITSELF. The 2020 table covered its 403 units exactly; the 16 solar and wind candidates added from 2031 had no line, and a generator absent from pAvailability is not defaulted to one, it is READ AS ZERO, base.gms:812 then writing vPwrOut = 0 over the whole horizon. Solar was rescued by the generic fallback of the model, which carries a PV/Solar line; wind was not, its technology being WT here and OnshoreWind there, so EIGHT WIND CANDIDATES COULD BE BUILT AND WOULD HAVE PRODUCED NOTHING. build_hydro.py now completes the table against the fleet, giving a missing unit what its own technology and fuel carry elsewhere by majority, and refusing to guess on a tie or on a pair it has never seen. RUN ORDER IS build_fleet.py THEN build_hydro.py.</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>1. Kambarata-2, Rogun and Shardara have a DeCA yearly production above their own capacity, the production of the full project against one unit, so their level could not be used. 2. Farhad is carried at 311 MW here against 126 MW in DeCA, and its DeCA production gives an annual 0.02: the plant identity has to be settled in phase 5. 3. Pakistan, 41 units, and Afghanistan, 15 units, are outside the DeCA perimeter and still rest on the 2020 model: they need the NTDC IGCEP and the DABS fleet. 4. The dry and wet hydrologies are in the same sheets, read with --scenario, and are waiting for the scenario phase.</t>
+          <t>0. The derating of an existing unit is a book figure and not a measurement, and the 7 unmatched Central Asian units rest on a median. Per-unit forced and scheduled outage rates from the TSOs would replace both, and the Pakistani and Afghan fleet needs its own before anything can be said about its condition. 1. Kambarata-2, Rogun and Shardara have a DeCA yearly production above their own capacity, the production of the full project against one unit, so their level could not be used. 2. Farhad is carried at 311 MW here against 126 MW in DeCA, and its DeCA production gives an annual 0.02: the plant identity has to be settled in phase 5. 3. Pakistan, 41 units, and Afghanistan, 15 units, are outside the DeCA perimeter and still rest on the 2020 model: they need the NTDC IGCEP and the DABS fleet. 4. The dry and wet hydrologies are in the same sheets, read with --scenario, and are waiting for the scenario phase.</t>
         </is>
       </c>
     </row>
@@ -1557,25 +1565,21 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>default availability (z,tech,fuel)</t>
+          <t>default availability (z,tech,fuel), empty by decision, header fixed</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>DECIDE</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -1593,15 +1597,19 @@
           <t>Thermal PP, columns Forced Outage Rate / Scheduled Outage Rate</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Empty, and it changes nothing today: all 403 units of the fleet carry a line of their own in pAvailability, and this table only speaks for a unit that has none. It will start to matter with the candidates of phase 5. CORRECTION to an earlier reading of the sources: DeCA DOES give outage rates. It carries 0.05 forced and 0.05 scheduled, 0.10 unavailable in all, for every thermal plant of the five countries, 136 units, with no distinction of country or technology. That is a convention, not a measurement, so adopting it would only trade the 0.85 of the 2020 model for a more generous 0.90.</t>
+          <t>PHASE 5 TOOK THE 0.90 OF DeCA over the 0.85 of the 2020 model, following the rule set for this build that DeCA wins where the two disagree. DeCA carries 0.05 forced and 0.05 scheduled, 0.10 unavailable in all, for every thermal plant of the five countries it covers, with no distinction of country or technology. The 2020 model wrote 0.85 everywhere and named no source. Neither is a measurement; one has a document behind it. THAT RATE IS THE ANSWER FOR A PLANT THAT DOES NOT EXIST YET, and only for that. An existing unit is written at its own derating instead, DeCA stating an Available capacity beside the Installed one plant by plant, which is why this table could never have carried the decision even if the model let it: a technology rate cannot say that Turkmenbashi runs at 0.39 and the second Dushanbe set at 0.90. See pAvailabilityCustom, where both live. THE DECISION LANDS ON pAvailabilityCustom AND NOT HERE, which is worth stating because this file is the one that looks like it should carry it. The chain is in input_treatment.py: the custom table is read into pAvailabilityInput(g,q), expanded over the years into pAvailability(g,y,q), and only then is this default reached for, to fill the units the custom table left out. It leaves none out: 419 units, 419 lines. So this table is inert whatever it holds. IT STAYS EMPTY, AND THAT IS A DECISION THE MODEL FORCED. The build first filled it with the 98 (zone, tech, fuel) triples whose availability is a technology property, so that a generator added later without a line of its own would land on a stated number rather than on zero, and the run refused to compile: input_treatment.py:1403 skips the table when it is empty and input_treatment.py:1426 aborts when it is present and does not cover EVERY (zone, tech, fuel) of pGenDataInput. It is all or nothing. Covering everything would mean writing a default availability for hydro, solar, wind and imports, and for those the column is not an outage rate but the resource itself, the seasonal water of a reservoir or a profile that already carries the weather. A technology-level number must not stand behind plant-level data, so the table is left empty and the partial fill is kept out. build_hydro.py still writes extracted/pAvailabilityDefault.csv, which is the table that would be used if the day comes when every pair can honestly be given one. WHAT DID CHANGE HERE IS THE HEADER. It read z,tech,fuel,Q1,Q2, the two seasons of data_test, inherited when the folder was set up. This model has five, and the header carries the index of the parameter.</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>PHASE 5, with the candidates: either keep the 0.85 of the 2020 model, or take the 0.90 of DeCA, and say which. A real outage rate would have to come from the TSOs.</t>
+          <t>A measured outage rate would have to come from the TSOs, unit by unit, and would replace both the 0.90 of a candidate and the book derating of an existing unit. Ask for it with the fleet data request.</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1988,12 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>PHASE 5 done. The table was empty, in a model that runs to 2050. It now carries one four-hour battery candidate per Central Asian zone, eight of them, open from 2028. The cost is read, not assumed. DeCA prices a battery at 2, 4, 6 and 8 hours and those four prices are exactly linear in duration in every year from 2023 to 2060, so the slope is the cost of an hour of energy and the intercept is the cost of the power: 247,638 $/MW and 202.3 $/kWh in 2026, falling to 198,754 $/MW and 118.2 $/kWh in 2050. build_fleet.py re-checks that linearity and refuses to write anything if a later version of the book breaks it. Four hours is a choice, and it is the one that makes EPM exact: EPM applies a single CAPEX multiplier to both the power and the energy part of a battery, and those two decline at different rates in DeCA. At a fixed duration the multiplier is exact on the total, which is what is being bought. The perimeter is the five DeCA countries, mappings/country_book.csv. Pakistan and Afghanistan keep no storage, as in the 2020 model. DeCA gives no round-trip efficiency and no operating life for storage: 0.9 and 20 years are the EPM reference values, data_test.</t>
+          <t>PHASE 5 done. The table was empty, in a model that runs to 2050. It now carries one four-hour battery candidate per Central Asian zone, eight of them, open from 2028. The cost is read, not assumed. DeCA prices a battery at 2, 4, 6 and 8 hours and those four prices are exactly linear in duration in every year from 2023 to 2060, so the slope is the cost of an hour of energy and the intercept is the cost of the power: 247,638 $/MW and 202.3 $/kWh in 2026, falling to 198,754 $/MW and 118.2 $/kWh in 2050. build_fleet.py re-checks that linearity and refuses to write anything if a later version of the book breaks it. Four hours is a choice, and it is the one that makes EPM exact: EPM applies a single CAPEX multiplier to both the power and the energy part of a battery, and those two decline at different rates in DeCA. At a fixed duration the multiplier is exact on the total, which is what is being bought. The perimeter is the five DeCA countries, mappings/country_book.csv. Pakistan and Afghanistan keep no storage, as in the 2020 model. DeCA gives no round-trip efficiency and no operating life for storage: 0.9 and 20 years are the EPM reference values, data_test. PHASE 5 SWITCHED IT ON. fEnableStorage was 0, and under a 0 base.gms generates none of the storage balance, charge and state-of-charge equations, so these eight rows were read into the model and then never entered one: the candidate existed and could not be built. The flag is now set by the build, see pSettings. The chronology it was waiting on arrived with phase 3, 24 consecutive hours on each of three representative days per season, which is what a four-hour battery needs in order to have something to arbitrage.</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Storage only earns its keep once the model has intra-day chronology. The candidate is in place so that phase 8 has something to switch on, but nothing will be built until pHours carries real hours. Pumped storage is a separate question: DeCA carries Hodjikent PSH-2 in Uzbekistan, which sits in pGenDataInput as a hydro candidate rather than here.</t>
+          <t>Pumped storage is a separate question: DeCA carries Hodjikent PSH-2 in Uzbekistan, which sits in pGenDataInput as a hydro candidate rather than here.</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3607,7 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>11 done | 13 partial | 17 to do | 7 out of scope</t>
+          <t>11 done | 15 partial | 15 to do | 7 out of scope</t>
         </is>
       </c>
     </row>

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -932,12 +932,12 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>q = 4 quarters, the 5th peak season is removed. It was not a structure but a patch: the reserve constraint takes a smax over all blocks (base.gms:991) and requires no dedicated season. Q5 only served to give that smax a block short enough to see the true peak, for want of representative days (d=1 in the 2020 model). THE SEASONS ARE NOT CALENDAR QUARTERS, and the months behind them are written down in data_build/mappings/seasons_months.csv, which is the single place the year is cut: Q1 December to February, Q2 March and April, Q3 May and June, Q5 July to September, Q4 October and November. The first cut was read off the 2020 durations, Q1 and the peak block together 2180 h that is 90.8 days, Q2 1464 h exactly 61 days, Q3 3652 h that is 152.2 days, Q4 1464 h exactly 61 days, and it lands on 8760 h to the hour. Every season-indexed resource is built against that mapping. PHASE 4 SPLIT THE SUMMER IN TWO, May-June against July-September. One season of five months held two different things at once: the irrigation release, where the reservoirs open for the fields downstream and the hydro runs whether the load calls for it or not, and the cooling peak, where it is the load that is high. A single season had to pick one, and it picked the peak: its representative days were 24 July and two medians drawn from a five-month pool. They are now 27 June for Q3 and 24 July for Q5, and May-June has its own shape at last. THE NAME Q5 IS RECYCLED, not restored. The 2020 model had a Q5 too and it was the 130 h peak block, not a season. Nothing of that block is here. The seasons mapping carries a legacy column saying which 2020 season each of ours draws its inherited shapes from, and ours sends both halves of the summer to the 2020 Q3; without it build_vre matched on the name alone and dressed July-September in a winter peak block, which input_verification.py caught as a capacity factor of 1.24 on KAZ_N solar. NO SEASON IS NAMED ANYWHERE ELSE. The CASA-1000 contract window and the seasonal corridor to Afghanistan are written in months in their own mappings and resolved against this file, so the year can be re-cut again without touching them; a window that would take part of a season stops the build rather than being guessed at. PHASE 8 REBUILT IT, and this is the file that defines the sets q, d and t for the whole model: main.gms:214 reads pHours(q&lt;,d&lt;,t&lt;), so every other hourly resource follows whatever shape is written here. It is now four seasons by three representative days by twenty four chronological hours, the canonical EPM shape that epm/input/data_test also carries, and each cell holds THE NUMBER OF DAYS the representative day stands for, repeated over its 24 hours, summing to 8760. THE PEAK REPRESENTATIVE DAY REPLACES THE OLD PEAK SEASON. In each season d1 is a calendar day and weighs one day, which is what base.gms needs when it takes an smax over (q,d,t) for the reserve. The day chosen is the one that stresses the most zones at once, each zone counted against its own maximum rather than in megawatts, because a sum in megawatts is decided by Kazakhstan and Uzbekistan alone and the reserve of EPM is written per zone. The five days are 12 December, 1 March, 27 June, 24 July and 21 November. THE OTHER TWO ARE REAL DAYS AS WELL, AND THEIR WEIGHTS ARE SOLVED, NOT COUNTED. The rest of the season is split in two by daily energy and each half is represented by its medoid, the real day closest to the average of that half. A medoid is the most typical day of its group and not the day carrying its average energy, so the two weights are then solved rather than taken from the sizes of the groups: two unknowns, two equations, the days of the season and the energy of the season, rounded to whole days at the end because input_verification.py compares the sum of this table to 8760 with no tolerance at all and refuses a block of zero hours. The weights that come out are 53 and 36 days for Q1, 28 and 32 for Q2, 31 and 29 for Q3, 42 and 49 for Q5, 29 and 31 for Q4. WHY NOT THE MEAN OF EACH GROUP, WHICH IS WHAT THIS STEP DID FIRST. Averaging seventy-six days flattens every trough that does not fall at the same hour twice, and the model reads that flattening as a baseload the system does not have. See pDemandProfile, which carries the measurement and the table of it. The season durations are 90 / 61 / 61 / 92 / 61 days, and every seasonal resource is rebuilt from them: pDemandProfile, pVREProfile, pAvailability, pTransferLimit, pContractedTradeFlag and pContractedTradeEnergy.</t>
+          <t>q = 4 quarters, the 5th peak season is removed. It was not a structure but a patch: the reserve constraint takes a smax over all blocks (base.gms:991) and requires no dedicated season. Q5 only served to give that smax a block short enough to see the true peak, for want of representative days (d=1 in the 2020 model). THE SEASONS ARE NOT CALENDAR QUARTERS, and the months behind them are written down in data_build/mappings/seasons_months.csv, which is the single place the year is cut: Q1 December to February, Q2 March and April, Q3a May and June, Q3b July to September, Q4 October and November. The first cut was read off the 2020 durations, Q1 and the peak block together 2180 h that is 90.8 days, Q2 1464 h exactly 61 days, Q3 3652 h that is 152.2 days, Q4 1464 h exactly 61 days, and it lands on 8760 h to the hour. Every season-indexed resource is built against that mapping. PHASE 4 SPLIT THE SUMMER IN TWO, May-June against July-September. One season of five months held two different things at once: the irrigation release, where the reservoirs open for the fields downstream and the hydro runs whether the load calls for it or not, and the cooling peak, where it is the load that is high. A single season had to pick one, and it picked the peak: its representative days were 24 July and two medians drawn from a five-month pool. They are now 27 June for Q3a and 24 July for Q3b, and May-June has its own shape at last. THE TWO HALVES ARE NAMED Q3a AND Q3b, which is the whole of what the naming means: they are the season the 2020 model held as one, cut in two. An earlier pass called the second half Q5, on the reasoning that the name was free once the 2020 peak block was removed; free it was, but a reader meeting Q5 between Q3 and Q4 had to be told the story before the set made sense. Q1, Q2 and Q4 keep both their names and their months, so no label of this model has ever meant two different parts of the year. The seasons mapping carries a legacy column saying which 2020 season each of ours draws its inherited shapes from, and ours sends both halves of the summer to the 2020 Q3; without it build_vre matched on the name alone and dressed July-September in a winter peak block, which input_verification.py caught as a capacity factor of 1.24 on KAZ_N solar. NO SEASON IS NAMED ANYWHERE ELSE. The CASA-1000 contract window and the seasonal corridor to Afghanistan are written in months in their own mappings and resolved against this file, so the year can be re-cut again without touching them; a window that would take part of a season stops the build rather than being guessed at. PHASE 8 REBUILT IT, and this is the file that defines the sets q, d and t for the whole model: main.gms:214 reads pHours(q&lt;,d&lt;,t&lt;), so every other hourly resource follows whatever shape is written here. It is now four seasons by three representative days by twenty four chronological hours, the canonical EPM shape that epm/input/data_test also carries, and each cell holds THE NUMBER OF DAYS the representative day stands for, repeated over its 24 hours, summing to 8760. THE PEAK REPRESENTATIVE DAY REPLACES THE OLD PEAK SEASON. In each season d1 is a calendar day and weighs one day, which is what base.gms needs when it takes an smax over (q,d,t) for the reserve. The day chosen is the one that stresses the most zones at once, each zone counted against its own maximum rather than in megawatts, because a sum in megawatts is decided by Kazakhstan and Uzbekistan alone and the reserve of EPM is written per zone. The five days are 12 December, 1 March, 27 June, 24 July and 21 November. THE OTHER TWO ARE REAL DAYS AS WELL, AND THEIR WEIGHTS ARE SOLVED, NOT COUNTED. The rest of the season is split in two by daily energy and each half is represented by its medoid, the real day closest to the average of that half. A medoid is the most typical day of its group and not the day carrying its average energy, so the two weights are then solved rather than taken from the sizes of the groups: two unknowns, two equations, the days of the season and the energy of the season, rounded to whole days at the end because input_verification.py compares the sum of this table to 8760 with no tolerance at all and refuses a block of zero hours. The weights that come out are 53 and 36 days for Q1, 28 and 32 for Q2, 31 and 29 for Q3a, 42 and 49 for Q3b, 29 and 31 for Q4. WHY NOT THE MEAN OF EACH GROUP, WHICH IS WHAT THIS STEP DID FIRST. Averaging seventy-six days flattens every trough that does not fall at the same hour twice, and the model reads that flattening as a baseload the system does not have. See pDemandProfile, which carries the measurement and the table of it. The season durations are 90 / 61 / 61 / 92 / 61 days, and every seasonal resource is rebuilt from them: pDemandProfile, pVREProfile, pAvailability, pTransferLimit, pContractedTradeFlag and pContractedTradeEnergy.</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>THE NUMBER OF REPRESENTATIVE DAYS IS ONE ARGUMENT, --days, and three is a starting point rather than a result: the model went from 35 blocks in 2020 to 288 here, and if the solve turns out to be comfortable the count should go up, the days being grouped by demand alone today and therefore carrying no renewable variability. See pVREProfile, where the same limit bites harder. THE WEIGHT SOLVER IS EXACT FOR TWO GROUPS AND LEAST SQUARES BEYOND, so raising --days above three leaves a residual on the energy of the season. It is reported in the demand test and it is small; it would be removed by adding a third condition, the peak of each group, rather than by another solver. PHASE 4 SPLIT THE SUMMER: Q3 is May-June, the irrigation release, and Q5 is July-September, the cooling peak. 360 blocks now instead of 288. It shows in the representative days, which no longer share one: Q3 peaks on 27 June and Q5 on 24 July, where the single five-month season kept only 24 July and drowned May-June in two median days. The contract window did not move, it is written in months now and spans the two seasons.</t>
+          <t>THE NUMBER OF REPRESENTATIVE DAYS IS ONE ARGUMENT, --days, and three is a starting point rather than a result: the model went from 35 blocks in 2020 to 288 here, and if the solve turns out to be comfortable the count should go up, the days being grouped by demand alone today and therefore carrying no renewable variability. See pVREProfile, where the same limit bites harder. THE WEIGHT SOLVER IS EXACT FOR TWO GROUPS AND LEAST SQUARES BEYOND, so raising --days above three leaves a residual on the energy of the season. It is reported in the demand test and it is small; it would be removed by adding a third condition, the peak of each group, rather than by another solver. PHASE 4 SPLIT THE SUMMER: Q3a is May-June, the irrigation release, and Q3b is July-September, the cooling peak. 360 blocks now instead of 288. It shows in the representative days, which no longer share one: Q3a peaks on 27 June and Q3b on 24 July, where the single five-month season kept only 24 July and drowned May-June in two median days. The contract window did not move, it is written in months now and spans the two seasons.</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>PHASE 8 BUILT IT FROM TWO SOURCES BECAUSE NEITHER GIVES BOTH HALVES. base.gms:812 writes the output of every solar and wind unit as this profile times the availability times the capacity, so the table is the whole renewable production, in level as much as in shape. DeCA GIVES THE LEVEL AND NOT THE SHAPE: RenewableProfile states a monthly utilization factor per plant and no hour of the day. Its own header says so, in a line the authors left for themselves, "Hourly profiles are also needed for all WPP and SPP power plants". THE 2020 MODEL GIVES THE SHAPE and a level five years old. So the day shape comes from the 2020 profile, normalised to a mean of one, and is multiplied by the DeCA seasonal factor, the month length weighted mean over the months of the season and over the plants mappings/vre_profiles.csv selects. THE FACTOR IS A COUNTRY MEAN over every plant of the technology, existing and candidate, high yield and low yield sites together, because the five books name no zone for their existing plants. That is an average site, which is what a generic candidate is. Eighty of the 160 seasonal factors move; the Afghan and Pakistani zones keep their 2020 level, being outside the DeCA perimeter. WHAT MOVES: mean solar capacity factor 0.174 to 0.169, mean wind 0.333 to 0.369. Solar loses most in winter, KAZ_N Q1 going from 0.144 to 0.089, which matters in a system that peaks in December. THE 2020 SHAPE IS DRAWN BY MONTHS, NOT BY NAME, since phase 4 split the summer. Both halves take the 2020 Q3 day and are rescaled to their own DeCA factor, 0.208 for KAZ_N solar in Q3 against 0.207 in Q5. Matching on the name instead handed July-September the 2020 peak block, a 130 h winter artefact, and produced a capacity factor of 1.24; the column that says which season feeds which lives in mappings/seasons_months.csv. TWO TRAPS THE MAPPING STEPS AROUND. The Tajik book labels its own regions with a KZ prefix, Khatlon and Sougd and Gorno-Badakhshan all reading "KZ ...", so the selection keys on the workbook and not on the name. And one Kazakh SOLAR plant is named Arm Wind: the exclude column of the mapping settles it on the _SP suffix, and the builder refuses outright any row two technologies claim at once.</t>
+          <t>PHASE 8 BUILT IT FROM TWO SOURCES BECAUSE NEITHER GIVES BOTH HALVES. base.gms:812 writes the output of every solar and wind unit as this profile times the availability times the capacity, so the table is the whole renewable production, in level as much as in shape. DeCA GIVES THE LEVEL AND NOT THE SHAPE: RenewableProfile states a monthly utilization factor per plant and no hour of the day. Its own header says so, in a line the authors left for themselves, "Hourly profiles are also needed for all WPP and SPP power plants". THE 2020 MODEL GIVES THE SHAPE and a level five years old. So the day shape comes from the 2020 profile, normalised to a mean of one, and is multiplied by the DeCA seasonal factor, the month length weighted mean over the months of the season and over the plants mappings/vre_profiles.csv selects. THE FACTOR IS A COUNTRY MEAN over every plant of the technology, existing and candidate, high yield and low yield sites together, because the five books name no zone for their existing plants. That is an average site, which is what a generic candidate is. Eighty of the 160 seasonal factors move; the Afghan and Pakistani zones keep their 2020 level, being outside the DeCA perimeter. WHAT MOVES: mean solar capacity factor 0.174 to 0.169, mean wind 0.333 to 0.369. Solar loses most in winter, KAZ_N Q1 going from 0.144 to 0.089, which matters in a system that peaks in December. THE 2020 SHAPE IS DRAWN BY MONTHS, NOT BY NAME, since phase 4 split the summer. Both halves take the 2020 Q3 day and are rescaled to their own DeCA factor, 0.208 for KAZ_N solar in Q3a against 0.207 in Q3b. Matching on the name instead handed July-September the 2020 peak block, a 130 h winter artefact, and produced a capacity factor of 1.24; the column that says which season feeds which lives in mappings/seasons_months.csv. TWO TRAPS THE MAPPING STEPS AROUND. The Tajik book labels its own regions with a KZ prefix, Khatlon and Sougd and Gorno-Badakhshan all reading "KZ ...", so the selection keys on the workbook and not on the name. And one Kazakh SOLAR plant is named Arm Wind: the exclude column of the mapping settles it on the _SP suffix, and the builder refuses outright any row two technologies claim at once.</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Rebuilt from data_build/mappings/corridors.csv, which carries the 42 directed corridors with their anchor years and, for each, the source it rests on. Three corrections against the 2020 model. Turkmenistan to Afghanistan: the two directions were swapped, the 80 MW leg could not carry the 2100 GWh/y that pMaxAnnualTransfer requires. CASA-1000 to Pakistan: 1000 MW and not 1300, the 1300 being the rating of the whole DC link including the Afghan tap. Tajikistan to Afghanistan: 188 MW all year plus a May-September window at 638 MW, which is the first seasonal corridor of the model. That window is written in months and not in season names, so the phase 4 split carried it into Q3 and Q5 by itself. The file used to carry Q5 rows inherited from the 2020 season set while pHours had only four seasons: the season set now comes from seasons_months.csv like every other seasonal resource, so the two cannot drift apart again.</t>
+          <t>Rebuilt from data_build/mappings/corridors.csv, which carries the 42 directed corridors with their anchor years and, for each, the source it rests on. Three corrections against the 2020 model. Turkmenistan to Afghanistan: the two directions were swapped, the 80 MW leg could not carry the 2100 GWh/y that pMaxAnnualTransfer requires. CASA-1000 to Pakistan: 1000 MW and not 1300, the 1300 being the rating of the whole DC link including the Afghan tap. Tajikistan to Afghanistan: 188 MW all year plus a May-September window at 638 MW, which is the first seasonal corridor of the model. That window is written in months and not in season names, so the phase 4 split carried it into Q3a and Q3b by itself. The file used to carry Q5 rows inherited from the 2020 season set while pHours had only four seasons: the season set now comes from seasons_months.csv like every other seasonal resource, so the two cannot drift apart again.</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2228,7 +2228,7 @@
       <c r="L30" s="4" t="inlineStr"/>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>NO LONGER WRITTEN BY HAND, and no longer naming a season. The window of the contract is declared in months in data_build/mappings/contracts.csv, 1 May to 30 September for the five CASA-1000 legs, and the build turns it into whatever seasons cover those months. Phase 4 split the summer in two and the flags followed on their own: ten rows now, Q3 and Q5 for each leg, where there were five on Q3. Two of the five legs carry no volume on purpose; the contracted equality then reads zero and holds the counter-flow shut, which is how the 2020 model suppressed them.</t>
+          <t>NO LONGER WRITTEN BY HAND, and no longer naming a season. The window of the contract is declared in months in data_build/mappings/contracts.csv, 1 May to 30 September for the five CASA-1000 legs, and the build turns it into whatever seasons cover those months. Phase 4 split the summer in two and the flags followed on their own: ten rows now, Q3a and Q3b for each leg, where there were five on the single 2020 summer. Two of the five legs carry no volume on purpose; the contracted equality then reads zero and holds the counter-flow shut, which is how the 2020 model suppressed them.</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Re-based on the model years. The volumes stopped at 2030, so the contract simply disappeared from 2031 on, a year GAMS reads as zero. The 2030 value is now held to 2050, which ASSUMES the contract is renewed. The three flows total 4343 GWh over the window, against a 4434 GWh plateau in the PPA note: consistent. PHASE 4 SPLIT THE VOLUME, IT DID NOT DUPLICATE IT. The contracted equality of base.gms is written season by season, so the May-September total is now shared between Q3 and Q5 PRO RATA BY DAYS, 61 against 92: KGZ_S to TAJ_N goes from 1595 GWh on one season to 636 and 959 on two. Copying the figure into both would have doubled every contracted flow of the model. The seasons of the reference table are ignored on the way in, only the pair and the yearly total are kept: Q3 there was the 2020 way of cutting the year, not a property of the contract.</t>
+          <t>Re-based on the model years. The volumes stopped at 2030, so the contract simply disappeared from 2031 on, a year GAMS reads as zero. The 2030 value is now held to 2050, which ASSUMES the contract is renewed. The three flows total 4343 GWh over the window, against a 4434 GWh plateau in the PPA note: consistent. PHASE 4 SPLIT THE VOLUME, IT DID NOT DUPLICATE IT. The contracted equality of base.gms is written season by season, so the May-September total is now shared between Q3a and Q3b PRO RATA BY DAYS, 61 against 92: KGZ_S to TAJ_N goes from 1595 GWh on one season to 636 and 959 on two. Copying the figure into both would have doubled every contracted flow of the model. The seasons of the reference table are ignored on the way in, only the pair and the yearly total are kept: Q3 there was the 2020 way of cutting the year, not a property of the contract.</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -4127,7 +4127,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Hourly solar and wind profiles by coordinates. Already used by pre-analysis/pipelines/vre_pipeline.py.</t>
+          <t>Hourly solar and wind profiles by coordinates. FETCHED: 2022, one year, all sixteen zones and both technologies, by pre-analysis/pipelines/run_casa_vre_fetch.py. Two things to know before using it. THE LEVEL IS NOT DECA'S. Solar comes out 3 to 46 per cent above the profiles now in the model, mean 0.204 against 0.167, which is what a clean modelled array with a flat ten per cent loss does against metered output carrying outages, soiling and curtailment. Wind does not differ by a level at all but by which zones are windy: the model gives every zone 0.33 to 0.42, a placeholder, while this says Herat 0.63, Kazakhstan 0.51 and the mountain zones near zero, TAJ_S at 0.016. The ranking is physically right and the model's flat value is wrong, but neither number is usable as a level -- the default turbine is a low specific power machine that reads high by design, and MERRA-2 at half a degree cannot resolve a Pamir valley at all. USE THE SHAPE, KEEP DECA'S LEVEL. THE COORDINATES ARE POLYGON POINTS, one per zone, from data_build/build_vre_coords.py, because no plant in the fleet carries a latitude anywhere. Global Wind Atlas at one kilometre is the source that would settle the wind level properly.</t>
         </is>
       </c>
     </row>
@@ -4939,19 +4939,19 @@
           <t>renewables.ninja, globalwindatlas.info</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>TESTED - AVAILABLE</t>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>TESTED - FETCHED</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Hourly solar and wind profiles simulated anywhere on the globe from the ERA5 reanalysis.</t>
+          <t>Hourly solar and wind profiles simulated anywhere on the globe. FETCHED for 2022, sixteen zones, both technologies, 8760 h each, relabelled to zone local time. Held outside the repo in pre-analysis/representative_days/input as PV_casa.csv and WT_casa.csv.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>The only route to pVREProfile in Turkmenistan, in Afghanistan and wherever DeCA gives nothing. Already wired into pre-analysis/pipelines/vre_pipeline.py.</t>
+          <t>The route out of the pVREProfile staircase, and the only route at all in Turkmenistan and Afghanistan. Take the SHAPE and keep the DeCA level: solar reads 22 per cent high on average and the wind levels are a turbine-model artifact over a half-degree grid. Global Wind Atlas, still untested, is what would settle the wind level.</t>
         </is>
       </c>
     </row>

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, casa_2020</t>
+          <t>deca_v51, renewables_ninja, casa_2020</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1727,17 +1727,17 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>2025 level / 2020 shape</t>
+          <t>2025 level / 2022 weather</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>PHASE 8 BUILT IT FROM TWO SOURCES BECAUSE NEITHER GIVES BOTH HALVES. base.gms:812 writes the output of every solar and wind unit as this profile times the availability times the capacity, so the table is the whole renewable production, in level as much as in shape. DeCA GIVES THE LEVEL AND NOT THE SHAPE: RenewableProfile states a monthly utilization factor per plant and no hour of the day. Its own header says so, in a line the authors left for themselves, "Hourly profiles are also needed for all WPP and SPP power plants". THE 2020 MODEL GIVES THE SHAPE and a level five years old. So the day shape comes from the 2020 profile, normalised to a mean of one, and is multiplied by the DeCA seasonal factor, the month length weighted mean over the months of the season and over the plants mappings/vre_profiles.csv selects. THE FACTOR IS A COUNTRY MEAN over every plant of the technology, existing and candidate, high yield and low yield sites together, because the five books name no zone for their existing plants. That is an average site, which is what a generic candidate is. Eighty of the 160 seasonal factors move; the Afghan and Pakistani zones keep their 2020 level, being outside the DeCA perimeter. WHAT MOVES: mean solar capacity factor 0.174 to 0.169, mean wind 0.333 to 0.369. Solar loses most in winter, KAZ_N Q1 going from 0.144 to 0.089, which matters in a system that peaks in December. THE 2020 SHAPE IS DRAWN BY MONTHS, NOT BY NAME, since phase 4 split the summer. Both halves take the 2020 Q3 day and are rescaled to their own DeCA factor, 0.208 for KAZ_N solar in Q3a against 0.207 in Q3b. Matching on the name instead handed July-September the 2020 peak block, a 130 h winter artefact, and produced a capacity factor of 1.24; the column that says which season feeds which lives in mappings/seasons_months.csv. TWO TRAPS THE MAPPING STEPS AROUND. The Tajik book labels its own regions with a KZ prefix, Khatlon and Sougd and Gorno-Badakhshan all reading "KZ ...", so the selection keys on the workbook and not on the name. And one Kazakh SOLAR plant is named Arm Wind: the exclude column of the mapping settles it on the _SP suffix, and the builder refuses outright any row two technologies claim at once.</t>
+          <t>PHASE 8 BUILT IT FROM TWO SOURCES BECAUSE NEITHER GIVES BOTH HALVES. base.gms:812 writes the output of every solar and wind unit as this profile times the availability times the capacity, so the table is the whole renewable production, in level as much as in shape. DeCA GIVES THE LEVEL AND NOT THE SHAPE: RenewableProfile states a monthly utilization factor per plant and no hour of the day. Its own header says so, in a line the authors left for themselves, "Hourly profiles are also needed for all WPP and SPP power plants". THE 2020 MODEL GIVES THE SHAPE and a level five years old. So the day shape comes from the 2020 profile, normalised to a mean of one, and is multiplied by the DeCA seasonal factor, the month length weighted mean over the months of the season and over the plants mappings/vre_profiles.csv selects. That is still how the table is built wherever the third source below cannot reach. THE FACTOR IS A COUNTRY MEAN over every plant of the technology, existing and candidate, high yield and low yield sites together, because the five books name no zone for their existing plants. That is an average site, which is what a generic candidate is. Eighty of the 160 seasonal factors move; the Afghan and Pakistani zones keep their 2020 level, being outside the DeCA perimeter. WHAT MOVES: mean solar capacity factor 0.174 to 0.169, mean wind 0.333 to 0.369. Solar loses most in winter, KAZ_N Q1 going from 0.144 to 0.089, which matters in a system that peaks in December. PHASE 9 PUT REAL WEATHER BEHIND 101 OF THE 160 ZONE-SEASONS, and changed no level at all: the annual capacity factor of all 32 series is the same to four decimals before and after. Two steps do it. build_vre_hourly.py takes the Renewables.ninja year fetched for 2022 and multiplies each zone, technology and month onto its stated DeCA factor, writing the plain PV_casa.csv and WT_casa.csv beside the _rninja files it read, so that the Poncelet clustering and this builder read the same corrected series rather than each rescaling its own copy. It refuses a series it would have to stretch more than twofold or that a single month cannot reach: ten wind series fail, all of them in mountain zones, and TAJ_S would have needed 23.6. Those ten keep the construction described above. build_vre.py then reads each block off the CALENDAR DAY it stands for, recorded by build_demand.py in extracted/demand_report.csv: the winter peak block is 12 December, the second late-summer block is 8 September. The three days of a season differ from each other for the first time -- Karachi solar in Q3b runs 0.244, 0.499 and 0.549 at its peak hour, a monsoon day beside two clear ones -- and one multiplier per season, bounded to 1.5 either way, puts the season back on its DeCA level without flattening those differences. A season needing more than that is one whose three days are not a sample of it, KAZ_N winter solar wanting 2.3 because the days it drew were overcast, and it falls back on its own without costing the other four seasons of the zone. THE 2020 SHAPE IS DRAWN BY MONTHS, NOT BY NAME, since phase 4 split the summer. Both halves take the 2020 Q3 day and are rescaled to their own DeCA factor, 0.208 for KAZ_N solar in Q3a against 0.207 in Q3b. Matching on the name instead handed July-September the 2020 peak block, a 130 h winter artefact, and produced a capacity factor of 1.24; the column that says which season feeds which lives in mappings/seasons_months.csv. TWO TRAPS THE MAPPING STEPS AROUND. The Tajik book labels its own regions with a KZ prefix, Khatlon and Sougd and Gorno-Badakhshan all reading "KZ ...", so the selection keys on the workbook and not on the name. And one Kazakh SOLAR plant is named Arm Wind: the exclude column of the mapping settles it on the _SP suffix, and the builder refuses outright any row two technologies claim at once.</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>EVERY REPRESENTATIVE DAY OF A SEASON CARRIES THE SAME RENEWABLE DAY, because a monthly factor holds no day to day variation. There is no cloudy day and no calm day in this model, only an average one, which understates the backup a large renewable fleet needs. It costs little today, the VRE fleet being small, and it becomes the binding weakness of the time structure as soon as the model starts building solar and wind at scale. The repair is an hourly renewable source, Renewables.ninja or the ERA5 reanalysis, clustered on the same representative days as the demand.</t>
+          <t>FIFTY-NINE ZONE-SEASONS STILL CARRY THREE IDENTICAL DAYS, and 56 of them are wind. Fifty are a whole year at a time: every season of KGZ_N, KGZ_S, NEPS_AFG, NEPS_TAJ, NEPS_TKM, NEPS_UZB, PAK_N, PAK_S, TAJ_N and TAJ_S wind, where the fetched resource is too far from the stated level to be rescaled into it. There is no calm day in those zones, only an average one. Global Wind Atlas at one kilometre is what would settle whether the 2020 flat 0.33 to 0.42 or the near-zero reanalysis is closer to the truth; until then the flat value stands and it is the weakest number in this table. AND THE DAYS ARE STILL CHOSEN ON THE LOAD ALONE. build_demand.py picked the peak day and the median days without looking at the weather, so a still evening of high demand is in the set only by luck, and the seasonal multiplier that repairs the level is the measure of that luck. Choosing days on load and renewables jointly is the Poncelet clustering in pre-analysis/representative_days, which waits on the Pakistani and Afghan hourly load. THE YEARS DO NOT LINE UP EVERYWHERE either: DeCA load vintages, Kazakhstan 2022 and Tajikistan 2021 with the rest unstated, against a 2022 weather year. Kazakhstan is a true same-day pairing; elsewhere it is the same date of another year, which is seasonally right and synoptically a coincidence.</t>
         </is>
       </c>
     </row>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Hourly solar and wind profiles by coordinates. FETCHED: 2022, one year, all sixteen zones and both technologies, by pre-analysis/pipelines/run_casa_vre_fetch.py. Two things to know before using it. THE LEVEL IS NOT DECA'S. Solar comes out 3 to 46 per cent above the profiles now in the model, mean 0.204 against 0.167, which is what a clean modelled array with a flat ten per cent loss does against metered output carrying outages, soiling and curtailment. Wind does not differ by a level at all but by which zones are windy: the model gives every zone 0.33 to 0.42, a placeholder, while this says Herat 0.63, Kazakhstan 0.51 and the mountain zones near zero, TAJ_S at 0.016. The ranking is physically right and the model's flat value is wrong, but neither number is usable as a level -- the default turbine is a low specific power machine that reads high by design, and MERRA-2 at half a degree cannot resolve a Pamir valley at all. USE THE SHAPE, KEEP DECA'S LEVEL. THE COORDINATES ARE POLYGON POINTS, one per zone, from data_build/build_vre_coords.py, because no plant in the fleet carries a latitude anywhere. Global Wind Atlas at one kilometre is the source that would settle the wind level properly.</t>
+          <t>Hourly solar and wind profiles by coordinates. FETCHED: 2022, one year, all sixteen zones and both technologies, by pre-analysis/pipelines/run_casa_vre_fetch.py. Two things to know before using it. THE LEVEL IS NOT DECA'S. Solar comes out 3 to 46 per cent above the profiles now in the model, mean 0.204 against 0.167, which is what a clean modelled array with a flat ten per cent loss does against metered output carrying outages, soiling and curtailment. Wind does not differ by a level at all but by which zones are windy: the model gives every zone 0.33 to 0.42, a placeholder, while this says Herat 0.63, Kazakhstan 0.51 and the mountain zones near zero, TAJ_S at 0.016. The ranking is physically right and the model's flat value is wrong, but neither number is usable as a level -- the default turbine is a low specific power machine that reads high by design, and MERRA-2 at half a degree cannot resolve a Pamir valley at all. USE THE SHAPE, KEEP DECA'S LEVEL. THE COORDINATES ARE POLYGON POINTS, one per zone, from data_build/build_vre_coords.py, because no plant in the fleet carries a latitude anywhere. Global Wind Atlas at one kilometre is the source that would settle the wind level properly. NOW IN THE MODEL, on exactly those terms, through two steps. data_build/build_vre_hourly.py multiplies each zone, technology and month onto its stated DeCA factor and writes PV_casa.csv and WT_casa.csv beside the untouched _rninja files it read; 22 of the 32 series land exactly, and the ten that do not are all wind in mountain zones, where the gap is not a loss to be scaled away but a disagreement about whether the resource exists at all -- TAJ_S would need a factor of 23.6. Those ten keep the 2020 construction. build_vre.py then reads each representative block off the CALENDAR DAY that block stands for, taken from extracted/demand_report.csv, so the winter peak block is the weather of 12 December and not a seasonal average. 101 of the 160 zone-seasons now carry real days; the annual capacity factor of every zone is unchanged to four decimals, because only the shape moved.</t>
         </is>
       </c>
     </row>
@@ -4941,17 +4941,17 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>TESTED - FETCHED</t>
+          <t>TESTED - IN USE</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Hourly solar and wind profiles simulated anywhere on the globe. FETCHED for 2022, sixteen zones, both technologies, 8760 h each, relabelled to zone local time. Held outside the repo in pre-analysis/representative_days/input as PV_casa.csv and WT_casa.csv.</t>
+          <t>Hourly solar and wind profiles simulated anywhere on the globe. FETCHED for 2022, sixteen zones, both technologies, 8760 h each, relabelled to zone local time. Held outside the repo in pre-analysis/representative_days/input, as _rninja files at their own level and plain ones rescaled to DeCA.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>The route out of the pVREProfile staircase, and the only route at all in Turkmenistan and Afghanistan. Take the SHAPE and keep the DeCA level: solar reads 22 per cent high on average and the wind levels are a turbine-model artifact over a half-degree grid. Global Wind Atlas, still untested, is what would settle the wind level.</t>
+          <t>Now the shape of 101 of the 160 zone-seasons of pVREProfile, read off the calendar day each block stands for, with the DeCA level kept. The ten wind series it could not be rescaled into keep the 2020 construction. Global Wind Atlas, still untested, is what would settle the wind level.</t>
         </is>
       </c>
     </row>

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -1737,7 +1737,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>FIFTY-NINE ZONE-SEASONS STILL CARRY THREE IDENTICAL DAYS, and 56 of them are wind. Fifty are a whole year at a time: every season of KGZ_N, KGZ_S, NEPS_AFG, NEPS_TAJ, NEPS_TKM, NEPS_UZB, PAK_N, PAK_S, TAJ_N and TAJ_S wind, where the fetched resource is too far from the stated level to be rescaled into it. There is no calm day in those zones, only an average one. Global Wind Atlas at one kilometre is what would settle whether the 2020 flat 0.33 to 0.42 or the near-zero reanalysis is closer to the truth; until then the flat value stands and it is the weakest number in this table. AND THE DAYS ARE STILL CHOSEN ON THE LOAD ALONE. build_demand.py picked the peak day and the median days without looking at the weather, so a still evening of high demand is in the set only by luck, and the seasonal multiplier that repairs the level is the measure of that luck. Choosing days on load and renewables jointly is the Poncelet clustering in pre-analysis/representative_days, which waits on the Pakistani and Afghan hourly load. THE YEARS DO NOT LINE UP EVERYWHERE either: DeCA load vintages, Kazakhstan 2022 and Tajikistan 2021 with the rest unstated, against a 2022 weather year. Kazakhstan is a true same-day pairing; elsewhere it is the same date of another year, which is seasonally right and synoptically a coincidence.</t>
+          <t>FIFTY-NINE ZONE-SEASONS STILL CARRY THREE IDENTICAL DAYS, and 56 of them are wind. Fifty are a whole year at a time: every season of KGZ_N, KGZ_S, NEPS_AFG, NEPS_TAJ, NEPS_TKM, NEPS_UZB, PAK_N, PAK_S, TAJ_N and TAJ_S wind, where the fetched resource is too far from the stated level to be rescaled into it. There is no calm day in those zones, only an average one. THE ATLAS HAS NOW ANSWERED, and it clears both sources and convicts the coordinate. data_build/build_wind_atlas.py samples all sixteen zone polygons against the Global Wind Atlas at 250 m. Read at the exact point each Renewables.ninja series was fetched from, the atlas agrees with it, r = 0.90: 0.010 against 0.016 at TAJ_S, 0.048 against 0.106 at TAJ_N. The reanalysis was never wrong about the mountains, it was asked about a valley floor, because build_vre_coords.py sets the point at the geometric centre of the zone. Read instead over the whole polygon, the atlas puts the DeCA level within reach of the best ground of fourteen zones -- TAJ_S P95 0.393 against a stated 0.373 -- and out of reach in exactly two, NEPS_TAJ at 0.215 and PAK_N at 0.241, both of which the build currently states at 0.333. It also says casa_2020 understates NEPS_HERAT twofold, P95 0.596 in the Wind of 120 Days corridor. SO THE REPAIR IS THE POINT, NOT THE MULTIPLIER. The best ground of each zone lies 28 to 498 km from where its series was fetched, further than a MERRA-2 cell is wide, so refetching there samples different weather and not merely a rescaled copy of the same. Until that is done the flat value stands in those ten zones, and stretching it onto them by raising the twofold bound would buy the right annual mean at the price of a fabricated shape -- the hour-to-hour pattern of a dead valley, multiplied. AND THE DAYS ARE STILL CHOSEN ON THE LOAD ALONE. build_demand.py picked the peak day and the median days without looking at the weather, so a still evening of high demand is in the set only by luck, and the seasonal multiplier that repairs the level is the measure of that luck. Choosing days on load and renewables jointly is the Poncelet clustering in pre-analysis/representative_days, which waits on the Pakistani and Afghan hourly load. THE YEARS DO NOT LINE UP EVERYWHERE either: DeCA load vintages, Kazakhstan 2022 and Tajikistan 2021 with the rest unstated, against a 2022 weather year. Kazakhstan is a true same-day pairing; elsewhere it is the same date of another year, which is seasonally right and synoptically a coincidence.</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4127,29 +4127,29 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Hourly solar and wind profiles by coordinates. FETCHED: 2022, one year, all sixteen zones and both technologies, by pre-analysis/pipelines/run_casa_vre_fetch.py. Two things to know before using it. THE LEVEL IS NOT DECA'S. Solar comes out 3 to 46 per cent above the profiles now in the model, mean 0.204 against 0.167, which is what a clean modelled array with a flat ten per cent loss does against metered output carrying outages, soiling and curtailment. Wind does not differ by a level at all but by which zones are windy: the model gives every zone 0.33 to 0.42, a placeholder, while this says Herat 0.63, Kazakhstan 0.51 and the mountain zones near zero, TAJ_S at 0.016. The ranking is physically right and the model's flat value is wrong, but neither number is usable as a level -- the default turbine is a low specific power machine that reads high by design, and MERRA-2 at half a degree cannot resolve a Pamir valley at all. USE THE SHAPE, KEEP DECA'S LEVEL. THE COORDINATES ARE POLYGON POINTS, one per zone, from data_build/build_vre_coords.py, because no plant in the fleet carries a latitude anywhere. Global Wind Atlas at one kilometre is the source that would settle the wind level properly. NOW IN THE MODEL, on exactly those terms, through two steps. data_build/build_vre_hourly.py multiplies each zone, technology and month onto its stated DeCA factor and writes PV_casa.csv and WT_casa.csv beside the untouched _rninja files it read; 22 of the 32 series land exactly, and the ten that do not are all wind in mountain zones, where the gap is not a loss to be scaled away but a disagreement about whether the resource exists at all -- TAJ_S would need a factor of 23.6. Those ten keep the 2020 construction. build_vre.py then reads each representative block off the CALENDAR DAY that block stands for, taken from extracted/demand_report.csv, so the winter peak block is the weather of 12 December and not a seasonal average. 101 of the 160 zone-seasons now carry real days; the annual capacity factor of every zone is unchanged to four decimals, because only the shape moved.</t>
+          <t>Hourly solar and wind profiles by coordinates. FETCHED: 2022, one year, all sixteen zones and both technologies, by pre-analysis/pipelines/run_casa_vre_fetch.py. Two things to know before using it. THE LEVEL IS NOT DECA'S. Solar comes out 3 to 46 per cent above the profiles now in the model, mean 0.204 against 0.167, which is what a clean modelled array with a flat ten per cent loss does against metered output carrying outages, soiling and curtailment. Wind does not differ by a level at all but by which zones are windy: the model gives every zone 0.33 to 0.42, a placeholder, while this says Herat 0.63, Kazakhstan 0.51 and the mountain zones near zero, TAJ_S at 0.016. The ranking is physically right and the model's flat value is wrong, but neither number is usable as a level -- the default turbine is a low specific power machine that reads high by design, and MERRA-2 at half a degree cannot resolve a Pamir valley at all. USE THE SHAPE, KEEP DECA'S LEVEL. THE COORDINATES ARE POLYGON POINTS, one per zone, from data_build/build_vre_coords.py, because no plant in the fleet carries a latitude anywhere. Global Wind Atlas at one kilometre is the source that would settle the wind level properly. NOW IN THE MODEL, on exactly those terms, through two steps. data_build/build_vre_hourly.py multiplies each zone, technology and month onto its stated DeCA factor and writes PV_casa.csv and WT_casa.csv beside the untouched _rninja files it read; 22 of the 32 series land exactly, and the ten that do not are all wind in mountain zones, where the gap is not a loss to be scaled away but a disagreement about whether the resource exists at all -- TAJ_S would need a factor of 23.6. Those ten keep the 2020 construction. build_vre.py then reads each representative block off the CALENDAR DAY that block stands for, taken from extracted/demand_report.csv, so the winter peak block is the weather of 12 December and not a seasonal average. 101 of the 160 zone-seasons now carry real days; the annual capacity factor of every zone is unchanged to four decimals, because only the shape moved. AND THE WIND LEVEL WAS NOT ITS FAULT. Sampled against the Global Wind Atlas AT THE VERY POINT EACH SERIES WAS FETCHED FROM, these numbers agree: r = 0.90 across the fourteen zones where MERRA-2 is not smearing a corridor across its cell. The atlas reads 0.010 at the point TAJ_S was fetched from and Renewables.ninja read 0.016. The mountain zones are not a modelling failure, they are dead ground correctly reported, and the fault is the CENTROID: build_vre_coords.py put the point at the geometric middle of the zone, which in a mountain country is a valley floor.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>epa_ghg_factors</t>
+          <t>global_wind_atlas</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>US EPA greenhouse gas emission factors for stationary combustion</t>
+          <t>Global Wind Atlas 3.3 (DTU Wind Energy / World Bank / ESMAP)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -4164,39 +4164,39 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>epa.gov, Emission Factors for Greenhouse Gas Inventories</t>
+          <t>globalwindatlas.info</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Combustion chemistry rather than country data, hence covers everything: natural gas 53.06 kg CO2 per MMBtu, sub-bituminous coal 97.17, residual fuel oil No. 6 75.10. These are the values pFuelCarbonContent has always carried; naming the source only makes visible what was already there.</t>
+          <t>Microscale downscaling of ERA5 onto a 0.0025 degree grid, about 250 m, with the roughness and the orography in it, publishing capacity factor directly for three IEC turbine classes at 100 m hub height. A LEVEL SOURCE AND ONLY A LEVEL SOURCE: there are no hours in it, so it settles how much wind a zone has and never when. FETCHED by data_build/build_wind_atlas.py, which samples every zone polygon of the deployed zones.geojson against its national raster -- the ISO 3166 code is read off each feature, so nothing here is written down twice -- and reports the area-weighted distribution of capacity factor over the zone rather than a single point, because nobody builds at the average square kilometre of a country. Gross figures: a net of gross factor of 0.85 is applied for wakes, availability, electrical losses and curtailment, and it is an assumption, not a measurement. WHAT IT SETTLED, and it is not what was expected. The build states a wind capacity factor near 0.33 in every zone; the atlas says that level is REACHABLE at the best ground of fourteen of the sixteen zones, and unreachable anywhere in NEPS_TAJ (P95 0.215) and PAK_N (P95 0.241). It also says casa_2020 understates NEPS_HERAT by a factor of two -- P95 0.596, the Wind of 120 Days corridor, which Renewables.ninja also saw at 0.628. The turbine class moves these by 0.05 to 0.09 at most, an order of magnitude below the disagreement it was brought in to arbitrate. IT ALSO NAMED THE REAL DEFECT. The zone points feeding Renewables.ninja are polygon centroids, and in this region the centroid of a zone is a valley floor: the atlas reads 0.010 at TAJ_S's point against 0.393 at that zone's P95, 0.048 at TAJ_N's against 0.433, 0.038 at NEPS_UZB's against 0.398. The best ground lies 28 to 498 km away from where every series was fetched, further than a MERRA-2 cell is wide. Independent corroboration that the atlas is pointing somewhere real: its best ground in Turkmenistan is the Balkan Caspian coast, where Serdar sits, and in Uzbekistan Karakalpakstan near Nukus, where the 2 x 500 MW is being built. Cached outside the repo in pre-analysis/pipelines/output/gwa_casa, about 350 MB per IEC class.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>tso_request</t>
+          <t>epa_ghg_factors</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Direct request to the transmission system operators</t>
+          <t>US EPA greenhouse gas emission factors for stationary combustion</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>internal_wb</t>
+          <t>open_source</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -4204,22 +4204,26 @@
           <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>epa.gov, Emission Factors for Greenhouse Gas Inventories</t>
+        </is>
+      </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>NTCs and commissioning schedules of the corridors. Not started to date.</t>
+          <t>Combustion chemistry rather than country data, hence covers everything: natural gas 53.06 kg CO2 per MMBtu, sub-bituminous coal 97.17, residual fuel oil No. 6 75.10. These are the values pFuelCarbonContent has always carried; naming the source only makes visible what was already there.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>tso_request</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Modelling team decision</t>
+          <t>Direct request to the transmission system operators</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4243,17 +4247,21 @@
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>NTCs and commissioning schedules of the corridors. Not started to date.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>assumed</t>
+          <t>team</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>No source - assumption made</t>
+          <t>Modelling team decision</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4268,7 +4276,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>internal_wb</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -4277,49 +4285,83 @@
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>To be made explicit in the methodology note: every value carried here is to be justified or replaced.</t>
-        </is>
-      </c>
+      <c r="H16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>No source - assumption made</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>To be made explicit in the methodology note: every value carried here is to be justified or replaced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>team_emails</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>CASA team emails</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>internal_wb</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>AFG, KAZ, KGZ, PAK, TAJ, TUR, UZB</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Context/opening_emails/</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Mandated validation channel: Mercados, then template, then TTL review, then EPM. INTERNAL exercise, not to be shared externally (Kabir Malik, 5 August 2026).</t>
         </is>
@@ -4951,7 +4993,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Now the shape of 101 of the 160 zone-seasons of pVREProfile, read off the calendar day each block stands for, with the DeCA level kept. The ten wind series it could not be rescaled into keep the 2020 construction. Global Wind Atlas, still untested, is what would settle the wind level.</t>
+          <t>Now the shape of 101 of the 160 zone-seasons of pVREProfile, read off the calendar day each block stands for, with the DeCA level kept. The ten wind series it could not be rescaled into keep the 2020 construction. GLOBAL WIND ATLAS NOW TESTED AND SAMPLED, 250 m, all sixteen zones and three IEC classes, by data_build/build_wind_atlas.py -&gt; extracted/wind_atlas.csv: it corroborates the DeCA wind level at the best ground of fourteen zones, contradicts it in NEPS_TAJ and PAK_N, and shows the Renewables.ninja fetch points are sitting on valley floors 28 to 498 km from the wind.</t>
         </is>
       </c>
     </row>

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -1732,12 +1732,12 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>PHASE 8 BUILT IT FROM TWO SOURCES BECAUSE NEITHER GIVES BOTH HALVES. base.gms:812 writes the output of every solar and wind unit as this profile times the availability times the capacity, so the table is the whole renewable production, in level as much as in shape. DeCA GIVES THE LEVEL AND NOT THE SHAPE: RenewableProfile states a monthly utilization factor per plant and no hour of the day. Its own header says so, in a line the authors left for themselves, "Hourly profiles are also needed for all WPP and SPP power plants". THE 2020 MODEL GIVES THE SHAPE and a level five years old. So the day shape comes from the 2020 profile, normalised to a mean of one, and is multiplied by the DeCA seasonal factor, the month length weighted mean over the months of the season and over the plants mappings/vre_profiles.csv selects. That is still how the table is built wherever the third source below cannot reach. THE FACTOR IS A COUNTRY MEAN over every plant of the technology, existing and candidate, high yield and low yield sites together, because the five books name no zone for their existing plants. That is an average site, which is what a generic candidate is. Eighty of the 160 seasonal factors move; the Afghan and Pakistani zones keep their 2020 level, being outside the DeCA perimeter. WHAT MOVES: mean solar capacity factor 0.174 to 0.169, mean wind 0.333 to 0.369. Solar loses most in winter, KAZ_N Q1 going from 0.144 to 0.089, which matters in a system that peaks in December. PHASE 9 PUT REAL WEATHER BEHIND 101 OF THE 160 ZONE-SEASONS, and changed no level at all: the annual capacity factor of all 32 series is the same to four decimals before and after. Two steps do it. build_vre_hourly.py takes the Renewables.ninja year fetched for 2022 and multiplies each zone, technology and month onto its stated DeCA factor, writing the plain PV_casa.csv and WT_casa.csv beside the _rninja files it read, so that the Poncelet clustering and this builder read the same corrected series rather than each rescaling its own copy. It refuses a series it would have to stretch more than twofold or that a single month cannot reach: ten wind series fail, all of them in mountain zones, and TAJ_S would have needed 23.6. Those ten keep the construction described above. build_vre.py then reads each block off the CALENDAR DAY it stands for, recorded by build_demand.py in extracted/demand_report.csv: the winter peak block is 12 December, the second late-summer block is 8 September. The three days of a season differ from each other for the first time -- Karachi solar in Q3b runs 0.244, 0.499 and 0.549 at its peak hour, a monsoon day beside two clear ones -- and one multiplier per season, bounded to 1.5 either way, puts the season back on its DeCA level without flattening those differences. A season needing more than that is one whose three days are not a sample of it, KAZ_N winter solar wanting 2.3 because the days it drew were overcast, and it falls back on its own without costing the other four seasons of the zone. THE 2020 SHAPE IS DRAWN BY MONTHS, NOT BY NAME, since phase 4 split the summer. Both halves take the 2020 Q3 day and are rescaled to their own DeCA factor, 0.208 for KAZ_N solar in Q3a against 0.207 in Q3b. Matching on the name instead handed July-September the 2020 peak block, a 130 h winter artefact, and produced a capacity factor of 1.24; the column that says which season feeds which lives in mappings/seasons_months.csv. TWO TRAPS THE MAPPING STEPS AROUND. The Tajik book labels its own regions with a KZ prefix, Khatlon and Sougd and Gorno-Badakhshan all reading "KZ ...", so the selection keys on the workbook and not on the name. And one Kazakh SOLAR plant is named Arm Wind: the exclude column of the mapping settles it on the _SP suffix, and the builder refuses outright any row two technologies claim at once.</t>
+          <t>PHASE 8 BUILT IT FROM TWO SOURCES BECAUSE NEITHER GIVES BOTH HALVES. base.gms:812 writes the output of every solar and wind unit as this profile times the availability times the capacity, so the table is the whole renewable production, in level as much as in shape. DeCA GIVES THE LEVEL AND NOT THE SHAPE: RenewableProfile states a monthly utilization factor per plant and no hour of the day. Its own header says so, in a line the authors left for themselves, "Hourly profiles are also needed for all WPP and SPP power plants". THE 2020 MODEL GIVES THE SHAPE and a level five years old. So the day shape comes from the 2020 profile, normalised to a mean of one, and is multiplied by the DeCA seasonal factor, the month length weighted mean over the months of the season and over the plants mappings/vre_profiles.csv selects. That is still how the table is built wherever the third source below cannot reach. THE FACTOR IS A COUNTRY MEAN over every plant of the technology, existing and candidate, high yield and low yield sites together, because the five books name no zone for their existing plants. That is an average site, which is what a generic candidate is. Eighty of the 160 seasonal factors move; the Afghan and Pakistani zones keep their 2020 level, being outside the DeCA perimeter. WHAT MOVES: mean solar capacity factor 0.174 to 0.169, mean wind 0.333 to 0.369. Solar loses most in winter, KAZ_N Q1 going from 0.144 to 0.089, which matters in a system that peaks in December. PHASE 9 PUT REAL WEATHER BEHIND 101 OF THE 160 ZONE-SEASONS, and changed no level at all: the annual capacity factor of all 32 series is the same to four decimals before and after. Two steps do it. build_vre_hourly.py takes the Renewables.ninja year fetched for 2022 and multiplies each zone, technology and month onto its stated DeCA factor, writing the plain PV_casa.csv and WT_casa.csv beside the _rninja files it read, so that the Poncelet clustering and this builder read the same corrected series rather than each rescaling its own copy. It refuses a series it would have to stretch more than twofold or that a single month cannot reach: ten wind series fail, all of them in mountain zones, and TAJ_S would have needed 23.6. Those ten keep the construction described above. build_vre.py then reads each block off the CALENDAR DAY it stands for, recorded by build_demand.py in extracted/demand_report.csv: the winter peak block is 12 December, the second late-summer block is 8 September. The three days of a season differ from each other for the first time -- Karachi solar in Q3b runs 0.244, 0.499 and 0.549 at its peak hour, a monsoon day beside two clear ones -- and one multiplier per season, bounded to 1.5 either way, puts the season back on its DeCA level without flattening those differences. A season needing more than that is one whose three days are not a sample of it, KAZ_N winter solar wanting 2.3 because the days it drew were overcast, and it falls back on its own without costing the other four seasons of the zone. THE 2020 SHAPE IS DRAWN BY MONTHS, NOT BY NAME, since phase 4 split the summer. Both halves take the 2020 Q3 day and are rescaled to their own DeCA factor, 0.208 for KAZ_N solar in Q3a against 0.207 in Q3b. Matching on the name instead handed July-September the 2020 peak block, a 130 h winter artefact, and produced a capacity factor of 1.24; the column that says which season feeds which lives in mappings/seasons_months.csv. AND A THIRD SOURCE FOR THE LEVEL WHERE DECA IS SILENT. A mapping row may carry level_source = atlas_p90, and eight do: the Afghan and Pakistani wind zones, which have no DeCA book and which the 2020 model gave the same 0.333 apiece. Those take their annual level from extracted/wind_atlas.csv and keep the 2020 seasonal shape. The override is applied in build_vre.py, which both builders share, because applying it in build_vre_hourly.py alone would lift the hourly year onto the atlas and let build_vre.py squash the representative days straight back onto the 2020 seasonal factor -- which is exactly what happened the first time, and cost NEPS_HERAT four of its five seasons. The order of preference is therefore DeCA, then the atlas, then 2020. TWO TRAPS THE MAPPING STEPS AROUND. The Tajik book labels its own regions with a KZ prefix, Khatlon and Sougd and Gorno-Badakhshan all reading "KZ ...", so the selection keys on the workbook and not on the name. And one Kazakh SOLAR plant is named Arm Wind: the exclude column of the mapping settles it on the _SP suffix, and the builder refuses outright any row two technologies claim at once.</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>FIFTY-NINE ZONE-SEASONS STILL CARRY THREE IDENTICAL DAYS, and 56 of them are wind. Fifty are a whole year at a time: every season of KGZ_N, KGZ_S, NEPS_AFG, NEPS_TAJ, NEPS_TKM, NEPS_UZB, PAK_N, PAK_S, TAJ_N and TAJ_S wind, where the fetched resource is too far from the stated level to be rescaled into it. There is no calm day in those zones, only an average one. THE ATLAS HAS NOW ANSWERED, and it clears both sources and convicts the coordinate. data_build/build_wind_atlas.py samples all sixteen zone polygons against the Global Wind Atlas at 250 m. Read at the exact point each Renewables.ninja series was fetched from, the atlas agrees with it, r = 0.90: 0.010 against 0.016 at TAJ_S, 0.048 against 0.106 at TAJ_N. The reanalysis was never wrong about the mountains, it was asked about a valley floor, because build_vre_coords.py sets the point at the geometric centre of the zone. Read instead over the whole polygon, the atlas puts the DeCA level within reach of the best ground of fourteen zones -- TAJ_S P95 0.393 against a stated 0.373 -- and out of reach in exactly two, NEPS_TAJ at 0.215 and PAK_N at 0.241, both of which the build currently states at 0.333. It also says casa_2020 understates NEPS_HERAT twofold, P95 0.596 in the Wind of 120 Days corridor. SO THE REPAIR IS THE POINT, NOT THE MULTIPLIER. The best ground of each zone lies 28 to 498 km from where its series was fetched, further than a MERRA-2 cell is wide, so refetching there samples different weather and not merely a rescaled copy of the same. Until that is done the flat value stands in those ten zones, and stretching it onto them by raising the twofold bound would buy the right annual mean at the price of a fabricated shape -- the hour-to-hour pattern of a dead valley, multiplied. AND THE DAYS ARE STILL CHOSEN ON THE LOAD ALONE. build_demand.py picked the peak day and the median days without looking at the weather, so a still evening of high demand is in the set only by luck, and the seasonal multiplier that repairs the level is the measure of that luck. Choosing days on load and renewables jointly is the Poncelet clustering in pre-analysis/representative_days, which waits on the Pakistani and Afghan hourly load. THE YEARS DO NOT LINE UP EVERYWHERE either: DeCA load vintages, Kazakhstan 2022 and Tajikistan 2021 with the rest unstated, against a 2022 weather year. Kazakhstan is a true same-day pairing; elsewhere it is the same date of another year, which is seasonally right and synoptically a coincidence.</t>
+          <t>FORTY-NINE ZONE-SEASONS STILL CARRY THREE IDENTICAL DAYS, and 46 of them are wind. Thirty-five are a whole year at a time: every season of KAZ_S, KGZ_N, KGZ_S, NEPS_AFG, NEPS_TAJ, PAK_N and TAJ_S wind, where the fetched resource is still too far from the stated level to be rescaled into it. There is no calm day in those zones, only an average one. It was 59 before the wind points were moved. THE LEVEL OF THOSE SEVEN IS NOW RIGHT EVEN WHERE THE SHAPE IS NOT, which is the part worth saying plainly: NEPS_TAJ and PAK_N carry the atlas level on the 2020 flat day rather than an unreachable 0.333 on it, so the energy they contribute is defensible and only its hour-to-hour distribution is not. WHAT WOULD FIX THE REMAINING SEVEN, and it is not another multiplier. Renewables.ninja runs on MERRA-2 at half a degree, and on a Pamir or Hindu Kush ridge that grid does not represent the site at any coordinate you give it -- asked about the atlas's best ground in PAK_N it returns 0.015, LOWER than at the valley centroid it was asked about before. A reanalysis with real orography is the answer: ERA5-Land at 9 km through atlite, or a mesoscale run. Raising the twofold bound instead would buy the right annual mean at the price of a fabricated shape -- the hour-to-hour pattern of a dead valley, multiplied. ONE ZONE REGRESSED AND IT IS A JUDGEMENT CALL. KAZ_S passed on its centroid and fails on its atlas site, because the Dzungarian Gate is a ten kilometre gap that a half degree cell cannot hold. Keeping KAZ_S on its centroid is expressible in data -- the override column of extracted/zone_points.csv already outranks the atlas site -- and has not been done, because choosing per zone whichever point happens to pass is selection on the outcome and needs to be a decision taken openly rather than a rule the builder applies quietly. AND THE DAYS ARE STILL CHOSEN ON THE LOAD ALONE. build_demand.py picked the peak day and the median days without looking at the weather, so a still evening of high demand is in the set only by luck, and the seasonal multiplier that repairs the level is the measure of that luck. Choosing days on load and renewables jointly is the Poncelet clustering in pre-analysis/representative_days, which waits on the Pakistani and Afghan hourly load. THE YEARS DO NOT LINE UP EVERYWHERE either: DeCA load vintages, Kazakhstan 2022 and Tajikistan 2021 with the rest unstated, against a 2022 weather year. Kazakhstan is a true same-day pairing; elsewhere it is the same date of another year, which is seasonally right and synoptically a coincidence.</t>
         </is>
       </c>
     </row>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Hourly solar and wind profiles by coordinates. FETCHED: 2022, one year, all sixteen zones and both technologies, by pre-analysis/pipelines/run_casa_vre_fetch.py. Two things to know before using it. THE LEVEL IS NOT DECA'S. Solar comes out 3 to 46 per cent above the profiles now in the model, mean 0.204 against 0.167, which is what a clean modelled array with a flat ten per cent loss does against metered output carrying outages, soiling and curtailment. Wind does not differ by a level at all but by which zones are windy: the model gives every zone 0.33 to 0.42, a placeholder, while this says Herat 0.63, Kazakhstan 0.51 and the mountain zones near zero, TAJ_S at 0.016. The ranking is physically right and the model's flat value is wrong, but neither number is usable as a level -- the default turbine is a low specific power machine that reads high by design, and MERRA-2 at half a degree cannot resolve a Pamir valley at all. USE THE SHAPE, KEEP DECA'S LEVEL. THE COORDINATES ARE POLYGON POINTS, one per zone, from data_build/build_vre_coords.py, because no plant in the fleet carries a latitude anywhere. Global Wind Atlas at one kilometre is the source that would settle the wind level properly. NOW IN THE MODEL, on exactly those terms, through two steps. data_build/build_vre_hourly.py multiplies each zone, technology and month onto its stated DeCA factor and writes PV_casa.csv and WT_casa.csv beside the untouched _rninja files it read; 22 of the 32 series land exactly, and the ten that do not are all wind in mountain zones, where the gap is not a loss to be scaled away but a disagreement about whether the resource exists at all -- TAJ_S would need a factor of 23.6. Those ten keep the 2020 construction. build_vre.py then reads each representative block off the CALENDAR DAY that block stands for, taken from extracted/demand_report.csv, so the winter peak block is the weather of 12 December and not a seasonal average. 101 of the 160 zone-seasons now carry real days; the annual capacity factor of every zone is unchanged to four decimals, because only the shape moved. AND THE WIND LEVEL WAS NOT ITS FAULT. Sampled against the Global Wind Atlas AT THE VERY POINT EACH SERIES WAS FETCHED FROM, these numbers agree: r = 0.90 across the fourteen zones where MERRA-2 is not smearing a corridor across its cell. The atlas reads 0.010 at the point TAJ_S was fetched from and Renewables.ninja read 0.016. The mountain zones are not a modelling failure, they are dead ground correctly reported, and the fault is the CENTROID: build_vre_coords.py put the point at the geometric middle of the zone, which in a mountain country is a valley floor.</t>
+          <t>Hourly solar and wind profiles by coordinates. FETCHED: 2022, one year, all sixteen zones and both technologies, by pre-analysis/pipelines/run_casa_vre_fetch.py. Two things to know before using it. THE LEVEL IS NOT DECA'S. Solar comes out 3 to 46 per cent above the profiles now in the model, mean 0.204 against 0.167, which is what a clean modelled array with a flat ten per cent loss does against metered output carrying outages, soiling and curtailment. Wind does not differ by a level at all but by which zones are windy: the model gives every zone 0.33 to 0.42, a placeholder, while this says Herat 0.63, Kazakhstan 0.51 and the mountain zones near zero, TAJ_S at 0.016. The ranking is physically right and the model's flat value is wrong, but neither number is usable as a level -- the default turbine is a low specific power machine that reads high by design, and MERRA-2 at half a degree cannot resolve a Pamir valley at all. USE THE SHAPE, KEEP DECA'S LEVEL. THE COORDINATES ARE POLYGON POINTS, one per zone, from data_build/build_vre_coords.py, because no plant in the fleet carries a latitude anywhere, AND THE CENTROID IS NO LONGER THE WIND POINT: see below. NOW IN THE MODEL, on exactly those terms, through two steps. data_build/build_vre_hourly.py multiplies each zone, technology and month onto its stated DeCA factor and writes PV_casa.csv and WT_casa.csv beside the untouched _rninja files it read; 25 of the 32 series land exactly, and the seven that do not are all wind in mountain zones, where the gap is not a loss to be scaled away but a disagreement about whether the resource exists at all. Those seven keep the 2020 construction. build_vre.py then reads each representative block off the CALENDAR DAY that block stands for, taken from extracted/demand_report.csv, so the winter peak block is the weather of 12 December and not a seasonal average. 111 of the 160 zone-seasons now carry real days. AND THE WIND LEVEL WAS NOT ITS FAULT. Sampled against the Global Wind Atlas AT THE VERY POINT EACH SERIES WAS FETCHED FROM, these numbers agree: r = 0.90 across the fourteen zones where MERRA-2 is not smearing a corridor across its cell. The atlas reads 0.010 at the point TAJ_S was fetched from and Renewables.ninja read 0.016. The mountain zones are not a modelling failure, they are dead ground correctly reported, and the fault was the CENTROID: build_vre_coords.py put the point at the geometric middle of the zone, which in a mountain country is a valley floor. SO THE WIND WAS REFETCHED SOMEWHERE ELSE. build_wind_atlas.py writes the best ten kilometre square of each zone to extracted/wind_sites.csv and pipelines/run_casa_vre_fetch.py now fetches WIND from those points and SOLAR from the centroids, which is the whole of the difference: solar is near uniform over a zone and its sixteen series always rescaled cleanly, wind is not and did not. The new points are 29 to 936 km from the old ones and the timezone each series is relabelled into follows the point it was fetched from, not the zone's centroid. WHAT THE MOVE BOUGHT, AND WHAT IT DID NOT. Four zones came into reach that were out of it -- TAJ_N 0.106 to 0.342, NEPS_UZB 0.161 to 0.366, PAK_S 0.244 to 0.505, NEPS_TKM 0.292 to 0.367 -- and one went the other way: KAZ_S fell from 0.513 to 0.273 because its best ground is the Dzungarian Gate, a ten kilometre gap in the mountains that a half degree cell smears into the plateau around it. Six others barely moved. The lesson is that a reanalysis can be pointed at better ground only where its own grid can represent that ground; on a Hindu Kush or Pamir ridge it reads LOWER at the good point than at the valley, PAK_N falling from 0.156 to 0.015, which is the grid failing and not the wind.</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Microscale downscaling of ERA5 onto a 0.0025 degree grid, about 250 m, with the roughness and the orography in it, publishing capacity factor directly for three IEC turbine classes at 100 m hub height. A LEVEL SOURCE AND ONLY A LEVEL SOURCE: there are no hours in it, so it settles how much wind a zone has and never when. FETCHED by data_build/build_wind_atlas.py, which samples every zone polygon of the deployed zones.geojson against its national raster -- the ISO 3166 code is read off each feature, so nothing here is written down twice -- and reports the area-weighted distribution of capacity factor over the zone rather than a single point, because nobody builds at the average square kilometre of a country. Gross figures: a net of gross factor of 0.85 is applied for wakes, availability, electrical losses and curtailment, and it is an assumption, not a measurement. WHAT IT SETTLED, and it is not what was expected. The build states a wind capacity factor near 0.33 in every zone; the atlas says that level is REACHABLE at the best ground of fourteen of the sixteen zones, and unreachable anywhere in NEPS_TAJ (P95 0.215) and PAK_N (P95 0.241). It also says casa_2020 understates NEPS_HERAT by a factor of two -- P95 0.596, the Wind of 120 Days corridor, which Renewables.ninja also saw at 0.628. The turbine class moves these by 0.05 to 0.09 at most, an order of magnitude below the disagreement it was brought in to arbitrate. IT ALSO NAMED THE REAL DEFECT. The zone points feeding Renewables.ninja are polygon centroids, and in this region the centroid of a zone is a valley floor: the atlas reads 0.010 at TAJ_S's point against 0.393 at that zone's P95, 0.048 at TAJ_N's against 0.433, 0.038 at NEPS_UZB's against 0.398. The best ground lies 28 to 498 km away from where every series was fetched, further than a MERRA-2 cell is wide. Independent corroboration that the atlas is pointing somewhere real: its best ground in Turkmenistan is the Balkan Caspian coast, where Serdar sits, and in Uzbekistan Karakalpakstan near Nukus, where the 2 x 500 MW is being built. Cached outside the repo in pre-analysis/pipelines/output/gwa_casa, about 350 MB per IEC class.</t>
+          <t>Microscale downscaling of ERA5 onto a 0.0025 degree grid, about 250 m, with the roughness and the orography in it, publishing capacity factor directly for three IEC turbine classes at 100 m hub height. A LEVEL SOURCE AND ONLY A LEVEL SOURCE: there are no hours in it, so it settles how much wind a zone has and never when. FETCHED by data_build/build_wind_atlas.py, which samples every zone polygon of the deployed zones.geojson against its national raster -- the ISO 3166 code is read off each feature, so nothing here is written down twice -- and reports the area-weighted distribution of capacity factor over the zone rather than a single point, because nobody builds at the average square kilometre of a country. Gross figures: a net of gross factor of 0.85 is applied for wakes, availability, electrical losses and curtailment, and it is an assumption, not a measurement. WHAT IT SETTLED, and it is not what was expected. The build states a wind capacity factor near 0.33 in every zone; the atlas says that level is REACHABLE at the best ground of fourteen of the sixteen zones, and unreachable anywhere in NEPS_TAJ (P95 0.215) and PAK_N (P95 0.241). It also says casa_2020 understates NEPS_HERAT by a factor of two -- P95 0.596, the Wind of 120 Days corridor, which Renewables.ninja also saw at 0.628. The turbine class moves these by 0.05 to 0.09 at most, an order of magnitude below the disagreement it was brought in to arbitrate. IT ALSO NAMED THE REAL DEFECT. The zone points feeding Renewables.ninja are polygon centroids, and in this region the centroid of a zone is a valley floor: the atlas reads 0.010 at TAJ_S's point against 0.393 at that zone's P95, 0.048 at TAJ_N's against 0.433, 0.038 at NEPS_UZB's against 0.398. The best ground lies 28 to 498 km away from where every series was fetched, further than a MERRA-2 cell is wide. Independent corroboration that the atlas is pointing somewhere real: its best ground in Turkmenistan is the Balkan Caspian coast, where Serdar sits, and in Uzbekistan Karakalpakstan near Nukus, where the 2 x 500 MW is being built. AND IT IS NOW A LEVEL IN THE MODEL, not only a diagnosis. The eight wind zones with no DeCA book -- the Afghan and Pakistani ones -- carried the same 0.333 in the 2020 model, which is one placeholder repeated eight times rather than eight readings. They now carry level_source = atlas_p90 in mappings/vre_profiles.csv and take their annual level from the atlas: the capacity factor of the best TENTH of the zone's own land, area weighted, net of the 0.85 factor. That is the statistic a capacity expansion model wants, because it builds on the good ground first. The spread that replaces the flat 0.333 runs from 0.176 at NEPS_TAJ to 0.560 at NEPS_HERAT, and the 2020 month-to-month shape is kept underneath it because the atlas has no calendar to offer. The seven zones WITH a DeCA book are deliberately left alone: DeCA is the client's consultant reading metered plant and the atlas is a model of terrain, and where the two agree within a few points there is no case for overruling the measurement with the model. WHAT P90 DOES NOT SCREEN FOR. The best tenth of a mountain zone includes ridges with no road, no grid and no slope or protected-area exclusion applied. The ten kilometre averaging window mitigates this and does not remove it. The plains zones -- KAZ, TUR, UZB, PAK_S -- are unaffected; KGZ_S and TAJ_S sites are in the Pamir-Alay and any methodology note has to say so. Cached outside the repo in pre-analysis/pipelines/output/gwa_casa, about 350 MB per IEC class.</t>
         </is>
       </c>
     </row>
@@ -4988,12 +4988,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Hourly solar and wind profiles simulated anywhere on the globe. FETCHED for 2022, sixteen zones, both technologies, 8760 h each, relabelled to zone local time. Held outside the repo in pre-analysis/representative_days/input, as _rninja files at their own level and plain ones rescaled to DeCA.</t>
+          <t>Hourly solar and wind profiles simulated anywhere on the globe. FETCHED for 2022, sixteen zones, both technologies, 8760 h each, relabelled to zone local time. Solar is fetched at the zone centroid and WIND AT THE BEST TEN KILOMETRE SQUARE THE ATLAS FOUND IN THAT ZONE, 29 to 936 km away. Held outside the repo in pre-analysis/representative_days/input, as _rninja files at their own level and plain ones rescaled to DeCA.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Now the shape of 101 of the 160 zone-seasons of pVREProfile, read off the calendar day each block stands for, with the DeCA level kept. The ten wind series it could not be rescaled into keep the 2020 construction. GLOBAL WIND ATLAS NOW TESTED AND SAMPLED, 250 m, all sixteen zones and three IEC classes, by data_build/build_wind_atlas.py -&gt; extracted/wind_atlas.csv: it corroborates the DeCA wind level at the best ground of fourteen zones, contradicts it in NEPS_TAJ and PAK_N, and shows the Renewables.ninja fetch points are sitting on valley floors 28 to 498 km from the wind.</t>
+          <t>Now the shape of 111 of the 160 zone-seasons of pVREProfile, read off the calendar day each block stands for. The seven wind series it could not be rescaled into keep the 2020 construction. GLOBAL WIND ATLAS NOW TESTED AND SAMPLED, 250 m, all sixteen zones and three IEC classes, by data_build/build_wind_atlas.py -&gt; extracted/wind_atlas.csv: it corroborates the DeCA wind level at the best ground of fourteen zones and NOW SETS THE LEVEL OUTRIGHT in the eight zones with no DeCA book, where the 2020 model repeated one placeholder of 0.333 eight times.</t>
         </is>
       </c>
     </row>

--- a/data_build/DATA_SOURCES_casa.xlsx
+++ b/data_build/DATA_SOURCES_casa.xlsx
@@ -79,12 +79,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -825,36 +825,36 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>config</t>
+          <t>cplex_baseline</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>config.csv</t>
+          <t>cplex/cplex_baseline.opt</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>modeltype RMIP + cplex options</t>
+          <t>CPLEX options for the baseline solve</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>inherited, fit for purpose</t>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>KEEP</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -870,10 +870,14 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Switch to MIP only if unit commitment is turned on.</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr"/>
+          <t>THE ONLY VALUE THE BUILD OVERRIDES HERE IS threads, AND IT IS ABOUT THIS MACHINE AND NOT ABOUT CENTRAL ASIA. The reference asks for barrier on 8 threads (lpmethod 4, startalg 4), and barrier holds its Cholesky factor per thread: the reduced LP is 1.5 million rows by 2.0 million columns with 1.5 million rows in the factor, and on a 31 GB machine already sitting at 56 GB of commit charge CPLEX failed three times with error 1001, out of memory, before it had finished presolve. Four threads fit. The run that produced the comparison baseline had got through on eight earlier the same day, so this is a headroom question and not a model one -- nothing about the formulation or the data changed between them. IT IS DECLARED HERE RATHER THAN EDITED IN PLACE because build.py copies the whole reference tree before applying its verbs, so an option file edited in the deployment is silently reverted by the next --apply. Anything that has to survive a rebuild has to be said in this file. Raise it back to 8, or drop lpmethod to 2 for dual simplex, on a machine with room.</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>The value is a property of the machine the run happens on and the build has no way to read that. If the model is ever run somewhere with real headroom, this override is the first thing to remove.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -883,63 +887,55 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>pHours</t>
+          <t>config</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>pHours.csv</t>
+          <t>config.csv</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>5 seasons x 3 representative days x 24 chronological hours = 360 blocks, 8760 h</t>
+          <t>modeltype RMIP + cplex options</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>filled, more to come</t>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>inherited, fit for purpose</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>KEEP</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, team</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>DeCA Demand Profile 8760h</t>
-        </is>
-      </c>
+          <t>casa_2020</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>q = 4 quarters, the 5th peak season is removed. It was not a structure but a patch: the reserve constraint takes a smax over all blocks (base.gms:991) and requires no dedicated season. Q5 only served to give that smax a block short enough to see the true peak, for want of representative days (d=1 in the 2020 model). THE SEASONS ARE NOT CALENDAR QUARTERS, and the months behind them are written down in data_build/mappings/seasons_months.csv, which is the single place the year is cut: Q1 December to February, Q2 March and April, Q3a May and June, Q3b July to September, Q4 October and November. The first cut was read off the 2020 durations, Q1 and the peak block together 2180 h that is 90.8 days, Q2 1464 h exactly 61 days, Q3 3652 h that is 152.2 days, Q4 1464 h exactly 61 days, and it lands on 8760 h to the hour. Every season-indexed resource is built against that mapping. PHASE 4 SPLIT THE SUMMER IN TWO, May-June against July-September. One season of five months held two different things at once: the irrigation release, where the reservoirs open for the fields downstream and the hydro runs whether the load calls for it or not, and the cooling peak, where it is the load that is high. A single season had to pick one, and it picked the peak: its representative days were 24 July and two medians drawn from a five-month pool. They are now 27 June for Q3a and 24 July for Q3b, and May-June has its own shape at last. THE TWO HALVES ARE NAMED Q3a AND Q3b, which is the whole of what the naming means: they are the season the 2020 model held as one, cut in two. An earlier pass called the second half Q5, on the reasoning that the name was free once the 2020 peak block was removed; free it was, but a reader meeting Q5 between Q3 and Q4 had to be told the story before the set made sense. Q1, Q2 and Q4 keep both their names and their months, so no label of this model has ever meant two different parts of the year. The seasons mapping carries a legacy column saying which 2020 season each of ours draws its inherited shapes from, and ours sends both halves of the summer to the 2020 Q3; without it build_vre matched on the name alone and dressed July-September in a winter peak block, which input_verification.py caught as a capacity factor of 1.24 on KAZ_N solar. NO SEASON IS NAMED ANYWHERE ELSE. The CASA-1000 contract window and the seasonal corridor to Afghanistan are written in months in their own mappings and resolved against this file, so the year can be re-cut again without touching them; a window that would take part of a season stops the build rather than being guessed at. PHASE 8 REBUILT IT, and this is the file that defines the sets q, d and t for the whole model: main.gms:214 reads pHours(q&lt;,d&lt;,t&lt;), so every other hourly resource follows whatever shape is written here. It is now four seasons by three representative days by twenty four chronological hours, the canonical EPM shape that epm/input/data_test also carries, and each cell holds THE NUMBER OF DAYS the representative day stands for, repeated over its 24 hours, summing to 8760. THE PEAK REPRESENTATIVE DAY REPLACES THE OLD PEAK SEASON. In each season d1 is a calendar day and weighs one day, which is what base.gms needs when it takes an smax over (q,d,t) for the reserve. The day chosen is the one that stresses the most zones at once, each zone counted against its own maximum rather than in megawatts, because a sum in megawatts is decided by Kazakhstan and Uzbekistan alone and the reserve of EPM is written per zone. The five days are 12 December, 1 March, 27 June, 24 July and 21 November. THE OTHER TWO ARE REAL DAYS AS WELL, AND THEIR WEIGHTS ARE SOLVED, NOT COUNTED. The rest of the season is split in two by daily energy and each half is represented by its medoid, the real day closest to the average of that half. A medoid is the most typical day of its group and not the day carrying its average energy, so the two weights are then solved rather than taken from the sizes of the groups: two unknowns, two equations, the days of the season and the energy of the season, rounded to whole days at the end because input_verification.py compares the sum of this table to 8760 with no tolerance at all and refuses a block of zero hours. The weights that come out are 53 and 36 days for Q1, 28 and 32 for Q2, 31 and 29 for Q3a, 42 and 49 for Q3b, 29 and 31 for Q4. WHY NOT THE MEAN OF EACH GROUP, WHICH IS WHAT THIS STEP DID FIRST. Averaging seventy-six days flattens every trough that does not fall at the same hour twice, and the model reads that flattening as a baseload the system does not have. See pDemandProfile, which carries the measurement and the table of it. The season durations are 90 / 61 / 61 / 92 / 61 days, and every seasonal resource is rebuilt from them: pDemandProfile, pVREProfile, pAvailability, pTransferLimit, pContractedTradeFlag and pContractedTradeEnergy.</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>THE NUMBER OF REPRESENTATIVE DAYS IS ONE ARGUMENT, --days, and three is a starting point rather than a result: the model went from 35 blocks in 2020 to 288 here, and if the solve turns out to be comfortable the count should go up, the days being grouped by demand alone today and therefore carrying no renewable variability. See pVREProfile, where the same limit bites harder. THE WEIGHT SOLVER IS EXACT FOR TWO GROUPS AND LEAST SQUARES BEYOND, so raising --days above three leaves a residual on the energy of the season. It is reported in the demand test and it is small; it would be removed by adding a third condition, the peak of each group, rather than by another solver. PHASE 4 SPLIT THE SUMMER: Q3a is May-June, the irrigation release, and Q3b is July-September, the cooling peak. 360 blocks now instead of 288. It shows in the representative days, which no longer share one: Q3a peaks on 27 June and Q3b on 24 July, where the single five-month season kept only 24 July and drowned May-June in two median days. The contract window did not move, it is written in months now and spans the two seasons.</t>
-        </is>
-      </c>
+          <t>Switch to MIP only if unit commitment is turned on.</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -949,61 +945,61 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>pTechFuel</t>
+          <t>pHours</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>pTechFuel.csv</t>
+          <t>pHours.csv</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>26 tech/fuel pairs, two of them wrongly flagged</t>
+          <t>5 seasons x 3 representative days x 24 chronological hours = 360 blocks, 8760 h</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>structure adapted, data to do</t>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>REVISE</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>casa_2020, epm_resources</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr"/>
+          <t>deca_v51, team</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>DeCA Demand Profile 8760h</t>
+        </is>
+      </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2020, two flags corrected in 2026</t>
+          <t>2021-2022</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>THIS TABLE IS THE VOCABULARY OF THE MODEL. main.gms:169 declares the tech and f sets from it and from nothing else, main.gms:598 and 601 read HourlyVariation to build the VRE set and RETechnology to build the RE set, and base.gms:811 then writes a different equation for a unit inside the VRE set than for one outside it. A wrong flag here is not a label, it is a change of formulation. TWO WERE WRONG AND ARE CORRECTED, both against the EPM reference vocabulary in epm/resources/pTechFuel.csv. 1. INT/Import CARRIED HourlyVariation 1, so every import contract landed in the VRE set and base.gms:811 forced its output to pVREgenProfile x availability x capacity. pVREProfile holds solar and wind only, so the profile of an import is zero and the equation reads: produce nothing, every hour of every year. The model has one such unit, IRAN_Import, 400 MW into NEPS_HERAT, and the solved run confirms it: pPlantMerged carries its 400 MW of capacity in all 13 years and not one row of energy. The 2020 model had the same flag and the same silence. At 0 it becomes what it is, a dispatchable 400 MW at 70 USD/MWh, availability 0.9. The reference calls the technology ImportTransmission and flags it 0,0. 2. HY/Water CARRIED RETechnology 0, so no hydro of the model counted as renewable. It is inert today, base.gms:786 firing only when a renewable target is set and sMinRenewableSharePct being 0, but it would have quietly halved the renewable share of any target scenario. The reference flags ReservoirHydro/Water 1. HourlyVariation stays 0: reservoir hydro is dispatched against its seasonal availability, not against an hourly profile. FOUR ROWS ARE USED BY NO UNIT and are kept all the same, aligned on the reference: CSPPlant/CSP, PVwSTO/Solar, STOPV/Solar and ROR/Water. They are not spare labels. main.gms:604-625 names those four strings literally to build the cs, so, stp and ror sets, and the strings exist only because this table declares them; deleting the rows would stop the compilation. Storage/Battery WAS ALREADY HERE and needed nothing. What the eight battery candidates were missing was not a vocabulary entry but the switch, and phase 5 turned it on: see fEnableStorage in pSettings.</t>
+          <t>q = 4 quarters, the 5th peak season is removed. It was not a structure but a patch: the reserve constraint takes a smax over all blocks (base.gms:991) and requires no dedicated season. Q5 only served to give that smax a block short enough to see the true peak, for want of representative days (d=1 in the 2020 model). THE SEASONS ARE NOT CALENDAR QUARTERS, and the months behind them are written down in data_build/mappings/seasons_months.csv, which is the single place the year is cut: Q1 December to February, Q2 March and April, Q3a May and June, Q3b July to September, Q4 October and November. The first cut was read off the 2020 durations, Q1 and the peak block together 2180 h that is 90.8 days, Q2 1464 h exactly 61 days, Q3 3652 h that is 152.2 days, Q4 1464 h exactly 61 days, and it lands on 8760 h to the hour. Every season-indexed resource is built against that mapping. PHASE 4 SPLIT THE SUMMER IN TWO, May-June against July-September. One season of five months held two different things at once: the irrigation release, where the reservoirs open for the fields downstream and the hydro runs whether the load calls for it or not, and the cooling peak, where it is the load that is high. A single season had to pick one, and it picked the peak: its representative days were 24 July and two medians drawn from a five-month pool. They are now 27 June for Q3a and 24 July for Q3b, and May-June has its own shape at last. THE TWO HALVES ARE NAMED Q3a AND Q3b, which is the whole of what the naming means: they are the season the 2020 model held as one, cut in two. An earlier pass called the second half Q5, on the reasoning that the name was free once the 2020 peak block was removed; free it was, but a reader meeting Q5 between Q3 and Q4 had to be told the story before the set made sense. Q1, Q2 and Q4 keep both their names and their months, so no label of this model has ever meant two different parts of the year. The seasons mapping carries a legacy column saying which 2020 season each of ours draws its inherited shapes from, and ours sends both halves of the summer to the 2020 Q3; without it build_vre matched on the name alone and dressed July-September in a winter peak block, which input_verification.py caught as a capacity factor of 1.24 on KAZ_N solar. NO SEASON IS NAMED ANYWHERE ELSE. The CASA-1000 contract window and the seasonal corridor to Afghanistan are written in months in their own mappings and resolved against this file, so the year can be re-cut again without touching them; a window that would take part of a season stops the build rather than being guessed at. PHASE 8 REBUILT IT, and this is the file that defines the sets q, d and t for the whole model: main.gms:214 reads pHours(q&lt;,d&lt;,t&lt;), so every other hourly resource follows whatever shape is written here. It is now four seasons by three representative days by twenty four chronological hours, the canonical EPM shape that epm/input/data_test also carries, and each cell holds THE NUMBER OF DAYS the representative day stands for, repeated over its 24 hours, summing to 8760. THE PEAK REPRESENTATIVE DAY REPLACES THE OLD PEAK SEASON. In each season d1 is a calendar day and weighs one day, which is what base.gms needs when it takes an smax over (q,d,t) for the reserve. The day chosen is the one that stresses the most zones at once, each zone counted against its own maximum rather than in megawatts, because a sum in megawatts is decided by Kazakhstan and Uzbekistan alone and the reserve of EPM is written per zone. The five days are 12 December, 1 March, 27 June, 24 July and 21 November. THE OTHER TWO ARE REAL DAYS AS WELL, AND THEIR WEIGHTS ARE SOLVED, NOT COUNTED. The rest of the season is split in two by daily energy and each half is represented by its medoid, the real day closest to the average of that half. A medoid is the most typical day of its group and not the day carrying its average energy, so the two weights are then solved rather than taken from the sizes of the groups: two unknowns, two equations, the days of the season and the energy of the season, rounded to whole days at the end because input_verification.py compares the sum of this table to 8760 with no tolerance at all and refuses a block of zero hours. The weights that come out are 53 and 36 days for Q1, 28 and 32 for Q2, 31 and 29 for Q3a, 42 and 49 for Q3b, 29 and 31 for Q4. WHY NOT THE MEAN OF EACH GROUP, WHICH IS WHAT THIS STEP DID FIRST. Averaging seventy-six days flattens every trough that does not fall at the same hour twice, and the model reads that flattening as a baseload the system does not have. See pDemandProfile, which carries the measurement and the table of it. The season durations are 90 / 61 / 61 / 92 / 61 days, and every seasonal resource is rebuilt from them: pDemandProfile, pVREProfile, pAvailability, pTransferLimit, pContractedTradeFlag and pContractedTradeEnergy.</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>PHASE 9: the DeCA candidate menu this model has no vocabulary for, CCGT with CCS, coal with CCS, ultrasupercritical coal, CCGT on biogas and the dual gas/hydrogen machine. Each needs a row here before it can need anything else.</t>
+          <t>THE NUMBER OF REPRESENTATIVE DAYS IS ONE ARGUMENT, --days, and three is a starting point rather than a result: the model went from 35 blocks in 2020 to 288 here, and if the solve turns out to be comfortable the count should go up, the days being grouped by demand alone today and therefore carrying no renewable variability. See pVREProfile, where the same limit bites harder. THE WEIGHT SOLVER IS EXACT FOR TWO GROUPS AND LEAST SQUARES BEYOND, so raising --days above three leaves a residual on the energy of the season. It is reported in the demand test and it is small; it would be removed by adding a third condition, the peak of each group, rather than by another solver. PHASE 4 SPLIT THE SUMMER: Q3a is May-June, the irrigation release, and Q3b is July-September, the cooling peak. 360 blocks now instead of 288. It shows in the representative days, which no longer share one: Q3a peaks on 27 June and Q3b on 24 July, where the single five-month season kept only 24 July and drowned May-June in two median days. The contract window did not move, it is written in months now and spans the two seasons.</t>
         </is>
       </c>
     </row>
@@ -1015,141 +1011,141 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>pFuelCarbonContent</t>
+          <t>pTechFuel</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>pFuelCarbonContent.csv</t>
+          <t>pTechFuel.csv</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>CO2 factors by fuel, tCO2 per MMBtu</t>
+          <t>26 tech/fuel pairs, two of them wrongly flagged</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>inherited, fit for purpose</t>
+        <v>26</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>KEEP</t>
+          <t>REVISE</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>casa_2020, epa_ghg_factors</t>
+          <t>casa_2020, epm_resources</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="inlineStr">
         <is>
+          <t>2020, two flags corrected in 2026</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>THIS TABLE IS THE VOCABULARY OF THE MODEL. main.gms:169 declares the tech and f sets from it and from nothing else, main.gms:598 and 601 read HourlyVariation to build the VRE set and RETechnology to build the RE set, and base.gms:811 then writes a different equation for a unit inside the VRE set than for one outside it. A wrong flag here is not a label, it is a change of formulation. TWO WERE WRONG AND ARE CORRECTED, both against the EPM reference vocabulary in epm/resources/pTechFuel.csv. 1. INT/Import CARRIED HourlyVariation 1, so every import contract landed in the VRE set and base.gms:811 forced its output to pVREgenProfile x availability x capacity. pVREProfile holds solar and wind only, so the profile of an import is zero and the equation reads: produce nothing, every hour of every year. The model has one such unit, IRAN_Import, 400 MW into NEPS_HERAT, and the solved run confirms it: pPlantMerged carries its 400 MW of capacity in all 13 years and not one row of energy. The 2020 model had the same flag and the same silence. At 0 it becomes what it is, a dispatchable 400 MW at 70 USD/MWh, availability 0.9. The reference calls the technology ImportTransmission and flags it 0,0. 2. HY/Water CARRIED RETechnology 0, so no hydro of the model counted as renewable. It is inert today, base.gms:786 firing only when a renewable target is set and sMinRenewableSharePct being 0, but it would have quietly halved the renewable share of any target scenario. The reference flags ReservoirHydro/Water 1. HourlyVariation stays 0: reservoir hydro is dispatched against its seasonal availability, not against an hourly profile. FOUR ROWS ARE USED BY NO UNIT and are kept all the same, aligned on the reference: CSPPlant/CSP, PVwSTO/Solar, STOPV/Solar and ROR/Water. They are not spare labels. main.gms:604-625 names those four strings literally to build the cs, so, stp and ror sets, and the strings exist only because this table declares them; deleting the rows would stop the compilation. Storage/Battery WAS ALREADY HERE and needed nothing. What the eight battery candidates were missing was not a vocabulary entry but the switch, and phase 5 turned it on: see fEnableStorage in pSettings.</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 9: the DeCA candidate menu this model has no vocabulary for, CCGT with CCS, coal with CCS, ultrasupercritical coal, CCGT on biogas and the dual gas/hydrogen machine. Each needs a row here before it can need anything else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>pFuelCarbonContent</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>pFuelCarbonContent.csv</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>CO2 factors by fuel, tCO2 per MMBtu</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>inherited, fit for purpose</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>casa_2020, epa_ghg_factors</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
           <t>EPA factors, stable since 2014</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>PHASE 6.4 checked and sourced, and nothing moves. The table is not a CASA estimate at all, it is the EPA emission factor set read off the standard table: natural gas 53.06 kg CO2 per MMBtu, sub-bituminous coal 97.17, residual fuel oil No. 6 75.10, which are the 0.05306, 0.09717 and 0.0751 of this file to the last digit. They are combustion chemistry rather than country data, so no DeCA book could improve them and none of the five tries. Coal_KAZ_S carries the same factor as Coal, both being the sub-bituminous line; the two are separated by their price and their transport, not by their carbon. Import = 0 IS AN ASSUMPTION AND NOT A FACT: electricity imported from outside the sixteen zones is counted as emitting nothing, so any accounting that leans on it will flatter a zone that imports. It is the right default here, the model having no view of what is on the other side of an external tie, but a national footprint drawn from these results has to say so.</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>pDemandData</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>load/pDemandData.csv</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>absolute MW by (z,q,d,y)</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>structure adapted, data to do</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>REBUILD</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>deca_v51, template_2026</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Demand Profile (8760h) + Demand Evolution</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>KZ 2022 / TJ 2021 / KG / UZ</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>DELIBERATELY EMPTY, and it stays that way. Phase 8 chose the other of the two routes generate_demand.gms offers: pDemandProfile carries the shape, the peak and the energy of pDemandForecast carry the level, and the model builds pDemandData itself, year by year, by the NLP at generate_demand.gms:63. Writing it here would mean freezing thirteen years of hourly load in a csv, which is neither reviewable nor scenario friendly.</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>Only if a study needs a load shape that changes with the year, which nothing in the sources supports today.</t>
-        </is>
-      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1159,65 +1155,61 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>pDemandForecast</t>
+          <t>pDemandData</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>load/pDemandForecast.csv</t>
+          <t>load/pDemandData.csv</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>demand trajectory by zone, energy GWh and peak MW</t>
+          <t>absolute MW by (z,q,d,y)</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>filled, more to come</t>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>REBUILD</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, casa_2020</t>
+          <t>deca_v51, template_2026</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Demand Evolution + Demand Profile</t>
+          <t>Demand Profile (8760h) + Demand Evolution</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2023-2060</t>
+          <t>KZ 2022 / TJ 2021 / KG / UZ</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Filled by extract_demand.py, DeCA Reference scenario. Demand Evolution covers 2023-2060 BY COUNTRY: no extrapolation is needed for Central Asia. The intra- country split comes from the 8760 h profiles and stays constant over time, DeCA giving no regional trajectory. The zonal peak is NON COINCIDENT, as required by generate_demand.gms which multiplies it by the normalised profile of the zone: the own peak is therefore rescaled by the growth of the country peak, through the observed coincidence factor (KG 1.03, KZ 1.02, TJ 1.07, TM and UZ 1.00). Three deliberate departures, all documented in mappings/zones_demand.csv: the Tajik split is REVERSED with respect to the 2020 model (North 27.7 % against 74.9 %), the Kyrgyz split too (North 63.9 % against 93.2 %), and Western Kazakhstan is OUT OF PERIMETER. The West (Atyrau, Mangystau) is a gas island synchronous with Russia, unable to trade with CAPS; the 2020 model folded its load into KAZ_N without its plants, which overstated the tightness of the North. It keeps its 12.9 % share of the national energy so that the North and the South are not inflated by it, and is dropped from the output: the KZ split is KAZ_N 64.4 %, KAZ_S 22.7 %, out of perimeter 12.9 %. Modelled Kazakhstan is North plus South, about 87 % of national consumption, which is what the results must be read against. The peak block of the TJ book was in GW under a MW label: corrected by a generic guard, a peak not being allowed to fall below the average power. AFG and PAK have no 2026 source: carried over from the 2020 pDemandData and extended at their own rate, LOW confidence.</t>
+          <t>DELIBERATELY EMPTY, and it stays that way. Phase 8 chose the other of the two routes generate_demand.gms offers: pDemandProfile carries the shape, the peak and the energy of pDemandForecast carry the level, and the model builds pDemandData itself, year by year, by the NLP at generate_demand.gms:63. Writing it here would mean freezing thirteen years of hourly load in a csv, which is neither reviewable nor scenario friendly.</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>PHASE 9. Add the DeCA Net Zero scenario as a variant. Replace AFG and PAK as soon as a source arrives (NTDC IGCEP first). Review the TAJ and KGZ splits with the TTLs: they change the unserved energy diagnosis of the 2020 model.</t>
+          <t>Only if a study needs a load shape that changes with the year, which nothing in the sources supports today.</t>
         </is>
       </c>
     </row>
@@ -1229,23 +1221,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>pDemandProfile</t>
+          <t>pDemandForecast</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>load/pDemandProfile.csv</t>
+          <t>load/pDemandForecast.csv</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>normalised load shape by (z,q,d,t), maximum 1</t>
+          <t>demand trajectory by zone, energy GWh and peak MW</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
           <t>filled, more to come</t>
@@ -1268,22 +1264,22 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Demand Profile (8760 h)</t>
+          <t>Demand Evolution + Demand Profile</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>KZ 2022 / TJ 2021 / KG / UZ</t>
+          <t>2023-2060</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>PHASE 8 FILLED IT, AND IT IS WHAT MAKES THE MODEL RUNNABLE. Until this step both pDemandData and pDemandProfile were empty, every zone was dead and nothing could be solved. EIGHT ZONES READ THEIR OWN 8760 HOURS, the series extract_demand.py aggregated in phase 2: the two Kazakh zones, the two Kyrgyz, the two Tajik, Turkmenistan and Uzbekistan. Turkmenistan states one average day per month, 288 points, expanded over the days of each month; the zone is single and only its shape is used. EIGHT ZONES READ THE 2020 MODEL, the five Afghan ones and the three Pakistani ones, DeCA covering neither country. Their blocks are chronological hour of day groups and not a load duration curve, which the 2020 pVREProfile proves on its own: solar reads zero in the first and the last block and peaks in the middle one. The widths are read off the 2020 pHours, 6-5-3-3-4-3 hours, and each block is held flat over its own hours. Those zones have one shape per season and no day to day variation; their peak day is lifted by the ratio the old peak season carried over their seasonal days, which is the one piece of peak information it held. THE PEAK DAY OF EACH SEASON IS CHOSEN ON THE EIGHT SOURCED ZONES ALONE. Pakistan is a large share of the demand of the model and cannot vote on it, so the coincidence between Central Asia and Pakistan is inherited from the 2020 shapes rather than modelled. THE PROFILE IS NORMALISED TO A MAXIMUM OF EXACTLY 1, which is what generate_demand.gms expects: with fUseSimplifiedDemand at 1 it multiplies the profile by the peak of pDemandForecast, then adds a correction proportional to (max - profile) until the annual energy matches, a correction that is null at the peak. The peak of the profile is therefore the peak of the forecast, and the shape carries the rest. pDemandData stays empty on purpose: the year by year scaling is the work of the model, not of the pipeline. THE OTHER DAYS ARE REAL DAYS TOO, WHICH THEY WERE NOT AT FIRST. Each group was first represented by the average of its days, and averaging seventy-six days flattens every trough that does not fall at the same hour twice. The model does not read that flattening as a flat shape, it reads it as a baseload the system does not have: the load factor of northern Tajikistan came out at 0.715 where its own series shows 0.600, and generate_demand.gms, which is handed both the peak and the energy of the zone and has to make the shape fit both, took the excess out of the nights and left TAJ_S at three per cent of its peak at four in the morning, under a smelter that never stops. Each group is now represented by its medoid, the real day closest to the average of the group, and the number of days it stands for is solved so that the energy of the season comes out right: two unknowns, the count of days and the energy, two equations. Nothing else changed, the structure is still 4 x 3 x 24. THE PEAK DAY IS CHOSEN ON THE STRESS OF EVERY ZONE, NOT ON THE MEGAWATTS. Summed in MW the peak day of a season is decided by Kazakhstan and Uzbekistan alone, and on the days that won southern Tajikistan sat at 78 per cent of its own maximum and Turkmenistan at 91. The planning reserve of EPM is written per zone, so those two would have been sized against a peak the model never sees. Each zone is divided by its own maximum before the sum, which gives every zone one vote. Energy is still counted in megawatts: that question is about size, this one is not. AND EACH ZONE IS LIFTED ONTO ITS OWN MAXIMUM. One day per season is shared by sixteen zones, so no single day is the day on which each of them separately peaks; northern Tajikistan still only reached 84 per cent of its own. The peak days are therefore multiplied, one factor per zone, until the highest hour of the profile is the highest hour of the series, 1.185 for TAJ_N and 1.05 or less for six of the eight. It is an assumption about coincidence, it is reported per zone as peak_uplift, and it is the same convention the 2020 model already used for Afghanistan and Pakistan, applied here to measured data instead of an inherited one. THE BUILD NOW TESTS ITSELF, which is the point of the table above. Twelve days are asked to stand for three hundred and sixty five and nothing in the model would ever have said how well they do it, so build_demand.py measures it against the series the days were drawn from and writes the answer beside them: the load factor the twelve days produce against the one the year really has, the annual energy, and the largest gap between the two load duration curves read at every five per cent of the year. Every sourced zone now lands within 0.02 of its true load factor, against 0.15 before, the annual energy is within 2.7 per cent, and the duration curve within 5.2 per cent of the peak. The measurement is rerun by the build, so the next change to this step cannot pass unnoticed.</t>
+          <t>Filled by extract_demand.py, DeCA Reference scenario. Demand Evolution covers 2023-2060 BY COUNTRY: no extrapolation is needed for Central Asia. The intra- country split comes from the 8760 h profiles and stays constant over time, DeCA giving no regional trajectory. The zonal peak is NON COINCIDENT, as required by generate_demand.gms which multiplies it by the normalised profile of the zone: the own peak is therefore rescaled by the growth of the country peak, through the observed coincidence factor (KG 1.03, KZ 1.02, TJ 1.07, TM and UZ 1.00). Three deliberate departures, all documented in mappings/zones_demand.csv: the Tajik split is REVERSED with respect to the 2020 model (North 27.7 % against 74.9 %), the Kyrgyz split too (North 63.9 % against 93.2 %), and Western Kazakhstan is OUT OF PERIMETER. The West (Atyrau, Mangystau) is a gas island synchronous with Russia, unable to trade with CAPS; the 2020 model folded its load into KAZ_N without its plants, which overstated the tightness of the North. It keeps its 12.9 % share of the national energy so that the North and the South are not inflated by it, and is dropped from the output: the KZ split is KAZ_N 64.4 %, KAZ_S 22.7 %, out of perimeter 12.9 %. Modelled Kazakhstan is North plus South, about 87 % of national consumption, which is what the results must be read against. The peak block of the TJ book was in GW under a MW label: corrected by a generic guard, a peak not being allowed to fall below the average power. AFG and PAK have no 2026 source: carried over from the 2020 pDemandData and extended at their own rate, LOW confidence.</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>TURKMENISTAN IS THE ONE ZONE LEFT WHERE THE PROFILE AND THE FORECAST DISAGREE, 0.693 against 0.815, and the disagreement is inside DeCA rather than in this step: the TM book states one average day per month, 288 points and no day to day variation at all, so the shape cannot show the peak the Demand Evolution sheet implies. The simplified demand routine absorbs it by raising the nights of Turkmenistan some 40 per cent above what the profile says. ASK THE TM SOURCE for an hourly series, or fall back on Renewables.ninja for the shape. A NOTE ON WHAT IS NOW SETTLED, since it was written here as an open question and it was wrong: the Tajik profiles do not disagree with the Tajik forecast. Measured against the 8760 hour series, DeCA agrees with itself to within 0.02 of load factor on both zones. The gap of 0.15 recorded here earlier was made by this pipeline, by averaging days, and it is gone. No day to day variation for Afghanistan and Pakistan. The NTDC IGCEP would replace the Pakistani shape, which is the largest single gap left in the demand.</t>
+          <t>PHASE 9. Add the DeCA Net Zero scenario as a variant. Replace AFG and PAK as soon as a source arrives (NTDC IGCEP first). Review the TAJ and KGZ splits with the TTLs: they change the unserved energy diagnosis of the 2020 model.</t>
         </is>
       </c>
     </row>
@@ -1295,45 +1291,61 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>pEnergyEfficiencyFactor</t>
+          <t>pDemandProfile</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>load/pEnergyEfficiencyFactor.csv</t>
+          <t>load/pDemandProfile.csv</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>energy efficiency factor</t>
+          <t>normalised load shape by (z,q,d,t), maximum 1</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>out of scope</t>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>deca_v51, casa_2020</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Demand Profile (8760 h)</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>KZ 2022 / TJ 2021 / KG / UZ</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 8 FILLED IT, AND IT IS WHAT MAKES THE MODEL RUNNABLE. Until this step both pDemandData and pDemandProfile were empty, every zone was dead and nothing could be solved. EIGHT ZONES READ THEIR OWN 8760 HOURS, the series extract_demand.py aggregated in phase 2: the two Kazakh zones, the two Kyrgyz, the two Tajik, Turkmenistan and Uzbekistan. Turkmenistan states one average day per month, 288 points, expanded over the days of each month; the zone is single and only its shape is used. EIGHT ZONES READ THE 2020 MODEL, the five Afghan ones and the three Pakistani ones, DeCA covering neither country. Their blocks are chronological hour of day groups and not a load duration curve, which the 2020 pVREProfile proves on its own: solar reads zero in the first and the last block and peaks in the middle one. The widths are read off the 2020 pHours, 6-5-3-3-4-3 hours, and each block is held flat over its own hours. Those zones have one shape per season and no day to day variation; their peak day is lifted by the ratio the old peak season carried over their seasonal days, which is the one piece of peak information it held. THE PEAK DAY OF EACH SEASON IS CHOSEN ON THE EIGHT SOURCED ZONES ALONE. Pakistan is a large share of the demand of the model and cannot vote on it, so the coincidence between Central Asia and Pakistan is inherited from the 2020 shapes rather than modelled. THE PROFILE IS NORMALISED TO A MAXIMUM OF EXACTLY 1, which is what generate_demand.gms expects: with fUseSimplifiedDemand at 1 it multiplies the profile by the peak of pDemandForecast, then adds a correction proportional to (max - profile) until the annual energy matches, a correction that is null at the peak. The peak of the profile is therefore the peak of the forecast, and the shape carries the rest. pDemandData stays empty on purpose: the year by year scaling is the work of the model, not of the pipeline. THE OTHER DAYS ARE REAL DAYS TOO, WHICH THEY WERE NOT AT FIRST. Each group was first represented by the average of its days, and averaging seventy-six days flattens every trough that does not fall at the same hour twice. The model does not read that flattening as a flat shape, it reads it as a baseload the system does not have: the load factor of northern Tajikistan came out at 0.715 where its own series shows 0.600, and generate_demand.gms, which is handed both the peak and the energy of the zone and has to make the shape fit both, took the excess out of the nights and left TAJ_S at three per cent of its peak at four in the morning, under a smelter that never stops. Each group is now represented by its medoid, the real day closest to the average of the group, and the number of days it stands for is solved so that the energy of the season comes out right: two unknowns, the count of days and the energy, two equations. Nothing else changed, the structure is still 4 x 3 x 24. THE PEAK DAY IS CHOSEN ON THE STRESS OF EVERY ZONE, NOT ON THE MEGAWATTS. Summed in MW the peak day of a season is decided by Kazakhstan and Uzbekistan alone, and on the days that won southern Tajikistan sat at 78 per cent of its own maximum and Turkmenistan at 91. The planning reserve of EPM is written per zone, so those two would have been sized against a peak the model never sees. Each zone is divided by its own maximum before the sum, which gives every zone one vote. Energy is still counted in megawatts: that question is about size, this one is not. AND EACH ZONE IS LIFTED ONTO ITS OWN MAXIMUM. One day per season is shared by sixteen zones, so no single day is the day on which each of them separately peaks; northern Tajikistan still only reached 84 per cent of its own. The peak days are therefore multiplied, one factor per zone, until the highest hour of the profile is the highest hour of the series, 1.185 for TAJ_N and 1.05 or less for six of the eight. It is an assumption about coincidence, it is reported per zone as peak_uplift, and it is the same convention the 2020 model already used for Afghanistan and Pakistan, applied here to measured data instead of an inherited one. THE BUILD NOW TESTS ITSELF, which is the point of the table above. Twelve days are asked to stand for three hundred and sixty five and nothing in the model would ever have said how well they do it, so build_demand.py measures it against the series the days were drawn from and writes the answer beside them: the load factor the twelve days produce against the one the year really has, the annual energy, and the largest gap between the two load duration curves read at every five per cent of the year. Every sourced zone now lands within 0.02 of its true load factor, against 0.15 before, the annual energy is within 2.7 per cent, and the duration curve within 5.2 per cent of the peak. The measurement is rerun by the build, so the next change to this step cannot pass unnoticed.</t>
+        </is>
+      </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Only if an efficiency scenario is requested.</t>
+          <t>TURKMENISTAN IS THE ONE ZONE LEFT WHERE THE PROFILE AND THE FORECAST DISAGREE, 0.693 against 0.815, and the disagreement is inside DeCA rather than in this step: the TM book states one average day per month, 288 points and no day to day variation at all, so the shape cannot show the peak the Demand Evolution sheet implies. The simplified demand routine absorbs it by raising the nights of Turkmenistan some 40 per cent above what the profile says. ASK THE TM SOURCE for an hourly series, or fall back on Renewables.ninja for the shape. A NOTE ON WHAT IS NOW SETTLED, since it was written here as an open question and it was wrong: the Tajik profiles do not disagree with the Tajik forecast. Measured against the 8760 hour series, DeCA agrees with itself to within 0.02 of load factor on both zones. The gap of 0.15 recorded here earlier was made by this pipeline, by averaging days, and it is gone. No day to day variation for Afghanistan and Pakistan. The NTDC IGCEP would replace the Pakistani shape, which is the largest single gap left in the demand.</t>
         </is>
       </c>
     </row>
@@ -1345,141 +1357,121 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>sRelevant</t>
+          <t>pEnergyEfficiencyFactor</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>load/sRelevant.csv</t>
+          <t>load/pEnergyEfficiencyFactor.csv</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>day types retained</t>
+          <t>energy efficiency factor</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>REBUILD</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
+      <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="4" t="inlineStr"/>
       <c r="M15" s="4" t="inlineStr"/>
       <c r="N15" s="4" t="inlineStr">
         <is>
+          <t>Only if an efficiency scenario is requested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>sRelevant</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>load/sRelevant.csv</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>day types retained</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>inherited 2020, to process</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>REBUILD</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
           <t>Output of the representative days pipeline. Deferred with pHours.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Fleet</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Fleet</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>pGenDataInput</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>supply/pGenDataInput.csv</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>power plants: capacity, status, HR, costs, 403 units</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>419</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>structure adapted, data to do</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>deca_v51, casa_2020, assumed</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>RenewableMaxEntry and CAPEX of the five books, tech_lifetime.csv and fleet_retirement.csv, over the 2020 table</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>2022 base, retirement rebuilt 2026</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>PHASE 5 done, on the structure. Two rebuilds, both driven by mappings/ and both re-runnable with data_build/build_fleet.py. THE RETIREMENT SCHEDULE. The 2020 schedule was mechanical, min(max(StYr + Life, 2023), 2031), and that reproduces 208 of its 232 existing units exactly. Neither bound was a decision: 2031 was where that model stopped looking, 2023 was the day it was built. Carried into a run that goes to 2050 they wiped out 66 GW in one year, Nurek, Toktogul and Ekibastuz included, and left 375 MW standing in the whole model in 2050. Rebuilt from an operating life stated per technology in mappings/tech_lifetime.csv, with a floor at the start year plus four so that a plant running today does not vanish at the first year, and anything reaching 2050 still standing written as 2051, which in EPM means it never retires inside the run. Central Asia now goes 51.3 GW in 2026 to 23.5 GW in 2050, hydro holding at 16.4 GW throughout. 12 units keep a dated year, held in mappings/fleet_retirement.csv: the eight Nurek units taken off one at a time for rehabilitation, whose refurbished replacements are already in the table, and Bishkek CHP, which the 2020 model had itself singled out. DeCA GIVES NO RETIREMENT DATES. It carries a commissioning year and nothing on the end of life, so the lives in tech_lifetime.csv are an assumption, not a measurement, and they are the assumption most worth challenging with the TSOs. PHASE 8 FOUND THAT LIFE IS NOT A DURATION TO THIS MODEL, IT IS A FLAG, and the first run stopped on it. main.gms:879 reads a life of 99 as "this unit may never be retired" and fixes vRetire to zero for it, while main.gms:864 fixes the capacity of any unit to zero from its retirement year on. A unit carrying both a life of 99, which tech_lifetime.csv gives to hydro, and a dated stop inside the horizon is therefore asked to lose its whole capacity with nothing allowed to move: base.gms:770 and base.gms:775 came out infeasible on the eight Nurek units and the run aborted before solving. build_fleet.py now writes, for a unit whose stop is dated, the life that decision implies rather than the flag, Nurek 3 for instance stopping after 53 years. Nothing else changes: no equation of the model reads the life of a generator for anything but that flag, and retirement carries no cost in the objective. THE CANDIDATES, 124 lines touched, driven by mappings/candidate_limits.csv. Three things were wrong for a 2050 run. First the closed door: main.gms:754 makes the Capacity column the cumulative build limit of a candidate and it was 0 for 30 of them, every generic candidate of KGZ_N, KGZ_S, TAJ_N and TAJ_S bar a 200 MW CCGT, and four of KAZ_S. Kyrgyzstan and Tajikistan could build nothing at all outside named hydro projects, which alone explains why the winter unserved energy of TAJ_N only cleared with Rogun. Opened. Second the missing speed limit: BuildLimitperYear was ten million MW everywhere, so solar and wind could appear at any rate. DeCA states a real one per country in RenewableMaxEntry, 3000 MW a year of each for KZ and UZ, 500 for KG, TJ and TM, and it steps up after 2030 to 6000, 1500 and 3000. EPM has one column and cannot step, so each zone carries two candidates: the first from the opening of the run with the early rate, a second from 2031 with the increment. The national rate is shared across the zones of a country by their share of the national peak in 2050. Third, the cumulative cap of those VRE candidates is now derived from the rate rather than left at the round 10000 of the 2020 table, which was another number that meant no cap over a horizon stopping in 2031 and would have meant four years of Kazakh solar over one running to 2050. THE SPEED LIMIT NOW COVERS EVERYTHING, NOT ONLY SOLAR AND WIND. Until this step the ten million MW a year still stood on every thermal, nuclear and hydro menu entry, and the first run spent it: 27 GW of new gas in 2026 alone, and ten gigawatts of Kazakh nuclear available from 2022 because that is the year the 2020 table carried. No source states how fast a country can commission a thermal unit the way DeCA states it for renewables, so a rate is assumed, and it is assumed in the open: mappings/candidate_limits.csv now carries, per technology, a share of the peak the zone already serves and a floor in MW below which that share may not fall. Combined cycle and open cycle gas and reciprocating engines get 5 per cent a year, coal and oil steam and cogeneration 3 per cent, the two Kazakh hydro menu entries 2 per cent, with floors of one machine, 400 MW for a CCGT block, 300 for a supercritical unit, 200 for a gas turbine, 100 for an engine or a CHP, 50 for small hydro. Northern Kazakhstan may therefore add 574 MW of CCGT a year and Kyrgyzstan 400, which is the floor doing its work: the share alone would have barred a small system from ever building one machine. NUCLEAR IS DATED, NOT ONLY RATED. Two per cent of the zone peak is 230 MW a year in northern Kazakhstan, one 1200 MW unit every five years, which is the pace of a real programme rather than a wall of capacity; and the same file now carries a first year, 2035, against a candidate whose start year in the 2020 table was 2022. The October 2024 referendum approved a first plant at Ulken, Rosatom was selected in June 2025, and the commissioning date stated publicly is 2035 to 2036. Nothing else in the table has a first year imposed on it. PAKISTAN AND AFGHANISTAN KEEP A RATE THEY WERE NEVER GIVEN. DeCA has no book for them, so their solar and wind candidates fell through the RenewableMaxEntry rule and kept the ten million MW. Rather than invent a number, the rate DeCA states for the five countries it does cover is read as a share of the peak each of them already serves, 18.7 per cent for Kazakhstan down to 11.6 for Tajikistan, and the median of those five, 15.7 per cent, is applied to the Pakistani and Afghan zones. It is a substitute taken from the source rather than from nowhere, and it is flat: the step up after 2030 that the five countries get is not extended to the two, so the two are the conservative case until the IGCEP arrives. WHAT THIS IS NOT. It is not a source. The shares and the floors are an assumption about how fast a power system can build, they are the first numbers to challenge with the TSOs, and they are the reason this resource is graded on assumed as well as on DeCA. Every named project is untouched: a project is not a menu entry, its capacity is the capacity of that project, and the loop never asks this file about it. PHASE 6, THE COST COLUMNS. HeatRate and VOM of the existing Central Asian thermal fleet are rebuilt by build_costs.py from mappings/thermal_plants.csv, which carries all 70 of those units one by one against the DeCA Thermal PP sheets. 63 are matched to a named DeCA plant and 7 are not, each with its reason in the mapping: two Kazakh residual aggregates that are not plants, the Balkhash Ulken project and Karaganda TPS-2 which DeCA does not carry, Yavan likewise, and Almaty-1 and Fergana where the model and DeCA disagree on the fuel itself. THE HEAT RATE IS TAKEN FROM DeCA WHEREVER A UNIT IS MATCHED, because a stated per-plant efficiency beats a per-technology constant: the 2020 model gave every Kazakh coal CHP the same 11.23 where DeCA separates them from 0.208 at Astana-2, which becomes 16.40, to 0.275 at Pavlodar-3, which becomes 12.42. 15 of the 63 units were already carrying the DeCA value, which is a good sign on the match. Shymkent moves the other way, 11.23 to 6.09, DeCA giving it a combined cycle efficiency of 0.560. THE VOM IS TAKEN ONLY WHERE DeCA DEPARTS FROM ITS OWN DEFAULT. It writes 3.400 $/MWh for 128 of its 136 thermal units, across five countries and every technology at once, which is a filler and not a measurement, and adopting it would flatten the technology spread the 2020 model does carry. Where it does depart, the departure is the information: the old Uzbek steam sets at 9.100, Takhiatash at 3.540, Navoi at 3.500, the combined cycles at 4.250. KAZAKH GAS TRANSPORT LANDS IN THE VOM rather than in pFuelPrice, because it is the one genuinely regional fuel cost in the region and the model carries only two Kazakh gas plants, at opposite ends of it. Zhambyl takes 0.370 $/MMBtu over its own 9.399 MMBtu/MWh and Shymkent 4.998 over 6.093, so their VOM reads 18.9 and 39.2 $/MWh. That looks alarming and is not: the decomposition moved, the total did not, and both plants come out cheaper than before, 67.2 to 50.0 $/MWh at Zhambyl and 64.7 to 59.4 at Shymkent. The step is idempotent, every value it writes being absolute and the VOM baseline always read from the 2020 reference rather than from the file under the pen. RUN ORDER IS build_fleet.py THEN build_costs.py, the second rewriting the file the first produces. PHASE 6, THE CANDIDATE COSTS. HeatRate, Capex, FOMperMW, VOM and Life of the 86 thermal candidates are rebuilt from the Thermal PP Candidates sheet through mappings/thermal_candidates.csv, which says which DeCA line each of the eleven (tech, fuel) pairs of the model reads. 79 rows move and 7 keep their 2020 costs, the coal fired CHPs and the oil fired steam turbines, DeCA carrying neither. THAT SHEET IS A TECHNOLOGY TABLE AND NOT A COUNTRY ONE: the five books state the same numbers to the dollar, so it is read from all five at once and any book that departs is outvoted and the departure printed. One does, TJ pricing new coal at 500,000 $/MW where the other four say 2,500,000, which is a typo and not a Tajik discount. Being a technology table is also what licenses using it in Pakistan and Afghanistan, outside the DeCA perimeter: the 2020 model applied ONE GLOBAL COST SET to all sixteen zones, so holding those two on 2020 while the five move would not preserve a country difference, it would invent one and let the model arbitrage on it. NEW COAL IS READ ON THE Supercritical LINE AND NOT ON THE ONE HEADED Coal, which is the judgement of the step. The Coal line states an efficiency of 0.33 at 2,500,000 $/MW while Supercritical, four rows below it in the same table, states 0.46137 at 2,250,000: cheaper to build, cheaper to run and half again as efficient, so the plain line is dominated by its own neighbour and no planner would ever pick it. The 2020 model already carried 0.42 here, a supercritical class unit. One word in the mapping falls back to the subcritical line. LIFE MOVES WITH THE COSTS BECAUSE IT MUST: main.gms:742 builds the capital recovery factor out of it, so taking a CAPEX without the amortization period stated beside it would annualize the new number on the old horizon. CCGT and gas turbines go from 30 years to 25, coal from 40 to 35, engines from 20 to 25, and nuclear from 40 to 60. WHAT IT COSTS, levelised at a 75 per cent capacity factor and a WACC of 10 per cent, before and after: CCGT 77.8 to 68.9 $/MWh, gas turbine 109.2 to 90.2, gas CHP 119.9 to 104.3, coal 58.9 to 52.6, engines 26.1 to 17.8, nuclear 107.0 to 106.6. EVERY THERMAL CANDIDATE GETS CHEAPER, which is the honest reading of a 2025 cost book against a 2020 one, and nuclear barely moves because its CAPEX rising by a third is cancelled by sixty years to amortize it over and a variable cost that falls from 16.83 to 0.67. Capacity, StYr and BuildLimitperYear are untouched, being the shape of the menu and not its cost, and so is the DeCA Max Capacity column, which is carried in the report and out of the table: it reads like a unit size, 300 MW for a coal or combined cycle block and 1200 for a nuclear one, but DeCA never says so and EPM reads Capacity as a cumulative build limit, so writing 300 there would silently cap all new coal in a country at one block. The fixed cost of the EXISTING units is still the 2020 value, DeCA stating none. PHASE 5, THE NAMED PROJECTS THAT COULD NEVER BE BUILT. Six hydro rows of the 2020 table named a real plant and carried a capacity of 0, and in this table that column is the cumulative build limit, so the model was shown 5.9 GW of Kyrgyz and Tajik hydro and forbidden to build one megawatt of it. Two of them were not even candidates, KAMBARATA-1 and NUREK-2 being written with the existing status, so they also counted as zero standing capacity. Five are now sized from DeCA through mappings/named_candidates.csv, which holds one line per project against the sheet and the row it comes from, 4126 MW in all. KOKEMEREN-1 takes Kokomerenskaya, 360 MW at 4.4667 M$/MW, and KOKEMEREN-2 takes Kokomeren, 912 MW at 1.6206, both from 2035. NARYN takes the whole Upper Naryn cascade, 237.7 MW at 3.0627 from 2035, which is what its name says and what DeCA aggregates; ITS ZONE MOVES FROM KGZ_S TO KGZ_N, DeCA putting every plant of the cascade in the Naryn region, area North, and KGZ_N having had no hydro candidate at all. KAMBARATA-1 takes 1860 MW at 1.5677 from 2032, DeCA calling it Committed where it calls the cascades Candidate; the status is left at 1, which lets the model build it rather than forcing it, turning it into a forced commitment being a scenario switch and not a data fix. DASHTIJUM IS THE ONE TO ARGUE ABOUT. DeCA does not name it: its Tajik candidate list is Fondaryo, Nurobad 1 and 2, Shurob, Yavan, Sanobod and Ayni, plus one generic envelope per region, and the dam on the Panj is not in it. What DeCA does state for uncommitted Khatlon hydro is that envelope, TJ Khatlon HPP, 756 MW at 2.4653 M$/MW from 2035, and Dashtijum sits in Khatlon, which is TAJ_S. So the row now carries the provincial envelope and no longer the dam, which the feasibility literature sizes an order of magnitude larger. The rule for this build is DeCA over 2020 and that is what was applied, but a TTL could as easily restore the project size or drop the row, and the mapping is one line either way. NUREK-2 IS LEFT AT ZERO, deliberately. It is a dead duplicate: the Nurek rehabilitation is already in the table as the NUREK_*_REHAB units that fleet_retirement.csv pairs with the retiring NUREK_1 to 9, and sizing this row too would count the same plant twice. NO DOUBLE COUNTING WITH THE GENERIC MENU. The only generic hydro candidates of the model are in KAZ_N and KAZ_S; KGZ_N, KGZ_S and TAJ_S have none, so nothing competes with the five projects in their own zones. WHAT DeCA CARRIES AND THIS TABLE DOES NOT, reported rather than silently added, the model having no row to put it in: Karakol 33 MW, the third plant of the Suusamyr-Kokomeren cascade; Kulanak 100 MW; the Kazarman cascade 997 MW; about 32 MW of Kyrgyz small hydro; and Nurobad 1 and 2, 920 MW in Tajikistan.</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>PHASE 6, WHAT THE HEAT RATE REBUILD EXPOSES. DeCA states the ELECTRICAL efficiency of a plant, and for a CHP that is only part of the story: Astana-2 at 0.208 sends most of its fuel to district heat, so charging all of it to electricity at 16.40 MMBtu/MWh over-prices the unit, and the flat 11.23 of the 2020 model was implicitly crediting the heat. EPM carries no heat, so the honest repair is not a softer heat rate but a winter must-run. PHASE 7 LOOKED FOR THAT LEVER AND IT IS NOT THERE: MinLimitShare is a dead column in this version, read by no equation of base.gms or main.gms, and the real must-run switch is MinGenCommitment, which base.gms:847 guards with fDispatchMode. It therefore binds in an hourly dispatch run and NOT in the expansion, which is what this model is. So the Kazakh CHPs stay too far down the merit order for now, and the two honest ways out are both later: run the dispatch of phase 8 with MinGenCommitment on, or credit the CHPs for their heat inside the heat rate itself, which is a phase 9 assumption and not a repair. PHASE 6, WHAT IS NOT DONE. FOMperMW of the EXISTING units is still the 2020 value everywhere. DeCA states no fixed cost for an existing unit at all, only for its candidates, and putting a candidate figure on a fifty year old CHP would be worse than leaving it. A NEW KAZAKH GAS UNIT PAYS NO FUEL TRANSPORT WHERE AN EXISTING ONE DOES, and that asymmetry is the one thing the candidate step leaves crooked. Kazakh gas transport is regional, 0 on the Atyrau fields to 13.3 at the end of the pipeline, so it sits in the VOM of the two existing plants rather than in the price; a candidate has no site, so it pays the molecule alone and comes out systematically cheaper to fuel than the fleet it competes with. The capacity weighted national mean is 3.851 $/MMBtu, some 21 $/MWh on a combined cycle, which is not a rounding error. The repair is either a zone mean adder on the Kazakh gas candidates or siting them, and it wants the Zones_Regions sheet. THERMAL CANDIDATES CARRY NO CAPEX TRAJECTORY: only solar, wind and batteries have one, so a 2025 combined cycle cost is charged unchanged in 2050. That is defensible for mature thermal plant and it is what DeCA states, but it should be said out loud rather than left as a silent flat line. THE DeCA CANDIDATE MENU IS WIDER THAN THE MODEL USES. CCGT with CCS, coal with CCS, ultrasupercritical coal, CCGT on biogas and the dual gas/hydrogen machine are all priced in the same sheet and none of them exists as a candidate in this model. They are the natural furniture of a decarbonization scenario in phase 9, alongside the CCS capture costs the KZ book carries region by region, 13.32 to 19.32 $/tCO2. PHASE 5, what is left: the existing fleet against DeCA. Its Thermal PP sheets carry 136 units and 51.9 GW over the five countries, where this table has 31.5 GW of Central Asian plant of every kind. Whole plants are missing: the 598 MW of Tajik thermal, Dushanbe-1 and Dushanbe-2, sits here at zero capacity and retired; Bishkek is 666 MW here against 812 MW in DeCA; Turkmenistan is 5.8 GW here against 7.7 GW. Those three are still open and are a fleet question, to be put to the TSOs with the rest of the fleet data request. THE OTHER HALF OF IT IS NOW CLOSED. The named hydro candidates stuck at Capacity 0, NARYN, KOKEMEREN-1 and 2, KAMBARATA-1 and DASHTIJUM, are sized from DeCA through mappings/named_candidates.csv, 4126 MW, and the reasoning is written out under pGenDataInput. What the DeCA pipeline carries and this model still has no row for: Kambarata-2 at 240 MW, Kulanak at 100, Mullalak at 240, an uprating of Kayrakum of 48, the Kazarman cascade at 997 and Nurobad 1 and 2 at 920. Rogun at 3380 MW by 2033, Pskem at 404 and the Nurek uprating of 385 are already in the table under their own names. DeCA also caps its own solar and wind candidates by region, Max. Capacity (MW) in Renewable PP Candidates. That is a resource limit and not a connection rate, and it is not used here because it is stated per oblast and not per model zone.</t>
-        </is>
-      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1489,31 +1481,35 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>pAvailability</t>
+          <t>pGenDataInput</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>supply/pAvailabilityCustom.csv</t>
+          <t>supply/pGenDataInput.csv</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>seasonal availability by plant, 419 units x 5 seasons</t>
+          <t>power plants: capacity, status, HR, costs, 403 units</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
         <v>419</v>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>filled, more to come</t>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>FILL</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1523,27 +1519,27 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, casa_2020</t>
+          <t>deca_v51, casa_2020, assumed</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>HydroPP + Hydro Profile, Reference hydrology</t>
+          <t>RenewableMaxEntry and CAPEX of the five books, tech_lifetime.csv and fleet_retirement.csv, over the 2020 table</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022 base, retirement rebuilt 2026</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Rebuilt by build_hydro.py from data_build/mappings/hydro_plants.csv, which carries the 134 hydro units of the model one by one, and from data_build/mappings/seasons_months.csv, which says which months each season holds. 45 units out of 134 now rest on DeCA: 11 take its monthly profile directly, the 5 Kazakh plants whose profile is plant-specific and the Pskem and Upper Naryn candidates; 34 keep the 2020 seasonal shape, which describes the reservoir operation, and have their level brought back to the DeCA capacity factor. THE 2020 MODEL WAS OPTIMISTIC ON CENTRAL ASIAN HYDRO: it allowed Toktogul 1.64 times, Uch-Kurgan 1.71 times and Charvak 1.75 times the energy DeCA gives them. The seasonal availability is the water constraint of the model, base.gms:806 caps the energy of a season with it, so that gap was a gift of water. Kazakhstan runs the other way, DeCA being more generous than 2020 on Bukhtarma and Ust-Kamenogorsk. The 89 remaining units keep their 2020 values, each with its reason in the mapping. The peak column of the 2020 model is gone with the peak season, see pHours. It carried a convention, 267 plants out of 403 at Q5 = 1.0 and 313 valued above their Q1, that is firm capacity at the peak. PHASE 7 SETTLED WHAT BECOMES OF IT: the convention is not restored, the credit stays at the real 0.85, and the consequence is measured in pPlanningReserveMarginZone. PHASE 5 REBUILT THE THERMAL SIDE OF THIS TABLE, and it asks a different question of a plant that exists than of one that does not. 156 of the 228 thermal units moved; the other 72 are Pakistani and Afghan and deliberately did not. A CANDIDATE GETS 0.90, the pair rate of data_build/mappings/availability.csv over the ten (tech, fuel) pairs it states. That is DeCA's own arithmetic for a plant in working order, 0.05 forced outage and 0.05 scheduled, against the 0.85 the 2020 model wrote without a source. 86 units. A plant not yet built has no history of neglect, so the technology rate is the whole of what can be said about it. Three of those 86 were not even at 0.85 and the same pass corrects them: KGZ_N_ST_Coal_cand and KGZ_S_ST_Coal_cand sat at 1.00, a fifth of a year of outage missing on 15 GW of candidate coal, and NEPS_HERAT_ST_Coal_cand had 0.0328654 in Q1 and 0.85 in the other four, which is a typing accident and not an assumption. AN EXISTING UNIT GETS ITS OWN DERATING, which is the correction phase 5 owes the first pass of this table. DeCA states an Available capacity beside the Installed capacity of every plant it carries, and the gap between the two is that plant's condition, stated unit by unit; the first pass wrote a flat 0.90 and threw that column away. 70 units now carry it, 63 read off their own book plant and 7 at the median of the fleet DeCA does describe, and the spread is the point: 0.3857 for the three Turkmenbashi sets, 180 MW available out of 420, against 0.90 for the second Dushanbe set, 360 out of 400. A flat rate said a Soviet CHP nobody has maintained since 1991 and a 2018 combined cycle were the same machine. 17 of the 63 sit below 0.60. The ratio is carried and not the absolute capacity, because 17 DeCA plants map to several rows of this model at once and a row-by-row capacity rewrite would invent or destroy gigawatts; the Capacity column is left to the fleet data request, see pGenDataInput. BISHKEK_CHP_2023 IS THE ROW THAT SETTLED THE METHOD. It sat at 0.308528 in the 2020 table, a real derating written in the availability column rather than in the capacity one, and the flat 0.90 of the first pass would have taken the plant from 205 MW effective to 599 on the strength of nothing. DeCA derates Bishkek itself, 420 MW available out of 812, so the number is 0.4655 and the plant reads 310 MW effective on the 666 MW this model carries. The 2020 team's instinct was right and its arithmetic was undocumented; DeCA documents it. NOTHING MOVES OUTSIDE THE FIVE COUNTRIES. The 41 Pakistani and 15 Afghan thermal units, plus the 16 the completion pass added, keep their 2020 availability, because the rule of this build is that DeCA wins where DeCA and 2020 DISAGREE and on a Pakistani plant DeCA says nothing at all. Carrying the Central Asian median south would invent a number for a fleet no source in hand describes, and invent it in the one place it moves the answer: Pakistan is the demand this study asks whether Central Asian power is worth exporting to, and derating it is the assumption that makes the interconnector look good. The median is written into extracted/thermal_derating.csv all the same, applied only to the 7 units inside the perimeter that the mapping could not match to a book plant, where the country is described and only the plant is not. HYDRO, SOLAR, WIND, IMPORTS AND STORAGE ARE UNTOUCHED by all of it: for them the column is the resource and not an outage. PHASE 7 ALSO CLOSED A HOLE THIS BUILD HAD OPENED ITSELF. The 2020 table covered its 403 units exactly; the 16 solar and wind candidates added from 2031 had no line, and a generator absent from pAvailability is not defaulted to one, it is READ AS ZERO, base.gms:812 then writing vPwrOut = 0 over the whole horizon. Solar was rescued by the generic fallback of the model, which carries a PV/Solar line; wind was not, its technology being WT here and OnshoreWind there, so EIGHT WIND CANDIDATES COULD BE BUILT AND WOULD HAVE PRODUCED NOTHING. build_hydro.py now completes the table against the fleet, giving a missing unit what its own technology and fuel carry elsewhere by majority, and refusing to guess on a tie or on a pair it has never seen. RUN ORDER IS build_fleet.py THEN build_hydro.py.</t>
+          <t>PHASE 5 done, on the structure. Two rebuilds, both driven by mappings/ and both re-runnable with data_build/build_fleet.py. THE RETIREMENT SCHEDULE. The 2020 schedule was mechanical, min(max(StYr + Life, 2023), 2031), and that reproduces 208 of its 232 existing units exactly. Neither bound was a decision: 2031 was where that model stopped looking, 2023 was the day it was built. Carried into a run that goes to 2050 they wiped out 66 GW in one year, Nurek, Toktogul and Ekibastuz included, and left 375 MW standing in the whole model in 2050. Rebuilt from an operating life stated per technology in mappings/tech_lifetime.csv, with a floor at the start year plus four so that a plant running today does not vanish at the first year, and anything reaching 2050 still standing written as 2051, which in EPM means it never retires inside the run. Central Asia now goes 51.3 GW in 2026 to 23.5 GW in 2050, hydro holding at 16.4 GW throughout. 12 units keep a dated year, held in mappings/fleet_retirement.csv: the eight Nurek units taken off one at a time for rehabilitation, whose refurbished replacements are already in the table, and Bishkek CHP, which the 2020 model had itself singled out. DeCA GIVES NO RETIREMENT DATES. It carries a commissioning year and nothing on the end of life, so the lives in tech_lifetime.csv are an assumption, not a measurement, and they are the assumption most worth challenging with the TSOs. PHASE 8 FOUND THAT LIFE IS NOT A DURATION TO THIS MODEL, IT IS A FLAG, and the first run stopped on it. main.gms:879 reads a life of 99 as "this unit may never be retired" and fixes vRetire to zero for it, while main.gms:864 fixes the capacity of any unit to zero from its retirement year on. A unit carrying both a life of 99, which tech_lifetime.csv gives to hydro, and a dated stop inside the horizon is therefore asked to lose its whole capacity with nothing allowed to move: base.gms:770 and base.gms:775 came out infeasible on the eight Nurek units and the run aborted before solving. build_fleet.py now writes, for a unit whose stop is dated, the life that decision implies rather than the flag, Nurek 3 for instance stopping after 53 years. Nothing else changes: no equation of the model reads the life of a generator for anything but that flag, and retirement carries no cost in the objective. THE CANDIDATES, 124 lines touched, driven by mappings/candidate_limits.csv. Three things were wrong for a 2050 run. First the closed door: main.gms:754 makes the Capacity column the cumulative build limit of a candidate and it was 0 for 30 of them, every generic candidate of KGZ_N, KGZ_S, TAJ_N and TAJ_S bar a 200 MW CCGT, and four of KAZ_S. Kyrgyzstan and Tajikistan could build nothing at all outside named hydro projects, which alone explains why the winter unserved energy of TAJ_N only cleared with Rogun. Opened. Second the missing speed limit: BuildLimitperYear was ten million MW everywhere, so solar and wind could appear at any rate. DeCA states a real one per country in RenewableMaxEntry, 3000 MW a year of each for KZ and UZ, 500 for KG, TJ and TM, and it steps up after 2030 to 6000, 1500 and 3000. EPM has one column and cannot step, so each zone carries two candidates: the first from the opening of the run with the early rate, a second from 2031 with the increment. The national rate is shared across the zones of a country by their share of the national peak in 2050. Third, the cumulative cap of those VRE candidates is now derived from the rate rather than left at the round 10000 of the 2020 table, which was another number that meant no cap over a horizon stopping in 2031 and would have meant four years of Kazakh solar over one running to 2050. THE SPEED LIMIT NOW COVERS EVERYTHING, NOT ONLY SOLAR AND WIND. Until this step the ten million MW a year still stood on every thermal, nuclear and hydro menu entry, and the first run spent it: 27 GW of new gas in 2026 alone, and ten gigawatts of Kazakh nuclear available from 2022 because that is the year the 2020 table carried. No source states how fast a country can commission a thermal unit the way DeCA states it for renewables, so a rate is assumed, and it is assumed in the open: mappings/candidate_limits.csv now carries, per technology, a share of the peak the zone already serves and a floor in MW below which that share may not fall. Combined cycle and open cycle gas and reciprocating engines get 5 per cent a year, coal and oil steam and cogeneration 3 per cent, the two Kazakh hydro menu entries 2 per cent, with floors of one machine, 400 MW for a CCGT block, 300 for a supercritical unit, 200 for a gas turbine, 100 for an engine or a CHP, 50 for small hydro. Northern Kazakhstan may therefore add 574 MW of CCGT a year and Kyrgyzstan 400, which is the floor doing its work: the share alone would have barred a small system from ever building one machine. NUCLEAR IS DATED, NOT ONLY RATED. Two per cent of the zone peak is 230 MW a year in northern Kazakhstan, one 1200 MW unit every five years, which is the pace of a real programme rather than a wall of capacity; and the same file now carries a first year, 2035, against a candidate whose start year in the 2020 table was 2022. The October 2024 referendum approved a first plant at Ulken, Rosatom was selected in June 2025, and the commissioning date stated publicly is 2035 to 2036. Nothing else in the table has a first year imposed on it. PAKISTAN AND AFGHANISTAN KEEP A RATE THEY WERE NEVER GIVEN. DeCA has no book for them, so their solar and wind candidates fell through the RenewableMaxEntry rule and kept the ten million MW. Rather than invent a number, the rate DeCA states for the five countries it does cover is read as a share of the peak each of them already serves, 18.7 per cent for Kazakhstan down to 11.6 for Tajikistan, and the median of those five, 15.7 per cent, is applied to the Pakistani and Afghan zones. It is a substitute taken from the source rather than from nowhere, and it is flat: the step up after 2030 that the five countries get is not extended to the two, so the two are the conservative case until the IGCEP arrives. WHAT THIS IS NOT. It is not a source. The shares and the floors are an assumption about how fast a power system can build, they are the first numbers to challenge with the TSOs, and they are the reason this resource is graded on assumed as well as on DeCA. Every named project is untouched: a project is not a menu entry, its capacity is the capacity of that project, and the loop never asks this file about it. PHASE 6, THE COST COLUMNS. HeatRate and VOM of the existing Central Asian thermal fleet are rebuilt by build_costs.py from mappings/thermal_plants.csv, which carries all 70 of those units one by one against the DeCA Thermal PP sheets. 63 are matched to a named DeCA plant and 7 are not, each with its reason in the mapping: two Kazakh residual aggregates that are not plants, the Balkhash Ulken project and Karaganda TPS-2 which DeCA does not carry, Yavan likewise, and Almaty-1 and Fergana where the model and DeCA disagree on the fuel itself. THE HEAT RATE IS TAKEN FROM DeCA WHEREVER A UNIT IS MATCHED, because a stated per-plant efficiency beats a per-technology constant: the 2020 model gave every Kazakh coal CHP the same 11.23 where DeCA separates them from 0.208 at Astana-2, which becomes 16.40, to 0.275 at Pavlodar-3, which becomes 12.42. 15 of the 63 units were already carrying the DeCA value, which is a good sign on the match. Shymkent moves the other way, 11.23 to 6.09, DeCA giving it a combined cycle efficiency of 0.560. THE VOM IS TAKEN ONLY WHERE DeCA DEPARTS FROM ITS OWN DEFAULT. It writes 3.400 $/MWh for 128 of its 136 thermal units, across five countries and every technology at once, which is a filler and not a measurement, and adopting it would flatten the technology spread the 2020 model does carry. Where it does depart, the departure is the information: the old Uzbek steam sets at 9.100, Takhiatash at 3.540, Navoi at 3.500, the combined cycles at 4.250. KAZAKH GAS TRANSPORT LANDS IN THE VOM rather than in pFuelPrice, because it is the one genuinely regional fuel cost in the region and the model carries only two Kazakh gas plants, at opposite ends of it. Zhambyl takes 0.370 $/MMBtu over its own 9.399 MMBtu/MWh and Shymkent 4.998 over 6.093, so their VOM reads 18.9 and 39.2 $/MWh. That looks alarming and is not: the decomposition moved, the total did not, and both plants come out cheaper than before, 67.2 to 50.0 $/MWh at Zhambyl and 64.7 to 59.4 at Shymkent. The step is idempotent, every value it writes being absolute and the VOM baseline always read from the 2020 reference rather than from the file under the pen. RUN ORDER IS build_fleet.py THEN build_costs.py, the second rewriting the file the first produces. PHASE 6, THE CANDIDATE COSTS. HeatRate, Capex, FOMperMW, VOM and Life of the 86 thermal candidates are rebuilt from the Thermal PP Candidates sheet through mappings/thermal_candidates.csv, which says which DeCA line each of the eleven (tech, fuel) pairs of the model reads. 79 rows move and 7 keep their 2020 costs, the coal fired CHPs and the oil fired steam turbines, DeCA carrying neither. THAT SHEET IS A TECHNOLOGY TABLE AND NOT A COUNTRY ONE: the five books state the same numbers to the dollar, so it is read from all five at once and any book that departs is outvoted and the departure printed. One does, TJ pricing new coal at 500,000 $/MW where the other four say 2,500,000, which is a typo and not a Tajik discount. Being a technology table is also what licenses using it in Pakistan and Afghanistan, outside the DeCA perimeter: the 2020 model applied ONE GLOBAL COST SET to all sixteen zones, so holding those two on 2020 while the five move would not preserve a country difference, it would invent one and let the model arbitrage on it. NEW COAL IS READ ON THE Supercritical LINE AND NOT ON THE ONE HEADED Coal, which is the judgement of the step. The Coal line states an efficiency of 0.33 at 2,500,000 $/MW while Supercritical, four rows below it in the same table, states 0.46137 at 2,250,000: cheaper to build, cheaper to run and half again as efficient, so the plain line is dominated by its own neighbour and no planner would ever pick it. The 2020 model already carried 0.42 here, a supercritical class unit. One word in the mapping falls back to the subcritical line. LIFE MOVES WITH THE COSTS BECAUSE IT MUST: main.gms:742 builds the capital recovery factor out of it, so taking a CAPEX without the amortization period stated beside it would annualize the new number on the old horizon. CCGT and gas turbines go from 30 years to 25, coal from 40 to 35, engines from 20 to 25, and nuclear from 40 to 60. WHAT IT COSTS, levelised at a 75 per cent capacity factor and a WACC of 10 per cent, before and after: CCGT 77.8 to 68.9 $/MWh, gas turbine 109.2 to 90.2, gas CHP 119.9 to 104.3, coal 58.9 to 52.6, engines 26.1 to 17.8, nuclear 107.0 to 106.6. EVERY THERMAL CANDIDATE GETS CHEAPER, which is the honest reading of a 2025 cost book against a 2020 one, and nuclear barely moves because its CAPEX rising by a third is cancelled by sixty years to amortize it over and a variable cost that falls from 16.83 to 0.67. Capacity, StYr and BuildLimitperYear are untouched, being the shape of the menu and not its cost, and so is the DeCA Max Capacity column, which is carried in the report and out of the table: it reads like a unit size, 300 MW for a coal or combined cycle block and 1200 for a nuclear one, but DeCA never says so and EPM reads Capacity as a cumulative build limit, so writing 300 there would silently cap all new coal in a country at one block. The fixed cost of the EXISTING units is still the 2020 value, DeCA stating none. PHASE 5, THE NAMED PROJECTS THAT COULD NEVER BE BUILT. Six hydro rows of the 2020 table named a real plant and carried a capacity of 0, and in this table that column is the cumulative build limit, so the model was shown 5.9 GW of Kyrgyz and Tajik hydro and forbidden to build one megawatt of it. Two of them were not even candidates, KAMBARATA-1 and NUREK-2 being written with the existing status, so they also counted as zero standing capacity. Five are now sized from DeCA through mappings/named_candidates.csv, which holds one line per project against the sheet and the row it comes from, 4126 MW in all. KOKEMEREN-1 takes Kokomerenskaya, 360 MW at 4.4667 M$/MW, and KOKEMEREN-2 takes Kokomeren, 912 MW at 1.6206, both from 2035. NARYN takes the whole Upper Naryn cascade, 237.7 MW at 3.0627 from 2035, which is what its name says and what DeCA aggregates; ITS ZONE MOVES FROM KGZ_S TO KGZ_N, DeCA putting every plant of the cascade in the Naryn region, area North, and KGZ_N having had no hydro candidate at all. KAMBARATA-1 takes 1860 MW at 1.5677 from 2032, DeCA calling it Committed where it calls the cascades Candidate; the status is left at 1, which lets the model build it rather than forcing it, turning it into a forced commitment being a scenario switch and not a data fix. DASHTIJUM IS THE ONE TO ARGUE ABOUT. DeCA does not name it: its Tajik candidate list is Fondaryo, Nurobad 1 and 2, Shurob, Yavan, Sanobod and Ayni, plus one generic envelope per region, and the dam on the Panj is not in it. What DeCA does state for uncommitted Khatlon hydro is that envelope, TJ Khatlon HPP, 756 MW at 2.4653 M$/MW from 2035, and Dashtijum sits in Khatlon, which is TAJ_S. So the row now carries the provincial envelope and no longer the dam, which the feasibility literature sizes an order of magnitude larger. The rule for this build is DeCA over 2020 and that is what was applied, but a TTL could as easily restore the project size or drop the row, and the mapping is one line either way. NUREK-2 IS LEFT AT ZERO, deliberately. It is a dead duplicate: the Nurek rehabilitation is already in the table as the NUREK_*_REHAB units that fleet_retirement.csv pairs with the retiring NUREK_1 to 9, and sizing this row too would count the same plant twice. NO DOUBLE COUNTING WITH THE GENERIC MENU. The only generic hydro candidates of the model are in KAZ_N and KAZ_S; KGZ_N, KGZ_S and TAJ_S have none, so nothing competes with the five projects in their own zones. WHAT DeCA CARRIES AND THIS TABLE DOES NOT, reported rather than silently added, the model having no row to put it in: Karakol 33 MW, the third plant of the Suusamyr-Kokomeren cascade; Kulanak 100 MW; the Kazarman cascade 997 MW; about 32 MW of Kyrgyz small hydro; and Nurobad 1 and 2, 920 MW in Tajikistan.</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>0. The derating of an existing unit is a book figure and not a measurement, and the 7 unmatched Central Asian units rest on a median. Per-unit forced and scheduled outage rates from the TSOs would replace both, and the Pakistani and Afghan fleet needs its own before anything can be said about its condition. 1. Kambarata-2, Rogun and Shardara have a DeCA yearly production above their own capacity, the production of the full project against one unit, so their level could not be used. 2. Farhad is carried at 311 MW here against 126 MW in DeCA, and its DeCA production gives an annual 0.02: the plant identity has to be settled in phase 5. 3. Pakistan, 41 units, and Afghanistan, 15 units, are outside the DeCA perimeter and still rest on the 2020 model: they need the NTDC IGCEP and the DABS fleet. 4. The dry and wet hydrologies are in the same sheets, read with --scenario, and are waiting for the scenario phase.</t>
+          <t>PHASE 6, WHAT THE HEAT RATE REBUILD EXPOSES. DeCA states the ELECTRICAL efficiency of a plant, and for a CHP that is only part of the story: Astana-2 at 0.208 sends most of its fuel to district heat, so charging all of it to electricity at 16.40 MMBtu/MWh over-prices the unit, and the flat 11.23 of the 2020 model was implicitly crediting the heat. EPM carries no heat, so the honest repair is not a softer heat rate but a winter must-run. PHASE 7 LOOKED FOR THAT LEVER AND IT IS NOT THERE: MinLimitShare is a dead column in this version, read by no equation of base.gms or main.gms, and the real must-run switch is MinGenCommitment, which base.gms:847 guards with fDispatchMode. It therefore binds in an hourly dispatch run and NOT in the expansion, which is what this model is. So the Kazakh CHPs stay too far down the merit order for now, and the two honest ways out are both later: run the dispatch of phase 8 with MinGenCommitment on, or credit the CHPs for their heat inside the heat rate itself, which is a phase 9 assumption and not a repair. PHASE 6, WHAT IS NOT DONE. FOMperMW of the EXISTING units is still the 2020 value everywhere. DeCA states no fixed cost for an existing unit at all, only for its candidates, and putting a candidate figure on a fifty year old CHP would be worse than leaving it. A NEW KAZAKH GAS UNIT PAYS NO FUEL TRANSPORT WHERE AN EXISTING ONE DOES, and that asymmetry is the one thing the candidate step leaves crooked. Kazakh gas transport is regional, 0 on the Atyrau fields to 13.3 at the end of the pipeline, so it sits in the VOM of the two existing plants rather than in the price; a candidate has no site, so it pays the molecule alone and comes out systematically cheaper to fuel than the fleet it competes with. The capacity weighted national mean is 3.851 $/MMBtu, some 21 $/MWh on a combined cycle, which is not a rounding error. The repair is either a zone mean adder on the Kazakh gas candidates or siting them, and it wants the Zones_Regions sheet. THERMAL CANDIDATES CARRY NO CAPEX TRAJECTORY: only solar, wind and batteries have one, so a 2025 combined cycle cost is charged unchanged in 2050. That is defensible for mature thermal plant and it is what DeCA states, but it should be said out loud rather than left as a silent flat line. THE DeCA CANDIDATE MENU IS WIDER THAN THE MODEL USES. CCGT with CCS, coal with CCS, ultrasupercritical coal, CCGT on biogas and the dual gas/hydrogen machine are all priced in the same sheet and none of them exists as a candidate in this model. They are the natural furniture of a decarbonization scenario in phase 9, alongside the CCS capture costs the KZ book carries region by region, 13.32 to 19.32 $/tCO2. PHASE 5, what is left: the existing fleet against DeCA. Its Thermal PP sheets carry 136 units and 51.9 GW over the five countries, where this table has 31.5 GW of Central Asian plant of every kind. Whole plants are missing: the 598 MW of Tajik thermal, Dushanbe-1 and Dushanbe-2, sits here at zero capacity and retired; Bishkek is 666 MW here against 812 MW in DeCA; Turkmenistan is 5.8 GW here against 7.7 GW. Those three are still open and are a fleet question, to be put to the TSOs with the rest of the fleet data request. THE OTHER HALF OF IT IS NOW CLOSED. The named hydro candidates stuck at Capacity 0, NARYN, KOKEMEREN-1 and 2, KAMBARATA-1 and DASHTIJUM, are sized from DeCA through mappings/named_candidates.csv, 4126 MW, and the reasoning is written out under pGenDataInput. What the DeCA pipeline carries and this model still has no row for: Kambarata-2 at 240 MW, Kulanak at 100, Mullalak at 240, an uprating of Kayrakum of 48, the Kazarman cascade at 997 and Nurobad 1 and 2 at 920. Rogun at 3380 MW by 2033, Pskem at 404 and the Nurek uprating of 385 are already in the table under their own names. DeCA also caps its own solar and wind candidates by region, Max. Capacity (MW) in Renewable PP Candidates. That is a resource limit and not a connection rate, and it is not used here because it is stated per oblast and not per model zone.</t>
         </is>
       </c>
     </row>
@@ -1555,21 +1551,21 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>pAvailabilityDefault</t>
+          <t>pAvailability</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>supply/pAvailabilityDefault.csv</t>
+          <t>supply/pAvailabilityCustom.csv</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>default availability (z,tech,fuel), empty by decision, header fixed</t>
+          <t>seasonal availability by plant, 419 units x 5 seasons</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0</v>
+        <v>419</v>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="8" t="inlineStr">
@@ -1582,19 +1578,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, assumed</t>
+          <t>deca_v51, casa_2020</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Thermal PP, columns Forced Outage Rate / Scheduled Outage Rate</t>
+          <t>HydroPP + Hydro Profile, Reference hydrology</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1604,12 +1600,12 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>PHASE 5 TOOK THE 0.90 OF DeCA over the 0.85 of the 2020 model, following the rule set for this build that DeCA wins where the two disagree. DeCA carries 0.05 forced and 0.05 scheduled, 0.10 unavailable in all, for every thermal plant of the five countries it covers, with no distinction of country or technology. The 2020 model wrote 0.85 everywhere and named no source. Neither is a measurement; one has a document behind it. THAT RATE IS THE ANSWER FOR A PLANT THAT DOES NOT EXIST YET, and only for that. An existing unit is written at its own derating instead, DeCA stating an Available capacity beside the Installed one plant by plant, which is why this table could never have carried the decision even if the model let it: a technology rate cannot say that Turkmenbashi runs at 0.39 and the second Dushanbe set at 0.90. See pAvailabilityCustom, where both live. THE DECISION LANDS ON pAvailabilityCustom AND NOT HERE, which is worth stating because this file is the one that looks like it should carry it. The chain is in input_treatment.py: the custom table is read into pAvailabilityInput(g,q), expanded over the years into pAvailability(g,y,q), and only then is this default reached for, to fill the units the custom table left out. It leaves none out: 419 units, 419 lines. So this table is inert whatever it holds. IT STAYS EMPTY, AND THAT IS A DECISION THE MODEL FORCED. The build first filled it with the 98 (zone, tech, fuel) triples whose availability is a technology property, so that a generator added later without a line of its own would land on a stated number rather than on zero, and the run refused to compile: input_treatment.py:1403 skips the table when it is empty and input_treatment.py:1426 aborts when it is present and does not cover EVERY (zone, tech, fuel) of pGenDataInput. It is all or nothing. Covering everything would mean writing a default availability for hydro, solar, wind and imports, and for those the column is not an outage rate but the resource itself, the seasonal water of a reservoir or a profile that already carries the weather. A technology-level number must not stand behind plant-level data, so the table is left empty and the partial fill is kept out. build_hydro.py still writes extracted/pAvailabilityDefault.csv, which is the table that would be used if the day comes when every pair can honestly be given one. WHAT DID CHANGE HERE IS THE HEADER. It read z,tech,fuel,Q1,Q2, the two seasons of data_test, inherited when the folder was set up. This model has five, and the header carries the index of the parameter.</t>
+          <t>Rebuilt by build_hydro.py from data_build/mappings/hydro_plants.csv, which carries the 134 hydro units of the model one by one, and from data_build/mappings/seasons_months.csv, which says which months each season holds. 45 units out of 134 now rest on DeCA: 11 take its monthly profile directly, the 5 Kazakh plants whose profile is plant-specific and the Pskem and Upper Naryn candidates; 34 keep the 2020 seasonal shape, which describes the reservoir operation, and have their level brought back to the DeCA capacity factor. THE 2020 MODEL WAS OPTIMISTIC ON CENTRAL ASIAN HYDRO: it allowed Toktogul 1.64 times, Uch-Kurgan 1.71 times and Charvak 1.75 times the energy DeCA gives them. The seasonal availability is the water constraint of the model, base.gms:806 caps the energy of a season with it, so that gap was a gift of water. Kazakhstan runs the other way, DeCA being more generous than 2020 on Bukhtarma and Ust-Kamenogorsk. The 89 remaining units keep their 2020 values, each with its reason in the mapping. The peak column of the 2020 model is gone with the peak season, see pHours. It carried a convention, 267 plants out of 403 at Q5 = 1.0 and 313 valued above their Q1, that is firm capacity at the peak. PHASE 7 SETTLED WHAT BECOMES OF IT: the convention is not restored, the credit stays at the real 0.85, and the consequence is measured in pPlanningReserveMarginZone. PHASE 5 REBUILT THE THERMAL SIDE OF THIS TABLE, and it asks a different question of a plant that exists than of one that does not. 156 of the 228 thermal units moved; the other 72 are Pakistani and Afghan and deliberately did not. A CANDIDATE GETS 0.90, the pair rate of data_build/mappings/availability.csv over the ten (tech, fuel) pairs it states. That is DeCA's own arithmetic for a plant in working order, 0.05 forced outage and 0.05 scheduled, against the 0.85 the 2020 model wrote without a source. 86 units. A plant not yet built has no history of neglect, so the technology rate is the whole of what can be said about it. Three of those 86 were not even at 0.85 and the same pass corrects them: KGZ_N_ST_Coal_cand and KGZ_S_ST_Coal_cand sat at 1.00, a fifth of a year of outage missing on 15 GW of candidate coal, and NEPS_HERAT_ST_Coal_cand had 0.0328654 in Q1 and 0.85 in the other four, which is a typing accident and not an assumption. AN EXISTING UNIT GETS ITS OWN DERATING, which is the correction phase 5 owes the first pass of this table. DeCA states an Available capacity beside the Installed capacity of every plant it carries, and the gap between the two is that plant's condition, stated unit by unit; the first pass wrote a flat 0.90 and threw that column away. 70 units now carry it, 63 read off their own book plant and 7 at the median of the fleet DeCA does describe, and the spread is the point: 0.3857 for the three Turkmenbashi sets, 180 MW available out of 420, against 0.90 for the second Dushanbe set, 360 out of 400. A flat rate said a Soviet CHP nobody has maintained since 1991 and a 2018 combined cycle were the same machine. 17 of the 63 sit below 0.60. The ratio is carried and not the absolute capacity, because 17 DeCA plants map to several rows of this model at once and a row-by-row capacity rewrite would invent or destroy gigawatts; the Capacity column is left to the fleet data request, see pGenDataInput. BISHKEK_CHP_2023 IS THE ROW THAT SETTLED THE METHOD. It sat at 0.308528 in the 2020 table, a real derating written in the availability column rather than in the capacity one, and the flat 0.90 of the first pass would have taken the plant from 205 MW effective to 599 on the strength of nothing. DeCA derates Bishkek itself, 420 MW available out of 812, so the number is 0.4655 and the plant reads 310 MW effective on the 666 MW this model carries. The 2020 team's instinct was right and its arithmetic was undocumented; DeCA documents it. NOTHING MOVES OUTSIDE THE FIVE COUNTRIES. The 41 Pakistani and 15 Afghan thermal units, plus the 16 the completion pass added, keep their 2020 availability, because the rule of this build is that DeCA wins where DeCA and 2020 DISAGREE and on a Pakistani plant DeCA says nothing at all. Carrying the Central Asian median south would invent a number for a fleet no source in hand describes, and invent it in the one place it moves the answer: Pakistan is the demand this study asks whether Central Asian power is worth exporting to, and derating it is the assumption that makes the interconnector look good. The median is written into extracted/thermal_derating.csv all the same, applied only to the 7 units inside the perimeter that the mapping could not match to a book plant, where the country is described and only the plant is not. HYDRO, SOLAR, WIND, IMPORTS AND STORAGE ARE UNTOUCHED by all of it: for them the column is the resource and not an outage. PHASE 7 ALSO CLOSED A HOLE THIS BUILD HAD OPENED ITSELF. The 2020 table covered its 403 units exactly; the 16 solar and wind candidates added from 2031 had no line, and a generator absent from pAvailability is not defaulted to one, it is READ AS ZERO, base.gms:812 then writing vPwrOut = 0 over the whole horizon. Solar was rescued by the generic fallback of the model, which carries a PV/Solar line; wind was not, its technology being WT here and OnshoreWind there, so EIGHT WIND CANDIDATES COULD BE BUILT AND WOULD HAVE PRODUCED NOTHING. build_hydro.py now completes the table against the fleet, giving a missing unit what its own technology and fuel carry elsewhere by majority, and refusing to guess on a tie or on a pair it has never seen. RUN ORDER IS build_fleet.py THEN build_hydro.py.</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>A measured outage rate would have to come from the TSOs, unit by unit, and would replace both the 0.90 of a candidate and the book derating of an existing unit. Ask for it with the fleet data request.</t>
+          <t>0. The derating of an existing unit is a book figure and not a measurement, and the 7 unmatched Central Asian units rest on a median. Per-unit forced and scheduled outage rates from the TSOs would replace both, and the Pakistani and Afghan fleet needs its own before anything can be said about its condition. 1. Kambarata-2, Rogun and Shardara have a DeCA yearly production above their own capacity, the production of the full project against one unit, so their level could not be used. 2. Farhad is carried at 311 MW here against 126 MW in DeCA, and its DeCA production gives an annual 0.02: the plant identity has to be settled in phase 5. 3. Pakistan, 41 units, and Afghanistan, 15 units, are outside the DeCA perimeter and still rest on the 2020 model: they need the NTDC IGCEP and the DABS fleet. 4. The dry and wet hydrologies are in the same sheets, read with --scenario, and are waiting for the scenario phase.</t>
         </is>
       </c>
     </row>
@@ -1621,46 +1617,46 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>pGenDataInputDefault</t>
+          <t>pAvailabilityDefault</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>supply/pGenDataInputDefault.csv</t>
+          <t>supply/pAvailabilityDefault.csv</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>generic candidates by zone</t>
+          <t>default availability (z,tech,fuel), empty by decision, header fixed</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>deca_v51</t>
+          <t>deca_v51, assumed</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>PP Candidates + RenewableMaxEntry</t>
+          <t>Thermal PP, columns Forced Outage Rate / Scheduled Outage Rate</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1668,10 +1664,14 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 5 TOOK THE 0.90 OF DeCA over the 0.85 of the 2020 model, following the rule set for this build that DeCA wins where the two disagree. DeCA carries 0.05 forced and 0.05 scheduled, 0.10 unavailable in all, for every thermal plant of the five countries it covers, with no distinction of country or technology. The 2020 model wrote 0.85 everywhere and named no source. Neither is a measurement; one has a document behind it. THAT RATE IS THE ANSWER FOR A PLANT THAT DOES NOT EXIST YET, and only for that. An existing unit is written at its own derating instead, DeCA stating an Available capacity beside the Installed one plant by plant, which is why this table could never have carried the decision even if the model let it: a technology rate cannot say that Turkmenbashi runs at 0.39 and the second Dushanbe set at 0.90. See pAvailabilityCustom, where both live. THE DECISION LANDS ON pAvailabilityCustom AND NOT HERE, which is worth stating because this file is the one that looks like it should carry it. The chain is in input_treatment.py: the custom table is read into pAvailabilityInput(g,q), expanded over the years into pAvailability(g,y,q), and only then is this default reached for, to fill the units the custom table left out. It leaves none out: 419 units, 419 lines. So this table is inert whatever it holds. IT STAYS EMPTY, AND THAT IS A DECISION THE MODEL FORCED. The build first filled it with the 98 (zone, tech, fuel) triples whose availability is a technology property, so that a generator added later without a line of its own would land on a stated number rather than on zero, and the run refused to compile: input_treatment.py:1403 skips the table when it is empty and input_treatment.py:1426 aborts when it is present and does not cover EVERY (zone, tech, fuel) of pGenDataInput. It is all or nothing. Covering everything would mean writing a default availability for hydro, solar, wind and imports, and for those the column is not an outage rate but the resource itself, the seasonal water of a reservoir or a profile that already carries the weather. A technology-level number must not stand behind plant-level data, so the table is left empty and the partial fill is kept out. build_hydro.py still writes extracted/pAvailabilityDefault.csv, which is the table that would be used if the day comes when every pair can honestly be given one. WHAT DID CHANGE HERE IS THE HEADER. It read z,tech,fuel,Q1,Q2, the two seasons of data_test, inherited when the folder was set up. This model has five, and the header carries the index of the parameter.</t>
+        </is>
+      </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Determines what the model is ALLOWED to build. Empty today: expansion is driven by pGenDataInput alone.</t>
+          <t>A measured outage rate would have to come from the TSOs, unit by unit, and would replace both the 0.90 of a candidate and the book derating of an existing unit. Ask for it with the fleet data request.</t>
         </is>
       </c>
     </row>
@@ -1683,61 +1683,57 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>pVREProfile</t>
+          <t>pGenDataInputDefault</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>supply/pVREProfile.csv</t>
+          <t>supply/pGenDataInputDefault.csv</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>solar and wind production by (z,tech,q,d,t), as a fraction of capacity</t>
+          <t>generic candidates by zone</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>filled, more to come</t>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>FILL</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, renewables_ninja, casa_2020</t>
+          <t>deca_v51</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>RenewableProfile, monthly utilization factors</t>
+          <t>PP Candidates + RenewableMaxEntry</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>2025 level / 2022 weather</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>PHASE 8 BUILT IT FROM TWO SOURCES BECAUSE NEITHER GIVES BOTH HALVES. base.gms:812 writes the output of every solar and wind unit as this profile times the availability times the capacity, so the table is the whole renewable production, in level as much as in shape. DeCA GIVES THE LEVEL AND NOT THE SHAPE: RenewableProfile states a monthly utilization factor per plant and no hour of the day. Its own header says so, in a line the authors left for themselves, "Hourly profiles are also needed for all WPP and SPP power plants". THE 2020 MODEL GIVES THE SHAPE and a level five years old. So the day shape comes from the 2020 profile, normalised to a mean of one, and is multiplied by the DeCA seasonal factor, the month length weighted mean over the months of the season and over the plants mappings/vre_profiles.csv selects. That is still how the table is built wherever the third source below cannot reach. THE FACTOR IS A COUNTRY MEAN over every plant of the technology, existing and candidate, high yield and low yield sites together, because the five books name no zone for their existing plants. That is an average site, which is what a generic candidate is. Eighty of the 160 seasonal factors move; the Afghan and Pakistani zones keep their 2020 level, being outside the DeCA perimeter. WHAT MOVES: mean solar capacity factor 0.174 to 0.169, mean wind 0.333 to 0.369. Solar loses most in winter, KAZ_N Q1 going from 0.144 to 0.089, which matters in a system that peaks in December. PHASE 9 PUT REAL WEATHER BEHIND 101 OF THE 160 ZONE-SEASONS, and changed no level at all: the annual capacity factor of all 32 series is the same to four decimals before and after. Two steps do it. build_vre_hourly.py takes the Renewables.ninja year fetched for 2022 and multiplies each zone, technology and month onto its stated DeCA factor, writing the plain PV_casa.csv and WT_casa.csv beside the _rninja files it read, so that the Poncelet clustering and this builder read the same corrected series rather than each rescaling its own copy. It refuses a series it would have to stretch more than twofold or that a single month cannot reach: ten wind series fail, all of them in mountain zones, and TAJ_S would have needed 23.6. Those ten keep the construction described above. build_vre.py then reads each block off the CALENDAR DAY it stands for, recorded by build_demand.py in extracted/demand_report.csv: the winter peak block is 12 December, the second late-summer block is 8 September. The three days of a season differ from each other for the first time -- Karachi solar in Q3b runs 0.244, 0.499 and 0.549 at its peak hour, a monsoon day beside two clear ones -- and one multiplier per season, bounded to 1.5 either way, puts the season back on its DeCA level without flattening those differences. A season needing more than that is one whose three days are not a sample of it, KAZ_N winter solar wanting 2.3 because the days it drew were overcast, and it falls back on its own without costing the other four seasons of the zone. THE 2020 SHAPE IS DRAWN BY MONTHS, NOT BY NAME, since phase 4 split the summer. Both halves take the 2020 Q3 day and are rescaled to their own DeCA factor, 0.208 for KAZ_N solar in Q3a against 0.207 in Q3b. Matching on the name instead handed July-September the 2020 peak block, a 130 h winter artefact, and produced a capacity factor of 1.24; the column that says which season feeds which lives in mappings/seasons_months.csv. AND A THIRD SOURCE FOR THE LEVEL WHERE DECA IS SILENT. A mapping row may carry level_source = atlas_p90, and eight do: the Afghan and Pakistani wind zones, which have no DeCA book and which the 2020 model gave the same 0.333 apiece. Those take their annual level from extracted/wind_atlas.csv and keep the 2020 seasonal shape. The override is applied in build_vre.py, which both builders share, because applying it in build_vre_hourly.py alone would lift the hourly year onto the atlas and let build_vre.py squash the representative days straight back onto the 2020 seasonal factor -- which is exactly what happened the first time, and cost NEPS_HERAT four of its five seasons. The order of preference is therefore DeCA, then the atlas, then 2020. TWO TRAPS THE MAPPING STEPS AROUND. The Tajik book labels its own regions with a KZ prefix, Khatlon and Sougd and Gorno-Badakhshan all reading "KZ ...", so the selection keys on the workbook and not on the name. And one Kazakh SOLAR plant is named Arm Wind: the exclude column of the mapping settles it on the _SP suffix, and the builder refuses outright any row two technologies claim at once.</t>
-        </is>
-      </c>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr"/>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>FORTY-NINE ZONE-SEASONS STILL CARRY THREE IDENTICAL DAYS, and 46 of them are wind. Thirty-five are a whole year at a time: every season of KAZ_S, KGZ_N, KGZ_S, NEPS_AFG, NEPS_TAJ, PAK_N and TAJ_S wind, where the fetched resource is still too far from the stated level to be rescaled into it. There is no calm day in those zones, only an average one. It was 59 before the wind points were moved. THE LEVEL OF THOSE SEVEN IS NOW RIGHT EVEN WHERE THE SHAPE IS NOT, which is the part worth saying plainly: NEPS_TAJ and PAK_N carry the atlas level on the 2020 flat day rather than an unreachable 0.333 on it, so the energy they contribute is defensible and only its hour-to-hour distribution is not. WHAT WOULD FIX THE REMAINING SEVEN, and it is not another multiplier. Renewables.ninja runs on MERRA-2 at half a degree, and on a Pamir or Hindu Kush ridge that grid does not represent the site at any coordinate you give it -- asked about the atlas's best ground in PAK_N it returns 0.015, LOWER than at the valley centroid it was asked about before. A reanalysis with real orography is the answer: ERA5-Land at 9 km through atlite, or a mesoscale run. Raising the twofold bound instead would buy the right annual mean at the price of a fabricated shape -- the hour-to-hour pattern of a dead valley, multiplied. ONE ZONE REGRESSED AND IT IS A JUDGEMENT CALL. KAZ_S passed on its centroid and fails on its atlas site, because the Dzungarian Gate is a ten kilometre gap that a half degree cell cannot hold. Keeping KAZ_S on its centroid is expressible in data -- the override column of extracted/zone_points.csv already outranks the atlas site -- and has not been done, because choosing per zone whichever point happens to pass is selection on the outcome and needs to be a decision taken openly rather than a rule the builder applies quietly. AND THE DAYS ARE STILL CHOSEN ON THE LOAD ALONE. build_demand.py picked the peak day and the median days without looking at the weather, so a still evening of high demand is in the set only by luck, and the seasonal multiplier that repairs the level is the measure of that luck. Choosing days on load and renewables jointly is the Poncelet clustering in pre-analysis/representative_days, which waits on the Pakistani and Afghan hourly load. THE YEARS DO NOT LINE UP EVERYWHERE either: DeCA load vintages, Kazakhstan 2022 and Tajikistan 2021 with the rest unstated, against a 2022 weather year. Kazakhstan is a true same-day pairing; elsewhere it is the same date of another year, which is seasonally right and synoptically a coincidence.</t>
+          <t>Determines what the model is ALLOWED to build. Empty today: expansion is driven by pGenDataInput alone.</t>
         </is>
       </c>
     </row>
@@ -1749,57 +1745,61 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>pCapexTrajectoriesCustom</t>
+          <t>pVREProfile</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>supply/pCapexTrajectoriesCustom.csv</t>
+          <t>supply/pVREProfile.csv</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>CAPEX by plant over time</t>
+          <t>solar and wind production by (z,tech,q,d,t), as a fraction of capacity</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>deca_v51</t>
+          <t>deca_v51, renewables_ninja, casa_2020</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>RenewableProfile, monthly utilization factors</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2025-2050</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr"/>
+          <t>2025 level / 2022 weather</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 8 BUILT IT FROM TWO SOURCES BECAUSE NEITHER GIVES BOTH HALVES. base.gms:812 writes the output of every solar and wind unit as this profile times the availability times the capacity, so the table is the whole renewable production, in level as much as in shape. DeCA GIVES THE LEVEL AND NOT THE SHAPE: RenewableProfile states a monthly utilization factor per plant and no hour of the day. Its own header says so, in a line the authors left for themselves, "Hourly profiles are also needed for all WPP and SPP power plants". THE 2020 MODEL GIVES THE SHAPE and a level five years old. So the day shape comes from the 2020 profile, normalised to a mean of one, and is multiplied by the DeCA seasonal factor, the month length weighted mean over the months of the season and over the plants mappings/vre_profiles.csv selects. That is still how the table is built wherever the third source below cannot reach. THE FACTOR IS A COUNTRY MEAN over every plant of the technology, existing and candidate, high yield and low yield sites together, because the five books name no zone for their existing plants. That is an average site, which is what a generic candidate is. Eighty of the 160 seasonal factors move; the Afghan and Pakistani zones keep their 2020 level, being outside the DeCA perimeter. WHAT MOVES: mean solar capacity factor 0.174 to 0.169, mean wind 0.333 to 0.369. Solar loses most in winter, KAZ_N Q1 going from 0.144 to 0.089, which matters in a system that peaks in December. PHASE 9 PUT REAL WEATHER BEHIND 101 OF THE 160 ZONE-SEASONS, and changed no level at all: the annual capacity factor of all 32 series is the same to four decimals before and after. Two steps do it. build_vre_hourly.py takes the Renewables.ninja year fetched for 2022 and multiplies each zone, technology and month onto its stated DeCA factor, writing the plain PV_casa.csv and WT_casa.csv beside the _rninja files it read, so that the Poncelet clustering and this builder read the same corrected series rather than each rescaling its own copy. It refuses a series it would have to stretch more than twofold or that a single month cannot reach: ten wind series fail, all of them in mountain zones, and TAJ_S would have needed 23.6. Those ten keep the construction described above. build_vre.py then reads each block off the CALENDAR DAY it stands for, recorded by build_demand.py in extracted/demand_report.csv: the winter peak block is 12 December, the second late-summer block is 8 September. The three days of a season differ from each other for the first time -- Karachi solar in Q3b runs 0.244, 0.499 and 0.549 at its peak hour, a monsoon day beside two clear ones -- and one multiplier per season, bounded to 1.5 either way, puts the season back on its DeCA level without flattening those differences. A season needing more than that is one whose three days are not a sample of it, KAZ_N winter solar wanting 2.3 because the days it drew were overcast, and it falls back on its own without costing the other four seasons of the zone. THE 2020 SHAPE IS DRAWN BY MONTHS, NOT BY NAME, since phase 4 split the summer. Both halves take the 2020 Q3 day and are rescaled to their own DeCA factor, 0.208 for KAZ_N solar in Q3a against 0.207 in Q3b. Matching on the name instead handed July-September the 2020 peak block, a 130 h winter artefact, and produced a capacity factor of 1.24; the column that says which season feeds which lives in mappings/seasons_months.csv. AND A THIRD SOURCE FOR THE LEVEL WHERE DECA IS SILENT. A mapping row may carry level_source = atlas_p90, and eight do: the Afghan and Pakistani wind zones, which have no DeCA book and which the 2020 model gave the same 0.333 apiece. Those take their annual level from extracted/wind_atlas.csv and keep the 2020 seasonal shape. The override is applied in build_vre.py, which both builders share, because applying it in build_vre_hourly.py alone would lift the hourly year onto the atlas and let build_vre.py squash the representative days straight back onto the 2020 seasonal factor -- which is exactly what happened the first time, and cost NEPS_HERAT four of its five seasons. The order of preference is therefore DeCA, then the atlas, then 2020. TWO TRAPS THE MAPPING STEPS AROUND. The Tajik book labels its own regions with a KZ prefix, Khatlon and Sougd and Gorno-Badakhshan all reading "KZ ...", so the selection keys on the workbook and not on the name. And one Kazakh SOLAR plant is named Arm Wind: the exclude column of the mapping settles it on the _SP suffix, and the builder refuses outright any row two technologies claim at once.</t>
+        </is>
+      </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Rebase in real 2025 USD (requirement of the template).</t>
+          <t>FORTY-NINE ZONE-SEASONS STILL CARRY THREE IDENTICAL DAYS, and 46 of them are wind. Thirty-five are a whole year at a time: every season of KAZ_S, KGZ_N, KGZ_S, NEPS_AFG, NEPS_TAJ, PAK_N and TAJ_S wind, where the fetched resource is still too far from the stated level to be rescaled into it. There is no calm day in those zones, only an average one. It was 59 before the wind points were moved. THE LEVEL OF THOSE SEVEN IS NOW RIGHT EVEN WHERE THE SHAPE IS NOT, which is the part worth saying plainly: NEPS_TAJ and PAK_N carry the atlas level on the 2020 flat day rather than an unreachable 0.333 on it, so the energy they contribute is defensible and only its hour-to-hour distribution is not. WHAT WOULD FIX THE REMAINING SEVEN, and it is not another multiplier. Renewables.ninja runs on MERRA-2 at half a degree, and on a Pamir or Hindu Kush ridge that grid does not represent the site at any coordinate you give it -- asked about the atlas's best ground in PAK_N it returns 0.015, LOWER than at the valley centroid it was asked about before. A reanalysis with real orography is the answer: ERA5-Land at 9 km through atlite, or a mesoscale run. Raising the twofold bound instead would buy the right annual mean at the price of a fabricated shape -- the hour-to-hour pattern of a dead valley, multiplied. FOUR ZONES REGRESSED AND THE DECISION WAS TAKEN TO LEAVE THEM. KAZ_S, NEPS_AFG, KGZ_N and PAK_N all passed on their centroid and fail on their atlas site. Each could be put back with the override column of extracted/zone_points.csv, which outranks the atlas site by design, and none has been: choosing per zone whichever point happens to clear the bound is selection on the outcome, and it would encode a coordinate we believe to be wrong for the sole reason that a reanalysis is comfortable there. KAZ_S is the clearest case -- its best ground is the Dzungarian Gate, a ten kilometre gap between mountain ranges, and MERRA-2 averages that gap into the plateau around it. The Gate is where the wind is and where turbines get built; the half degree cell is what is wrong. Giving KAZ_S its centroid back would model a plateau in place of a corridor and would look like an improvement only because a number would stop being refused. SO THOSE FOUR KEEP THE 2020 FLAT DAY FOR THEIR SHAPE, WITH A LEVEL THAT IS RIGHT: DeCA's for KAZ_S and KGZ_N, the atlas's for NEPS_AFG and PAK_N. That is the honest state -- the energy is defensible, the hour-to-hour distribution is not -- and it is what a mesoscale wind year would repair. AND THE DAYS ARE STILL CHOSEN ON THE LOAD ALONE. build_demand.py picked the peak day and the median days without looking at the weather, so a still evening of high demand is in the set only by luck, and the seasonal multiplier that repairs the level is the measure of that luck. Choosing days on load and renewables jointly is the Poncelet clustering in pre-analysis/representative_days, which waits on the Pakistani and Afghan hourly load. THE YEARS DO NOT LINE UP EVERYWHERE either: DeCA load vintages, Kazakhstan 2022 and Tajikistan 2021 with the rest unstated, against a 2022 weather year. Kazakhstan is a true same-day pairing; elsewhere it is the same date of another year, which is seasonally right and synoptically a coincidence.</t>
         </is>
       </c>
     </row>
@@ -1811,26 +1811,26 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>pCapexTrajectoriesDefault</t>
+          <t>pCapexTrajectoriesCustom</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>supply/pCapexTrajectoriesDefault.csv</t>
+          <t>supply/pCapexTrajectoriesCustom.csv</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>CAPEX by (zone,tech,fuel)</t>
+          <t>CAPEX by plant over time</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>done</t>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1838,7 +1838,7 @@
           <t>FILL</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1855,15 +1855,15 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>2023-2050, normalised at 2026</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>PHASE 5 done. The table was empty, so every candidate cost the same in 2050 as in 2026. It now carries the DeCA cost curve as a multiplier normalised at 2026, for solar, wind and the battery, in every zone: solar to 0.46 by 2050, wind to 0.88, the four-hour battery to 0.64. Applied in every zone, Pakistan and Afghanistan included, because the five DeCA books carry the same CAPEX sheet byte for byte. That makes it a technology curve and not a country one, and there is no reason a Pakistani panel would be spared a fall in the world price of panels. The battery rows stop at the DeCA perimeter, only because that is where the battery candidates are. PHASE 8 HAD TO COMPLETE THE TABLE, and the reason is worth recording because it contradicts what phase 5 wrote here. Leaving thermal out is not neutral: input_treatment.py joins this table on the (zone, tech, fuel) of EVERY generator of the fleet and stops the run when one of them finds no row, "Missing values in default is not permitted". Forty rows against a hundred and thirty-eight triples was an aborted run, not a flat cost. So the builder now writes a FLAT CURVE, one everywhere, for every triple the fleet carries and the cost curve says nothing about: a gas turbine of 2050 is assumed to cost in real terms what it costs today, which is what DeCA says of it and what the model would otherwise have assumed by default. The DeCA curve still applies to solar, wind and the battery alone, and the print of build_fleet.py says how many rows are on a curve.</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr"/>
+          <t>2025-2050</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>Rebase in real 2025 USD (requirement of the template).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1873,63 +1873,59 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>pFuelPrice</t>
+          <t>pCapexTrajectoriesDefault</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>supply/pFuelPrice.csv</t>
+          <t>supply/pCapexTrajectoriesDefault.csv</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>fuel prices by country (c,fuel,year)</t>
+          <t>CAPEX by (zone,tech,fuel)</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>filled, more to come</t>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>done</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>FILL</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, casa_2020</t>
+          <t>deca_v51</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Fuel Prices for gas and nuclear, Thermal PP column Local Fuel Costs Adopted for coal</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2024-2060 real 2021 USD, read on 2026-2050</t>
+          <t>2023-2050, normalised at 2026</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>PHASE 6 done. THE TABLE WAS THE MOST DAMAGING DEFECT LEFT IN THE MODEL: it ran 2017 to 2030 against a horizon that runs 2026 to 2050, and main.gms:737 reads pFuelCost = pFuelPrice * pHeatRate with no interpolation and no default, so every fuel in every zone was FREE from 2031 on. Half the horizon was arbitrating thermal against renewable at zero fuel cost. Rebuilt by build_costs.py from mappings/fuel_prices.csv, which carries the 25 country and fuel pairs one by one. 8 rest on DeCA and 17 keep the 2020 series held flat: DeCA prices neither heavy fuel oil nor LNG, Pakistan and Afghanistan are outside its perimeter, and its coal is unusable in two of the five countries, see below. GAS AND NUCLEAR COME FROM THE Fuel Prices SHEET. Gas is already in $/MMBtu and is taken as it stands; the stated method is the actual 2024 price of each country converging linearly to the netback value of the Chinese gas price by 2030, which is a documented economic price and the right thing for a planning model. Nuclear is stated at 2.92 $/MWh of electricity and divided by the heat rate the model itself carries for its uranium units, 8.322 MMBtu/MWh, giving 0.3509 $/MMBtu against 0.3842 in the 2020 model, a 9 per cent gap that is a good check on the method. Where the transport adder of DeCA is a national constant it is added here: Uzbek gas 1.866 over 22 units, Turkmen gas 0.140 over 17. COAL DOES NOT COME FROM THAT SHEET, and this is the judgement of the phase. The sheet is headed International Prices, its coal row is the same 33.53 $/mt in all five countries and in every year from 2024 to 2060, and the convergence method printed underneath is written for gas alone. It is the seaborne benchmark. Nobody burns Angren lignite or Ekibastuz coal at the seaborne price, and taking it would have tripled Kazakh coal and quadrupled Uzbek coal on no evidence at all. Coal is read instead from the Local Fuel Costs Adopted column of Thermal PP, the price DeCA fed its own plants. THAT COLUMN IS FILLED FOR TWO BOOKS ONLY, and not in the same unit in both: in UZ it is $/MWh of electricity, the product of the value and the plant efficiency being constant at 9.0 to 9.4 across the 22 gas units, while in KG it is $/MMBtu per plant. Reconverted and capacity weighted it gives 3.438 $/MMBtu for Angren, against 1.202 in the 2020 model, and 2.684 for Kyrgyzstan, against 4.280. Both are delivered prices per plant, so no transport is added on top and NO CALORIFIC VALUE IS ASSUMED ANYWHERE, which removes what was the weakest link of an earlier draft of this table. KAZAKH AND TAJIK COAL THEREFORE HAVE NO DeCA PRICE AT ALL: those books leave the local column empty. They keep the 2020 model held flat, which also preserves the 1.467 delivered ratio between northern and southern Kazakhstan. KAZAKH GAS TRANSPORT IS NOT HERE EITHER. It is the one genuinely regional fuel cost in the region, 0 on the Atyrau gas fields to 13.3 at the end of the pipeline in Akmola, a spread wider than the commodity itself. A national mean would be meaningless when the model carries two Kazakh gas plants sitting at opposite ends of that range, so each takes its own through its VOM. See pGenDataInput. WHAT IT DOES TO THE MERIT ORDER, short-run marginal cost in 2026, before and after: Ekibastuz 19.7 to 19.5 $/MWh, Aksu 19.7 to 18.4, Astana-2 22.5 to 26.9, Angren 24.0 to 47.9, Novo-Angren 24.3 to 46.3, Bishkek 60.9 to 43.0, Syrdarya 68.0 to 73.1, Mary 57.3 to 40.0, Zhambyl 67.2 to 50.0. Uzbek coal doubling is the one number to challenge, and it is DeCA saying the 2020 model priced it too low.</t>
-        </is>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>1. KAZAKH AND TAJIK COAL ARE THE FIRST DATA REQUEST of this phase: neither book states a local price, so both still rest on a 2020 figure held flat to 2050. The Kazakh one matters most, it prices roughly 10 GW of the fleet. 2. Coal carries no trajectory anywhere: the two DeCA local prices are single 2020 figures and the other two are held flat. Nothing in this table makes coal dearer or cheaper over twenty-five years. 3. Heavy fuel oil, LNG, and everything Pakistani and Afghan rest on the 2020 model held flat. Pakistan needs the NTDC IGCEP fuel assumptions.</t>
-        </is>
-      </c>
+          <t>PHASE 5 done. The table was empty, so every candidate cost the same in 2050 as in 2026. It now carries the DeCA cost curve as a multiplier normalised at 2026, for solar, wind and the battery, in every zone: solar to 0.46 by 2050, wind to 0.88, the four-hour battery to 0.64. Applied in every zone, Pakistan and Afghanistan included, because the five DeCA books carry the same CAPEX sheet byte for byte. That makes it a technology curve and not a country one, and there is no reason a Pakistani panel would be spared a fall in the world price of panels. The battery rows stop at the DeCA perimeter, only because that is where the battery candidates are. PHASE 8 HAD TO COMPLETE THE TABLE, and the reason is worth recording because it contradicts what phase 5 wrote here. Leaving thermal out is not neutral: input_treatment.py joins this table on the (zone, tech, fuel) of EVERY generator of the fleet and stops the run when one of them finds no row, "Missing values in default is not permitted". Forty rows against a hundred and thirty-eight triples was an aborted run, not a flat cost. So the builder now writes a FLAT CURVE, one everywhere, for every triple the fleet carries and the cost curve says nothing about: a gas turbine of 2050 is assumed to cost in real terms what it costs today, which is what DeCA says of it and what the model would otherwise have assumed by default. The DeCA curve still applies to solar, wind and the battery alone, and the print of build_fleet.py says how many rows are on a curve.</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1939,61 +1935,61 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>pStorageDataInput</t>
+          <t>pFuelPrice</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>supply/pStorageDataInput.csv</t>
+          <t>supply/pFuelPrice.csv</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>storage (batteries, pumped hydro)</t>
+          <t>fuel prices by country (c,fuel,year)</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>structure adapted, data to do</t>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, assumed</t>
+          <t>deca_v51, casa_2020</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>CAPEX, columns 2h / 4h / 6h / 8h BESS</t>
+          <t>Fuel Prices for gas and nuclear, Thermal PP column Local Fuel Costs Adopted for coal</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>2023-2060, read at 2026</t>
+          <t>2024-2060 real 2021 USD, read on 2026-2050</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>PHASE 5 done. The table was empty, in a model that runs to 2050. It now carries one four-hour battery candidate per Central Asian zone, eight of them, open from 2028. The cost is read, not assumed. DeCA prices a battery at 2, 4, 6 and 8 hours and those four prices are exactly linear in duration in every year from 2023 to 2060, so the slope is the cost of an hour of energy and the intercept is the cost of the power: 247,638 $/MW and 202.3 $/kWh in 2026, falling to 198,754 $/MW and 118.2 $/kWh in 2050. build_fleet.py re-checks that linearity and refuses to write anything if a later version of the book breaks it. Four hours is a choice, and it is the one that makes EPM exact: EPM applies a single CAPEX multiplier to both the power and the energy part of a battery, and those two decline at different rates in DeCA. At a fixed duration the multiplier is exact on the total, which is what is being bought. The perimeter is the five DeCA countries, mappings/country_book.csv. Pakistan and Afghanistan keep no storage, as in the 2020 model. DeCA gives no round-trip efficiency and no operating life for storage: 0.9 and 20 years are the EPM reference values, data_test. PHASE 5 SWITCHED IT ON. fEnableStorage was 0, and under a 0 base.gms generates none of the storage balance, charge and state-of-charge equations, so these eight rows were read into the model and then never entered one: the candidate existed and could not be built. The flag is now set by the build, see pSettings. The chronology it was waiting on arrived with phase 3, 24 consecutive hours on each of three representative days per season, which is what a four-hour battery needs in order to have something to arbitrage.</t>
+          <t>PHASE 6 done. THE TABLE WAS THE MOST DAMAGING DEFECT LEFT IN THE MODEL: it ran 2017 to 2030 against a horizon that runs 2026 to 2050, and main.gms:737 reads pFuelCost = pFuelPrice * pHeatRate with no interpolation and no default, so every fuel in every zone was FREE from 2031 on. Half the horizon was arbitrating thermal against renewable at zero fuel cost. Rebuilt by build_costs.py from mappings/fuel_prices.csv, which carries the 25 country and fuel pairs one by one. 8 rest on DeCA and 17 keep the 2020 series held flat: DeCA prices neither heavy fuel oil nor LNG, Pakistan and Afghanistan are outside its perimeter, and its coal is unusable in two of the five countries, see below. GAS AND NUCLEAR COME FROM THE Fuel Prices SHEET. Gas is already in $/MMBtu and is taken as it stands; the stated method is the actual 2024 price of each country converging linearly to the netback value of the Chinese gas price by 2030, which is a documented economic price and the right thing for a planning model. Nuclear is stated at 2.92 $/MWh of electricity and divided by the heat rate the model itself carries for its uranium units, 8.322 MMBtu/MWh, giving 0.3509 $/MMBtu against 0.3842 in the 2020 model, a 9 per cent gap that is a good check on the method. Where the transport adder of DeCA is a national constant it is added here: Uzbek gas 1.866 over 22 units, Turkmen gas 0.140 over 17. COAL DOES NOT COME FROM THAT SHEET, and this is the judgement of the phase. The sheet is headed International Prices, its coal row is the same 33.53 $/mt in all five countries and in every year from 2024 to 2060, and the convergence method printed underneath is written for gas alone. It is the seaborne benchmark. Nobody burns Angren lignite or Ekibastuz coal at the seaborne price, and taking it would have tripled Kazakh coal and quadrupled Uzbek coal on no evidence at all. Coal is read instead from the Local Fuel Costs Adopted column of Thermal PP, the price DeCA fed its own plants. THAT COLUMN IS FILLED FOR TWO BOOKS ONLY, and not in the same unit in both: in UZ it is $/MWh of electricity, the product of the value and the plant efficiency being constant at 9.0 to 9.4 across the 22 gas units, while in KG it is $/MMBtu per plant. Reconverted and capacity weighted it gives 3.438 $/MMBtu for Angren, against 1.202 in the 2020 model, and 2.684 for Kyrgyzstan, against 4.280. Both are delivered prices per plant, so no transport is added on top and NO CALORIFIC VALUE IS ASSUMED ANYWHERE, which removes what was the weakest link of an earlier draft of this table. KAZAKH AND TAJIK COAL THEREFORE HAVE NO DeCA PRICE AT ALL: those books leave the local column empty. They keep the 2020 model held flat, which also preserves the 1.467 delivered ratio between northern and southern Kazakhstan. KAZAKH GAS TRANSPORT IS NOT HERE EITHER. It is the one genuinely regional fuel cost in the region, 0 on the Atyrau gas fields to 13.3 at the end of the pipeline in Akmola, a spread wider than the commodity itself. A national mean would be meaningless when the model carries two Kazakh gas plants sitting at opposite ends of that range, so each takes its own through its VOM. See pGenDataInput. WHAT IT DOES TO THE MERIT ORDER, short-run marginal cost in 2026, before and after: Ekibastuz 19.7 to 19.5 $/MWh, Aksu 19.7 to 18.4, Astana-2 22.5 to 26.9, Angren 24.0 to 47.9, Novo-Angren 24.3 to 46.3, Bishkek 60.9 to 43.0, Syrdarya 68.0 to 73.1, Mary 57.3 to 40.0, Zhambyl 67.2 to 50.0. Uzbek coal doubling is the one number to challenge, and it is DeCA saying the 2020 model priced it too low.</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Pumped storage is a separate question: DeCA carries Hodjikent PSH-2 in Uzbekistan, which sits in pGenDataInput as a hydro candidate rather than here.</t>
+          <t>1. KAZAKH AND TAJIK COAL ARE THE FIRST DATA REQUEST of this phase: neither book states a local price, so both still rest on a 2020 figure held flat to 2050. The Kazakh one matters most, it prices roughly 10 GW of the fleet. 2. Coal carries no trajectory anywhere: the two DeCA local prices are single 2020 figures and the other two are held flat. Nothing in this table makes coal dearer or cheaper over twenty-five years. 3. Heavy fuel oil, LNG, and everything Pakistani and Afghan rest on the 2020 model held flat. Pakistan needs the NTDC IGCEP fuel assumptions.</t>
         </is>
       </c>
     </row>
@@ -2005,43 +2001,63 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>pEvolutionAvailability</t>
+          <t>pStorageDataInput</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>supply/pEvolutionAvailability.csv</t>
+          <t>supply/pStorageDataInput.csv</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>availability drift over time</t>
+          <t>storage (batteries, pumped hydro)</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>out of scope</t>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>structure adapted, data to do</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>FILL</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="4" t="inlineStr"/>
-      <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>deca_v51, assumed</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>CAPEX, columns 2h / 4h / 6h / 8h BESS</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>2023-2060, read at 2026</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 5 done. The table was empty, in a model that runs to 2050. It now carries one four-hour battery candidate per Central Asian zone, eight of them, open from 2028. The cost is read, not assumed. DeCA prices a battery at 2, 4, 6 and 8 hours and those four prices are exactly linear in duration in every year from 2023 to 2060, so the slope is the cost of an hour of energy and the intercept is the cost of the power: 247,638 $/MW and 202.3 $/kWh in 2026, falling to 198,754 $/MW and 118.2 $/kWh in 2050. build_fleet.py re-checks that linearity and refuses to write anything if a later version of the book breaks it. Four hours is a choice, and it is the one that makes EPM exact: EPM applies a single CAPEX multiplier to both the power and the energy part of a battery, and those two decline at different rates in DeCA. At a fixed duration the multiplier is exact on the total, which is what is being bought. The perimeter is the five DeCA countries, mappings/country_book.csv. Pakistan and Afghanistan keep no storage, as in the 2020 model. DeCA gives no round-trip efficiency and no operating life for storage: 0.9 and 20 years are the EPM reference values, data_test. PHASE 5 SWITCHED IT ON. fEnableStorage was 0, and under a 0 base.gms generates none of the storage balance, charge and state-of-charge equations, so these eight rows were read into the model and then never entered one: the candidate existed and could not be built. The flag is now set by the build, see pSettings. The chronology it was waiting on arrived with phase 3, 24 consecutive hours on each of three representative days per season, which is what a four-hour battery needs in order to have something to arbitrage.</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Pumped storage is a separate question: DeCA carries Hodjikent PSH-2 in Uzbekistan, which sits in pGenDataInput as a hydro candidate rather than here.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2051,17 +2067,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>pCSPData</t>
+          <t>pEvolutionAvailability</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>supply/pCSPData.csv</t>
+          <t>supply/pEvolutionAvailability.csv</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>concentrated solar power</t>
+          <t>availability drift over time</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -2078,7 +2094,7 @@
           <t>SKIP</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -2087,97 +2103,77 @@
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="4" t="inlineStr"/>
       <c r="M27" s="4" t="inlineStr"/>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Fleet</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>pCSPData</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>supply/pCSPData.csv</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>concentrated solar power</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>out of scope</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>No CSP in the perimeter.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Trade</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-      <c r="N28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Trade</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>pTransferLimit</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>trade/pTransferLimit.csv</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>NTC by corridor x season x year</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>210</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>deca_v51, casa_2020, tso_request</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>TJ &gt; Exchanges ; KZ &gt; Exchanges with non CA countries</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>2024-2060</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Rebuilt from data_build/mappings/corridors.csv, which carries the 42 directed corridors with their anchor years and, for each, the source it rests on. Three corrections against the 2020 model. Turkmenistan to Afghanistan: the two directions were swapped, the 80 MW leg could not carry the 2100 GWh/y that pMaxAnnualTransfer requires. CASA-1000 to Pakistan: 1000 MW and not 1300, the 1300 being the rating of the whole DC link including the Afghan tap. Tajikistan to Afghanistan: 188 MW all year plus a May-September window at 638 MW, which is the first seasonal corridor of the model. That window is written in months and not in season names, so the phase 4 split carried it into Q3a and Q3b by itself. The file used to carry Q5 rows inherited from the 2020 season set while pHours had only four seasons: the season set now comes from seasons_months.csv like every other seasonal resource, so the two cannot drift apart again.</t>
-        </is>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>DONE for the corridors that have a source. Two gaps left, both needing an external answer: the intra-CAPS NTCs rest on the 2020 model alone (TSO request pending), and the Surkhan to Puli-Khumri 500 kV between Uzbekistan and Afghanistan is not in any source we hold, so UZB to NEPS_UZB stays at 400 MW.</t>
-        </is>
-      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2187,21 +2183,21 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>pContractedTradeFlag</t>
+          <t>pTransferLimit</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>trade/pContractedTradeFlag.csv</t>
+          <t>trade/pTransferLimit.csv</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>contracted corridors, by season</t>
+          <t>NTC by corridor x season x year</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
@@ -2221,19 +2217,27 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>casa1000_ppa</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr"/>
+          <t>deca_v51, casa_2020, tso_request</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>TJ &gt; Exchanges ; KZ &gt; Exchanges with non CA countries</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>2024-2060</t>
+        </is>
+      </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>NO LONGER WRITTEN BY HAND, and no longer naming a season. The window of the contract is declared in months in data_build/mappings/contracts.csv, 1 May to 30 September for the five CASA-1000 legs, and the build turns it into whatever seasons cover those months. Phase 4 split the summer in two and the flags followed on their own: ten rows now, Q3a and Q3b for each leg, where there were five on the single 2020 summer. Two of the five legs carry no volume on purpose; the contracted equality then reads zero and holds the counter-flow shut, which is how the 2020 model suppressed them.</t>
+          <t>Rebuilt from data_build/mappings/corridors.csv, which carries the 42 directed corridors with their anchor years and, for each, the source it rests on. Three corrections against the 2020 model. Turkmenistan to Afghanistan: the two directions were swapped, the 80 MW leg could not carry the 2100 GWh/y that pMaxAnnualTransfer requires. CASA-1000 to Pakistan: 1000 MW and not 1300, the 1300 being the rating of the whole DC link including the Afghan tap. Tajikistan to Afghanistan: 188 MW all year plus a May-September window at 638 MW, which is the first seasonal corridor of the model. That window is written in months and not in season names, so the phase 4 split carried it into Q3a and Q3b by itself. The file used to carry Q5 rows inherited from the 2020 season set while pHours had only four seasons: the season set now comes from seasons_months.csv like every other seasonal resource, so the two cannot drift apart again.</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>DONE. The build refuses a window that takes part of a season, so a later re-cut of the year cannot move the contract silently: it stops.</t>
+          <t>DONE for the corridors that have a source. Two gaps left, both needing an external answer: the intra-CAPS NTCs rest on the 2020 model alone (TSO request pending), and the Surkhan to Puli-Khumri 500 kV between Uzbekistan and Afghanistan is not in any source we hold, so UZB to NEPS_UZB stays at 400 MW.</t>
         </is>
       </c>
     </row>
@@ -2245,26 +2249,26 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>pContractedTradeEnergy</t>
+          <t>pContractedTradeFlag</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>trade/pContractedTradeEnergy.csv</t>
+          <t>trade/pContractedTradeFlag.csv</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>contracted energy GWh by corridor</t>
+          <t>contracted corridors, by season</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>filled, more to come</t>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>done</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2279,23 +2283,19 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>casa1000_ppa, casa_2020, assumed</t>
+          <t>casa1000_ppa</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>2022-2030 held to 2050</t>
-        </is>
-      </c>
+      <c r="L31" s="4" t="inlineStr"/>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Re-based on the model years. The volumes stopped at 2030, so the contract simply disappeared from 2031 on, a year GAMS reads as zero. The 2030 value is now held to 2050, which ASSUMES the contract is renewed. The three flows total 4343 GWh over the window, against a 4434 GWh plateau in the PPA note: consistent. PHASE 4 SPLIT THE VOLUME, IT DID NOT DUPLICATE IT. The contracted equality of base.gms is written season by season, so the May-September total is now shared between Q3a and Q3b PRO RATA BY DAYS, 61 against 92: KGZ_S to TAJ_N goes from 1595 GWh on one season to 636 and 959 on two. Copying the figure into both would have doubled every contracted flow of the model. The seasons of the reference table are ignored on the way in, only the pair and the yearly total are kept: Q3 there was the 2020 way of cutting the year, not a property of the contract.</t>
+          <t>NO LONGER WRITTEN BY HAND, and no longer naming a season. The window of the contract is declared in months in data_build/mappings/contracts.csv, 1 May to 30 September for the five CASA-1000 legs, and the build turns it into whatever seasons cover those months. Phase 4 split the summer in two and the flags followed on their own: ten rows now, Q3a and Q3b for each leg, where there were five on the single 2020 summer. Two of the five legs carry no volume on purpose; the contracted equality then reads zero and holds the counter-flow shut, which is how the 2020 model suppressed them.</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Needs the PPA file, still to be located, to replace the assumption by the real schedule: year 1 is said to be 2028 and the term 15 years, so the flows should start in 2028 and stop in 2042, where the model holds them flat throughout.</t>
+          <t>DONE. The build refuses a window that takes part of a season, so a later re-cut of the year cannot move the contract silently: it stops.</t>
         </is>
       </c>
     </row>
@@ -2307,53 +2307,57 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>pHistoricalTradeFlag</t>
+          <t>pContractedTradeEnergy</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>trade/pHistoricalTradeFlag.csv</t>
+          <t>trade/pContractedTradeEnergy.csv</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>corridors capped at historical levels</t>
+          <t>contracted energy GWh by corridor</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>REVISE</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>casa_2020</t>
+          <t>casa1000_ppa, casa_2020, assumed</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr"/>
+          <t>2022-2030 held to 2050</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Re-based on the model years. The volumes stopped at 2030, so the contract simply disappeared from 2031 on, a year GAMS reads as zero. The 2030 value is now held to 2050, which ASSUMES the contract is renewed. The three flows total 4343 GWh over the window, against a 4434 GWh plateau in the PPA note: consistent. PHASE 4 SPLIT THE VOLUME, IT DID NOT DUPLICATE IT. The contracted equality of base.gms is written season by season, so the May-September total is now shared between Q3a and Q3b PRO RATA BY DAYS, 61 against 92: KGZ_S to TAJ_N goes from 1595 GWh on one season to 636 and 959 on two. Copying the figure into both would have doubled every contracted flow of the model. The seasons of the reference table are ignored on the way in, only the pair and the yearly total are kept: Q3 there was the 2020 way of cutting the year, not a property of the contract.</t>
+        </is>
+      </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Only acts until 2021: becomes inert if the model starts later.</t>
+          <t>Needs the PPA file, still to be located, to replace the assumption by the real schedule: year 1 is said to be 2028 and the term 15 years, so the flows should start in 2028 and stop in 2042, where the model holds them flat throughout.</t>
         </is>
       </c>
     </row>
@@ -2365,36 +2369,36 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>pLossFactorInternal</t>
+          <t>pHistoricalTradeFlag</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>trade/pLossFactorInternal.csv</t>
+          <t>trade/pHistoricalTradeFlag.csv</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>losses by corridor (0.5 % everywhere)</t>
+          <t>corridors capped at historical levels</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>inherited, fit for purpose</t>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>KEEP</t>
+          <t>REVISE</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2408,12 +2412,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>Uniform inherited value, low stakes.</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>Only acts until 2021: becomes inert if the model starts later.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2423,36 +2427,36 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>pMaxAnnualTransfer</t>
+          <t>pLossFactorInternal</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>trade/pMaxAnnualTransfer.csv</t>
+          <t>trade/pLossFactorInternal.csv</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>annual trade cap by corridor</t>
+          <t>losses by corridor (0.5 % everywhere)</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>inherited, fit for purpose</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>REVISE</t>
+          <t>KEEP</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2466,12 +2470,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>8 corridors only. Check consistency with the new NTCs.</t>
-        </is>
-      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Uniform inherited value, low stakes.</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2481,21 +2485,21 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>pNewTransmission</t>
+          <t>pMaxAnnualTransfer</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>trade/pNewTransmission.csv</t>
+          <t>trade/pMaxAnnualTransfer.csv</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>candidate lines for construction</t>
+          <t>annual trade cap by corridor</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="7" t="inlineStr">
@@ -2505,25 +2509,29 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
+          <t>REVISE</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>mercados_plexos</t>
+          <t>casa_2020</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr"/>
-      <c r="L35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
       <c r="M35" s="4" t="inlineStr"/>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Empty = frozen grid. To test reinforcements (including a CASA-1000 phase 2), it has to be filled.</t>
+          <t>8 corridors only. Check consistency with the new NTCs.</t>
         </is>
       </c>
     </row>
@@ -2535,45 +2543,49 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>pMinImport</t>
+          <t>pNewTransmission</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>trade/pMinImport.csv</t>
+          <t>trade/pNewTransmission.csv</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>mandatory minimum import</t>
+          <t>candidate lines for construction</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>out of scope</t>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>mercados_plexos</t>
+        </is>
+      </c>
       <c r="K36" s="4" t="inlineStr"/>
       <c r="L36" s="4" t="inlineStr"/>
       <c r="M36" s="4" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Alternative to pContractedTrade should a firm offtake be needed.</t>
+          <t>Empty = frozen grid. To test reinforcements (including a CASA-1000 phase 2), it has to be filled.</t>
         </is>
       </c>
     </row>
@@ -2585,36 +2597,36 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>pExtTransferLimit</t>
+          <t>pMinImport</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>trade/pExtTransferLimit.csv</t>
+          <t>trade/pMinImport.csv</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>NTC towards external zones</t>
+          <t>mandatory minimum import</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>DECIDE</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr"/>
@@ -2623,7 +2635,7 @@
       <c r="M37" s="4" t="inlineStr"/>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>At stake: Russia (KAZ_N), Iran (HERAT), China, India. Today the Iranian import is modelled as a POWER PLANT (IRAN_Import, 400 MW), not as an exchange.</t>
+          <t>Alternative to pContractedTrade should a firm offtake be needed.</t>
         </is>
       </c>
     </row>
@@ -2635,17 +2647,17 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>pTradePrice</t>
+          <t>pExtTransferLimit</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>trade/pTradePrice.csv</t>
+          <t>trade/pExtTransferLimit.csv</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>prices at the external borders</t>
+          <t>NTC towards external zones</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -2662,22 +2674,18 @@
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>assumed</t>
-        </is>
-      </c>
+      <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr"/>
       <c r="L38" s="4" t="inlineStr"/>
       <c r="M38" s="4" t="inlineStr"/>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>No source. To be built consistently and owned as an assumption.</t>
+          <t>At stake: Russia (KAZ_N), Iran (HERAT), China, India. Today the Iranian import is modelled as a POWER PLANT (IRAN_Import, 400 MW), not as an exchange.</t>
         </is>
       </c>
     </row>
@@ -2689,17 +2697,17 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>zext</t>
+          <t>pTradePrice</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>trade/zext.csv</t>
+          <t>trade/pTradePrice.csv</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>list of external zones</t>
+          <t>prices at the external borders</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -2716,18 +2724,22 @@
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr"/>
       <c r="M39" s="4" t="inlineStr"/>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>Depends on pExtTransferLimit.</t>
+          <t>No source. To be built consistently and owned as an assumption.</t>
         </is>
       </c>
     </row>
@@ -2739,129 +2751,121 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>pMaxAnnualExternalTradeShare</t>
+          <t>zext</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>trade/pMaxAnnualExternalTradeShare.csv</t>
+          <t>trade/zext.csv</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>max share of external trade</t>
+          <t>list of external zones</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>done</t>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>casa_2020</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr"/>
       <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr"/>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr"/>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>Depends on pExtTransferLimit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>pMaxAnnualExternalTradeShare</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>trade/pMaxAnnualExternalTradeShare.csv</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>max share of external trade</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>casa_2020</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="inlineStr"/>
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>The header carried the countries of an African study (Angola, Burundi, Cameroon, CAR, Chad, Congo, DRC, Equatorial Guinea, Gabon, Rwanda, Sao Tome). Replaced by the seven countries of the perimeter. The file holds no row: the parameter is empty either way, but the index was wrong.</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="N41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Constraints</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Constraints</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>pCarbonPrice</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>constraint/pCarbonPrice.csv</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>carbon price 32 -&gt; 50 $/t</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>casa_2020</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>DATA PRESENT BUT INACTIVE (fEnableCarbonPrice = 0). Turning it on is the cheapest lever to correct the 17 GW of new coal in Kazakhstan. PHASE 6.4 LEFT IT ALONE, ON PURPOSE, but it carries the same 2030 cliff as the fuel limits did: the series runs 2017 to 2030 and main.gms reads it year by year, so switching the flag on today would price carbon at 50 $/t to 2030 and at nothing whatever afterwards, which is worse than not pricing it at all. It has to be extended to 2050 in the same movement as it is enabled, and that is phase 9 with the scenarios, alongside the emission caps above and the CCS candidates DeCA prices and this model does not carry.</t>
-        </is>
-      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="n"/>
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" s="3" t="n"/>
+      <c r="N42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -2871,27 +2875,23 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>pEmissionsCountry</t>
+          <t>pCarbonPrice</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>constraint/pEmissionsCountry.csv</t>
+          <t>constraint/pCarbonPrice.csv</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>CO2 cap by country, tons</t>
+          <t>carbon price 32 -&gt; 50 $/t</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="7" t="inlineStr">
         <is>
           <t>inherited 2020, to process</t>
@@ -2899,37 +2899,29 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>deca_v51</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>Emissions</t>
-        </is>
-      </c>
+          <t>casa_2020</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr"/>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>2030-2060</t>
-        </is>
-      </c>
-      <c r="M43" s="4" t="inlineStr">
-        <is>
-          <t>PHASE 6.4 PREPARED BUT DELIBERATELY NOT WIRED IN. The file stays empty and fApplyCountryCo2Constraint stays 0. build_constraints.py writes the DeCA path out to extracted/pEmissionsCountry_netzero.csv, on the horizon and in the tons EPM counts in, so that phase 9 can switch it on in one line once three things are settled. The path itself: the first Net Zero row of each Emissions sheet, five books of the seven countries, held flat before the first year it states and interpolated between the years it does. Kazakhstan 93.1 MtCO2-eq in 2030 to 4.66 in 2050, Uzbekistan 63.3 to 3.16, Turkmenistan 16.3 to 0.82, Tajikistan 4.17 to 0.21, Kyrgyzstan 1.36 to 0.068. Each is built by DeCA off the country NDC and then run down to a residual by 2060, and each book states its own arithmetic: Kazakhstan takes a third of the 1990 heat and power sector, Turkmenistan 0.85 of energy times 0.36 of electricity and heat, and so on. THE UZ BOOK STATES THE PATH TWICE, once economy-wide and once for electricity and heat at three tenths of it, and it is the sector row that is read. WHY IT IS NOT A BASELINE. It is a scenario, DeCA says so, and dropping it into the reference case would silently make the reference case a net zero case.</t>
-        </is>
-      </c>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr"/>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>PHASE 9, THE THREE THINGS TO SETTLE BEFORE THIS BECOMES A CONSTRAINT. 1. SCOPE. The path covers ELECTRICITY AND HEAT and EPM carries no heat. In Kazakhstan heat was 87.1 of the 112.4 MtCO2-eq the sector emitted in 1990, so a heat and power cap read onto a power only model is loose by a factor nobody has measured, and the Kazakh CHPs sit on both sides of that line. 2. COVERAGE. base.gms:1253 writes eEmissionsCountry for EVERY country at once when the flag is on, and a country absent from the table gets a cap of zero, softened only by the penalised backstop. Pakistan and Afghanistan have no NDC path in these books, so switching the flag on with this file as it stands would order them to emit nothing. Either they get a path of their own or the constraint has to be written for a subset. 3. THE FIRST FOUR YEARS. Nothing is stated before 2030, so the path is held flat backwards to 2026, which binds four years earlier than any NDC intended. Harmless while the cap is loose, not harmless if it is tight.</t>
+          <t>DATA PRESENT BUT INACTIVE (fEnableCarbonPrice = 0). Turning it on is the cheapest lever to correct the 17 GW of new coal in Kazakhstan. PHASE 6.4 LEFT IT ALONE, ON PURPOSE, but it carries the same 2030 cliff as the fuel limits did: the series runs 2017 to 2030 and main.gms reads it year by year, so switching the flag on today would price carbon at 50 $/t to 2030 and at nothing whatever afterwards, which is worse than not pricing it at all. It has to be extended to 2050 in the same movement as it is enabled, and that is phase 9 with the scenarios, alongside the emission caps above and the CCS candidates DeCA prices and this model does not carry.</t>
         </is>
       </c>
     </row>
@@ -2941,17 +2933,17 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>pEmissionsTotal</t>
+          <t>pEmissionsCountry</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>constraint/pEmissionsTotal.csv</t>
+          <t>constraint/pEmissionsCountry.csv</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>system-wide CO2 cap, tons</t>
+          <t>CO2 cap by country, tons</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
@@ -2969,21 +2961,37 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>DECIDE</t>
+          <t>FILL</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr"/>
-      <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr"/>
-      <c r="M44" s="4" t="inlineStr"/>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>deca_v51</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>2030-2060</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 6.4 PREPARED BUT DELIBERATELY NOT WIRED IN. The file stays empty and fApplyCountryCo2Constraint stays 0. build_constraints.py writes the DeCA path out to extracted/pEmissionsCountry_netzero.csv, on the horizon and in the tons EPM counts in, so that phase 9 can switch it on in one line once three things are settled. The path itself: the first Net Zero row of each Emissions sheet, five books of the seven countries, held flat before the first year it states and interpolated between the years it does. Kazakhstan 93.1 MtCO2-eq in 2030 to 4.66 in 2050, Uzbekistan 63.3 to 3.16, Turkmenistan 16.3 to 0.82, Tajikistan 4.17 to 0.21, Kyrgyzstan 1.36 to 0.068. Each is built by DeCA off the country NDC and then run down to a residual by 2060, and each book states its own arithmetic: Kazakhstan takes a third of the 1990 heat and power sector, Turkmenistan 0.85 of energy times 0.36 of electricity and heat, and so on. THE UZ BOOK STATES THE PATH TWICE, once economy-wide and once for electricity and heat at three tenths of it, and it is the sector row that is read. WHY IT IS NOT A BASELINE. It is a scenario, DeCA says so, and dropping it into the reference case would silently make the reference case a net zero case.</t>
+        </is>
+      </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>PHASE 9. Empty, and fApplySystemCo2Constraint is 0. A regional cap over seven countries five of which have separate national NDCs is a different scenario from the national caps in pEmissionsCountry, not a complement to them: it would let Kazakh coal buy its way out on a Kyrgyz margin. To be chosen against the country caps rather than filled in beside them.</t>
+          <t>PHASE 9, THE THREE THINGS TO SETTLE BEFORE THIS BECOMES A CONSTRAINT. 1. SCOPE. The path covers ELECTRICITY AND HEAT and EPM carries no heat. In Kazakhstan heat was 87.1 of the 112.4 MtCO2-eq the sector emitted in 1990, so a heat and power cap read onto a power only model is loose by a factor nobody has measured, and the Kazakh CHPs sit on both sides of that line. 2. COVERAGE. base.gms:1253 writes eEmissionsCountry for EVERY country at once when the flag is on, and a country absent from the table gets a cap of zero, softened only by the penalised backstop. Pakistan and Afghanistan have no NDC path in these books, so switching the flag on with this file as it stands would order them to emit nothing. Either they get a path of their own or the constraint has to be written for a subset. 3. THE FIRST FOUR YEARS. Nothing is stated before 2030, so the path is held flat backwards to 2026, which binds four years earlier than any NDC intended. Harmless while the cap is loose, not harmless if it is tight.</t>
         </is>
       </c>
     </row>
@@ -2995,61 +3003,49 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>pMaxFuellimit</t>
+          <t>pEmissionsTotal</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>constraint/pMaxFuellimit.csv</t>
+          <t>constraint/pEmissionsTotal.csv</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>supply limit by country and fuel, million MMBtu</t>
+          <t>system-wide CO2 cap, tons</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>filled, more to come</t>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>casa_2020</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>2020 series, carried to 2050</t>
-        </is>
-      </c>
-      <c r="M45" s="4" t="inlineStr">
-        <is>
-          <t>PHASE 6.4 done, and it is the same defect as the fuel prices. The table ran 2017 to 2030 against a horizon that runs 2026 to 2050, and base.gms:817 writes the constraint only where the value is strictly positive, so PAST 2030 EVERY LIMIT SIMPLY VANISHED while fApplyFuelConstraint stayed on. Nothing crashed, which is what made it dangerous. Rebuilt by build_constraints.py from mappings/fuel_limits.csv, which carries the nine rows of the two tables one by one. All five country rows are the 2020 series held flat past its last year: DeCA states a national fuel availability nowhere, Pakistan and Afghanistan are outside its perimeter, and an assumption of no further change is at least visible where a silent zero was not. THE UZBEK COAL LINE IS THE ONE PLACE DeCA COULD HAVE SPOKEN AND IS NOT USED. Its Fuel Availability sheet states coal for power in M m3, a VOLUME, and turning that into MMBtu would need a density and a calorific value the book never states, which is exactly the assumption phase 6 spent its time removing from the coal prices. The 2020 series is held flat instead, and the gap is written down rather than papered over with two invented conversion factors.</t>
-        </is>
-      </c>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr"/>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>PHASE 6.4, WHAT RESTS ON 2020. Pakistani gas and LNG both do, and both want the NTDC IGCEP: indigenous Pakistani gas is on a declining path that a flat line does not represent, and the LNG row is a regasification terminal limit rather than a resource one, so holding it flat quietly forbids any new terminal. Kyrgyz and Tajik gas are import contracts of the 2020 model, neither of them binding. Uzbek coal is discussed in the note.</t>
+          <t>PHASE 9. Empty, and fApplySystemCo2Constraint is 0. A regional cap over seven countries five of which have separate national NDCs is a different scenario from the national caps in pEmissionsCountry, not a complement to them: it would let Kazakh coal buy its way out on a Kyrgyz margin. To be chosen against the country caps rather than filled in beside them.</t>
         </is>
       </c>
     </row>
@@ -3061,21 +3057,21 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>pMaxFuellimitZone</t>
+          <t>pMaxFuellimit</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>constraint/pMaxFuellimitZone.csv</t>
+          <t>constraint/pMaxFuellimit.csv</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>supply limit by zone and fuel, million MMBtu</t>
+          <t>supply limit by country and fuel, million MMBtu</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
@@ -3092,34 +3088,30 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>deca_v51, casa_2020</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>UZ &gt; Fuel Availability</t>
-        </is>
-      </c>
+          <t>casa_2020</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr"/>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2022-2030 stated, held to 2050</t>
+          <t>2020 series, carried to 2050</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>PHASE 6.4 done. Same repair as the country table, carried to 2050 by build_constraints.py, and one of the four rows genuinely moves. UZBEK GAS FOR POWER FALLS BY A THIRD. The UZ Fuel Availability sheet is the only one of the five books to exist, and it states 12.1 bcm available for electricity production, sourced to the Concept Note for ensuring electricity supply in Uzbekistan in 2020-2030, with the book saying in as many words that it holds that limit to 2060. At 36 million MMBtu per bcm, which is the BP conversion and the only one this step makes, that is 435.6 against the 667.6 the 2020 model allowed, and the sheet shows why: Uzbek gas production does rise to 2030, 51.7 to 66.1 bcm, but domestic demand rises faster and exports have already been cut to zero, so power gets less of a bigger pie. The 2026 to 2029 values interpolate between the 12.7 bcm stated for 2025 and the 12.1 of 2030 rather than jumping. THIS WILL STRUCTURE THE UZBEK EXPANSION, roughly 36 TWh at a modern combined cycle where the fleet needs more. The three other zone rows are the 2020 series held flat, Pakistani coal being outside the DeCA perimeter and Kazakh gas being the decision below.</t>
+          <t>PHASE 6.4 done, and it is the same defect as the fuel prices. The table ran 2017 to 2030 against a horizon that runs 2026 to 2050, and base.gms:817 writes the constraint only where the value is strictly positive, so PAST 2030 EVERY LIMIT SIMPLY VANISHED while fApplyFuelConstraint stayed on. Nothing crashed, which is what made it dangerous. Rebuilt by build_constraints.py from mappings/fuel_limits.csv, which carries the nine rows of the two tables one by one. All five country rows are the 2020 series held flat past its last year: DeCA states a national fuel availability nowhere, Pakistan and Afghanistan are outside its perimeter, and an assumption of no further change is at least visible where a silent zero was not. THE UZBEK COAL LINE IS THE ONE PLACE DeCA COULD HAVE SPOKEN AND IS NOT USED. Its Fuel Availability sheet states coal for power in M m3, a VOLUME, and turning that into MMBtu would need a density and a calorific value the book never states, which is exactly the assumption phase 6 spent its time removing from the coal prices. The 2020 series is held flat instead, and the gap is written down rather than papered over with two invented conversion factors.</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>PHASE 6.4, THE DECISION OF THE PHASE, and it is left to the team rather than taken here. KAZ_N Gas = 0.1 million MMBtu is not a limit, it is a statement that NORTHERN KAZAKHSTAN HAS NO GAS AT ALL, and it is what forces the coal expansion there: no gas candidate can run whatever the carbon price, so the only thermal answer to Kazakh load growth is more coal. The assumption was defensible in 2020. It is doubtful in 2026, the Saryarka pipeline having reached Nur-Sultan in 2019 and Kokshetau since, and DeCA'S OWN KZ TRANSPORT TABLE QUOTES A DELIVERED GAS PRICE IN AKMOLA, 13.3 $/MMBtu on top of the commodity, which is a strange thing to state for a region where no gas can arrive. Raising it needs the Saryarka throughput and the volumes already committed to heat and industry, and it is the single most consequential unresolved number left in this model. Kept as it stands until then, so that it is a decision and not a drift.</t>
+          <t>PHASE 6.4, WHAT RESTS ON 2020. Pakistani gas and LNG both do, and both want the NTDC IGCEP: indigenous Pakistani gas is on a declining path that a flat line does not represent, and the LNG row is a regasification terminal limit rather than a resource one, so holding it flat quietly forbids any new terminal. Kyrgyz and Tajik gas are import contracts of the 2020 model, neither of them binding. Uzbek coal is discussed in the note.</t>
         </is>
       </c>
     </row>
@@ -3131,133 +3123,137 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
+          <t>pMaxFuellimitZone</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>constraint/pMaxFuellimitZone.csv</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>supply limit by zone and fuel, million MMBtu</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>filled, more to come</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>deca_v51, casa_2020</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>UZ &gt; Fuel Availability</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>2022-2030 stated, held to 2050</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 6.4 done. Same repair as the country table, carried to 2050 by build_constraints.py, and one of the four rows genuinely moves. UZBEK GAS FOR POWER FALLS BY A THIRD. The UZ Fuel Availability sheet is the only one of the five books to exist, and it states 12.1 bcm available for electricity production, sourced to the Concept Note for ensuring electricity supply in Uzbekistan in 2020-2030, with the book saying in as many words that it holds that limit to 2060. At 36 million MMBtu per bcm, which is the BP conversion and the only one this step makes, that is 435.6 against the 667.6 the 2020 model allowed, and the sheet shows why: Uzbek gas production does rise to 2030, 51.7 to 66.1 bcm, but domestic demand rises faster and exports have already been cut to zero, so power gets less of a bigger pie. The 2026 to 2029 values interpolate between the 12.7 bcm stated for 2025 and the 12.1 of 2030 rather than jumping. THIS WILL STRUCTURE THE UZBEK EXPANSION, roughly 36 TWh at a modern combined cycle where the fleet needs more. The three other zone rows are the 2020 series held flat, Pakistani coal being outside the DeCA perimeter and Kazakh gas being the decision below.</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 6.4, THE DECISION OF THE PHASE, and it is left to the team rather than taken here. KAZ_N Gas = 0.1 million MMBtu is not a limit, it is a statement that NORTHERN KAZAKHSTAN HAS NO GAS AT ALL, and it is what forces the coal expansion there: no gas candidate can run whatever the carbon price, so the only thermal answer to Kazakh load growth is more coal. The assumption was defensible in 2020. It is doubtful in 2026, the Saryarka pipeline having reached Nur-Sultan in 2019 and Kokshetau since, and DeCA'S OWN KZ TRANSPORT TABLE QUOTES A DELIVERED GAS PRICE IN AKMOLA, 13.3 $/MMBtu on top of the commodity, which is a strange thing to state for a region where no gas can arrive. Raising it needs the Saryarka throughput and the volumes already committed to heat and industry, and it is the single most consequential unresolved number left in this model. Kept as it stands until then, so that it is a decision and not a drift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Constraints</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
           <t>pMaxGenerationByFuel</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>constraint/pMaxGenerationByFuel.csv</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>max share by fuel</t>
         </is>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="11" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="11" t="inlineStr">
         <is>
           <t>out of scope</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I48" s="9" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr"/>
-      <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="4" t="inlineStr"/>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr">
         <is>
           <t>PHASE 6.4 checked, still empty and still out of scope. Its header runs z, tech, f, 2025, 2040 and it would cap the generation of a fuel in a zone. Nothing in DeCA is stated in that form, and the two things it would be used for are already carried elsewhere: the physical availability of a fuel by pMaxFuellimitZone, and any policy share by the emission caps.</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Reserves</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="n"/>
-      <c r="F48" s="3" t="n"/>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="n"/>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="n"/>
-      <c r="L48" s="3" t="n"/>
-      <c r="M48" s="3" t="n"/>
-      <c r="N48" s="3" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Reserves</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>pPlanningReserveMarginZone</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>reserve/pPlanningReserveMarginZone.csv</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>reserve margin, 15 % on each of the 16 zones</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>assumed, team</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr"/>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="inlineStr">
-        <is>
-          <t>PHASE 7 examined, and the 0.15 does not move. What moved is what it is applied to, and the change is large enough that it has to be written down. THE 2020 MODEL VALUED FIRM CAPACITY AT NAMEPLATE. base.gms:1005 counts the firm capacity of a zone at the availability of each unit IN THE FLAGGED SEASON alone, and the 2020 model flagged an artificial peak season in which 267 units out of 403 carried 1.0, and 313 were worth more than in Q1. That season was an artefact of the old time slicing and phase 1 removed it, so the flag now points at Q1, where those same units carry their true 0.85. A coal CHP is no longer worth its nameplate at the winter peak. WHAT IT COSTS, measured by data_build/check_reserve.py against the DeCA peaks: in 2026 the region has to find some 11 GW MORE firm capacity than the same model would have asked for under the 2020 convention. Kazakhstan 2.2 GW, Pakistan 4.8, Uzbekistan 2.1, Kyrgyzstan 0.6, Turkmenistan 0.9, Tajikistan 0.5. THE NEW CONVENTION IS THE RIGHT ONE and that is why it is kept: a planning margin belongs on top of DERATED capacity, and a 15 per cent margin over nameplate is not a margin at all once forced outages are counted, it is roughly zero. The model is now tighter than the 2020 reference and will build more firm plant. That is a real change in the results and not an accounting detail. The margin is uniform across sixteen zones with no source behind it. DeCA states none: the five books carry no reserve margin, no loss of load expectation and no capacity credit of any kind.</t>
-        </is>
-      </c>
-      <c r="N49" s="4" t="inlineStr">
-        <is>
-          <t>PHASE 7, WHAT IS LEFT TO DECIDE, and it is a team call rather than a data gap. 1. THE 0.15 ITSELF has no source. It is defensible as a placeholder, it is not defensible in a published result, and the same number is applied to a Pakistani zone with a thermal fleet and a Kyrgyz zone that is nearly all hydro. The national regulators are the source to ask for. 2. THE 0.85 UNDER IT is inherited too, and the two multiply: the requirement is really 1.15 / 0.85 = 1.35 times the peak in nameplate terms. Whether the thermal fleet of the region is available 85 or 90 per cent of the time is worth one question to the TTLs, because it moves the answer by 4 GW in 2026. 3. SOLAR IS VALUED AT ITS BEST HOUR OF Q1 (main.gms:700), which for a system whose winter peak is in the evening is generous. Nothing depends on it yet, the VRE candidates being small, but it should be reviewed before the capacity mix is published.</t>
-        </is>
-      </c>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" s="3" t="n"/>
+      <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="n"/>
+      <c r="L49" s="3" t="n"/>
+      <c r="M49" s="3" t="n"/>
+      <c r="N49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -3267,53 +3263,61 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>pReserveSeasonFlag</t>
+          <t>pPlanningReserveMarginZone</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>reserve/pReserveSeasonFlag.csv</t>
+          <t>reserve/pPlanningReserveMarginZone.csv</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>peak season = Q5</t>
+          <t>reserve margin, 15 % on each of the 16 zones</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>done</t>
+        <v>16</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>inherited 2020, to process</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>REBUILD</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>assumed, team</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr"/>
-      <c r="L50" s="4" t="inlineStr"/>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>Follows the removal of the peak season. This flag only serves to choose the season whose NTC is used for firm capacity sharing (base.gms:1005); it does not size the reserve, which goes through a smax over all blocks.</t>
+          <t>PHASE 7 examined, and the 0.15 does not move. What moved is what it is applied to, and the change is large enough that it has to be written down. THE 2020 MODEL VALUED FIRM CAPACITY AT NAMEPLATE. base.gms:1005 counts the firm capacity of a zone at the availability of each unit IN THE FLAGGED SEASON alone, and the 2020 model flagged an artificial peak season in which 267 units out of 403 carried 1.0, and 313 were worth more than in Q1. That season was an artefact of the old time slicing and phase 1 removed it, so the flag now points at Q1, where those same units carry their true 0.85. A coal CHP is no longer worth its nameplate at the winter peak. WHAT IT COSTS, measured by data_build/check_reserve.py against the DeCA peaks: in 2026 the region has to find some 11 GW MORE firm capacity than the same model would have asked for under the 2020 convention. Kazakhstan 2.2 GW, Pakistan 4.8, Uzbekistan 2.1, Kyrgyzstan 0.6, Turkmenistan 0.9, Tajikistan 0.5. THE NEW CONVENTION IS THE RIGHT ONE and that is why it is kept: a planning margin belongs on top of DERATED capacity, and a 15 per cent margin over nameplate is not a margin at all once forced outages are counted, it is roughly zero. The model is now tighter than the 2020 reference and will build more firm plant. That is a real change in the results and not an accounting detail. The margin is uniform across sixteen zones with no source behind it. DeCA states none: the five books carry no reserve margin, no loss of load expectation and no capacity credit of any kind.</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>DONE (phase 1): Q5 -&gt; Q1. This flag serves one purpose only (base.gms:1005): choosing the season whose NTC is used for firm capacity sharing between zones. It does NOT drive the sizing of the reserve, which goes through a smax over all blocks. Q1 = winter quarter, correct. DONE (phase 7): the check this todo owed is made, and the answer is that the credit does fall from 1.0 to 0.85 and that it is kept there. Some 11 GW more firm capacity is asked of the region in 2026 as a result. The reasoning is in pPlanningReserveMarginZone, where it belongs; Q1 stays flagged.</t>
+          <t>PHASE 7, WHAT IS LEFT TO DECIDE, and it is a team call rather than a data gap. 1. THE 0.15 ITSELF has no source. It is defensible as a placeholder, it is not defensible in a published result, and the same number is applied to a Pakistani zone with a thermal fleet and a Kyrgyz zone that is nearly all hydro. The national regulators are the source to ask for. 2. THE 0.85 UNDER IT is inherited too, and the two multiply: the requirement is really 1.15 / 0.85 = 1.35 times the peak in nameplate terms. Whether the thermal fleet of the region is available 85 or 90 per cent of the time is worth one question to the TTLs, because it moves the answer by 4 GW in 2026. 3. SOLAR IS VALUED AT ITS BEST HOUR OF Q1 (main.gms:700), which for a system whose winter peak is in the evening is generous. Nothing depends on it yet, the VRE candidates being small, but it should be reviewed before the capacity mix is published.</t>
         </is>
       </c>
     </row>
@@ -3325,47 +3329,55 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>pPlanningReserveMargin</t>
+          <t>pReserveSeasonFlag</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>reserve/pPlanningReserveMargin.csv</t>
+          <t>reserve/pReserveSeasonFlag.csv</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>margin by country</t>
+          <t>peak season = Q5</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>out of scope</t>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>done</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr"/>
+          <t>REBUILD</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
       <c r="K51" s="4" t="inlineStr"/>
       <c r="L51" s="4" t="inlineStr"/>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>PHASE 7 checked, deliberately left empty. It is not redundant, it is the ALTERNATIVE: base.gms:1017 says a study that switches the zonal reserve on will normally leave this one empty, otherwise both apply at once and the zones are held to their own margin and to their country's. Empty here is what keeps the country equation from generating any row, since it is guarded by the margin itself and not by the flag, which is on. Pooling reserves by country rather than by zone would be a defensible variant for Kazakhstan and Kyrgyzstan, whose two zones are strongly connected; it would relax the model. It is a scenario, not a correction.</t>
-        </is>
-      </c>
-      <c r="N51" s="4" t="inlineStr"/>
+          <t>Follows the removal of the peak season. This flag only serves to choose the season whose NTC is used for firm capacity sharing (base.gms:1005); it does not size the reserve, which goes through a smax over all blocks.</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>DONE (phase 1): Q5 -&gt; Q1. This flag serves one purpose only (base.gms:1005): choosing the season whose NTC is used for firm capacity sharing between zones. It does NOT drive the sizing of the reserve, which goes through a smax over all blocks. Q1 = winter quarter, correct. DONE (phase 7): the check this todo owed is made, and the answer is that the credit does fall from 1.0 to 0.85 and that it is kept there. Some 11 GW more firm capacity is asked of the region in 2026 as a result. The reasoning is in pPlanningReserveMarginZone, where it belongs; Q1 stays flagged.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -3375,52 +3387,44 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>pSpinningReserveReqCountry</t>
+          <t>pPlanningReserveMargin</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>reserve/pSpinningReserveReqCountry.csv</t>
+          <t>reserve/pPlanningReserveMargin.csv</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>spinning reserve by country</t>
+          <t>margin by country</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>inherited, fit for purpose</t>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>KEEP</t>
-        </is>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>deca_v51, casa_2020</t>
-        </is>
-      </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>Thermal PP, column Operating Reserve</t>
-        </is>
-      </c>
+      <c r="J52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr"/>
       <c r="L52" s="4" t="inlineStr"/>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>PHASE 7 checked and left empty and off, and this is now a sourced decision rather than an omission. Every one of the five books carries an Operating Reserve column on its Thermal PP sheet, and IT IS ZERO ON ALL 112 UNITS THAT FILL IT, the UZ book leaving it blank altogether: the reference study holds no spinning reserve on its thermal fleet either. fApplyCountrySpinReserveConstraint and fApplySystemSpinReserveConstraint stay at 0. Turning it on is expensive for what it buys: the comment at base.gms:950 says the country equation multiplies solving time by three, and the model would need a ResLimShare per unit that nothing in the sources supports. The right place for an operating reserve in this study is the hourly dispatch run of phase 8, not the expansion.</t>
+          <t>PHASE 7 checked, deliberately left empty. It is not redundant, it is the ALTERNATIVE: base.gms:1017 says a study that switches the zonal reserve on will normally leave this one empty, otherwise both apply at once and the zones are held to their own margin and to their country's. Empty here is what keeps the country equation from generating any row, since it is guarded by the margin itself and not by the flag, which is on. Pooling reserves by country rather than by zone would be a defensible variant for Kazakhstan and Kyrgyzstan, whose two zones are strongly connected; it would relax the model. It is a scenario, not a correction.</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr"/>
@@ -3433,17 +3437,17 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>pSpinningReserveReqSystem</t>
+          <t>pSpinningReserveReqCountry</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>reserve/pSpinningReserveReqSystem.csv</t>
+          <t>reserve/pSpinningReserveReqCountry.csv</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>system-wide spinning reserve</t>
+          <t>spinning reserve by country</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
@@ -3460,7 +3464,7 @@
           <t>KEEP</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I53" s="9" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3470,84 +3474,92 @@
           <t>deca_v51, casa_2020</t>
         </is>
       </c>
-      <c r="K53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>Thermal PP, column Operating Reserve</t>
+        </is>
+      </c>
       <c r="L53" s="4" t="inlineStr"/>
       <c r="M53" s="4" t="inlineStr">
         <is>
+          <t>PHASE 7 checked and left empty and off, and this is now a sourced decision rather than an omission. Every one of the five books carries an Operating Reserve column on its Thermal PP sheet, and IT IS ZERO ON ALL 112 UNITS THAT FILL IT, the UZ book leaving it blank altogether: the reference study holds no spinning reserve on its thermal fleet either. fApplyCountrySpinReserveConstraint and fApplySystemSpinReserveConstraint stay at 0. Turning it on is expensive for what it buys: the comment at base.gms:950 says the country equation multiplies solving time by three, and the model would need a ResLimShare per unit that nothing in the sources supports. The right place for an operating reserve in this study is the hourly dispatch run of phase 8, not the expansion.</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Reserves</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>pSpinningReserveReqSystem</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>reserve/pSpinningReserveReqSystem.csv</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>system-wide spinning reserve</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>inherited, fit for purpose</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>deca_v51, casa_2020</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
           <t>PHASE 7, same decision and same reason as pSpinningReserveReqCountry: empty and off, DeCA holding no operating reserve either. A regional spinning reserve over seven countries that do not share a control area would in any case be a strong assumption about market integration, which is the subject of the study rather than an input to it.</t>
         </is>
       </c>
-      <c r="N53" s="4" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="N54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="3" t="n"/>
-      <c r="F54" s="3" t="n"/>
-      <c r="G54" s="3" t="n"/>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="3" t="n"/>
-      <c r="L54" s="3" t="n"/>
-      <c r="M54" s="3" t="n"/>
-      <c r="N54" s="3" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>pH2DataExcel</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>h2/pH2DataExcel.csv</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>hydrogen (5 files in h2/)</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="11" t="inlineStr">
-        <is>
-          <t>out of scope</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="I55" s="10" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr"/>
-      <c r="K55" s="4" t="inlineStr"/>
-      <c r="L55" s="4" t="inlineStr"/>
-      <c r="M55" s="4" t="inlineStr"/>
-      <c r="N55" s="4" t="inlineStr">
-        <is>
-          <t>No H2 stakes in the CASA perimeter.</t>
-        </is>
-      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="n"/>
+      <c r="L55" s="3" t="n"/>
+      <c r="M55" s="3" t="n"/>
+      <c r="N55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -3557,34 +3569,34 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>pGenDataInputGeneric</t>
+          <t>pH2DataExcel</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>generic/pGenDataInputGeneric.csv</t>
+          <t>h2/pH2DataExcel.csv</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>generic technology defaults</t>
+          <t>hydrogen (5 files in h2/)</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>inherited 2020, to process</t>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3595,19 +3607,69 @@
       <c r="M56" s="4" t="inlineStr"/>
       <c r="N56" s="4" t="inlineStr">
         <is>
+          <t>No H2 stakes in the CASA perimeter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>pGenDataInputGeneric</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>generic/pGenDataInputGeneric.csv</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>generic technology defaults</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>inherited 2020, to process</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr"/>
+      <c r="M57" s="4" t="inlineStr"/>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
           <t>Alternative to pGenDataInputDefault.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>11 done | 15 partial | 15 to do | 7 out of scope</t>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>11 done | 16 partial | 15 to do | 7 out of scope</t>
         </is>
       </c>
     </row>
